--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3732,55 +3732,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3562.7</v>
+        <v>3214.4</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>24.39</v>
+        <v>14.81</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>214</v>
+        <v>179.2</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2.35</v>
+        <v>3.13</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>13.47</v>
+        <v>15.98</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.54</v>
+        <v>3.54</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>243.55</v>
+        <v>185.48</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3793,65 +3793,61 @@
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3610.2</v>
+        <v>3562.7</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>18.74</v>
+        <v>24.39</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>332.6</v>
+        <v>214</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>11.79</v>
+        <v>13.47</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.98</v>
+        <v>2.54</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>235.07</v>
+        <v>243.55</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3874,55 +3870,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3652.6</v>
+        <v>3610.2</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>26.1</v>
+        <v>18.74</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>58.2</v>
+        <v>332.6</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1.79</v>
+        <v>2.33</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>12.35</v>
+        <v>11.79</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.86</v>
+        <v>3.98</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>236.64</v>
+        <v>235.07</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3945,55 +3941,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3445.3</v>
+        <v>3652.6</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>17.5</v>
+        <v>26.1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>506.9</v>
+        <v>58.2</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4.91</v>
+        <v>1.79</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>12.22</v>
+        <v>12.35</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>257.98</v>
+        <v>236.64</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4006,61 +4002,65 @@
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3238.8</v>
+        <v>3445.3</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>17.79</v>
+        <v>17.5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>723.8</v>
+        <v>506.9</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>7.33</v>
+        <v>4.91</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>9.06</v>
+        <v>12.22</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>293.61</v>
+        <v>257.98</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4073,65 +4073,61 @@
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3342.8</v>
+        <v>3238.8</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>16.68</v>
+        <v>17.79</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>197.6</v>
+        <v>723.8</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.96</v>
+        <v>7.33</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>11.2</v>
+        <v>9.06</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>204.43</v>
+        <v>293.61</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4154,55 +4150,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3398.5</v>
+        <v>3342.8</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>18.28</v>
+        <v>16.68</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>181.2</v>
+        <v>197.6</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>13.03</v>
+        <v>11.2</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.22</v>
+        <v>2.56</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>209.56</v>
+        <v>204.43</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4225,55 +4221,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3186.9</v>
+        <v>3398.5</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>14.24</v>
+        <v>18.28</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>179.1</v>
+        <v>181.2</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>3.09</v>
+        <v>2.48</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>16.14</v>
+        <v>13.03</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.53</v>
+        <v>3.22</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>181.55</v>
+        <v>209.56</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4286,61 +4282,65 @@
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3627.9</v>
+        <v>3186.9</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>22.95</v>
+        <v>14.24</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>171.1</v>
+        <v>179.1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1.92</v>
+        <v>3.09</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>12.02</v>
+        <v>16.14</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.79</v>
+        <v>3.53</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>235.93</v>
+        <v>181.55</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4353,65 +4353,61 @@
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3528.7</v>
+        <v>3627.9</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>23.83</v>
+        <v>22.95</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>551.1</v>
+        <v>171.1</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>4.04</v>
+        <v>1.92</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>15.78</v>
+        <v>12.02</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.96</v>
+        <v>2.79</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>278.34</v>
+        <v>235.93</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4434,55 +4430,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3563.2</v>
+        <v>3528.7</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>21.31</v>
+        <v>23.83</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>157.8</v>
+        <v>551.1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1.82</v>
+        <v>4.04</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>11</v>
+        <v>15.78</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.19</v>
+        <v>2.96</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>228.09</v>
+        <v>278.34</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4505,55 +4501,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3589.4</v>
+        <v>3563.2</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>22.04</v>
+        <v>21.31</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>213</v>
+        <v>157.8</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>3.04</v>
+        <v>1.82</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>13.18</v>
+        <v>11</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>241.3</v>
+        <v>228.09</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4576,55 +4572,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3415.2</v>
+        <v>3589.4</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>17.52</v>
+        <v>22.04</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>139.2</v>
+        <v>213</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2.41</v>
+        <v>3.04</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>13.27</v>
+        <v>13.18</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.97</v>
+        <v>1.81</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>200.59</v>
+        <v>241.3</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4647,55 +4643,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3235.3</v>
+        <v>3415.2</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>15.01</v>
+        <v>17.52</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>185.3</v>
+        <v>139.2</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>3.16</v>
+        <v>2.41</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>16.39</v>
+        <v>13.27</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.62</v>
+        <v>3.97</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>186.92</v>
+        <v>200.59</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4708,61 +4704,65 @@
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>3402</v>
+        <v>3235.3</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>16.98</v>
+        <v>15.01</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>285.2</v>
+        <v>185.3</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.69</v>
+        <v>3.16</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>11.8</v>
+        <v>16.39</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>219.04</v>
+        <v>186.92</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4775,65 +4775,61 @@
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3296.6</v>
+        <v>3402</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>16.01</v>
+        <v>16.98</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>180.8</v>
+        <v>285.2</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>15.52</v>
+        <v>11.8</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>7.66</v>
+        <v>3.01</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>183.58</v>
+        <v>219.04</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4846,61 +4842,65 @@
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3175.8</v>
+        <v>3296.6</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>14.08</v>
+        <v>16.01</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>198.3</v>
+        <v>180.8</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>15.87</v>
+        <v>15.52</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.49</v>
+        <v>7.66</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>182.76</v>
+        <v>183.58</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4913,65 +4913,61 @@
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Trey Lance</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>3277.4</v>
+        <v>3175.8</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>17.51</v>
+        <v>14.08</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>685.5</v>
+        <v>198.3</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>3.46</v>
+        <v>3.05</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>13.25</v>
+        <v>15.87</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.4</v>
+        <v>3.49</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>259.15</v>
+        <v>182.76</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4994,55 +4990,55 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Trey Lance</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>3263.2</v>
+        <v>3277.4</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>18.7</v>
+        <v>17.51</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>688.8</v>
+        <v>685.5</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>9.640000000000001</v>
+        <v>13.25</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>273.51</v>
+        <v>259.15</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5065,55 +5061,55 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>3465.2</v>
+        <v>3263.2</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>22.43</v>
+        <v>18.7</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>510</v>
+        <v>688.8</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>10.61</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>278.11</v>
+        <v>273.51</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5136,43 +5132,43 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>3524</v>
+        <v>3465.2</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>16.81</v>
+        <v>22.43</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>383.1</v>
+        <v>510</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>3.35</v>
+        <v>4.29</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>11.9</v>
+        <v>10.61</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -5184,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>237.07</v>
+        <v>278.11</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5203,6 +5199,77 @@
         </is>
       </c>
       <c r="W65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Tyson Bagent</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3524</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>237.07</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7817,7 +7884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8662,55 +8729,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3562.7</v>
+        <v>3214.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>24.39</v>
+        <v>14.81</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>214</v>
+        <v>179.2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.35</v>
+        <v>3.13</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13.47</v>
+        <v>15.98</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>3.54</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>243.55</v>
+        <v>185.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8723,65 +8790,61 @@
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3610.2</v>
+        <v>3562.7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>18.74</v>
+        <v>24.39</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>332.6</v>
+        <v>214</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>11.79</v>
+        <v>13.47</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.98</v>
+        <v>2.54</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>235.07</v>
+        <v>243.55</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8804,55 +8867,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3652.6</v>
+        <v>3610.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>26.1</v>
+        <v>18.74</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>58.2</v>
+        <v>332.6</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.79</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>12.35</v>
+        <v>11.79</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.86</v>
+        <v>3.98</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>236.64</v>
+        <v>235.07</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8875,55 +8938,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3445.3</v>
+        <v>3652.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>17.5</v>
+        <v>26.1</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>506.9</v>
+        <v>58.2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>4.91</v>
+        <v>1.79</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>12.22</v>
+        <v>12.35</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>257.98</v>
+        <v>236.64</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8936,61 +8999,65 @@
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3238.8</v>
+        <v>3445.3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>17.79</v>
+        <v>17.5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>723.8</v>
+        <v>506.9</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>7.33</v>
+        <v>4.91</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.06</v>
+        <v>12.22</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>293.61</v>
+        <v>257.98</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9003,65 +9070,61 @@
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3342.8</v>
+        <v>3238.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16.68</v>
+        <v>17.79</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>197.6</v>
+        <v>723.8</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.96</v>
+        <v>7.33</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>11.2</v>
+        <v>9.06</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>204.43</v>
+        <v>293.61</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9084,55 +9147,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3398.5</v>
+        <v>3342.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>18.28</v>
+        <v>16.68</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>181.2</v>
+        <v>197.6</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>13.03</v>
+        <v>11.2</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.22</v>
+        <v>2.56</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>209.56</v>
+        <v>204.43</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -9155,55 +9218,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3186.9</v>
+        <v>3398.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14.24</v>
+        <v>18.28</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>179.1</v>
+        <v>181.2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.09</v>
+        <v>2.48</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>16.14</v>
+        <v>13.03</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.53</v>
+        <v>3.22</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>181.55</v>
+        <v>209.56</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -9216,61 +9279,65 @@
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3627.9</v>
+        <v>3186.9</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>22.95</v>
+        <v>14.24</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>171.1</v>
+        <v>179.1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.92</v>
+        <v>3.09</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>12.02</v>
+        <v>16.14</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.79</v>
+        <v>3.53</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>235.93</v>
+        <v>181.55</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -9283,65 +9350,61 @@
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3528.7</v>
+        <v>3627.9</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>23.83</v>
+        <v>22.95</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>551.1</v>
+        <v>171.1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4.04</v>
+        <v>1.92</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>15.78</v>
+        <v>12.02</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.96</v>
+        <v>2.79</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>278.34</v>
+        <v>235.93</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -9364,55 +9427,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3563.2</v>
+        <v>3528.7</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>21.31</v>
+        <v>23.83</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>157.8</v>
+        <v>551.1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.82</v>
+        <v>4.04</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>11</v>
+        <v>15.78</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.19</v>
+        <v>2.96</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>228.09</v>
+        <v>278.34</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -9435,55 +9498,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3589.4</v>
+        <v>3563.2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>22.04</v>
+        <v>21.31</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>213</v>
+        <v>157.8</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.04</v>
+        <v>1.82</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>13.18</v>
+        <v>11</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>241.3</v>
+        <v>228.09</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -9506,55 +9569,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3415.2</v>
+        <v>3589.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>17.52</v>
+        <v>22.04</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>139.2</v>
+        <v>213</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.41</v>
+        <v>3.04</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>13.27</v>
+        <v>13.18</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.97</v>
+        <v>1.81</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>200.59</v>
+        <v>241.3</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -9577,55 +9640,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3235.3</v>
+        <v>3415.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>15.01</v>
+        <v>17.52</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>185.3</v>
+        <v>139.2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.16</v>
+        <v>2.41</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>16.39</v>
+        <v>13.27</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.62</v>
+        <v>3.97</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>186.92</v>
+        <v>200.59</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -9638,61 +9701,65 @@
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3402</v>
+        <v>3235.3</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>16.98</v>
+        <v>15.01</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>285.2</v>
+        <v>185.3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2.69</v>
+        <v>3.16</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>11.8</v>
+        <v>16.39</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>219.04</v>
+        <v>186.92</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -9705,65 +9772,61 @@
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3296.6</v>
+        <v>3402</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>16.01</v>
+        <v>16.98</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>180.8</v>
+        <v>285.2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>15.52</v>
+        <v>11.8</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>7.66</v>
+        <v>3.01</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>183.58</v>
+        <v>219.04</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -9776,61 +9839,65 @@
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3175.8</v>
+        <v>3296.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>14.08</v>
+        <v>16.01</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>198.3</v>
+        <v>180.8</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>15.87</v>
+        <v>15.52</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>7.66</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>182.76</v>
+        <v>183.58</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -9843,65 +9910,61 @@
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Trey Lance</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3277.4</v>
+        <v>3175.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>17.51</v>
+        <v>14.08</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>685.5</v>
+        <v>198.3</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3.46</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>13.25</v>
+        <v>15.87</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>3.49</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>259.15</v>
+        <v>182.76</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -9924,55 +9987,55 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Trey Lance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3263.2</v>
+        <v>3277.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>18.7</v>
+        <v>17.51</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>688.8</v>
+        <v>685.5</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>9.640000000000001</v>
+        <v>13.25</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>273.51</v>
+        <v>259.15</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -9995,55 +10058,55 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3465.2</v>
+        <v>3263.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>22.43</v>
+        <v>18.7</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>510</v>
+        <v>688.8</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.61</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>278.11</v>
+        <v>273.51</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -10066,43 +10129,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3524</v>
+        <v>3465.2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>16.81</v>
+        <v>22.43</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>383.1</v>
+        <v>510</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>4.29</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>11.9</v>
+        <v>10.61</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -10114,7 +10177,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>237.07</v>
+        <v>278.11</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -10133,6 +10196,77 @@
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tyson Bagent</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3524</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>237.07</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -69818,12 +69952,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -69834,11 +69968,11 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F642" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G642" t="n">
         <v>0</v>
@@ -69911,12 +70045,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C643" t="n">
@@ -69927,7 +70061,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F643" t="n">
@@ -70004,12 +70138,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -70020,7 +70154,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -70097,12 +70231,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -70113,14 +70247,14 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F645" t="n">
         <v>-1</v>
       </c>
       <c r="G645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -70190,12 +70324,12 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -70206,7 +70340,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F646" t="n">
@@ -70283,12 +70417,12 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -70299,14 +70433,14 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F647" t="n">
         <v>-1</v>
       </c>
       <c r="G647" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H647" t="n">
         <v>0</v>
@@ -70376,27 +70510,27 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C648" t="n">
         <v>2</v>
       </c>
       <c r="D648" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F648" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G648" t="n">
         <v>0</v>
@@ -70469,27 +70603,27 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C649" t="n">
         <v>2</v>
       </c>
       <c r="D649" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F649" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G649" t="n">
         <v>0</v>
@@ -70562,12 +70696,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -70578,14 +70712,14 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F650" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H650" t="n">
         <v>0</v>
@@ -70655,12 +70789,12 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -70671,14 +70805,14 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F651" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G651" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H651" t="n">
         <v>0</v>
@@ -70748,12 +70882,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -70764,7 +70898,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F652" t="n">
@@ -70841,12 +70975,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -70857,7 +70991,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -70934,12 +71068,12 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -70950,7 +71084,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F654" t="n">
@@ -71027,12 +71161,12 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -71043,7 +71177,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F655" t="n">
@@ -71120,12 +71254,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -71136,14 +71270,14 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F656" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H656" t="n">
         <v>0</v>
@@ -71213,12 +71347,12 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C657" t="n">
@@ -71229,14 +71363,14 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F657" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -71306,12 +71440,12 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -71322,11 +71456,11 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F658" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G658" t="n">
         <v>0</v>
@@ -71399,12 +71533,12 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -71415,7 +71549,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F659" t="n">
@@ -71492,12 +71626,12 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -71508,11 +71642,11 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F660" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G660" t="n">
         <v>0</v>
@@ -71585,12 +71719,12 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -71601,7 +71735,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -71678,12 +71812,12 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -71694,7 +71828,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F662" t="n">
@@ -71771,12 +71905,12 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -71787,7 +71921,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -71864,27 +71998,27 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C664" t="n">
         <v>2</v>
       </c>
       <c r="D664" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F664" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G664" t="n">
         <v>0</v>
@@ -71957,27 +72091,27 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C665" t="n">
         <v>2</v>
       </c>
       <c r="D665" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F665" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G665" t="n">
         <v>0</v>
@@ -72050,12 +72184,12 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -72066,7 +72200,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -72143,12 +72277,12 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C667" t="n">
@@ -72159,14 +72293,14 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F667" t="n">
         <v>-1</v>
       </c>
       <c r="G667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H667" t="n">
         <v>0</v>
@@ -72236,12 +72370,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -72252,7 +72386,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -72329,12 +72463,12 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -72345,7 +72479,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F669" t="n">
@@ -72422,12 +72556,12 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -72438,14 +72572,14 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F670" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -72515,12 +72649,12 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -72531,14 +72665,14 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F671" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G671" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -72608,12 +72742,12 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -72624,14 +72758,14 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F672" t="n">
         <v>-1</v>
       </c>
       <c r="G672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -72701,12 +72835,12 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C673" t="n">
@@ -72717,7 +72851,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -72794,12 +72928,12 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -72810,7 +72944,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F674" t="n">
@@ -72887,12 +73021,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -72903,7 +73037,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -72980,12 +73114,12 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -72996,11 +73130,11 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F676" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G676" t="n">
         <v>0</v>
@@ -73073,12 +73207,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -73089,14 +73223,14 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F677" t="n">
         <v>-1</v>
       </c>
       <c r="G677" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -73166,12 +73300,12 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -73182,7 +73316,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -73259,12 +73393,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -73275,14 +73409,14 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F679" t="n">
         <v>-1</v>
       </c>
       <c r="G679" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -73352,12 +73486,12 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C680" t="n">
@@ -73368,7 +73502,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F680" t="n">
@@ -73445,12 +73579,12 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -73461,7 +73595,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F681" t="n">
@@ -73538,12 +73672,12 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -73554,14 +73688,14 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F682" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -73631,12 +73765,12 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -73647,11 +73781,11 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F683" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G683" t="n">
         <v>0</v>
@@ -73724,12 +73858,12 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -73740,7 +73874,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -73817,12 +73951,12 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -73833,7 +73967,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -73910,12 +74044,12 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C686" t="n">
@@ -73926,14 +74060,14 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F686" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H686" t="n">
         <v>0</v>
@@ -74003,12 +74137,12 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -74019,14 +74153,14 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F687" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -74096,12 +74230,12 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -74112,11 +74246,11 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F688" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G688" t="n">
         <v>0</v>
@@ -74189,12 +74323,12 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -74205,14 +74339,14 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F689" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W66"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,141 +2568,149 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cooper Rush</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>220.7</v>
+        <v>3568.4</v>
       </c>
       <c r="E29" t="n">
-        <v>3729.8</v>
+        <v>3345.7</v>
       </c>
       <c r="F29" t="n">
-        <v>1.35</v>
+        <v>18.61</v>
       </c>
       <c r="G29" t="n">
-        <v>22.82</v>
+        <v>17.39</v>
       </c>
       <c r="H29" t="n">
-        <v>3.9</v>
+        <v>163.4</v>
       </c>
       <c r="I29" t="n">
-        <v>67.09999999999999</v>
+        <v>154.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.08</v>
+        <v>2.07</v>
       </c>
       <c r="K29" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="L29" t="n">
-        <v>0.64</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>10.9</v>
+        <v>8.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.22</v>
+        <v>2.42</v>
       </c>
       <c r="O29" t="n">
-        <v>3.64</v>
+        <v>2.28</v>
       </c>
       <c r="P29" t="n">
-        <v>13.38</v>
+        <v>222.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>227.88</v>
+        <v>208.14</v>
       </c>
       <c r="R29" t="n">
-        <v>-66.22</v>
+        <v>124.69</v>
       </c>
       <c r="S29" t="n">
-        <v>636.66</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+        <v>293.41</v>
+      </c>
+      <c r="T29" t="n">
+        <v>208</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3568.4</v>
+        <v>3370.8</v>
       </c>
       <c r="E30" t="n">
-        <v>3345.7</v>
+        <v>3165.1</v>
       </c>
       <c r="F30" t="n">
-        <v>18.61</v>
+        <v>19.16</v>
       </c>
       <c r="G30" t="n">
-        <v>17.39</v>
+        <v>17.93</v>
       </c>
       <c r="H30" t="n">
-        <v>163.4</v>
+        <v>176.5</v>
       </c>
       <c r="I30" t="n">
-        <v>154.1</v>
+        <v>166.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="K30" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="L30" t="n">
-        <v>9.460000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="M30" t="n">
-        <v>8.9</v>
+        <v>9.32</v>
       </c>
       <c r="N30" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>222.18</v>
+        <v>217.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>208.14</v>
+        <v>203.57</v>
       </c>
       <c r="R30" t="n">
-        <v>124.69</v>
+        <v>119.04</v>
       </c>
       <c r="S30" t="n">
-        <v>293.41</v>
+        <v>289.92</v>
       </c>
       <c r="T30" t="n">
-        <v>208</v>
+        <v>242.45</v>
       </c>
       <c r="U30" t="n">
-        <v>0.14</v>
+        <v>-38.88</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
@@ -2710,74 +2718,74 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3370.8</v>
+        <v>3460</v>
       </c>
       <c r="E31" t="n">
-        <v>3165.1</v>
+        <v>1434.6</v>
       </c>
       <c r="F31" t="n">
-        <v>19.16</v>
+        <v>20.46</v>
       </c>
       <c r="G31" t="n">
-        <v>17.93</v>
+        <v>8.68</v>
       </c>
       <c r="H31" t="n">
-        <v>176.5</v>
+        <v>421.3</v>
       </c>
       <c r="I31" t="n">
-        <v>166.1</v>
+        <v>172.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.27</v>
+        <v>4.15</v>
       </c>
       <c r="K31" t="n">
-        <v>2.13</v>
+        <v>1.61</v>
       </c>
       <c r="L31" t="n">
-        <v>9.91</v>
+        <v>9.51</v>
       </c>
       <c r="M31" t="n">
-        <v>9.32</v>
+        <v>3.93</v>
       </c>
       <c r="N31" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>217.08</v>
+        <v>262.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>203.57</v>
+        <v>108.88</v>
       </c>
       <c r="R31" t="n">
-        <v>119.04</v>
+        <v>70.8</v>
       </c>
       <c r="S31" t="n">
-        <v>289.92</v>
+        <v>147.11</v>
       </c>
       <c r="T31" t="n">
-        <v>242.45</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="U31" t="n">
-        <v>-38.88</v>
+        <v>10.81</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -2785,70 +2793,70 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>3460</v>
+        <v>3729.8</v>
       </c>
       <c r="E32" t="n">
-        <v>1434.6</v>
+        <v>1550.4</v>
       </c>
       <c r="F32" t="n">
-        <v>20.46</v>
+        <v>22.82</v>
       </c>
       <c r="G32" t="n">
-        <v>8.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>421.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>172.8</v>
+        <v>27.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4.15</v>
+        <v>1.63</v>
       </c>
       <c r="K32" t="n">
-        <v>1.61</v>
+        <v>0.68</v>
       </c>
       <c r="L32" t="n">
-        <v>9.51</v>
+        <v>10.9</v>
       </c>
       <c r="M32" t="n">
-        <v>3.93</v>
+        <v>4.48</v>
       </c>
       <c r="N32" t="n">
-        <v>2.82</v>
+        <v>3.64</v>
       </c>
       <c r="O32" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="P32" t="n">
-        <v>262.61</v>
+        <v>227.88</v>
       </c>
       <c r="Q32" t="n">
-        <v>108.88</v>
+        <v>94.73</v>
       </c>
       <c r="R32" t="n">
-        <v>70.8</v>
+        <v>61.32</v>
       </c>
       <c r="S32" t="n">
-        <v>147.11</v>
+        <v>133.01</v>
       </c>
       <c r="T32" t="n">
-        <v>98.06999999999999</v>
+        <v>75.86</v>
       </c>
       <c r="U32" t="n">
-        <v>10.81</v>
+        <v>18.87</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -2860,70 +2868,70 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Kirk Cousins</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3729.8</v>
+        <v>3580.2</v>
       </c>
       <c r="E33" t="n">
-        <v>1550.4</v>
+        <v>628.6</v>
       </c>
       <c r="F33" t="n">
-        <v>22.82</v>
+        <v>24.95</v>
       </c>
       <c r="G33" t="n">
-        <v>9.460000000000001</v>
+        <v>4.09</v>
       </c>
       <c r="H33" t="n">
-        <v>67.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I33" t="n">
-        <v>27.5</v>
+        <v>12</v>
       </c>
       <c r="J33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="K33" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="L33" t="n">
-        <v>10.9</v>
+        <v>11.27</v>
       </c>
       <c r="M33" t="n">
-        <v>4.48</v>
+        <v>1.99</v>
       </c>
       <c r="N33" t="n">
-        <v>3.64</v>
+        <v>2.69</v>
       </c>
       <c r="O33" t="n">
-        <v>1.5</v>
+        <v>0.47</v>
       </c>
       <c r="P33" t="n">
-        <v>227.88</v>
+        <v>231.86</v>
       </c>
       <c r="Q33" t="n">
-        <v>94.73</v>
+        <v>39.58</v>
       </c>
       <c r="R33" t="n">
-        <v>61.32</v>
+        <v>25.85</v>
       </c>
       <c r="S33" t="n">
-        <v>133.01</v>
+        <v>55.22</v>
       </c>
       <c r="T33" t="n">
-        <v>75.86</v>
+        <v>46.59</v>
       </c>
       <c r="U33" t="n">
-        <v>18.87</v>
+        <v>-7.01</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -2935,7 +2943,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2944,61 +2952,61 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>3580.2</v>
+        <v>3825.1</v>
       </c>
       <c r="E34" t="n">
-        <v>628.6</v>
+        <v>2921.4</v>
       </c>
       <c r="F34" t="n">
-        <v>24.95</v>
+        <v>17.47</v>
       </c>
       <c r="G34" t="n">
-        <v>4.09</v>
+        <v>13.4</v>
       </c>
       <c r="H34" t="n">
-        <v>69.3</v>
+        <v>222.4</v>
       </c>
       <c r="I34" t="n">
-        <v>12</v>
+        <v>170.4</v>
       </c>
       <c r="J34" t="n">
-        <v>1.64</v>
+        <v>3.89</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3</v>
+        <v>2.94</v>
       </c>
       <c r="L34" t="n">
-        <v>11.27</v>
+        <v>12.63</v>
       </c>
       <c r="M34" t="n">
-        <v>1.99</v>
+        <v>9.65</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
-        <v>0.47</v>
+        <v>2.07</v>
       </c>
       <c r="P34" t="n">
-        <v>231.86</v>
+        <v>237.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>39.58</v>
+        <v>181.7</v>
       </c>
       <c r="R34" t="n">
-        <v>25.85</v>
+        <v>111.32</v>
       </c>
       <c r="S34" t="n">
-        <v>55.22</v>
+        <v>251.86</v>
       </c>
       <c r="T34" t="n">
-        <v>46.59</v>
+        <v>181.46</v>
       </c>
       <c r="U34" t="n">
-        <v>-7.01</v>
+        <v>0.24</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3010,74 +3018,74 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3825.1</v>
+        <v>3520.1</v>
       </c>
       <c r="E35" t="n">
-        <v>2921.4</v>
+        <v>1847.7</v>
       </c>
       <c r="F35" t="n">
-        <v>17.47</v>
+        <v>20.94</v>
       </c>
       <c r="G35" t="n">
-        <v>13.4</v>
+        <v>10.99</v>
       </c>
       <c r="H35" t="n">
-        <v>222.4</v>
+        <v>117.6</v>
       </c>
       <c r="I35" t="n">
-        <v>170.4</v>
+        <v>62.5</v>
       </c>
       <c r="J35" t="n">
-        <v>3.89</v>
+        <v>2.47</v>
       </c>
       <c r="K35" t="n">
-        <v>2.94</v>
+        <v>1.32</v>
       </c>
       <c r="L35" t="n">
-        <v>12.63</v>
+        <v>11.96</v>
       </c>
       <c r="M35" t="n">
-        <v>9.65</v>
+        <v>6.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="O35" t="n">
-        <v>2.07</v>
+        <v>1.36</v>
       </c>
       <c r="P35" t="n">
-        <v>237.76</v>
+        <v>222.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>181.7</v>
+        <v>116.64</v>
       </c>
       <c r="R35" t="n">
-        <v>111.32</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>251.86</v>
+        <v>164.54</v>
       </c>
       <c r="T35" t="n">
-        <v>181.46</v>
+        <v>142.21</v>
       </c>
       <c r="U35" t="n">
-        <v>0.24</v>
+        <v>-25.57</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -3085,74 +3093,74 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3520.1</v>
+        <v>3362.9</v>
       </c>
       <c r="E36" t="n">
-        <v>1847.7</v>
+        <v>1772.5</v>
       </c>
       <c r="F36" t="n">
-        <v>20.94</v>
+        <v>16.64</v>
       </c>
       <c r="G36" t="n">
-        <v>10.99</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>117.6</v>
+        <v>281.8</v>
       </c>
       <c r="I36" t="n">
-        <v>62.5</v>
+        <v>150.3</v>
       </c>
       <c r="J36" t="n">
-        <v>2.47</v>
+        <v>2.89</v>
       </c>
       <c r="K36" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="L36" t="n">
-        <v>11.96</v>
+        <v>12.08</v>
       </c>
       <c r="M36" t="n">
-        <v>6.34</v>
+        <v>6.38</v>
       </c>
       <c r="N36" t="n">
-        <v>2.57</v>
+        <v>4.37</v>
       </c>
       <c r="O36" t="n">
-        <v>1.36</v>
+        <v>2.32</v>
       </c>
       <c r="P36" t="n">
-        <v>222.08</v>
+        <v>213.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>116.64</v>
+        <v>112.77</v>
       </c>
       <c r="R36" t="n">
-        <v>69.04000000000001</v>
+        <v>63.97</v>
       </c>
       <c r="S36" t="n">
-        <v>164.54</v>
+        <v>161.1</v>
       </c>
       <c r="T36" t="n">
-        <v>142.21</v>
+        <v>99.11</v>
       </c>
       <c r="U36" t="n">
-        <v>-25.57</v>
+        <v>13.66</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
@@ -3160,71 +3168,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Andy Dalton</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3362.9</v>
+        <v>3346.5</v>
       </c>
       <c r="E37" t="n">
-        <v>1772.5</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>16.64</v>
+        <v>21.45</v>
       </c>
       <c r="G37" t="n">
-        <v>8.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>281.8</v>
+        <v>117.1</v>
       </c>
       <c r="I37" t="n">
-        <v>150.3</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2.89</v>
+        <v>1.66</v>
       </c>
       <c r="K37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>12.08</v>
+        <v>11</v>
       </c>
       <c r="M37" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.37</v>
+        <v>2.14</v>
       </c>
       <c r="O37" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>213.7</v>
+        <v>215.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>112.77</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>63.97</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>161.1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>99.11</v>
-      </c>
-      <c r="U37" t="n">
-        <v>13.66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>50</t>
@@ -3235,55 +3239,55 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Andy Dalton</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3346.5</v>
+        <v>3459.7</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>21.45</v>
+        <v>17.56</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>117.1</v>
+        <v>742.5</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1.66</v>
+        <v>8.44</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>11</v>
+        <v>15.76</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.14</v>
+        <v>3.96</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>215.05</v>
+        <v>294.08</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3306,55 +3310,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3459.7</v>
+        <v>3103.6</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>17.56</v>
+        <v>13.7</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>742.5</v>
+        <v>180.5</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>8.44</v>
+        <v>3.08</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>15.76</v>
+        <v>16.82</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>294.08</v>
+        <v>174.79</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3365,8 +3369,12 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-22.59</v>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
           <t>50</t>
@@ -3377,55 +3385,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3103.6</v>
+        <v>3399.2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>13.7</v>
+        <v>21.66</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>180.5</v>
+        <v>217.9</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>16.82</v>
+        <v>10.42</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>174.79</v>
+        <v>230.08</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3436,71 +3444,63 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="U40" t="n">
-        <v>-22.59</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3399.2</v>
+        <v>3436.5</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>21.66</v>
+        <v>20.14</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>217.9</v>
+        <v>152.7</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>10.42</v>
+        <v>13.08</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.31</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>230.08</v>
+        <v>213.75</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3513,61 +3513,65 @@
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3436.5</v>
+        <v>3238.8</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>20.14</v>
+        <v>18.33</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>152.7</v>
+        <v>241.7</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>13.08</v>
+        <v>11.12</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>213.75</v>
+        <v>215.1</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3590,55 +3594,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3238.8</v>
+        <v>3444.4</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>18.33</v>
+        <v>15.56</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>241.7</v>
+        <v>119.7</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>11.12</v>
+        <v>11.48</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.1</v>
+        <v>4.07</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>215.1</v>
+        <v>191.69</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3661,55 +3665,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3444.4</v>
+        <v>3214.4</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>15.56</v>
+        <v>14.81</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>119.7</v>
+        <v>179.2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1.8</v>
+        <v>3.13</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>11.48</v>
+        <v>15.98</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.07</v>
+        <v>3.54</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>191.69</v>
+        <v>185.48</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3722,65 +3726,61 @@
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3214.4</v>
+        <v>3562.7</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>14.81</v>
+        <v>24.39</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>179.2</v>
+        <v>214</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3.13</v>
+        <v>2.35</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>15.98</v>
+        <v>13.47</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.54</v>
+        <v>2.54</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>185.48</v>
+        <v>243.55</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3793,61 +3793,65 @@
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3562.7</v>
+        <v>3610.2</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>24.39</v>
+        <v>18.74</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>214</v>
+        <v>332.6</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>13.47</v>
+        <v>11.79</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.54</v>
+        <v>3.98</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>243.55</v>
+        <v>235.07</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3870,55 +3874,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3610.2</v>
+        <v>3652.6</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>18.74</v>
+        <v>26.1</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>332.6</v>
+        <v>58.2</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>2.33</v>
+        <v>1.79</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>11.79</v>
+        <v>12.35</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.98</v>
+        <v>2.86</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>235.07</v>
+        <v>236.64</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3941,55 +3945,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3652.6</v>
+        <v>3445.3</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>26.1</v>
+        <v>17.5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>58.2</v>
+        <v>506.9</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1.79</v>
+        <v>4.91</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>12.35</v>
+        <v>12.22</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>236.64</v>
+        <v>257.98</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4002,65 +4006,61 @@
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3445.3</v>
+        <v>3238.8</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>17.5</v>
+        <v>17.79</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>506.9</v>
+        <v>723.8</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>4.91</v>
+        <v>7.33</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>12.22</v>
+        <v>9.06</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>257.98</v>
+        <v>293.61</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4073,61 +4073,65 @@
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3238.8</v>
+        <v>3342.8</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>17.79</v>
+        <v>16.68</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>723.8</v>
+        <v>197.6</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>7.33</v>
+        <v>1.96</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>293.61</v>
+        <v>204.43</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4150,55 +4154,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3342.8</v>
+        <v>3398.5</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>16.68</v>
+        <v>18.28</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>197.6</v>
+        <v>181.2</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>11.2</v>
+        <v>13.03</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.56</v>
+        <v>3.22</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>204.43</v>
+        <v>209.56</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4221,55 +4225,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3398.5</v>
+        <v>3186.9</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>18.28</v>
+        <v>14.24</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>181.2</v>
+        <v>179.1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2.48</v>
+        <v>3.09</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>13.03</v>
+        <v>16.14</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.22</v>
+        <v>3.53</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>209.56</v>
+        <v>181.55</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4282,65 +4286,61 @@
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3186.9</v>
+        <v>3627.9</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>14.24</v>
+        <v>22.95</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>179.1</v>
+        <v>171.1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>3.09</v>
+        <v>1.92</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>16.14</v>
+        <v>12.02</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.53</v>
+        <v>2.79</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>181.55</v>
+        <v>235.93</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4353,61 +4353,65 @@
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3627.9</v>
+        <v>3528.7</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>22.95</v>
+        <v>23.83</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>171.1</v>
+        <v>551.1</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.92</v>
+        <v>4.04</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>12.02</v>
+        <v>15.78</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>235.93</v>
+        <v>278.34</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4430,55 +4434,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3528.7</v>
+        <v>3563.2</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>23.83</v>
+        <v>21.31</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>551.1</v>
+        <v>157.8</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>4.04</v>
+        <v>1.82</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>15.78</v>
+        <v>11</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.96</v>
+        <v>2.19</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>278.34</v>
+        <v>228.09</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4501,55 +4505,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3563.2</v>
+        <v>3589.4</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>21.31</v>
+        <v>22.04</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>157.8</v>
+        <v>213</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1.82</v>
+        <v>3.04</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>11</v>
+        <v>13.18</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>228.09</v>
+        <v>241.3</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4572,55 +4576,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3589.4</v>
+        <v>3415.2</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>22.04</v>
+        <v>17.52</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>213</v>
+        <v>139.2</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.04</v>
+        <v>2.41</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>13.18</v>
+        <v>13.27</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.81</v>
+        <v>3.97</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>241.3</v>
+        <v>200.59</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4643,55 +4647,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3415.2</v>
+        <v>3235.3</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>17.52</v>
+        <v>15.01</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>139.2</v>
+        <v>185.3</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>2.41</v>
+        <v>3.16</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>13.27</v>
+        <v>16.39</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.97</v>
+        <v>3.62</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>200.59</v>
+        <v>186.92</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4704,65 +4708,61 @@
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>3235.3</v>
+        <v>3402</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>15.01</v>
+        <v>16.98</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>185.3</v>
+        <v>285.2</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>3.16</v>
+        <v>2.69</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>16.39</v>
+        <v>11.8</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>186.92</v>
+        <v>219.04</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4775,61 +4775,65 @@
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3402</v>
+        <v>3296.6</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>16.98</v>
+        <v>16.01</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>285.2</v>
+        <v>180.8</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>11.8</v>
+        <v>15.52</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.01</v>
+        <v>7.66</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>219.04</v>
+        <v>183.58</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4842,65 +4846,61 @@
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3296.6</v>
+        <v>3175.8</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>16.01</v>
+        <v>14.08</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>180.8</v>
+        <v>198.3</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>15.52</v>
+        <v>15.87</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>7.66</v>
+        <v>3.49</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>183.58</v>
+        <v>182.76</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4913,61 +4913,65 @@
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Trey Lance</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>3175.8</v>
+        <v>3277.4</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>14.08</v>
+        <v>17.51</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>198.3</v>
+        <v>685.5</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>3.05</v>
+        <v>3.46</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>15.87</v>
+        <v>13.25</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.49</v>
+        <v>2.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>182.76</v>
+        <v>259.15</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4990,55 +4994,55 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Trey Lance</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>3277.4</v>
+        <v>3263.2</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>17.51</v>
+        <v>18.7</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>685.5</v>
+        <v>688.8</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>13.25</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>259.15</v>
+        <v>273.51</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5061,55 +5065,55 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>3263.2</v>
+        <v>3465.2</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>18.7</v>
+        <v>22.43</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>688.8</v>
+        <v>510</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>9.640000000000001</v>
+        <v>10.61</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>273.51</v>
+        <v>278.11</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5132,43 +5136,43 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>3465.2</v>
+        <v>3524</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>22.43</v>
+        <v>16.81</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>510</v>
+        <v>383.1</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>4.29</v>
+        <v>3.35</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>10.61</v>
+        <v>11.9</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -5180,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>278.11</v>
+        <v>237.07</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5199,77 +5203,6 @@
         </is>
       </c>
       <c r="W65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Tyson Bagent</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>CHI</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" t="n">
-        <v>3524</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>383.1</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>237.07</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5282,7 +5215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W34"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,141 +7367,149 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cooper Rush</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>220.7</v>
+        <v>3568.4</v>
       </c>
       <c r="E29" t="n">
-        <v>3729.8</v>
+        <v>3345.7</v>
       </c>
       <c r="F29" t="n">
-        <v>1.35</v>
+        <v>18.61</v>
       </c>
       <c r="G29" t="n">
-        <v>22.82</v>
+        <v>17.39</v>
       </c>
       <c r="H29" t="n">
-        <v>3.9</v>
+        <v>163.4</v>
       </c>
       <c r="I29" t="n">
-        <v>67.09999999999999</v>
+        <v>154.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.08</v>
+        <v>2.07</v>
       </c>
       <c r="K29" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="L29" t="n">
-        <v>0.64</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>10.9</v>
+        <v>8.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.22</v>
+        <v>2.42</v>
       </c>
       <c r="O29" t="n">
-        <v>3.64</v>
+        <v>2.28</v>
       </c>
       <c r="P29" t="n">
-        <v>13.38</v>
+        <v>222.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>227.88</v>
+        <v>208.14</v>
       </c>
       <c r="R29" t="n">
-        <v>-66.22</v>
+        <v>124.69</v>
       </c>
       <c r="S29" t="n">
-        <v>636.66</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+        <v>293.41</v>
+      </c>
+      <c r="T29" t="n">
+        <v>208</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3568.4</v>
+        <v>3370.8</v>
       </c>
       <c r="E30" t="n">
-        <v>3345.7</v>
+        <v>3165.1</v>
       </c>
       <c r="F30" t="n">
-        <v>18.61</v>
+        <v>19.16</v>
       </c>
       <c r="G30" t="n">
-        <v>17.39</v>
+        <v>17.93</v>
       </c>
       <c r="H30" t="n">
-        <v>163.4</v>
+        <v>176.5</v>
       </c>
       <c r="I30" t="n">
-        <v>154.1</v>
+        <v>166.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="K30" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="L30" t="n">
-        <v>9.460000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="M30" t="n">
-        <v>8.9</v>
+        <v>9.32</v>
       </c>
       <c r="N30" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>222.18</v>
+        <v>217.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>208.14</v>
+        <v>203.57</v>
       </c>
       <c r="R30" t="n">
-        <v>124.69</v>
+        <v>119.04</v>
       </c>
       <c r="S30" t="n">
-        <v>293.41</v>
+        <v>289.92</v>
       </c>
       <c r="T30" t="n">
-        <v>208</v>
+        <v>242.45</v>
       </c>
       <c r="U30" t="n">
-        <v>0.14</v>
+        <v>-38.88</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
@@ -7576,74 +7517,74 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3370.8</v>
+        <v>3460</v>
       </c>
       <c r="E31" t="n">
-        <v>3165.1</v>
+        <v>1434.6</v>
       </c>
       <c r="F31" t="n">
-        <v>19.16</v>
+        <v>20.46</v>
       </c>
       <c r="G31" t="n">
-        <v>17.93</v>
+        <v>8.68</v>
       </c>
       <c r="H31" t="n">
-        <v>176.5</v>
+        <v>421.3</v>
       </c>
       <c r="I31" t="n">
-        <v>166.1</v>
+        <v>172.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.27</v>
+        <v>4.15</v>
       </c>
       <c r="K31" t="n">
-        <v>2.13</v>
+        <v>1.61</v>
       </c>
       <c r="L31" t="n">
-        <v>9.91</v>
+        <v>9.51</v>
       </c>
       <c r="M31" t="n">
-        <v>9.32</v>
+        <v>3.93</v>
       </c>
       <c r="N31" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>217.08</v>
+        <v>262.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>203.57</v>
+        <v>108.88</v>
       </c>
       <c r="R31" t="n">
-        <v>119.04</v>
+        <v>70.8</v>
       </c>
       <c r="S31" t="n">
-        <v>289.92</v>
+        <v>147.11</v>
       </c>
       <c r="T31" t="n">
-        <v>242.45</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="U31" t="n">
-        <v>-38.88</v>
+        <v>10.81</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -7651,70 +7592,70 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>3460</v>
+        <v>3729.8</v>
       </c>
       <c r="E32" t="n">
-        <v>1434.6</v>
+        <v>1550.4</v>
       </c>
       <c r="F32" t="n">
-        <v>20.46</v>
+        <v>22.82</v>
       </c>
       <c r="G32" t="n">
-        <v>8.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>421.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>172.8</v>
+        <v>27.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4.15</v>
+        <v>1.63</v>
       </c>
       <c r="K32" t="n">
-        <v>1.61</v>
+        <v>0.68</v>
       </c>
       <c r="L32" t="n">
-        <v>9.51</v>
+        <v>10.9</v>
       </c>
       <c r="M32" t="n">
-        <v>3.93</v>
+        <v>4.48</v>
       </c>
       <c r="N32" t="n">
-        <v>2.82</v>
+        <v>3.64</v>
       </c>
       <c r="O32" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="P32" t="n">
-        <v>262.61</v>
+        <v>227.88</v>
       </c>
       <c r="Q32" t="n">
-        <v>108.88</v>
+        <v>94.73</v>
       </c>
       <c r="R32" t="n">
-        <v>70.8</v>
+        <v>61.32</v>
       </c>
       <c r="S32" t="n">
-        <v>147.11</v>
+        <v>133.01</v>
       </c>
       <c r="T32" t="n">
-        <v>98.06999999999999</v>
+        <v>75.86</v>
       </c>
       <c r="U32" t="n">
-        <v>10.81</v>
+        <v>18.87</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -7726,70 +7667,70 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Kirk Cousins</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3729.8</v>
+        <v>3580.2</v>
       </c>
       <c r="E33" t="n">
-        <v>1550.4</v>
+        <v>628.6</v>
       </c>
       <c r="F33" t="n">
-        <v>22.82</v>
+        <v>24.95</v>
       </c>
       <c r="G33" t="n">
-        <v>9.460000000000001</v>
+        <v>4.09</v>
       </c>
       <c r="H33" t="n">
-        <v>67.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I33" t="n">
-        <v>27.5</v>
+        <v>12</v>
       </c>
       <c r="J33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="K33" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="L33" t="n">
-        <v>10.9</v>
+        <v>11.27</v>
       </c>
       <c r="M33" t="n">
-        <v>4.48</v>
+        <v>1.99</v>
       </c>
       <c r="N33" t="n">
-        <v>3.64</v>
+        <v>2.69</v>
       </c>
       <c r="O33" t="n">
-        <v>1.5</v>
+        <v>0.47</v>
       </c>
       <c r="P33" t="n">
-        <v>227.88</v>
+        <v>231.86</v>
       </c>
       <c r="Q33" t="n">
-        <v>94.73</v>
+        <v>39.58</v>
       </c>
       <c r="R33" t="n">
-        <v>61.32</v>
+        <v>25.85</v>
       </c>
       <c r="S33" t="n">
-        <v>133.01</v>
+        <v>55.22</v>
       </c>
       <c r="T33" t="n">
-        <v>75.86</v>
+        <v>46.59</v>
       </c>
       <c r="U33" t="n">
-        <v>18.87</v>
+        <v>-7.01</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -7797,81 +7738,6 @@
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Kirk Cousins</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3580.2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>628.6</v>
-      </c>
-      <c r="F34" t="n">
-        <v>24.95</v>
-      </c>
-      <c r="G34" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="H34" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="I34" t="n">
-        <v>12</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="P34" t="n">
-        <v>231.86</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>39.58</v>
-      </c>
-      <c r="R34" t="n">
-        <v>25.85</v>
-      </c>
-      <c r="S34" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="T34" t="n">
-        <v>46.59</v>
-      </c>
-      <c r="U34" t="n">
-        <v>-7.01</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -2418,74 +2418,74 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3868.6</v>
+        <v>3954.9</v>
       </c>
       <c r="E27" t="n">
-        <v>3638.4</v>
+        <v>3729.7</v>
       </c>
       <c r="F27" t="n">
-        <v>23.95</v>
+        <v>22.38</v>
       </c>
       <c r="G27" t="n">
-        <v>22.48</v>
+        <v>21.04</v>
       </c>
       <c r="H27" t="n">
-        <v>173.5</v>
+        <v>210.6</v>
       </c>
       <c r="I27" t="n">
-        <v>163.2</v>
+        <v>198.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="K27" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="L27" t="n">
-        <v>9.68</v>
+        <v>11.2</v>
       </c>
       <c r="M27" t="n">
-        <v>9.109999999999999</v>
+        <v>10.54</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>4.78</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>4.52</v>
       </c>
       <c r="P27" t="n">
-        <v>254.57</v>
+        <v>251.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>239.24</v>
+        <v>237.16</v>
       </c>
       <c r="R27" t="n">
-        <v>156.64</v>
+        <v>150.92</v>
       </c>
       <c r="S27" t="n">
-        <v>324.99</v>
+        <v>323.75</v>
       </c>
       <c r="T27" t="n">
-        <v>238.68</v>
+        <v>191.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5600000000000001</v>
+        <v>45.91</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -2493,74 +2493,74 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3954.9</v>
+        <v>3868.6</v>
       </c>
       <c r="E28" t="n">
-        <v>3729.7</v>
+        <v>3405.8</v>
       </c>
       <c r="F28" t="n">
-        <v>22.38</v>
+        <v>23.95</v>
       </c>
       <c r="G28" t="n">
-        <v>21.04</v>
+        <v>21.02</v>
       </c>
       <c r="H28" t="n">
-        <v>210.6</v>
+        <v>173.5</v>
       </c>
       <c r="I28" t="n">
-        <v>198.3</v>
+        <v>153.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2.48</v>
+        <v>1.89</v>
       </c>
       <c r="K28" t="n">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="L28" t="n">
-        <v>11.2</v>
+        <v>9.68</v>
       </c>
       <c r="M28" t="n">
-        <v>10.54</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>4.78</v>
+        <v>2.65</v>
       </c>
       <c r="O28" t="n">
-        <v>4.52</v>
+        <v>2.33</v>
       </c>
       <c r="P28" t="n">
-        <v>251.7</v>
+        <v>254.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>237.16</v>
+        <v>223.97</v>
       </c>
       <c r="R28" t="n">
-        <v>150.92</v>
+        <v>146.64</v>
       </c>
       <c r="S28" t="n">
-        <v>323.75</v>
+        <v>304.25</v>
       </c>
       <c r="T28" t="n">
-        <v>191.25</v>
+        <v>238.68</v>
       </c>
       <c r="U28" t="n">
-        <v>45.91</v>
+        <v>-14.71</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
@@ -3168,64 +3168,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Andy Dalton</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3346.5</v>
+        <v>3238.8</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>195.6</v>
       </c>
       <c r="F37" t="n">
-        <v>21.45</v>
+        <v>18.33</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="H37" t="n">
-        <v>117.1</v>
+        <v>241.7</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J37" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="L37" t="n">
-        <v>11</v>
+        <v>11.12</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="N37" t="n">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="P37" t="n">
-        <v>215.05</v>
+        <v>215.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>18.59</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3239,55 +3239,55 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Andy Dalton</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3459.7</v>
+        <v>3346.5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>17.56</v>
+        <v>21.45</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>742.5</v>
+        <v>117.1</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>8.44</v>
+        <v>1.66</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>15.76</v>
+        <v>11</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.96</v>
+        <v>2.14</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>294.08</v>
+        <v>215.05</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3310,55 +3310,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3103.6</v>
+        <v>3459.7</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>13.7</v>
+        <v>17.56</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>180.5</v>
+        <v>742.5</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3.08</v>
+        <v>8.44</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>16.82</v>
+        <v>15.76</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.52</v>
+        <v>3.96</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>174.79</v>
+        <v>294.08</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3369,12 +3369,8 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="U39" t="n">
-        <v>-22.59</v>
-      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>50</t>
@@ -3385,55 +3381,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3399.2</v>
+        <v>3103.6</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>21.66</v>
+        <v>13.7</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>217.9</v>
+        <v>180.5</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.42</v>
+        <v>16.82</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>230.08</v>
+        <v>174.79</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3444,63 +3440,71 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-22.59</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3436.5</v>
+        <v>3399.2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>20.14</v>
+        <v>21.66</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>152.7</v>
+        <v>217.9</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>13.08</v>
+        <v>10.42</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.45</v>
+        <v>3.31</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>213.75</v>
+        <v>230.08</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3513,65 +3517,61 @@
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3238.8</v>
+        <v>3436.5</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>18.33</v>
+        <v>20.14</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>241.7</v>
+        <v>152.7</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>11.12</v>
+        <v>13.08</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>215.1</v>
+        <v>213.75</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7217,74 +7217,74 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3868.6</v>
+        <v>3954.9</v>
       </c>
       <c r="E27" t="n">
-        <v>3638.4</v>
+        <v>3729.7</v>
       </c>
       <c r="F27" t="n">
-        <v>23.95</v>
+        <v>22.38</v>
       </c>
       <c r="G27" t="n">
-        <v>22.48</v>
+        <v>21.04</v>
       </c>
       <c r="H27" t="n">
-        <v>173.5</v>
+        <v>210.6</v>
       </c>
       <c r="I27" t="n">
-        <v>163.2</v>
+        <v>198.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="K27" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="L27" t="n">
-        <v>9.68</v>
+        <v>11.2</v>
       </c>
       <c r="M27" t="n">
-        <v>9.109999999999999</v>
+        <v>10.54</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>4.78</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>4.52</v>
       </c>
       <c r="P27" t="n">
-        <v>254.57</v>
+        <v>251.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>239.24</v>
+        <v>237.16</v>
       </c>
       <c r="R27" t="n">
-        <v>156.64</v>
+        <v>150.92</v>
       </c>
       <c r="S27" t="n">
-        <v>324.99</v>
+        <v>323.75</v>
       </c>
       <c r="T27" t="n">
-        <v>238.68</v>
+        <v>191.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5600000000000001</v>
+        <v>45.91</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -7292,74 +7292,74 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3954.9</v>
+        <v>3868.6</v>
       </c>
       <c r="E28" t="n">
-        <v>3729.7</v>
+        <v>3405.8</v>
       </c>
       <c r="F28" t="n">
-        <v>22.38</v>
+        <v>23.95</v>
       </c>
       <c r="G28" t="n">
-        <v>21.04</v>
+        <v>21.02</v>
       </c>
       <c r="H28" t="n">
-        <v>210.6</v>
+        <v>173.5</v>
       </c>
       <c r="I28" t="n">
-        <v>198.3</v>
+        <v>153.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2.48</v>
+        <v>1.89</v>
       </c>
       <c r="K28" t="n">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="L28" t="n">
-        <v>11.2</v>
+        <v>9.68</v>
       </c>
       <c r="M28" t="n">
-        <v>10.54</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>4.78</v>
+        <v>2.65</v>
       </c>
       <c r="O28" t="n">
-        <v>4.52</v>
+        <v>2.33</v>
       </c>
       <c r="P28" t="n">
-        <v>251.7</v>
+        <v>254.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>237.16</v>
+        <v>223.97</v>
       </c>
       <c r="R28" t="n">
-        <v>150.92</v>
+        <v>146.64</v>
       </c>
       <c r="S28" t="n">
-        <v>323.75</v>
+        <v>304.25</v>
       </c>
       <c r="T28" t="n">
-        <v>191.25</v>
+        <v>238.68</v>
       </c>
       <c r="U28" t="n">
-        <v>45.91</v>
+        <v>-14.71</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
@@ -8098,64 +8098,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andy Dalton</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3346.5</v>
+        <v>3238.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>195.6</v>
       </c>
       <c r="F5" t="n">
-        <v>21.45</v>
+        <v>18.33</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="H5" t="n">
-        <v>117.1</v>
+        <v>241.7</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>11.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="N5" t="n">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="P5" t="n">
-        <v>215.05</v>
+        <v>215.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>18.59</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -8169,55 +8169,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Andy Dalton</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3459.7</v>
+        <v>3346.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>17.56</v>
+        <v>21.45</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>742.5</v>
+        <v>117.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>8.44</v>
+        <v>1.66</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>15.76</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.96</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>294.08</v>
+        <v>215.05</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -8240,55 +8240,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3103.6</v>
+        <v>3459.7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>13.7</v>
+        <v>17.56</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>180.5</v>
+        <v>742.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.08</v>
+        <v>8.44</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16.82</v>
+        <v>15.76</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.52</v>
+        <v>3.96</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>174.79</v>
+        <v>294.08</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -8299,12 +8299,8 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-22.59</v>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>50</t>
@@ -8315,55 +8311,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3399.2</v>
+        <v>3103.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>21.66</v>
+        <v>13.7</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>217.9</v>
+        <v>180.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10.42</v>
+        <v>16.82</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>230.08</v>
+        <v>174.79</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -8374,63 +8370,71 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-22.59</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3436.5</v>
+        <v>3399.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>20.14</v>
+        <v>21.66</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>152.7</v>
+        <v>217.9</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13.08</v>
+        <v>10.42</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>3.31</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>213.75</v>
+        <v>230.08</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8443,65 +8447,61 @@
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3238.8</v>
+        <v>3436.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>18.33</v>
+        <v>20.14</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>241.7</v>
+        <v>152.7</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11.12</v>
+        <v>13.08</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>215.1</v>
+        <v>213.75</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -51988,67 +51988,67 @@
         <v>1</v>
       </c>
       <c r="H450" t="n">
-        <v>232.661</v>
+        <v>0</v>
       </c>
       <c r="I450" t="n">
-        <v>1.458</v>
+        <v>0</v>
       </c>
       <c r="J450" t="n">
-        <v>9.981999999999999</v>
+        <v>0</v>
       </c>
       <c r="K450" t="n">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="L450" t="n">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="M450" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="N450" t="n">
-        <v>139.537</v>
+        <v>0</v>
       </c>
       <c r="O450" t="n">
-        <v>325.784</v>
+        <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>0.505</v>
+        <v>0</v>
       </c>
       <c r="Q450" t="n">
-        <v>2.862</v>
+        <v>0</v>
       </c>
       <c r="R450" t="n">
-        <v>3.455</v>
+        <v>0</v>
       </c>
       <c r="S450" t="n">
-        <v>30.97</v>
+        <v>0</v>
       </c>
       <c r="T450" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="U450" t="n">
-        <v>0.628</v>
+        <v>0</v>
       </c>
       <c r="V450" t="n">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="W450" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="X450" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="Y450" t="n">
-        <v>0.764</v>
+        <v>0</v>
       </c>
       <c r="Z450" t="n">
-        <v>15.307</v>
+        <v>0</v>
       </c>
       <c r="AA450" t="n">
-        <v>3.224</v>
+        <v>0</v>
       </c>
       <c r="AB450" t="n">
-        <v>30.83</v>
+        <v>0</v>
       </c>
       <c r="AC450" t="inlineStr"/>
     </row>
@@ -65380,67 +65380,67 @@
         <v>1</v>
       </c>
       <c r="H594" t="n">
-        <v>0</v>
+        <v>195.618</v>
       </c>
       <c r="I594" t="n">
-        <v>0</v>
+        <v>1.118</v>
       </c>
       <c r="J594" t="n">
-        <v>0</v>
+        <v>13.993</v>
       </c>
       <c r="K594" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="L594" t="n">
-        <v>0</v>
+        <v>0.659</v>
       </c>
       <c r="M594" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="N594" t="n">
-        <v>0</v>
+        <v>102.496</v>
       </c>
       <c r="O594" t="n">
-        <v>0</v>
+        <v>288.736</v>
       </c>
       <c r="P594" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="Q594" t="n">
-        <v>0</v>
+        <v>2.522</v>
       </c>
       <c r="R594" t="n">
-        <v>0</v>
+        <v>4.843</v>
       </c>
       <c r="S594" t="n">
-        <v>0</v>
+        <v>34.98</v>
       </c>
       <c r="T594" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="U594" t="n">
-        <v>0</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V594" t="n">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="W594" t="n">
-        <v>0</v>
+        <v>1.795</v>
       </c>
       <c r="X594" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="Y594" t="n">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="Z594" t="n">
-        <v>0</v>
+        <v>13.017</v>
       </c>
       <c r="AA594" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB594" t="n">
-        <v>0</v>
+        <v>28.68</v>
       </c>
       <c r="AC594" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -4643,7 +4643,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4655,43 +4655,43 @@
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3415.2</v>
+        <v>3666</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>17.52</v>
+        <v>21.86</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>139.2</v>
+        <v>66.5</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>13.27</v>
+        <v>11.87</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.97</v>
+        <v>3.76</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>200.59</v>
+        <v>222.07</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9640,7 +9640,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9652,43 +9652,43 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3415.2</v>
+        <v>3666</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>17.52</v>
+        <v>21.86</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>139.2</v>
+        <v>66.5</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>13.27</v>
+        <v>11.87</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.97</v>
+        <v>3.76</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>200.59</v>
+        <v>222.07</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -90505,7 +90505,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -90598,7 +90598,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -90691,7 +90691,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -90784,7 +90784,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -90877,7 +90877,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -90970,7 +90970,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -91063,7 +91063,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -91156,7 +91156,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -91249,7 +91249,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -91342,7 +91342,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -91435,7 +91435,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -91528,7 +91528,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -91621,7 +91621,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -91714,7 +91714,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -91807,7 +91807,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -91900,7 +91900,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -604,16 +604,8 @@
       <c r="U2" t="n">
         <v>0.78</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -683,11 +675,7 @@
       <c r="U3" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -758,11 +746,7 @@
       <c r="U4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -833,11 +817,7 @@
       <c r="U5" t="n">
         <v>6.52</v>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -908,11 +888,7 @@
       <c r="U6" t="n">
         <v>7.94</v>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -983,11 +959,7 @@
       <c r="U7" t="n">
         <v>-10.74</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1058,11 +1030,7 @@
       <c r="U8" t="n">
         <v>12.71</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1133,11 +1101,7 @@
       <c r="U9" t="n">
         <v>-9.98</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1208,11 +1172,7 @@
       <c r="U10" t="n">
         <v>12.13</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1283,11 +1243,7 @@
       <c r="U11" t="n">
         <v>-24.31</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1358,11 +1314,7 @@
       <c r="U12" t="n">
         <v>-20.47</v>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1433,11 +1385,7 @@
       <c r="U13" t="n">
         <v>-12.62</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1508,11 +1456,7 @@
       <c r="U14" t="n">
         <v>-2.47</v>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1583,11 +1527,7 @@
       <c r="U15" t="n">
         <v>-31.77</v>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1658,11 +1598,7 @@
       <c r="U16" t="n">
         <v>-17.79</v>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1733,11 +1669,7 @@
       <c r="U17" t="n">
         <v>-37.58</v>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1808,11 +1740,7 @@
       <c r="U18" t="n">
         <v>2.88</v>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1883,11 +1811,7 @@
       <c r="U19" t="n">
         <v>-13.54</v>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1958,11 +1882,7 @@
       <c r="U20" t="n">
         <v>-26.39</v>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2033,11 +1953,7 @@
       <c r="U21" t="n">
         <v>-5.14</v>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -2108,11 +2024,7 @@
       <c r="U22" t="n">
         <v>-6.71</v>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2183,11 +2095,7 @@
       <c r="U23" t="n">
         <v>18.61</v>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2258,11 +2166,7 @@
       <c r="U24" t="n">
         <v>-65.38</v>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2333,11 +2237,7 @@
       <c r="U25" t="n">
         <v>0.62</v>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2408,11 +2308,7 @@
       <c r="U26" t="n">
         <v>-2.59</v>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2483,11 +2379,7 @@
       <c r="U27" t="n">
         <v>36.72</v>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2558,11 +2450,7 @@
       <c r="U28" t="n">
         <v>6.34</v>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2633,11 +2521,7 @@
       <c r="U29" t="n">
         <v>-27.55</v>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2708,457 +2592,429 @@
       <c r="U30" t="n">
         <v>62.14</v>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3614.7</v>
+        <v>3502.2</v>
       </c>
       <c r="E31" t="n">
-        <v>2112.5</v>
+        <v>1243.5</v>
       </c>
       <c r="F31" t="n">
-        <v>23.17</v>
+        <v>20.08</v>
       </c>
       <c r="G31" t="n">
-        <v>13.32</v>
+        <v>7.25</v>
       </c>
       <c r="H31" t="n">
-        <v>720</v>
+        <v>424.8</v>
       </c>
       <c r="I31" t="n">
-        <v>424</v>
+        <v>149.6</v>
       </c>
       <c r="J31" t="n">
-        <v>7.64</v>
+        <v>4.32</v>
       </c>
       <c r="K31" t="n">
-        <v>4.53</v>
+        <v>1.45</v>
       </c>
       <c r="L31" t="n">
-        <v>10.24</v>
+        <v>8.99</v>
       </c>
       <c r="M31" t="n">
-        <v>6.01</v>
+        <v>3.18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>3.65</v>
       </c>
       <c r="O31" t="n">
-        <v>2.42</v>
+        <v>1.28</v>
       </c>
       <c r="P31" t="n">
-        <v>326.47</v>
+        <v>263.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>190.5</v>
+        <v>93.48</v>
       </c>
       <c r="R31" t="n">
-        <v>136.95</v>
+        <v>60.93</v>
       </c>
       <c r="S31" t="n">
-        <v>244.23</v>
+        <v>126.21</v>
       </c>
       <c r="T31" t="n">
-        <v>278.65</v>
+        <v>91.94</v>
       </c>
       <c r="U31" t="n">
-        <v>-88.15000000000001</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>1.54</v>
+      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Kirk Cousins</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>3502.2</v>
+        <v>3426.8</v>
       </c>
       <c r="E32" t="n">
-        <v>1243.5</v>
+        <v>405.1</v>
       </c>
       <c r="F32" t="n">
-        <v>20.08</v>
+        <v>26.06</v>
       </c>
       <c r="G32" t="n">
-        <v>7.25</v>
+        <v>2.87</v>
       </c>
       <c r="H32" t="n">
-        <v>424.8</v>
+        <v>62.1</v>
       </c>
       <c r="I32" t="n">
-        <v>149.6</v>
+        <v>7.2</v>
       </c>
       <c r="J32" t="n">
-        <v>4.32</v>
+        <v>1.69</v>
       </c>
       <c r="K32" t="n">
-        <v>1.45</v>
+        <v>0.22</v>
       </c>
       <c r="L32" t="n">
-        <v>8.99</v>
+        <v>11.88</v>
       </c>
       <c r="M32" t="n">
-        <v>3.18</v>
+        <v>1.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>2.68</v>
       </c>
       <c r="O32" t="n">
-        <v>1.28</v>
+        <v>0.3</v>
       </c>
       <c r="P32" t="n">
-        <v>263.53</v>
+        <v>228.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>93.48</v>
+        <v>26.32</v>
       </c>
       <c r="R32" t="n">
-        <v>60.93</v>
+        <v>17.1</v>
       </c>
       <c r="S32" t="n">
-        <v>126.21</v>
+        <v>36.88</v>
       </c>
       <c r="T32" t="n">
-        <v>91.94</v>
+        <v>43.68</v>
       </c>
       <c r="U32" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-17.36</v>
+      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3426.8</v>
+        <v>3614.7</v>
       </c>
       <c r="E33" t="n">
-        <v>405.1</v>
+        <v>213.7</v>
       </c>
       <c r="F33" t="n">
-        <v>26.06</v>
+        <v>23.17</v>
       </c>
       <c r="G33" t="n">
-        <v>2.87</v>
+        <v>1.44</v>
       </c>
       <c r="H33" t="n">
-        <v>62.1</v>
+        <v>720</v>
       </c>
       <c r="I33" t="n">
-        <v>7.2</v>
+        <v>42.4</v>
       </c>
       <c r="J33" t="n">
-        <v>1.69</v>
+        <v>7.64</v>
       </c>
       <c r="K33" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="L33" t="n">
-        <v>11.88</v>
+        <v>10.24</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.68</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="P33" t="n">
-        <v>228.54</v>
+        <v>326.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>26.32</v>
+        <v>19.53</v>
       </c>
       <c r="R33" t="n">
-        <v>17.1</v>
+        <v>14.04</v>
       </c>
       <c r="S33" t="n">
-        <v>36.88</v>
+        <v>25.04</v>
       </c>
       <c r="T33" t="n">
-        <v>43.68</v>
+        <v>278.65</v>
       </c>
       <c r="U33" t="n">
-        <v>-17.36</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-259.12</v>
+      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>3779.2</v>
+        <v>3385.3</v>
       </c>
       <c r="E34" t="n">
-        <v>2870.1</v>
+        <v>2774.6</v>
       </c>
       <c r="F34" t="n">
-        <v>17.12</v>
+        <v>23.03</v>
       </c>
       <c r="G34" t="n">
-        <v>13.07</v>
+        <v>18.79</v>
       </c>
       <c r="H34" t="n">
-        <v>223.3</v>
+        <v>188.9</v>
       </c>
       <c r="I34" t="n">
-        <v>171.1</v>
+        <v>155.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.89</v>
+        <v>2.33</v>
       </c>
       <c r="K34" t="n">
-        <v>2.94</v>
+        <v>1.93</v>
       </c>
       <c r="L34" t="n">
-        <v>12.73</v>
+        <v>15.13</v>
       </c>
       <c r="M34" t="n">
-        <v>9.73</v>
+        <v>12.45</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.07</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>234.42</v>
+        <v>223.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>178.23</v>
+        <v>182.8</v>
       </c>
       <c r="R34" t="n">
-        <v>108.07</v>
+        <v>108.53</v>
       </c>
       <c r="S34" t="n">
-        <v>247.88</v>
-      </c>
-      <c r="T34" t="n">
-        <v>170.12</v>
-      </c>
-      <c r="U34" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>258.17</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3400.9</v>
+        <v>3779.2</v>
       </c>
       <c r="E35" t="n">
-        <v>1792.6</v>
+        <v>2870.1</v>
       </c>
       <c r="F35" t="n">
-        <v>16.16</v>
+        <v>17.12</v>
       </c>
       <c r="G35" t="n">
-        <v>8.529999999999999</v>
+        <v>13.07</v>
       </c>
       <c r="H35" t="n">
-        <v>282.1</v>
+        <v>223.3</v>
       </c>
       <c r="I35" t="n">
-        <v>150.4</v>
+        <v>171.1</v>
       </c>
       <c r="J35" t="n">
-        <v>2.89</v>
+        <v>3.89</v>
       </c>
       <c r="K35" t="n">
-        <v>1.56</v>
+        <v>2.94</v>
       </c>
       <c r="L35" t="n">
-        <v>12.11</v>
+        <v>12.73</v>
       </c>
       <c r="M35" t="n">
-        <v>6.4</v>
+        <v>9.73</v>
       </c>
       <c r="N35" t="n">
-        <v>4.97</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="P35" t="n">
-        <v>212.07</v>
+        <v>234.42</v>
       </c>
       <c r="Q35" t="n">
-        <v>112.12</v>
+        <v>178.23</v>
       </c>
       <c r="R35" t="n">
-        <v>63.43</v>
+        <v>108.07</v>
       </c>
       <c r="S35" t="n">
-        <v>160.74</v>
+        <v>247.88</v>
       </c>
       <c r="T35" t="n">
-        <v>92.91</v>
+        <v>170.12</v>
       </c>
       <c r="U35" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3385.3</v>
+        <v>3400.9</v>
       </c>
       <c r="E36" t="n">
-        <v>997.2</v>
+        <v>1792.6</v>
       </c>
       <c r="F36" t="n">
-        <v>23.03</v>
+        <v>16.16</v>
       </c>
       <c r="G36" t="n">
-        <v>6.88</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>188.9</v>
+        <v>282.1</v>
       </c>
       <c r="I36" t="n">
-        <v>55.3</v>
+        <v>150.4</v>
       </c>
       <c r="J36" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="L36" t="n">
-        <v>15.13</v>
+        <v>12.11</v>
       </c>
       <c r="M36" t="n">
-        <v>4.46</v>
+        <v>6.4</v>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>4.97</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>2.65</v>
       </c>
       <c r="P36" t="n">
-        <v>223.34</v>
+        <v>212.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>66.16</v>
+        <v>112.12</v>
       </c>
       <c r="R36" t="n">
-        <v>39.28</v>
+        <v>63.43</v>
       </c>
       <c r="S36" t="n">
-        <v>93.44</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>160.74</v>
+      </c>
+      <c r="T36" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="U36" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -3225,11 +3081,7 @@
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -3296,11 +3148,7 @@
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -3367,11 +3215,7 @@
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -3442,11 +3286,7 @@
       <c r="U40" t="n">
         <v>-21.18</v>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3580,11 +3420,7 @@
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3651,11 +3487,7 @@
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3722,11 +3554,7 @@
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3860,11 +3688,7 @@
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3931,11 +3755,7 @@
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -4069,11 +3889,7 @@
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -4140,11 +3956,7 @@
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -4211,11 +4023,7 @@
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -4349,11 +4157,7 @@
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -4420,11 +4224,7 @@
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -4491,11 +4291,7 @@
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -4562,11 +4358,7 @@
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -4700,11 +4492,7 @@
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -4838,11 +4626,7 @@
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -4909,11 +4693,7 @@
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -4984,11 +4764,7 @@
       <c r="U62" t="n">
         <v>-71.12</v>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -5055,11 +4831,7 @@
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -5126,11 +4898,7 @@
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -5197,11 +4965,7 @@
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5403,16 +5167,8 @@
       <c r="U2" t="n">
         <v>0.78</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5482,11 +5238,7 @@
       <c r="U3" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -5557,11 +5309,7 @@
       <c r="U4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -5632,11 +5380,7 @@
       <c r="U5" t="n">
         <v>6.52</v>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -5707,11 +5451,7 @@
       <c r="U6" t="n">
         <v>7.94</v>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -5782,11 +5522,7 @@
       <c r="U7" t="n">
         <v>-10.74</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -5857,11 +5593,7 @@
       <c r="U8" t="n">
         <v>12.71</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -5932,11 +5664,7 @@
       <c r="U9" t="n">
         <v>-9.98</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6007,11 +5735,7 @@
       <c r="U10" t="n">
         <v>12.13</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -6082,11 +5806,7 @@
       <c r="U11" t="n">
         <v>-24.31</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -6157,11 +5877,7 @@
       <c r="U12" t="n">
         <v>-20.47</v>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -6232,11 +5948,7 @@
       <c r="U13" t="n">
         <v>-12.62</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -6307,11 +6019,7 @@
       <c r="U14" t="n">
         <v>-2.47</v>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -6382,11 +6090,7 @@
       <c r="U15" t="n">
         <v>-31.77</v>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -6457,11 +6161,7 @@
       <c r="U16" t="n">
         <v>-17.79</v>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -6532,11 +6232,7 @@
       <c r="U17" t="n">
         <v>-37.58</v>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -6607,11 +6303,7 @@
       <c r="U18" t="n">
         <v>2.88</v>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -6682,11 +6374,7 @@
       <c r="U19" t="n">
         <v>-13.54</v>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -6757,11 +6445,7 @@
       <c r="U20" t="n">
         <v>-26.39</v>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -6832,11 +6516,7 @@
       <c r="U21" t="n">
         <v>-5.14</v>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -6907,11 +6587,7 @@
       <c r="U22" t="n">
         <v>-6.71</v>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -6982,11 +6658,7 @@
       <c r="U23" t="n">
         <v>18.61</v>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -7057,11 +6729,7 @@
       <c r="U24" t="n">
         <v>-65.38</v>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -7132,11 +6800,7 @@
       <c r="U25" t="n">
         <v>0.62</v>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -7207,11 +6871,7 @@
       <c r="U26" t="n">
         <v>-2.59</v>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -7282,11 +6942,7 @@
       <c r="U27" t="n">
         <v>36.72</v>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -7357,11 +7013,7 @@
       <c r="U28" t="n">
         <v>6.34</v>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -7432,11 +7084,7 @@
       <c r="U29" t="n">
         <v>-27.55</v>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -7507,236 +7155,220 @@
       <c r="U30" t="n">
         <v>62.14</v>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3614.7</v>
+        <v>3502.2</v>
       </c>
       <c r="E31" t="n">
-        <v>2112.5</v>
+        <v>1243.5</v>
       </c>
       <c r="F31" t="n">
-        <v>23.17</v>
+        <v>20.08</v>
       </c>
       <c r="G31" t="n">
-        <v>13.32</v>
+        <v>7.25</v>
       </c>
       <c r="H31" t="n">
-        <v>720</v>
+        <v>424.8</v>
       </c>
       <c r="I31" t="n">
-        <v>424</v>
+        <v>149.6</v>
       </c>
       <c r="J31" t="n">
-        <v>7.64</v>
+        <v>4.32</v>
       </c>
       <c r="K31" t="n">
-        <v>4.53</v>
+        <v>1.45</v>
       </c>
       <c r="L31" t="n">
-        <v>10.24</v>
+        <v>8.99</v>
       </c>
       <c r="M31" t="n">
-        <v>6.01</v>
+        <v>3.18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>3.65</v>
       </c>
       <c r="O31" t="n">
-        <v>2.42</v>
+        <v>1.28</v>
       </c>
       <c r="P31" t="n">
-        <v>326.47</v>
+        <v>263.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>190.5</v>
+        <v>93.48</v>
       </c>
       <c r="R31" t="n">
-        <v>136.95</v>
+        <v>60.93</v>
       </c>
       <c r="S31" t="n">
-        <v>244.23</v>
+        <v>126.21</v>
       </c>
       <c r="T31" t="n">
-        <v>278.65</v>
+        <v>91.94</v>
       </c>
       <c r="U31" t="n">
-        <v>-88.15000000000001</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>1.54</v>
+      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Kirk Cousins</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>3502.2</v>
+        <v>3426.8</v>
       </c>
       <c r="E32" t="n">
-        <v>1243.5</v>
+        <v>405.1</v>
       </c>
       <c r="F32" t="n">
-        <v>20.08</v>
+        <v>26.06</v>
       </c>
       <c r="G32" t="n">
-        <v>7.25</v>
+        <v>2.87</v>
       </c>
       <c r="H32" t="n">
-        <v>424.8</v>
+        <v>62.1</v>
       </c>
       <c r="I32" t="n">
-        <v>149.6</v>
+        <v>7.2</v>
       </c>
       <c r="J32" t="n">
-        <v>4.32</v>
+        <v>1.69</v>
       </c>
       <c r="K32" t="n">
-        <v>1.45</v>
+        <v>0.22</v>
       </c>
       <c r="L32" t="n">
-        <v>8.99</v>
+        <v>11.88</v>
       </c>
       <c r="M32" t="n">
-        <v>3.18</v>
+        <v>1.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>2.68</v>
       </c>
       <c r="O32" t="n">
-        <v>1.28</v>
+        <v>0.3</v>
       </c>
       <c r="P32" t="n">
-        <v>263.53</v>
+        <v>228.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>93.48</v>
+        <v>26.32</v>
       </c>
       <c r="R32" t="n">
-        <v>60.93</v>
+        <v>17.1</v>
       </c>
       <c r="S32" t="n">
-        <v>126.21</v>
+        <v>36.88</v>
       </c>
       <c r="T32" t="n">
-        <v>91.94</v>
+        <v>43.68</v>
       </c>
       <c r="U32" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-17.36</v>
+      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3426.8</v>
+        <v>3614.7</v>
       </c>
       <c r="E33" t="n">
-        <v>405.1</v>
+        <v>213.7</v>
       </c>
       <c r="F33" t="n">
-        <v>26.06</v>
+        <v>23.17</v>
       </c>
       <c r="G33" t="n">
-        <v>2.87</v>
+        <v>1.44</v>
       </c>
       <c r="H33" t="n">
-        <v>62.1</v>
+        <v>720</v>
       </c>
       <c r="I33" t="n">
-        <v>7.2</v>
+        <v>42.4</v>
       </c>
       <c r="J33" t="n">
-        <v>1.69</v>
+        <v>7.64</v>
       </c>
       <c r="K33" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="L33" t="n">
-        <v>11.88</v>
+        <v>10.24</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.68</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="P33" t="n">
-        <v>228.54</v>
+        <v>326.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>26.32</v>
+        <v>19.53</v>
       </c>
       <c r="R33" t="n">
-        <v>17.1</v>
+        <v>14.04</v>
       </c>
       <c r="S33" t="n">
-        <v>36.88</v>
+        <v>25.04</v>
       </c>
       <c r="T33" t="n">
-        <v>43.68</v>
+        <v>278.65</v>
       </c>
       <c r="U33" t="n">
-        <v>-17.36</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-259.12</v>
+      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
     </row>
   </sheetData>
@@ -7873,222 +7505,210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3779.2</v>
+        <v>3385.3</v>
       </c>
       <c r="E2" t="n">
-        <v>2870.1</v>
+        <v>2774.6</v>
       </c>
       <c r="F2" t="n">
-        <v>17.12</v>
+        <v>23.03</v>
       </c>
       <c r="G2" t="n">
-        <v>13.07</v>
+        <v>18.79</v>
       </c>
       <c r="H2" t="n">
-        <v>223.3</v>
+        <v>188.9</v>
       </c>
       <c r="I2" t="n">
-        <v>171.1</v>
+        <v>155.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.89</v>
+        <v>2.33</v>
       </c>
       <c r="K2" t="n">
-        <v>2.94</v>
+        <v>1.93</v>
       </c>
       <c r="L2" t="n">
-        <v>12.73</v>
+        <v>15.13</v>
       </c>
       <c r="M2" t="n">
-        <v>9.73</v>
+        <v>12.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>2.07</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>234.42</v>
+        <v>223.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>178.23</v>
+        <v>182.8</v>
       </c>
       <c r="R2" t="n">
-        <v>108.07</v>
+        <v>108.53</v>
       </c>
       <c r="S2" t="n">
-        <v>247.88</v>
-      </c>
-      <c r="T2" t="n">
-        <v>170.12</v>
-      </c>
-      <c r="U2" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>258.17</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3400.9</v>
+        <v>3779.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1792.6</v>
+        <v>2870.1</v>
       </c>
       <c r="F3" t="n">
-        <v>16.16</v>
+        <v>17.12</v>
       </c>
       <c r="G3" t="n">
-        <v>8.529999999999999</v>
+        <v>13.07</v>
       </c>
       <c r="H3" t="n">
-        <v>282.1</v>
+        <v>223.3</v>
       </c>
       <c r="I3" t="n">
-        <v>150.4</v>
+        <v>171.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2.89</v>
+        <v>3.89</v>
       </c>
       <c r="K3" t="n">
-        <v>1.56</v>
+        <v>2.94</v>
       </c>
       <c r="L3" t="n">
-        <v>12.11</v>
+        <v>12.73</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4</v>
+        <v>9.73</v>
       </c>
       <c r="N3" t="n">
-        <v>4.97</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="P3" t="n">
-        <v>212.07</v>
+        <v>234.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>112.12</v>
+        <v>178.23</v>
       </c>
       <c r="R3" t="n">
-        <v>63.43</v>
+        <v>108.07</v>
       </c>
       <c r="S3" t="n">
-        <v>160.74</v>
+        <v>247.88</v>
       </c>
       <c r="T3" t="n">
-        <v>92.91</v>
+        <v>170.12</v>
       </c>
       <c r="U3" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3385.3</v>
+        <v>3400.9</v>
       </c>
       <c r="E4" t="n">
-        <v>997.2</v>
+        <v>1792.6</v>
       </c>
       <c r="F4" t="n">
-        <v>23.03</v>
+        <v>16.16</v>
       </c>
       <c r="G4" t="n">
-        <v>6.88</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>188.9</v>
+        <v>282.1</v>
       </c>
       <c r="I4" t="n">
-        <v>55.3</v>
+        <v>150.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="L4" t="n">
-        <v>15.13</v>
+        <v>12.11</v>
       </c>
       <c r="M4" t="n">
-        <v>4.46</v>
+        <v>6.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>4.97</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>2.65</v>
       </c>
       <c r="P4" t="n">
-        <v>223.34</v>
+        <v>212.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>66.16</v>
+        <v>112.12</v>
       </c>
       <c r="R4" t="n">
-        <v>39.28</v>
+        <v>63.43</v>
       </c>
       <c r="S4" t="n">
-        <v>93.44</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>160.74</v>
+      </c>
+      <c r="T4" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="U4" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -8155,11 +7775,7 @@
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -8226,11 +7842,7 @@
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -8297,11 +7909,7 @@
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -8372,11 +7980,7 @@
       <c r="U8" t="n">
         <v>-21.18</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -8510,11 +8114,7 @@
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -8581,11 +8181,7 @@
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -8652,11 +8248,7 @@
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -8790,11 +8382,7 @@
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -8861,11 +8449,7 @@
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -8999,11 +8583,7 @@
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -9070,11 +8650,7 @@
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -9141,11 +8717,7 @@
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -9279,11 +8851,7 @@
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -9350,11 +8918,7 @@
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -9421,11 +8985,7 @@
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -9492,11 +9052,7 @@
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -9630,11 +9186,7 @@
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -9768,11 +9320,7 @@
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -9839,11 +9387,7 @@
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -9914,11 +9458,7 @@
       <c r="U30" t="n">
         <v>-71.12</v>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -9985,11 +9525,7 @@
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -10056,11 +9592,7 @@
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -10127,11 +9659,7 @@
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
     </row>
   </sheetData>
@@ -32644,67 +32172,67 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0</v>
+        <v>213.72</v>
       </c>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>1.438</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
+        <v>42.393</v>
       </c>
       <c r="K242" t="n">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>0.604</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>120.597</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
+        <v>306.843</v>
       </c>
       <c r="P242" t="n">
-        <v>0</v>
+        <v>0.498</v>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>21.402</v>
       </c>
       <c r="S242" t="n">
-        <v>0</v>
+        <v>63.38</v>
       </c>
       <c r="T242" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="U242" t="n">
-        <v>0</v>
+        <v>0.963</v>
       </c>
       <c r="V242" t="n">
-        <v>0</v>
+        <v>0.209</v>
       </c>
       <c r="W242" t="n">
-        <v>0</v>
+        <v>1.739</v>
       </c>
       <c r="X242" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="Y242" t="n">
-        <v>0</v>
+        <v>0.832</v>
       </c>
       <c r="Z242" t="n">
-        <v>0</v>
+        <v>19.534</v>
       </c>
       <c r="AA242" t="n">
-        <v>0</v>
+        <v>4.738</v>
       </c>
       <c r="AB242" t="n">
-        <v>0</v>
+        <v>35.182</v>
       </c>
       <c r="AC242" t="inlineStr"/>
     </row>
@@ -33109,67 +32637,67 @@
         <v>0</v>
       </c>
       <c r="H247" t="n">
-        <v>205.022</v>
+        <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>1.315</v>
+        <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>42.18</v>
+        <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0.601</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>111.904</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>298.144</v>
+        <v>0</v>
       </c>
       <c r="P247" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="Q247" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>21.191</v>
+        <v>0</v>
       </c>
       <c r="S247" t="n">
-        <v>63.169</v>
+        <v>0</v>
       </c>
       <c r="T247" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="U247" t="n">
-        <v>0.964</v>
+        <v>0</v>
       </c>
       <c r="V247" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="W247" t="n">
-        <v>1.737</v>
+        <v>0</v>
       </c>
       <c r="X247" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>18.681</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="n">
-        <v>4.204</v>
+        <v>0</v>
       </c>
       <c r="AB247" t="n">
-        <v>34.327</v>
+        <v>0</v>
       </c>
       <c r="AC247" t="inlineStr"/>
     </row>
@@ -33202,67 +32730,67 @@
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>209.761</v>
+        <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>1.444</v>
+        <v>0</v>
       </c>
       <c r="J248" t="n">
-        <v>42.628</v>
+        <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>0.471</v>
+        <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0.602</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>116.637</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
-        <v>302.884</v>
+        <v>0</v>
       </c>
       <c r="P248" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q248" t="n">
-        <v>2.849</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>21.64</v>
+        <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>63.618</v>
+        <v>0</v>
       </c>
       <c r="T248" t="n">
-        <v>0.163</v>
+        <v>0</v>
       </c>
       <c r="U248" t="n">
-        <v>0.989</v>
+        <v>0</v>
       </c>
       <c r="V248" t="n">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="W248" t="n">
-        <v>1.738</v>
+        <v>0</v>
       </c>
       <c r="X248" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="Z248" t="n">
-        <v>19.58</v>
+        <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>4.667</v>
+        <v>0</v>
       </c>
       <c r="AB248" t="n">
-        <v>35.227</v>
+        <v>0</v>
       </c>
       <c r="AC248" t="inlineStr"/>
     </row>
@@ -33295,67 +32823,67 @@
         <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>212.781</v>
+        <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>1.241</v>
+        <v>0</v>
       </c>
       <c r="J249" t="n">
-        <v>42.619</v>
+        <v>0</v>
       </c>
       <c r="K249" t="n">
-        <v>0.469</v>
+        <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>119.657</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>305.904</v>
+        <v>0</v>
       </c>
       <c r="P249" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>2.645</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>21.631</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>63.609</v>
+        <v>0</v>
       </c>
       <c r="T249" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>0.987</v>
+        <v>0</v>
       </c>
       <c r="V249" t="n">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="W249" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="X249" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="Z249" t="n">
-        <v>18.872</v>
+        <v>0</v>
       </c>
       <c r="AA249" t="n">
-        <v>4.497</v>
+        <v>0</v>
       </c>
       <c r="AB249" t="n">
-        <v>34.519</v>
+        <v>0</v>
       </c>
       <c r="AC249" t="inlineStr"/>
     </row>
@@ -33388,67 +32916,67 @@
         <v>1</v>
       </c>
       <c r="H250" t="n">
-        <v>216.434</v>
+        <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>1.336</v>
+        <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>42.172</v>
+        <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0.608</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>123.314</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
-        <v>309.555</v>
+        <v>0</v>
       </c>
       <c r="P250" t="n">
-        <v>0.463</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>21.182</v>
+        <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>63.16</v>
+        <v>0</v>
       </c>
       <c r="T250" t="n">
-        <v>0.159</v>
+        <v>0</v>
       </c>
       <c r="U250" t="n">
-        <v>0.977</v>
+        <v>0</v>
       </c>
       <c r="V250" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="W250" t="n">
-        <v>1.744</v>
+        <v>0</v>
       </c>
       <c r="X250" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="n">
-        <v>19.238</v>
+        <v>0</v>
       </c>
       <c r="AA250" t="n">
-        <v>4.656</v>
+        <v>0</v>
       </c>
       <c r="AB250" t="n">
-        <v>34.924</v>
+        <v>0</v>
       </c>
       <c r="AC250" t="inlineStr"/>
     </row>
@@ -33481,67 +33009,67 @@
         <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>214.566</v>
+        <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>1.337</v>
+        <v>0</v>
       </c>
       <c r="J251" t="n">
-        <v>42.601</v>
+        <v>0</v>
       </c>
       <c r="K251" t="n">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0.603</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>121.445</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
-        <v>307.686</v>
+        <v>0</v>
       </c>
       <c r="P251" t="n">
-        <v>0.463</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>21.611</v>
+        <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>63.589</v>
+        <v>0</v>
       </c>
       <c r="T251" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="U251" t="n">
-        <v>0.994</v>
+        <v>0</v>
       </c>
       <c r="V251" t="n">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="W251" t="n">
-        <v>1.739</v>
+        <v>0</v>
       </c>
       <c r="X251" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="Z251" t="n">
-        <v>19.367</v>
+        <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>4.716</v>
+        <v>0</v>
       </c>
       <c r="AB251" t="n">
-        <v>35.014</v>
+        <v>0</v>
       </c>
       <c r="AC251" t="inlineStr"/>
     </row>
@@ -33574,67 +33102,67 @@
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>210.139</v>
+        <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>1.254</v>
+        <v>0</v>
       </c>
       <c r="J252" t="n">
-        <v>42.275</v>
+        <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0.605</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>117.016</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>303.263</v>
+        <v>0</v>
       </c>
       <c r="P252" t="n">
-        <v>0.434</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="n">
-        <v>2.659</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>21.283</v>
+        <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>63.267</v>
+        <v>0</v>
       </c>
       <c r="T252" t="n">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>0.966</v>
+        <v>0</v>
       </c>
       <c r="V252" t="n">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="W252" t="n">
-        <v>1.741</v>
+        <v>0</v>
       </c>
       <c r="X252" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>18.656</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>34.304</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="inlineStr"/>
     </row>
@@ -33667,67 +33195,67 @@
         <v>0</v>
       </c>
       <c r="H253" t="n">
-        <v>212.349</v>
+        <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>1.339</v>
+        <v>0</v>
       </c>
       <c r="J253" t="n">
-        <v>42.67</v>
+        <v>0</v>
       </c>
       <c r="K253" t="n">
-        <v>0.467</v>
+        <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0.597</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N253" t="n">
-        <v>119.226</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>305.473</v>
+        <v>0</v>
       </c>
       <c r="P253" t="n">
-        <v>0.463</v>
+        <v>0</v>
       </c>
       <c r="Q253" t="n">
-        <v>2.743</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>21.681</v>
+        <v>0</v>
       </c>
       <c r="S253" t="n">
-        <v>63.659</v>
+        <v>0</v>
       </c>
       <c r="T253" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="U253" t="n">
-        <v>0.985</v>
+        <v>0</v>
       </c>
       <c r="V253" t="n">
-        <v>0.207</v>
+        <v>0</v>
       </c>
       <c r="W253" t="n">
-        <v>1.733</v>
+        <v>0</v>
       </c>
       <c r="X253" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="Y253" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="Z253" t="n">
-        <v>19.251</v>
+        <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="AB253" t="n">
-        <v>34.891</v>
+        <v>0</v>
       </c>
       <c r="AC253" t="inlineStr"/>
     </row>
@@ -33760,67 +33288,67 @@
         <v>1</v>
       </c>
       <c r="H254" t="n">
-        <v>211.606</v>
+        <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>1.341</v>
+        <v>0</v>
       </c>
       <c r="J254" t="n">
-        <v>42.122</v>
+        <v>0</v>
       </c>
       <c r="K254" t="n">
-        <v>0.433</v>
+        <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>0.602</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>118.485</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
-        <v>304.726</v>
+        <v>0</v>
       </c>
       <c r="P254" t="n">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="Q254" t="n">
-        <v>2.746</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>21.132</v>
+        <v>0</v>
       </c>
       <c r="S254" t="n">
-        <v>63.11</v>
+        <v>0</v>
       </c>
       <c r="T254" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="U254" t="n">
-        <v>0.952</v>
+        <v>0</v>
       </c>
       <c r="V254" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="W254" t="n">
-        <v>1.737</v>
+        <v>0</v>
       </c>
       <c r="X254" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="n">
-        <v>18.923</v>
+        <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>4.426</v>
+        <v>0</v>
       </c>
       <c r="AB254" t="n">
-        <v>34.6</v>
+        <v>0</v>
       </c>
       <c r="AC254" t="inlineStr"/>
     </row>
@@ -33853,67 +33381,67 @@
         <v>1</v>
       </c>
       <c r="H255" t="n">
-        <v>218.992</v>
+        <v>0</v>
       </c>
       <c r="I255" t="n">
-        <v>1.446</v>
+        <v>0</v>
       </c>
       <c r="J255" t="n">
-        <v>42.138</v>
+        <v>0</v>
       </c>
       <c r="K255" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0.598</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>125.874</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
-        <v>312.114</v>
+        <v>0</v>
       </c>
       <c r="P255" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q255" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>21.15</v>
+        <v>0</v>
       </c>
       <c r="S255" t="n">
-        <v>63.128</v>
+        <v>0</v>
       </c>
       <c r="T255" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="U255" t="n">
-        <v>0.951</v>
+        <v>0</v>
       </c>
       <c r="V255" t="n">
-        <v>0.207</v>
+        <v>0</v>
       </c>
       <c r="W255" t="n">
-        <v>1.733</v>
+        <v>0</v>
       </c>
       <c r="X255" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="Z255" t="n">
-        <v>19.641</v>
+        <v>0</v>
       </c>
       <c r="AA255" t="n">
-        <v>4.874</v>
+        <v>0</v>
       </c>
       <c r="AB255" t="n">
-        <v>35.311</v>
+        <v>0</v>
       </c>
       <c r="AC255" t="inlineStr"/>
     </row>
@@ -33946,67 +33474,67 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>200.869</v>
+        <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>1.263</v>
+        <v>0</v>
       </c>
       <c r="J256" t="n">
-        <v>42.62</v>
+        <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>0.433</v>
+        <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0.591</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>107.746</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
-        <v>293.993</v>
+        <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.437</v>
+        <v>0</v>
       </c>
       <c r="Q256" t="n">
-        <v>2.668</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>21.631</v>
+        <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>63.609</v>
+        <v>0</v>
       </c>
       <c r="T256" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="U256" t="n">
-        <v>0.951</v>
+        <v>0</v>
       </c>
       <c r="V256" t="n">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="W256" t="n">
-        <v>1.727</v>
+        <v>0</v>
       </c>
       <c r="X256" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="n">
-        <v>18.293</v>
+        <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>4.003</v>
+        <v>0</v>
       </c>
       <c r="AB256" t="n">
-        <v>33.924</v>
+        <v>0</v>
       </c>
       <c r="AC256" t="inlineStr"/>
     </row>
@@ -67519,67 +67047,67 @@
         <v>0</v>
       </c>
       <c r="H617" t="n">
-        <v>200.226</v>
+        <v>0</v>
       </c>
       <c r="I617" t="n">
-        <v>1.416</v>
+        <v>0</v>
       </c>
       <c r="J617" t="n">
-        <v>11.154</v>
+        <v>0</v>
       </c>
       <c r="K617" t="n">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="L617" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="M617" t="n">
-        <v>0.198</v>
+        <v>0</v>
       </c>
       <c r="N617" t="n">
-        <v>107.105</v>
+        <v>0</v>
       </c>
       <c r="O617" t="n">
-        <v>293.345</v>
+        <v>0</v>
       </c>
       <c r="P617" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="Q617" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R617" t="n">
-        <v>3.861</v>
+        <v>0</v>
       </c>
       <c r="S617" t="n">
-        <v>32.147</v>
+        <v>0</v>
       </c>
       <c r="T617" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="U617" t="n">
-        <v>0.657</v>
+        <v>0</v>
       </c>
       <c r="V617" t="n">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="W617" t="n">
-        <v>2.026</v>
+        <v>0</v>
       </c>
       <c r="X617" t="n">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="Y617" t="n">
-        <v>0.796</v>
+        <v>0</v>
       </c>
       <c r="Z617" t="n">
-        <v>13.442</v>
+        <v>0</v>
       </c>
       <c r="AA617" t="n">
-        <v>1.275</v>
+        <v>0</v>
       </c>
       <c r="AB617" t="n">
-        <v>29.417</v>
+        <v>0</v>
       </c>
       <c r="AC617" t="inlineStr"/>
     </row>
@@ -67984,67 +67512,67 @@
         <v>0</v>
       </c>
       <c r="H622" t="n">
-        <v>0</v>
+        <v>191.528</v>
       </c>
       <c r="I622" t="n">
-        <v>0</v>
+        <v>1.317</v>
       </c>
       <c r="J622" t="n">
-        <v>0</v>
+        <v>10.941</v>
       </c>
       <c r="K622" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="L622" t="n">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="M622" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="N622" t="n">
-        <v>0</v>
+        <v>98.40600000000001</v>
       </c>
       <c r="O622" t="n">
-        <v>0</v>
+        <v>284.646</v>
       </c>
       <c r="P622" t="n">
-        <v>0</v>
+        <v>0.456</v>
       </c>
       <c r="Q622" t="n">
-        <v>0</v>
+        <v>2.721</v>
       </c>
       <c r="R622" t="n">
-        <v>0</v>
+        <v>3.787</v>
       </c>
       <c r="S622" t="n">
-        <v>0</v>
+        <v>31.93</v>
       </c>
       <c r="T622" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="U622" t="n">
-        <v>0</v>
+        <v>0.657</v>
       </c>
       <c r="V622" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="W622" t="n">
-        <v>0</v>
+        <v>2.024</v>
       </c>
       <c r="X622" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y622" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="Z622" t="n">
-        <v>0</v>
+        <v>12.682</v>
       </c>
       <c r="AA622" t="n">
-        <v>0</v>
+        <v>0.787</v>
       </c>
       <c r="AB622" t="n">
-        <v>0</v>
+        <v>28.653</v>
       </c>
       <c r="AC622" t="inlineStr"/>
     </row>
@@ -68077,67 +67605,67 @@
         <v>0</v>
       </c>
       <c r="H623" t="n">
-        <v>0</v>
+        <v>196.267</v>
       </c>
       <c r="I623" t="n">
-        <v>0</v>
+        <v>1.451</v>
       </c>
       <c r="J623" t="n">
-        <v>0</v>
+        <v>11.389</v>
       </c>
       <c r="K623" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="L623" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="M623" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="N623" t="n">
-        <v>0</v>
+        <v>103.145</v>
       </c>
       <c r="O623" t="n">
-        <v>0</v>
+        <v>289.386</v>
       </c>
       <c r="P623" t="n">
-        <v>0</v>
+        <v>0.502</v>
       </c>
       <c r="Q623" t="n">
-        <v>0</v>
+        <v>2.856</v>
       </c>
       <c r="R623" t="n">
-        <v>0</v>
+        <v>3.942</v>
       </c>
       <c r="S623" t="n">
-        <v>0</v>
+        <v>32.379</v>
       </c>
       <c r="T623" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="U623" t="n">
-        <v>0</v>
+        <v>0.658</v>
       </c>
       <c r="V623" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="W623" t="n">
-        <v>0</v>
+        <v>2.026</v>
       </c>
       <c r="X623" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y623" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="Z623" t="n">
-        <v>0</v>
+        <v>13.456</v>
       </c>
       <c r="AA623" t="n">
-        <v>0</v>
+        <v>1.176</v>
       </c>
       <c r="AB623" t="n">
-        <v>0</v>
+        <v>29.431</v>
       </c>
       <c r="AC623" t="inlineStr"/>
     </row>
@@ -68170,67 +67698,67 @@
         <v>0</v>
       </c>
       <c r="H624" t="n">
-        <v>0</v>
+        <v>199.287</v>
       </c>
       <c r="I624" t="n">
-        <v>0</v>
+        <v>1.238</v>
       </c>
       <c r="J624" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="K624" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="L624" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="M624" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="N624" t="n">
-        <v>0</v>
+        <v>106.165</v>
       </c>
       <c r="O624" t="n">
-        <v>0</v>
+        <v>292.406</v>
       </c>
       <c r="P624" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="Q624" t="n">
-        <v>0</v>
+        <v>2.643</v>
       </c>
       <c r="R624" t="n">
-        <v>0</v>
+        <v>3.939</v>
       </c>
       <c r="S624" t="n">
-        <v>0</v>
+        <v>32.369</v>
       </c>
       <c r="T624" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="U624" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="V624" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="W624" t="n">
-        <v>0</v>
+        <v>2.027</v>
       </c>
       <c r="X624" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y624" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="Z624" t="n">
-        <v>0</v>
+        <v>12.699</v>
       </c>
       <c r="AA624" t="n">
-        <v>0</v>
+        <v>0.992</v>
       </c>
       <c r="AB624" t="n">
-        <v>0</v>
+        <v>28.675</v>
       </c>
       <c r="AC624" t="inlineStr"/>
     </row>
@@ -68263,67 +67791,67 @@
         <v>1</v>
       </c>
       <c r="H625" t="n">
-        <v>0</v>
+        <v>202.94</v>
       </c>
       <c r="I625" t="n">
-        <v>0</v>
+        <v>1.345</v>
       </c>
       <c r="J625" t="n">
-        <v>0</v>
+        <v>10.933</v>
       </c>
       <c r="K625" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="L625" t="n">
-        <v>0</v>
+        <v>0.895</v>
       </c>
       <c r="M625" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="N625" t="n">
-        <v>0</v>
+        <v>109.816</v>
       </c>
       <c r="O625" t="n">
-        <v>0</v>
+        <v>296.063</v>
       </c>
       <c r="P625" t="n">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="Q625" t="n">
-        <v>0</v>
+        <v>2.749</v>
       </c>
       <c r="R625" t="n">
-        <v>0</v>
+        <v>3.784</v>
       </c>
       <c r="S625" t="n">
-        <v>0</v>
+        <v>31.92</v>
       </c>
       <c r="T625" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="U625" t="n">
-        <v>0</v>
+        <v>0.658</v>
       </c>
       <c r="V625" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W625" t="n">
-        <v>0</v>
+        <v>2.031</v>
       </c>
       <c r="X625" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Y625" t="n">
-        <v>0</v>
+        <v>0.802</v>
       </c>
       <c r="Z625" t="n">
-        <v>0</v>
+        <v>13.227</v>
       </c>
       <c r="AA625" t="n">
-        <v>0</v>
+        <v>1.257</v>
       </c>
       <c r="AB625" t="n">
-        <v>0</v>
+        <v>29.217</v>
       </c>
       <c r="AC625" t="inlineStr"/>
     </row>
@@ -68356,67 +67884,67 @@
         <v>0</v>
       </c>
       <c r="H626" t="n">
-        <v>0</v>
+        <v>201.072</v>
       </c>
       <c r="I626" t="n">
-        <v>0</v>
+        <v>1.343</v>
       </c>
       <c r="J626" t="n">
-        <v>0</v>
+        <v>11.362</v>
       </c>
       <c r="K626" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="L626" t="n">
-        <v>0</v>
+        <v>0.891</v>
       </c>
       <c r="M626" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="N626" t="n">
-        <v>0</v>
+        <v>107.954</v>
       </c>
       <c r="O626" t="n">
-        <v>0</v>
+        <v>294.194</v>
       </c>
       <c r="P626" t="n">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="Q626" t="n">
-        <v>0</v>
+        <v>2.748</v>
       </c>
       <c r="R626" t="n">
-        <v>0</v>
+        <v>3.933</v>
       </c>
       <c r="S626" t="n">
-        <v>0</v>
+        <v>32.35</v>
       </c>
       <c r="T626" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="U626" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="V626" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="W626" t="n">
-        <v>0</v>
+        <v>2.027</v>
       </c>
       <c r="X626" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y626" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="Z626" t="n">
-        <v>0</v>
+        <v>13.193</v>
       </c>
       <c r="AA626" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB626" t="n">
-        <v>0</v>
+        <v>29.17</v>
       </c>
       <c r="AC626" t="inlineStr"/>
     </row>
@@ -68449,67 +67977,67 @@
         <v>0</v>
       </c>
       <c r="H627" t="n">
-        <v>0</v>
+        <v>196.645</v>
       </c>
       <c r="I627" t="n">
-        <v>0</v>
+        <v>1.262</v>
       </c>
       <c r="J627" t="n">
-        <v>0</v>
+        <v>11.036</v>
       </c>
       <c r="K627" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>0.893</v>
       </c>
       <c r="M627" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="N627" t="n">
-        <v>0</v>
+        <v>103.525</v>
       </c>
       <c r="O627" t="n">
-        <v>0</v>
+        <v>289.765</v>
       </c>
       <c r="P627" t="n">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="Q627" t="n">
-        <v>0</v>
+        <v>2.666</v>
       </c>
       <c r="R627" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S627" t="n">
-        <v>0</v>
+        <v>32.028</v>
       </c>
       <c r="T627" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="U627" t="n">
-        <v>0</v>
+        <v>0.653</v>
       </c>
       <c r="V627" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="W627" t="n">
-        <v>0</v>
+        <v>2.028</v>
       </c>
       <c r="X627" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y627" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="Z627" t="n">
-        <v>0</v>
+        <v>12.643</v>
       </c>
       <c r="AA627" t="n">
-        <v>0</v>
+        <v>0.902</v>
       </c>
       <c r="AB627" t="n">
-        <v>0</v>
+        <v>28.62</v>
       </c>
       <c r="AC627" t="inlineStr"/>
     </row>
@@ -68542,67 +68070,67 @@
         <v>0</v>
       </c>
       <c r="H628" t="n">
-        <v>0</v>
+        <v>198.855</v>
       </c>
       <c r="I628" t="n">
-        <v>0</v>
+        <v>1.331</v>
       </c>
       <c r="J628" t="n">
-        <v>0</v>
+        <v>11.431</v>
       </c>
       <c r="K628" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="L628" t="n">
-        <v>0</v>
+        <v>0.886</v>
       </c>
       <c r="M628" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="N628" t="n">
-        <v>0</v>
+        <v>105.735</v>
       </c>
       <c r="O628" t="n">
-        <v>0</v>
+        <v>291.975</v>
       </c>
       <c r="P628" t="n">
-        <v>0</v>
+        <v>0.461</v>
       </c>
       <c r="Q628" t="n">
-        <v>0</v>
+        <v>2.736</v>
       </c>
       <c r="R628" t="n">
-        <v>0</v>
+        <v>3.957</v>
       </c>
       <c r="S628" t="n">
-        <v>0</v>
+        <v>32.42</v>
       </c>
       <c r="T628" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="U628" t="n">
-        <v>0</v>
+        <v>0.661</v>
       </c>
       <c r="V628" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="W628" t="n">
-        <v>0</v>
+        <v>2.021</v>
       </c>
       <c r="X628" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y628" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="Z628" t="n">
-        <v>0</v>
+        <v>13.109</v>
       </c>
       <c r="AA628" t="n">
-        <v>0</v>
+        <v>1.131</v>
       </c>
       <c r="AB628" t="n">
-        <v>0</v>
+        <v>29.077</v>
       </c>
       <c r="AC628" t="inlineStr"/>
     </row>
@@ -68635,67 +68163,67 @@
         <v>1</v>
       </c>
       <c r="H629" t="n">
-        <v>0</v>
+        <v>198.112</v>
       </c>
       <c r="I629" t="n">
-        <v>0</v>
+        <v>1.347</v>
       </c>
       <c r="J629" t="n">
-        <v>0</v>
+        <v>10.883</v>
       </c>
       <c r="K629" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="L629" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="M629" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="N629" t="n">
-        <v>0</v>
+        <v>104.994</v>
       </c>
       <c r="O629" t="n">
-        <v>0</v>
+        <v>291.234</v>
       </c>
       <c r="P629" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="Q629" t="n">
-        <v>0</v>
+        <v>2.752</v>
       </c>
       <c r="R629" t="n">
-        <v>0</v>
+        <v>3.767</v>
       </c>
       <c r="S629" t="n">
-        <v>0</v>
+        <v>31.87</v>
       </c>
       <c r="T629" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="U629" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="V629" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="W629" t="n">
-        <v>0</v>
+        <v>2.025</v>
       </c>
       <c r="X629" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Y629" t="n">
-        <v>0</v>
+        <v>0.802</v>
       </c>
       <c r="Z629" t="n">
-        <v>0</v>
+        <v>13.027</v>
       </c>
       <c r="AA629" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB629" t="n">
-        <v>0</v>
+        <v>29.007</v>
       </c>
       <c r="AC629" t="inlineStr"/>
     </row>
@@ -68728,67 +68256,67 @@
         <v>1</v>
       </c>
       <c r="H630" t="n">
-        <v>0</v>
+        <v>205.498</v>
       </c>
       <c r="I630" t="n">
-        <v>0</v>
+        <v>1.436</v>
       </c>
       <c r="J630" t="n">
-        <v>0</v>
+        <v>10.899</v>
       </c>
       <c r="K630" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="L630" t="n">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="M630" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="N630" t="n">
-        <v>0</v>
+        <v>112.376</v>
       </c>
       <c r="O630" t="n">
-        <v>0</v>
+        <v>298.616</v>
       </c>
       <c r="P630" t="n">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="Q630" t="n">
-        <v>0</v>
+        <v>2.841</v>
       </c>
       <c r="R630" t="n">
-        <v>0</v>
+        <v>3.773</v>
       </c>
       <c r="S630" t="n">
-        <v>0</v>
+        <v>31.889</v>
       </c>
       <c r="T630" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="U630" t="n">
-        <v>0</v>
+        <v>0.656</v>
       </c>
       <c r="V630" t="n">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="W630" t="n">
-        <v>0</v>
+        <v>2.021</v>
       </c>
       <c r="X630" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Y630" t="n">
-        <v>0</v>
+        <v>0.802</v>
       </c>
       <c r="Z630" t="n">
-        <v>0</v>
+        <v>13.699</v>
       </c>
       <c r="AA630" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB630" t="n">
-        <v>0</v>
+        <v>29.677</v>
       </c>
       <c r="AC630" t="inlineStr"/>
     </row>
@@ -68821,67 +68349,67 @@
         <v>0</v>
       </c>
       <c r="H631" t="n">
-        <v>0</v>
+        <v>187.375</v>
       </c>
       <c r="I631" t="n">
-        <v>0</v>
+        <v>1.253</v>
       </c>
       <c r="J631" t="n">
-        <v>0</v>
+        <v>11.381</v>
       </c>
       <c r="K631" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="L631" t="n">
-        <v>0</v>
+        <v>0.879</v>
       </c>
       <c r="M631" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="N631" t="n">
-        <v>0</v>
+        <v>94.255</v>
       </c>
       <c r="O631" t="n">
-        <v>0</v>
+        <v>280.495</v>
       </c>
       <c r="P631" t="n">
-        <v>0</v>
+        <v>0.434</v>
       </c>
       <c r="Q631" t="n">
-        <v>0</v>
+        <v>2.658</v>
       </c>
       <c r="R631" t="n">
-        <v>0</v>
+        <v>3.939</v>
       </c>
       <c r="S631" t="n">
-        <v>0</v>
+        <v>32.369</v>
       </c>
       <c r="T631" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="U631" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="V631" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="W631" t="n">
-        <v>0</v>
+        <v>2.015</v>
       </c>
       <c r="X631" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y631" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="Z631" t="n">
-        <v>0</v>
+        <v>12.312</v>
       </c>
       <c r="AA631" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AB631" t="n">
-        <v>0</v>
+        <v>28.273</v>
       </c>
       <c r="AC631" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -604,8 +604,16 @@
       <c r="U2" t="n">
         <v>0.78</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -675,7 +683,11 @@
       <c r="U3" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -746,7 +758,11 @@
       <c r="U4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -817,7 +833,11 @@
       <c r="U5" t="n">
         <v>6.52</v>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -888,7 +908,11 @@
       <c r="U6" t="n">
         <v>7.94</v>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -959,7 +983,11 @@
       <c r="U7" t="n">
         <v>-10.74</v>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1030,7 +1058,11 @@
       <c r="U8" t="n">
         <v>12.71</v>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1101,7 +1133,11 @@
       <c r="U9" t="n">
         <v>-9.98</v>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1172,7 +1208,11 @@
       <c r="U10" t="n">
         <v>12.13</v>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1243,7 +1283,11 @@
       <c r="U11" t="n">
         <v>-24.31</v>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1314,7 +1358,11 @@
       <c r="U12" t="n">
         <v>-20.47</v>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1385,7 +1433,11 @@
       <c r="U13" t="n">
         <v>-12.62</v>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1456,7 +1508,11 @@
       <c r="U14" t="n">
         <v>-2.47</v>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1527,7 +1583,11 @@
       <c r="U15" t="n">
         <v>-31.77</v>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1598,7 +1658,11 @@
       <c r="U16" t="n">
         <v>-17.79</v>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1669,7 +1733,11 @@
       <c r="U17" t="n">
         <v>-37.58</v>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1740,7 +1808,11 @@
       <c r="U18" t="n">
         <v>2.88</v>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1811,7 +1883,11 @@
       <c r="U19" t="n">
         <v>-13.54</v>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1882,7 +1958,11 @@
       <c r="U20" t="n">
         <v>-26.39</v>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1953,7 +2033,11 @@
       <c r="U21" t="n">
         <v>-5.14</v>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -2024,7 +2108,11 @@
       <c r="U22" t="n">
         <v>-6.71</v>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2095,7 +2183,11 @@
       <c r="U23" t="n">
         <v>18.61</v>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2166,7 +2258,11 @@
       <c r="U24" t="n">
         <v>-65.38</v>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2237,7 +2333,11 @@
       <c r="U25" t="n">
         <v>0.62</v>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2308,7 +2408,11 @@
       <c r="U26" t="n">
         <v>-2.59</v>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2379,7 +2483,11 @@
       <c r="U27" t="n">
         <v>36.72</v>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2450,7 +2558,11 @@
       <c r="U28" t="n">
         <v>6.34</v>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2521,7 +2633,11 @@
       <c r="U29" t="n">
         <v>-27.55</v>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2592,7 +2708,11 @@
       <c r="U30" t="n">
         <v>62.14</v>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2663,7 +2783,11 @@
       <c r="U31" t="n">
         <v>1.54</v>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2734,7 +2858,11 @@
       <c r="U32" t="n">
         <v>-17.36</v>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2755,57 +2883,61 @@
         <v>3614.7</v>
       </c>
       <c r="E33" t="n">
-        <v>213.7</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>23.17</v>
       </c>
       <c r="G33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>720</v>
       </c>
       <c r="I33" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>7.64</v>
       </c>
       <c r="K33" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>10.24</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>326.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>19.53</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>25.04</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>278.65</v>
       </c>
       <c r="U33" t="n">
-        <v>-259.12</v>
-      </c>
-      <c r="V33" t="inlineStr"/>
+        <v>-278.65</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2826,53 +2958,57 @@
         <v>3385.3</v>
       </c>
       <c r="E34" t="n">
-        <v>2774.6</v>
+        <v>2974.8</v>
       </c>
       <c r="F34" t="n">
         <v>23.03</v>
       </c>
       <c r="G34" t="n">
-        <v>18.79</v>
+        <v>20.21</v>
       </c>
       <c r="H34" t="n">
         <v>188.9</v>
       </c>
       <c r="I34" t="n">
-        <v>155.8</v>
+        <v>166.9</v>
       </c>
       <c r="J34" t="n">
         <v>2.33</v>
       </c>
       <c r="K34" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="L34" t="n">
         <v>15.13</v>
       </c>
       <c r="M34" t="n">
-        <v>12.45</v>
+        <v>13.34</v>
       </c>
       <c r="N34" t="n">
         <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
         <v>223.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>182.8</v>
+        <v>196.2</v>
       </c>
       <c r="R34" t="n">
-        <v>108.53</v>
+        <v>116.49</v>
       </c>
       <c r="S34" t="n">
-        <v>258.17</v>
+        <v>277.09</v>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2943,7 +3079,11 @@
       <c r="U35" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -3014,7 +3154,11 @@
       <c r="U36" t="n">
         <v>19.21</v>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -3081,7 +3225,11 @@
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -3148,7 +3296,11 @@
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -3215,7 +3367,11 @@
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -3286,7 +3442,11 @@
       <c r="U40" t="n">
         <v>-21.18</v>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3420,7 +3580,11 @@
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3487,7 +3651,11 @@
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3554,7 +3722,11 @@
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3688,7 +3860,11 @@
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3755,7 +3931,11 @@
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3889,7 +4069,11 @@
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3956,7 +4140,11 @@
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -4023,7 +4211,11 @@
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -4157,7 +4349,11 @@
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -4224,7 +4420,11 @@
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -4291,7 +4491,11 @@
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -4358,7 +4562,11 @@
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -4492,7 +4700,11 @@
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -4626,7 +4838,11 @@
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -4693,7 +4909,11 @@
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -4764,7 +4984,11 @@
       <c r="U62" t="n">
         <v>-71.12</v>
       </c>
-      <c r="V62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -4831,7 +5055,11 @@
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -4898,7 +5126,11 @@
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -4965,7 +5197,11 @@
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5167,8 +5403,16 @@
       <c r="U2" t="n">
         <v>0.78</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5238,7 +5482,11 @@
       <c r="U3" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -5309,7 +5557,11 @@
       <c r="U4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -5380,7 +5632,11 @@
       <c r="U5" t="n">
         <v>6.52</v>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -5451,7 +5707,11 @@
       <c r="U6" t="n">
         <v>7.94</v>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -5522,7 +5782,11 @@
       <c r="U7" t="n">
         <v>-10.74</v>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -5593,7 +5857,11 @@
       <c r="U8" t="n">
         <v>12.71</v>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -5664,7 +5932,11 @@
       <c r="U9" t="n">
         <v>-9.98</v>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -5735,7 +6007,11 @@
       <c r="U10" t="n">
         <v>12.13</v>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -5806,7 +6082,11 @@
       <c r="U11" t="n">
         <v>-24.31</v>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -5877,7 +6157,11 @@
       <c r="U12" t="n">
         <v>-20.47</v>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -5948,7 +6232,11 @@
       <c r="U13" t="n">
         <v>-12.62</v>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -6019,7 +6307,11 @@
       <c r="U14" t="n">
         <v>-2.47</v>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -6090,7 +6382,11 @@
       <c r="U15" t="n">
         <v>-31.77</v>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -6161,7 +6457,11 @@
       <c r="U16" t="n">
         <v>-17.79</v>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -6232,7 +6532,11 @@
       <c r="U17" t="n">
         <v>-37.58</v>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -6303,7 +6607,11 @@
       <c r="U18" t="n">
         <v>2.88</v>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -6374,7 +6682,11 @@
       <c r="U19" t="n">
         <v>-13.54</v>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -6445,7 +6757,11 @@
       <c r="U20" t="n">
         <v>-26.39</v>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -6516,7 +6832,11 @@
       <c r="U21" t="n">
         <v>-5.14</v>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -6587,7 +6907,11 @@
       <c r="U22" t="n">
         <v>-6.71</v>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -6658,7 +6982,11 @@
       <c r="U23" t="n">
         <v>18.61</v>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -6729,7 +7057,11 @@
       <c r="U24" t="n">
         <v>-65.38</v>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -6800,7 +7132,11 @@
       <c r="U25" t="n">
         <v>0.62</v>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -6871,7 +7207,11 @@
       <c r="U26" t="n">
         <v>-2.59</v>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -6942,7 +7282,11 @@
       <c r="U27" t="n">
         <v>36.72</v>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -7013,7 +7357,11 @@
       <c r="U28" t="n">
         <v>6.34</v>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -7084,7 +7432,11 @@
       <c r="U29" t="n">
         <v>-27.55</v>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -7155,7 +7507,11 @@
       <c r="U30" t="n">
         <v>62.14</v>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -7226,7 +7582,11 @@
       <c r="U31" t="n">
         <v>1.54</v>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -7297,7 +7657,11 @@
       <c r="U32" t="n">
         <v>-17.36</v>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -7318,57 +7682,61 @@
         <v>3614.7</v>
       </c>
       <c r="E33" t="n">
-        <v>213.7</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>23.17</v>
       </c>
       <c r="G33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>720</v>
       </c>
       <c r="I33" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>7.64</v>
       </c>
       <c r="K33" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>10.24</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>326.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>19.53</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>25.04</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>278.65</v>
       </c>
       <c r="U33" t="n">
-        <v>-259.12</v>
-      </c>
-      <c r="V33" t="inlineStr"/>
+        <v>-278.65</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
     </row>
   </sheetData>
@@ -7520,53 +7888,57 @@
         <v>3385.3</v>
       </c>
       <c r="E2" t="n">
-        <v>2774.6</v>
+        <v>2974.8</v>
       </c>
       <c r="F2" t="n">
         <v>23.03</v>
       </c>
       <c r="G2" t="n">
-        <v>18.79</v>
+        <v>20.21</v>
       </c>
       <c r="H2" t="n">
         <v>188.9</v>
       </c>
       <c r="I2" t="n">
-        <v>155.8</v>
+        <v>166.9</v>
       </c>
       <c r="J2" t="n">
         <v>2.33</v>
       </c>
       <c r="K2" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="L2" t="n">
         <v>15.13</v>
       </c>
       <c r="M2" t="n">
-        <v>12.45</v>
+        <v>13.34</v>
       </c>
       <c r="N2" t="n">
         <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
         <v>223.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>182.8</v>
+        <v>196.2</v>
       </c>
       <c r="R2" t="n">
-        <v>108.53</v>
+        <v>116.49</v>
       </c>
       <c r="S2" t="n">
-        <v>258.17</v>
+        <v>277.09</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -7637,7 +8009,11 @@
       <c r="U3" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -7708,7 +8084,11 @@
       <c r="U4" t="n">
         <v>19.21</v>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -7775,7 +8155,11 @@
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -7842,7 +8226,11 @@
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -7909,7 +8297,11 @@
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -7980,7 +8372,11 @@
       <c r="U8" t="n">
         <v>-21.18</v>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -8114,7 +8510,11 @@
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -8181,7 +8581,11 @@
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -8248,7 +8652,11 @@
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -8382,7 +8790,11 @@
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -8449,7 +8861,11 @@
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -8583,7 +8999,11 @@
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -8650,7 +9070,11 @@
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -8717,7 +9141,11 @@
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -8851,7 +9279,11 @@
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -8918,7 +9350,11 @@
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -8985,7 +9421,11 @@
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -9052,7 +9492,11 @@
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -9186,7 +9630,11 @@
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -9320,7 +9768,11 @@
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -9387,7 +9839,11 @@
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -9458,7 +9914,11 @@
       <c r="U30" t="n">
         <v>-71.12</v>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -9525,7 +9985,11 @@
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -9592,7 +10056,11 @@
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -9659,7 +10127,11 @@
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
     </row>
   </sheetData>
@@ -32172,67 +32644,67 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>213.72</v>
+        <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>1.438</v>
+        <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>42.393</v>
+        <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>120.597</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
-        <v>306.843</v>
+        <v>0</v>
       </c>
       <c r="P242" t="n">
-        <v>0.498</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>2.843</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>21.402</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>63.38</v>
+        <v>0</v>
       </c>
       <c r="T242" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="U242" t="n">
-        <v>0.963</v>
+        <v>0</v>
       </c>
       <c r="V242" t="n">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="W242" t="n">
-        <v>1.739</v>
+        <v>0</v>
       </c>
       <c r="X242" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="Y242" t="n">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="Z242" t="n">
-        <v>19.534</v>
+        <v>0</v>
       </c>
       <c r="AA242" t="n">
-        <v>4.738</v>
+        <v>0</v>
       </c>
       <c r="AB242" t="n">
-        <v>35.182</v>
+        <v>0</v>
       </c>
       <c r="AC242" t="inlineStr"/>
     </row>
@@ -67047,67 +67519,67 @@
         <v>0</v>
       </c>
       <c r="H617" t="n">
-        <v>0</v>
+        <v>200.226</v>
       </c>
       <c r="I617" t="n">
-        <v>0</v>
+        <v>1.416</v>
       </c>
       <c r="J617" t="n">
-        <v>0</v>
+        <v>11.154</v>
       </c>
       <c r="K617" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="L617" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="M617" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="N617" t="n">
-        <v>0</v>
+        <v>107.105</v>
       </c>
       <c r="O617" t="n">
-        <v>0</v>
+        <v>293.345</v>
       </c>
       <c r="P617" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="Q617" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R617" t="n">
-        <v>0</v>
+        <v>3.861</v>
       </c>
       <c r="S617" t="n">
-        <v>0</v>
+        <v>32.147</v>
       </c>
       <c r="T617" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="U617" t="n">
-        <v>0</v>
+        <v>0.657</v>
       </c>
       <c r="V617" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="W617" t="n">
-        <v>0</v>
+        <v>2.026</v>
       </c>
       <c r="X617" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y617" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="Z617" t="n">
-        <v>0</v>
+        <v>13.442</v>
       </c>
       <c r="AA617" t="n">
-        <v>0</v>
+        <v>1.275</v>
       </c>
       <c r="AB617" t="n">
-        <v>0</v>
+        <v>29.417</v>
       </c>
       <c r="AC617" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -993,74 +993,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4066.6</v>
+        <v>4188.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3587.4</v>
+        <v>3700.7</v>
       </c>
       <c r="F8" t="n">
-        <v>27.62</v>
+        <v>29.67</v>
       </c>
       <c r="G8" t="n">
-        <v>24.35</v>
+        <v>26.22</v>
       </c>
       <c r="H8" t="n">
-        <v>479.9</v>
+        <v>358.5</v>
       </c>
       <c r="I8" t="n">
-        <v>424</v>
+        <v>316.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.01</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.56</v>
+        <v>3.18</v>
       </c>
       <c r="L8" t="n">
-        <v>8.69</v>
+        <v>9.1</v>
       </c>
       <c r="M8" t="n">
-        <v>7.66</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="P8" t="n">
-        <v>320.57</v>
+        <v>319.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>282.94</v>
+        <v>281.99</v>
       </c>
       <c r="R8" t="n">
-        <v>202.83</v>
+        <v>201.53</v>
       </c>
       <c r="S8" t="n">
-        <v>363.83</v>
+        <v>362.3</v>
       </c>
       <c r="T8" t="n">
-        <v>286.41</v>
+        <v>269.56</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.47</v>
+        <v>12.43</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1068,74 +1068,74 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4188.5</v>
+        <v>4396</v>
       </c>
       <c r="E9" t="n">
-        <v>3700.7</v>
+        <v>3877.5</v>
       </c>
       <c r="F9" t="n">
-        <v>29.67</v>
+        <v>32.61</v>
       </c>
       <c r="G9" t="n">
-        <v>26.22</v>
+        <v>28.71</v>
       </c>
       <c r="H9" t="n">
-        <v>358.5</v>
+        <v>145.5</v>
       </c>
       <c r="I9" t="n">
-        <v>316.2</v>
+        <v>128.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>2.17</v>
       </c>
       <c r="K9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.18</v>
       </c>
-      <c r="L9" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>319.17</v>
+        <v>308.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>281.99</v>
+        <v>272.18</v>
       </c>
       <c r="R9" t="n">
-        <v>201.53</v>
+        <v>193.93</v>
       </c>
       <c r="S9" t="n">
-        <v>362.3</v>
+        <v>352.58</v>
       </c>
       <c r="T9" t="n">
-        <v>269.56</v>
+        <v>292.94</v>
       </c>
       <c r="U9" t="n">
-        <v>12.43</v>
+        <v>-20.76</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1143,74 +1143,74 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4396</v>
+        <v>4512.9</v>
       </c>
       <c r="E10" t="n">
-        <v>3877.5</v>
+        <v>3974.5</v>
       </c>
       <c r="F10" t="n">
-        <v>32.61</v>
+        <v>35.79</v>
       </c>
       <c r="G10" t="n">
-        <v>28.71</v>
+        <v>31.71</v>
       </c>
       <c r="H10" t="n">
-        <v>145.5</v>
+        <v>21.2</v>
       </c>
       <c r="I10" t="n">
-        <v>128.6</v>
+        <v>18.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.17</v>
+        <v>1.27</v>
       </c>
       <c r="K10" t="n">
-        <v>1.91</v>
+        <v>1.13</v>
       </c>
       <c r="L10" t="n">
-        <v>9.34</v>
+        <v>13.32</v>
       </c>
       <c r="M10" t="n">
-        <v>8.24</v>
+        <v>11.76</v>
       </c>
       <c r="N10" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="O10" t="n">
         <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>308.81</v>
+        <v>300.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>272.18</v>
+        <v>265.33</v>
       </c>
       <c r="R10" t="n">
-        <v>193.93</v>
+        <v>200.57</v>
       </c>
       <c r="S10" t="n">
-        <v>352.58</v>
+        <v>345.57</v>
       </c>
       <c r="T10" t="n">
-        <v>292.94</v>
+        <v>257.82</v>
       </c>
       <c r="U10" t="n">
-        <v>-20.76</v>
+        <v>7.51</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1218,74 +1218,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4512.9</v>
+        <v>3887.2</v>
       </c>
       <c r="E11" t="n">
-        <v>3974.5</v>
+        <v>3435.5</v>
       </c>
       <c r="F11" t="n">
-        <v>35.79</v>
+        <v>30.24</v>
       </c>
       <c r="G11" t="n">
-        <v>31.71</v>
+        <v>26.76</v>
       </c>
       <c r="H11" t="n">
-        <v>21.2</v>
+        <v>315.6</v>
       </c>
       <c r="I11" t="n">
-        <v>18.5</v>
+        <v>278.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.27</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>1.13</v>
+        <v>3.41</v>
       </c>
       <c r="L11" t="n">
-        <v>13.32</v>
+        <v>12.4</v>
       </c>
       <c r="M11" t="n">
-        <v>11.76</v>
+        <v>10.94</v>
       </c>
       <c r="N11" t="n">
-        <v>3.17</v>
+        <v>3.54</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="P11" t="n">
-        <v>300.44</v>
+        <v>299.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>265.33</v>
+        <v>264.68</v>
       </c>
       <c r="R11" t="n">
-        <v>200.57</v>
+        <v>183.96</v>
       </c>
       <c r="S11" t="n">
-        <v>345.57</v>
+        <v>345.47</v>
       </c>
       <c r="T11" t="n">
-        <v>257.82</v>
+        <v>284.56</v>
       </c>
       <c r="U11" t="n">
-        <v>7.51</v>
+        <v>-19.88</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1293,74 +1293,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3887.2</v>
+        <v>4066.6</v>
       </c>
       <c r="E12" t="n">
-        <v>3435.5</v>
+        <v>3356</v>
       </c>
       <c r="F12" t="n">
-        <v>30.24</v>
+        <v>27.62</v>
       </c>
       <c r="G12" t="n">
-        <v>26.76</v>
+        <v>22.8</v>
       </c>
       <c r="H12" t="n">
-        <v>315.6</v>
+        <v>479.9</v>
       </c>
       <c r="I12" t="n">
-        <v>278.8</v>
+        <v>395.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="L12" t="n">
-        <v>12.4</v>
+        <v>8.69</v>
       </c>
       <c r="M12" t="n">
-        <v>10.94</v>
+        <v>7.15</v>
       </c>
       <c r="N12" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="P12" t="n">
-        <v>299.23</v>
+        <v>320.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>264.68</v>
+        <v>264.66</v>
       </c>
       <c r="R12" t="n">
-        <v>183.96</v>
+        <v>189.73</v>
       </c>
       <c r="S12" t="n">
-        <v>345.47</v>
+        <v>340.32</v>
       </c>
       <c r="T12" t="n">
-        <v>284.56</v>
+        <v>286.41</v>
       </c>
       <c r="U12" t="n">
-        <v>-19.88</v>
+        <v>-21.75</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -3160,64 +3160,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Andy Dalton</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3375.4</v>
+        <v>3512.6</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>198.8</v>
       </c>
       <c r="F37" t="n">
-        <v>22.01</v>
+        <v>16.84</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="H37" t="n">
-        <v>101.5</v>
+        <v>379.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J37" t="n">
-        <v>1.66</v>
+        <v>3.26</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="L37" t="n">
-        <v>10.13</v>
+        <v>12.16</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="N37" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P37" t="n">
-        <v>217.57</v>
+        <v>234.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>13.34</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>18.54</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3231,55 +3231,55 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Andy Dalton</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3470.3</v>
+        <v>3375.4</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>16.85</v>
+        <v>22.01</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>828.6</v>
+        <v>101.5</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>7.93</v>
+        <v>1.66</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>13.8</v>
+        <v>10.13</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.45</v>
+        <v>2.67</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>300.15</v>
+        <v>217.57</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3302,55 +3302,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3169.8</v>
+        <v>3470.3</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>13.85</v>
+        <v>16.85</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>186.9</v>
+        <v>828.6</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>17.41</v>
+        <v>13.8</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.71</v>
+        <v>4.45</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>177.12</v>
+        <v>300.15</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3361,12 +3361,8 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="n">
-        <v>21.18</v>
-      </c>
-      <c r="U39" t="n">
-        <v>-21.18</v>
-      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>50</t>
@@ -3377,55 +3373,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3394.4</v>
+        <v>3169.8</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>21.56</v>
+        <v>13.85</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>235.2</v>
+        <v>186.9</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2.16</v>
+        <v>3.08</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>13.14</v>
+        <v>17.41</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>225.1</v>
+        <v>177.12</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3436,63 +3432,71 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-21.18</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3531.4</v>
+        <v>3394.4</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>20.33</v>
+        <v>21.56</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>143.2</v>
+        <v>235.2</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>12.93</v>
+        <v>13.14</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>216.06</v>
+        <v>225.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3505,65 +3509,61 @@
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3391.2</v>
+        <v>3531.4</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>18.78</v>
+        <v>20.33</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>262.3</v>
+        <v>143.2</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2.69</v>
+        <v>1.93</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>11.16</v>
+        <v>12.93</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.93</v>
+        <v>3.28</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>224.96</v>
+        <v>216.06</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3586,55 +3586,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3435</v>
+        <v>3391.2</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>15.56</v>
+        <v>18.78</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>110.5</v>
+        <v>262.3</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1.84</v>
+        <v>2.69</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>11.6</v>
+        <v>11.16</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.61</v>
+        <v>2.93</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>191.31</v>
+        <v>224.96</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3657,55 +3657,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3275.4</v>
+        <v>3435</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>14.59</v>
+        <v>15.56</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>180.8</v>
+        <v>110.5</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>3.13</v>
+        <v>1.84</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>17.3</v>
+        <v>11.6</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.72</v>
+        <v>3.61</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>184.2</v>
+        <v>191.31</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3718,61 +3718,65 @@
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3737.2</v>
+        <v>3275.4</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>18.69</v>
+        <v>14.59</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>322.3</v>
+        <v>180.8</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2.33</v>
+        <v>3.13</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>10.89</v>
+        <v>17.3</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.59</v>
+        <v>3.72</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>241.5</v>
+        <v>184.2</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3785,65 +3789,61 @@
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3541.1</v>
+        <v>3737.2</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>22.12</v>
+        <v>18.69</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>778.4</v>
+        <v>322.3</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>7.46</v>
+        <v>2.33</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.74</v>
+        <v>10.89</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.07</v>
+        <v>3.59</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>323.1</v>
+        <v>241.5</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3854,15 +3854,11 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
-      <c r="T46" t="n">
-        <v>278.65</v>
-      </c>
-      <c r="U46" t="n">
-        <v>-278.65</v>
-      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -3870,55 +3866,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3609.6</v>
+        <v>3541.1</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>25.42</v>
+        <v>22.12</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>33.4</v>
+        <v>778.4</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1.76</v>
+        <v>7.46</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>11.37</v>
+        <v>10.74</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.44</v>
+        <v>4.07</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>230.34</v>
+        <v>323.1</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3929,11 +3925,15 @@
       <c r="S47" t="n">
         <v>0</v>
       </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="T47" t="n">
+        <v>278.65</v>
+      </c>
+      <c r="U47" t="n">
+        <v>-278.65</v>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
@@ -3941,55 +3941,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3494.9</v>
+        <v>3609.6</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>17.77</v>
+        <v>25.42</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>551.1</v>
+        <v>33.4</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4.94</v>
+        <v>1.76</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>10.66</v>
+        <v>11.37</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>267.53</v>
+        <v>230.34</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4002,61 +4002,65 @@
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3335.6</v>
+        <v>3494.9</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>18.19</v>
+        <v>17.77</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>840.6</v>
+        <v>551.1</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>7.25</v>
+        <v>4.94</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>10.83</v>
+        <v>10.66</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>305.22</v>
+        <v>267.53</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4069,65 +4073,61 @@
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3383.9</v>
+        <v>3335.6</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>16.16</v>
+        <v>18.19</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>185.6</v>
+        <v>840.6</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.88</v>
+        <v>7.25</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>11.23</v>
+        <v>10.83</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.18</v>
+        <v>3.43</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>201.02</v>
+        <v>305.22</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4150,55 +4150,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3481.6</v>
+        <v>3383.9</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>17.64</v>
+        <v>16.16</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>183.1</v>
+        <v>185.6</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>13.2</v>
+        <v>11.23</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>210.81</v>
+        <v>201.02</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4221,55 +4221,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3208</v>
+        <v>3481.6</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>13.86</v>
+        <v>17.64</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>181.8</v>
+        <v>183.1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>17.33</v>
+        <v>13.2</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.72</v>
+        <v>2.96</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>178.38</v>
+        <v>210.81</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4282,61 +4282,65 @@
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3613</v>
+        <v>3208</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>22.93</v>
+        <v>13.86</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>174.9</v>
+        <v>181.8</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>2.16</v>
+        <v>3.09</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10.15</v>
+        <v>17.33</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.57</v>
+        <v>3.72</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>241.25</v>
+        <v>178.38</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4349,65 +4353,61 @@
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3506.9</v>
+        <v>3613</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>19.99</v>
+        <v>22.93</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>146.7</v>
+        <v>174.9</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>11.57</v>
+        <v>10.15</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>216.43</v>
+        <v>241.25</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4430,55 +4430,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3597.8</v>
+        <v>3506.9</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>21.88</v>
+        <v>19.99</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>201.8</v>
+        <v>146.7</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>3.03</v>
+        <v>1.85</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>12.18</v>
+        <v>11.57</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.21</v>
+        <v>3.22</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>241.01</v>
+        <v>216.43</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4501,55 +4501,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3353</v>
+        <v>3597.8</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>17.35</v>
+        <v>21.88</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>152.4</v>
+        <v>201.8</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>15.01</v>
+        <v>12.18</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.83</v>
+        <v>2.21</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>195.48</v>
+        <v>241.01</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4572,55 +4572,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3196.3</v>
+        <v>3353</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>14.74</v>
+        <v>17.35</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>204.3</v>
+        <v>152.4</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>17.37</v>
+        <v>15.01</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>183.94</v>
+        <v>195.48</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4633,61 +4633,65 @@
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3437.6</v>
+        <v>3196.3</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>17.14</v>
+        <v>14.74</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>286.9</v>
+        <v>204.3</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>11.88</v>
+        <v>17.37</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>218.65</v>
+        <v>183.94</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4700,65 +4704,61 @@
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>3262.3</v>
+        <v>3437.6</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>16.01</v>
+        <v>17.14</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>182.6</v>
+        <v>286.9</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>16.12</v>
+        <v>11.88</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>5.36</v>
+        <v>3.88</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>185.79</v>
+        <v>218.65</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4771,61 +4771,65 @@
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3206.7</v>
+        <v>3262.3</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>14.57</v>
+        <v>16.01</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>242</v>
+        <v>182.6</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>17.33</v>
+        <v>16.12</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.7</v>
+        <v>5.36</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>186.99</v>
+        <v>185.79</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4838,65 +4842,61 @@
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Trey Lance</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3273.2</v>
+        <v>3206.7</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>17.24</v>
+        <v>14.57</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>682.7</v>
+        <v>242</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>3.49</v>
+        <v>3.05</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>11.98</v>
+        <v>17.33</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>258.34</v>
+        <v>186.99</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4919,55 +4919,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Trey Lance</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>3367.8</v>
+        <v>3273.2</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>21.58</v>
+        <v>17.24</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>38.9</v>
+        <v>682.7</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1.62</v>
+        <v>3.49</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>10.13</v>
+        <v>11.98</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>207.56</v>
+        <v>258.34</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4978,12 +4978,8 @@
       <c r="S62" t="n">
         <v>0</v>
       </c>
-      <c r="T62" t="n">
-        <v>66.38</v>
-      </c>
-      <c r="U62" t="n">
-        <v>-66.38</v>
-      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
           <t>50</t>
@@ -4994,55 +4990,55 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>3307.4</v>
+        <v>3367.8</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>18.02</v>
+        <v>21.58</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>725.9</v>
+        <v>38.9</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>4.09</v>
+        <v>1.62</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>9.890000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>274.23</v>
+        <v>207.56</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5053,8 +5049,12 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
+      <c r="T63" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="U63" t="n">
+        <v>-66.38</v>
+      </c>
       <c r="V63" t="inlineStr">
         <is>
           <t>50</t>
@@ -5065,55 +5065,55 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>3627.7</v>
+        <v>3307.4</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>22.83</v>
+        <v>18.02</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>544.2</v>
+        <v>725.9</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>10.09</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.79</v>
+        <v>3.75</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>290.05</v>
+        <v>274.23</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5136,55 +5136,55 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>3512.6</v>
+        <v>3627.7</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>16.84</v>
+        <v>22.83</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>379.2</v>
+        <v>544.2</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>3.26</v>
+        <v>4.16</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>12.16</v>
+        <v>10.09</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.48</v>
+        <v>2.79</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>234.06</v>
+        <v>290.05</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5792,74 +5792,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4066.6</v>
+        <v>4188.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3587.4</v>
+        <v>3700.7</v>
       </c>
       <c r="F8" t="n">
-        <v>27.62</v>
+        <v>29.67</v>
       </c>
       <c r="G8" t="n">
-        <v>24.35</v>
+        <v>26.22</v>
       </c>
       <c r="H8" t="n">
-        <v>479.9</v>
+        <v>358.5</v>
       </c>
       <c r="I8" t="n">
-        <v>424</v>
+        <v>316.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.01</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.56</v>
+        <v>3.18</v>
       </c>
       <c r="L8" t="n">
-        <v>8.69</v>
+        <v>9.1</v>
       </c>
       <c r="M8" t="n">
-        <v>7.66</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="P8" t="n">
-        <v>320.57</v>
+        <v>319.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>282.94</v>
+        <v>281.99</v>
       </c>
       <c r="R8" t="n">
-        <v>202.83</v>
+        <v>201.53</v>
       </c>
       <c r="S8" t="n">
-        <v>363.83</v>
+        <v>362.3</v>
       </c>
       <c r="T8" t="n">
-        <v>286.41</v>
+        <v>269.56</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.47</v>
+        <v>12.43</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -5867,74 +5867,74 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4188.5</v>
+        <v>4396</v>
       </c>
       <c r="E9" t="n">
-        <v>3700.7</v>
+        <v>3877.5</v>
       </c>
       <c r="F9" t="n">
-        <v>29.67</v>
+        <v>32.61</v>
       </c>
       <c r="G9" t="n">
-        <v>26.22</v>
+        <v>28.71</v>
       </c>
       <c r="H9" t="n">
-        <v>358.5</v>
+        <v>145.5</v>
       </c>
       <c r="I9" t="n">
-        <v>316.2</v>
+        <v>128.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>2.17</v>
       </c>
       <c r="K9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.18</v>
       </c>
-      <c r="L9" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>319.17</v>
+        <v>308.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>281.99</v>
+        <v>272.18</v>
       </c>
       <c r="R9" t="n">
-        <v>201.53</v>
+        <v>193.93</v>
       </c>
       <c r="S9" t="n">
-        <v>362.3</v>
+        <v>352.58</v>
       </c>
       <c r="T9" t="n">
-        <v>269.56</v>
+        <v>292.94</v>
       </c>
       <c r="U9" t="n">
-        <v>12.43</v>
+        <v>-20.76</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -5942,74 +5942,74 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4396</v>
+        <v>4512.9</v>
       </c>
       <c r="E10" t="n">
-        <v>3877.5</v>
+        <v>3974.5</v>
       </c>
       <c r="F10" t="n">
-        <v>32.61</v>
+        <v>35.79</v>
       </c>
       <c r="G10" t="n">
-        <v>28.71</v>
+        <v>31.71</v>
       </c>
       <c r="H10" t="n">
-        <v>145.5</v>
+        <v>21.2</v>
       </c>
       <c r="I10" t="n">
-        <v>128.6</v>
+        <v>18.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.17</v>
+        <v>1.27</v>
       </c>
       <c r="K10" t="n">
-        <v>1.91</v>
+        <v>1.13</v>
       </c>
       <c r="L10" t="n">
-        <v>9.34</v>
+        <v>13.32</v>
       </c>
       <c r="M10" t="n">
-        <v>8.24</v>
+        <v>11.76</v>
       </c>
       <c r="N10" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="O10" t="n">
         <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>308.81</v>
+        <v>300.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>272.18</v>
+        <v>265.33</v>
       </c>
       <c r="R10" t="n">
-        <v>193.93</v>
+        <v>200.57</v>
       </c>
       <c r="S10" t="n">
-        <v>352.58</v>
+        <v>345.57</v>
       </c>
       <c r="T10" t="n">
-        <v>292.94</v>
+        <v>257.82</v>
       </c>
       <c r="U10" t="n">
-        <v>-20.76</v>
+        <v>7.51</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -6017,74 +6017,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4512.9</v>
+        <v>3887.2</v>
       </c>
       <c r="E11" t="n">
-        <v>3974.5</v>
+        <v>3435.5</v>
       </c>
       <c r="F11" t="n">
-        <v>35.79</v>
+        <v>30.24</v>
       </c>
       <c r="G11" t="n">
-        <v>31.71</v>
+        <v>26.76</v>
       </c>
       <c r="H11" t="n">
-        <v>21.2</v>
+        <v>315.6</v>
       </c>
       <c r="I11" t="n">
-        <v>18.5</v>
+        <v>278.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.27</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>1.13</v>
+        <v>3.41</v>
       </c>
       <c r="L11" t="n">
-        <v>13.32</v>
+        <v>12.4</v>
       </c>
       <c r="M11" t="n">
-        <v>11.76</v>
+        <v>10.94</v>
       </c>
       <c r="N11" t="n">
-        <v>3.17</v>
+        <v>3.54</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="P11" t="n">
-        <v>300.44</v>
+        <v>299.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>265.33</v>
+        <v>264.68</v>
       </c>
       <c r="R11" t="n">
-        <v>200.57</v>
+        <v>183.96</v>
       </c>
       <c r="S11" t="n">
-        <v>345.57</v>
+        <v>345.47</v>
       </c>
       <c r="T11" t="n">
-        <v>257.82</v>
+        <v>284.56</v>
       </c>
       <c r="U11" t="n">
-        <v>7.51</v>
+        <v>-19.88</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -6092,74 +6092,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3887.2</v>
+        <v>4066.6</v>
       </c>
       <c r="E12" t="n">
-        <v>3435.5</v>
+        <v>3356</v>
       </c>
       <c r="F12" t="n">
-        <v>30.24</v>
+        <v>27.62</v>
       </c>
       <c r="G12" t="n">
-        <v>26.76</v>
+        <v>22.8</v>
       </c>
       <c r="H12" t="n">
-        <v>315.6</v>
+        <v>479.9</v>
       </c>
       <c r="I12" t="n">
-        <v>278.8</v>
+        <v>395.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="L12" t="n">
-        <v>12.4</v>
+        <v>8.69</v>
       </c>
       <c r="M12" t="n">
-        <v>10.94</v>
+        <v>7.15</v>
       </c>
       <c r="N12" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="P12" t="n">
-        <v>299.23</v>
+        <v>320.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>264.68</v>
+        <v>264.66</v>
       </c>
       <c r="R12" t="n">
-        <v>183.96</v>
+        <v>189.73</v>
       </c>
       <c r="S12" t="n">
-        <v>345.47</v>
+        <v>340.32</v>
       </c>
       <c r="T12" t="n">
-        <v>284.56</v>
+        <v>286.41</v>
       </c>
       <c r="U12" t="n">
-        <v>-19.88</v>
+        <v>-21.75</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -8090,64 +8090,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andy Dalton</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3375.4</v>
+        <v>3512.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>198.8</v>
       </c>
       <c r="F5" t="n">
-        <v>22.01</v>
+        <v>16.84</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="H5" t="n">
-        <v>101.5</v>
+        <v>379.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.66</v>
+        <v>3.26</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="L5" t="n">
-        <v>10.13</v>
+        <v>12.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="N5" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P5" t="n">
-        <v>217.57</v>
+        <v>234.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>13.34</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>18.54</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -8161,55 +8161,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Andy Dalton</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3470.3</v>
+        <v>3375.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>16.85</v>
+        <v>22.01</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>828.6</v>
+        <v>101.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7.93</v>
+        <v>1.66</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>13.8</v>
+        <v>10.13</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.45</v>
+        <v>2.67</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>300.15</v>
+        <v>217.57</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -8232,55 +8232,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3169.8</v>
+        <v>3470.3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>13.85</v>
+        <v>16.85</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>186.9</v>
+        <v>828.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>17.41</v>
+        <v>13.8</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.71</v>
+        <v>4.45</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>177.12</v>
+        <v>300.15</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -8291,12 +8291,8 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="n">
-        <v>21.18</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-21.18</v>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>50</t>
@@ -8307,55 +8303,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3394.4</v>
+        <v>3169.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>21.56</v>
+        <v>13.85</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>235.2</v>
+        <v>186.9</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.16</v>
+        <v>3.08</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>13.14</v>
+        <v>17.41</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>225.1</v>
+        <v>177.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -8366,63 +8362,71 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-21.18</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3531.4</v>
+        <v>3394.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>20.33</v>
+        <v>21.56</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>143.2</v>
+        <v>235.2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>12.93</v>
+        <v>13.14</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>216.06</v>
+        <v>225.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8435,65 +8439,61 @@
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3391.2</v>
+        <v>3531.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>18.78</v>
+        <v>20.33</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>262.3</v>
+        <v>143.2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.69</v>
+        <v>1.93</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11.16</v>
+        <v>12.93</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.93</v>
+        <v>3.28</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>224.96</v>
+        <v>216.06</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8516,55 +8516,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3435</v>
+        <v>3391.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>15.56</v>
+        <v>18.78</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>110.5</v>
+        <v>262.3</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.84</v>
+        <v>2.69</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11.6</v>
+        <v>11.16</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.61</v>
+        <v>2.93</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>191.31</v>
+        <v>224.96</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8587,55 +8587,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3275.4</v>
+        <v>3435</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>14.59</v>
+        <v>15.56</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>180.8</v>
+        <v>110.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3.13</v>
+        <v>1.84</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>17.3</v>
+        <v>11.6</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.72</v>
+        <v>3.61</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>184.2</v>
+        <v>191.31</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8648,61 +8648,65 @@
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3737.2</v>
+        <v>3275.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>18.69</v>
+        <v>14.59</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>322.3</v>
+        <v>180.8</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.33</v>
+        <v>3.13</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.89</v>
+        <v>17.3</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.59</v>
+        <v>3.72</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>241.5</v>
+        <v>184.2</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8715,65 +8719,61 @@
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3541.1</v>
+        <v>3737.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>22.12</v>
+        <v>18.69</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>778.4</v>
+        <v>322.3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7.46</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10.74</v>
+        <v>10.89</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.07</v>
+        <v>3.59</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>323.1</v>
+        <v>241.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8784,15 +8784,11 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
-        <v>278.65</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-278.65</v>
-      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -8800,55 +8796,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3609.6</v>
+        <v>3541.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>25.42</v>
+        <v>22.12</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>33.4</v>
+        <v>778.4</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.76</v>
+        <v>7.46</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>11.37</v>
+        <v>10.74</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.44</v>
+        <v>4.07</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>230.34</v>
+        <v>323.1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8859,11 +8855,15 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>278.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-278.65</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -8871,55 +8871,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3494.9</v>
+        <v>3609.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>17.77</v>
+        <v>25.42</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>551.1</v>
+        <v>33.4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.94</v>
+        <v>1.76</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.66</v>
+        <v>11.37</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>267.53</v>
+        <v>230.34</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -8932,61 +8932,65 @@
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3335.6</v>
+        <v>3494.9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>18.19</v>
+        <v>17.77</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>840.6</v>
+        <v>551.1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7.25</v>
+        <v>4.94</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10.83</v>
+        <v>10.66</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>305.22</v>
+        <v>267.53</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -8999,65 +9003,61 @@
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3383.9</v>
+        <v>3335.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>16.16</v>
+        <v>18.19</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>185.6</v>
+        <v>840.6</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.88</v>
+        <v>7.25</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>11.23</v>
+        <v>10.83</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.18</v>
+        <v>3.43</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>201.02</v>
+        <v>305.22</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -9080,55 +9080,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3481.6</v>
+        <v>3383.9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>17.64</v>
+        <v>16.16</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>183.1</v>
+        <v>185.6</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>13.2</v>
+        <v>11.23</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>210.81</v>
+        <v>201.02</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -9151,55 +9151,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3208</v>
+        <v>3481.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>13.86</v>
+        <v>17.64</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>181.8</v>
+        <v>183.1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>17.33</v>
+        <v>13.2</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.72</v>
+        <v>2.96</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>178.38</v>
+        <v>210.81</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -9212,61 +9212,65 @@
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3613</v>
+        <v>3208</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>22.93</v>
+        <v>13.86</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>174.9</v>
+        <v>181.8</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.16</v>
+        <v>3.09</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>10.15</v>
+        <v>17.33</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.57</v>
+        <v>3.72</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>241.25</v>
+        <v>178.38</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -9279,65 +9283,61 @@
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3506.9</v>
+        <v>3613</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>19.99</v>
+        <v>22.93</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>146.7</v>
+        <v>174.9</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>11.57</v>
+        <v>10.15</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.22</v>
+        <v>2.57</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>216.43</v>
+        <v>241.25</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -9360,55 +9360,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3597.8</v>
+        <v>3506.9</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>21.88</v>
+        <v>19.99</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>201.8</v>
+        <v>146.7</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.03</v>
+        <v>1.85</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>12.18</v>
+        <v>11.57</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.21</v>
+        <v>3.22</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>241.01</v>
+        <v>216.43</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -9431,55 +9431,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3353</v>
+        <v>3597.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>17.35</v>
+        <v>21.88</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>152.4</v>
+        <v>201.8</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>15.01</v>
+        <v>12.18</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>2.21</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>195.48</v>
+        <v>241.01</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -9502,55 +9502,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3196.3</v>
+        <v>3353</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>14.74</v>
+        <v>17.35</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>204.3</v>
+        <v>152.4</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>17.37</v>
+        <v>15.01</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>183.94</v>
+        <v>195.48</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -9563,61 +9563,65 @@
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3437.6</v>
+        <v>3196.3</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>17.14</v>
+        <v>14.74</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>286.9</v>
+        <v>204.3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>11.88</v>
+        <v>17.37</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>218.65</v>
+        <v>183.94</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -9630,65 +9634,61 @@
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3262.3</v>
+        <v>3437.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>16.01</v>
+        <v>17.14</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>182.6</v>
+        <v>286.9</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>16.12</v>
+        <v>11.88</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5.36</v>
+        <v>3.88</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>185.79</v>
+        <v>218.65</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -9701,61 +9701,65 @@
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3206.7</v>
+        <v>3262.3</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>14.57</v>
+        <v>16.01</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>242</v>
+        <v>182.6</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>17.33</v>
+        <v>16.12</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>5.36</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>186.99</v>
+        <v>185.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -9768,65 +9772,61 @@
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Trey Lance</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3273.2</v>
+        <v>3206.7</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>17.24</v>
+        <v>14.57</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>682.7</v>
+        <v>242</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3.49</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>11.98</v>
+        <v>17.33</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>258.34</v>
+        <v>186.99</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -9849,55 +9849,55 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Trey Lance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3367.8</v>
+        <v>3273.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>21.58</v>
+        <v>17.24</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>38.9</v>
+        <v>682.7</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1.62</v>
+        <v>3.49</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>10.13</v>
+        <v>11.98</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>207.56</v>
+        <v>258.34</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -9908,12 +9908,8 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="T30" t="n">
-        <v>66.38</v>
-      </c>
-      <c r="U30" t="n">
-        <v>-66.38</v>
-      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>50</t>
@@ -9924,55 +9920,55 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3307.4</v>
+        <v>3367.8</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>18.02</v>
+        <v>21.58</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>725.9</v>
+        <v>38.9</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4.09</v>
+        <v>1.62</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.890000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>274.23</v>
+        <v>207.56</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -9983,8 +9979,12 @@
       <c r="S31" t="n">
         <v>0</v>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-66.38</v>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
           <t>50</t>
@@ -9995,55 +9995,55 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3627.7</v>
+        <v>3307.4</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>22.83</v>
+        <v>18.02</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>544.2</v>
+        <v>725.9</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>10.09</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.79</v>
+        <v>3.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>290.05</v>
+        <v>274.23</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -10066,55 +10066,55 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>3512.6</v>
+        <v>3627.7</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>16.84</v>
+        <v>22.83</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>379.2</v>
+        <v>544.2</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3.26</v>
+        <v>4.16</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>12.16</v>
+        <v>10.09</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.48</v>
+        <v>2.79</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>234.06</v>
+        <v>290.05</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -18694,67 +18694,67 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>231.398</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1.555</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>28.387</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0.511</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>138.276</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>324.516</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.538</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.959</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>9.826000000000001</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>49.28</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>0.749</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>0.177</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.647</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.8080000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>18.253</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>4.235</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>33.738</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="inlineStr"/>
     </row>
@@ -97837,67 +97837,67 @@
         <v>0</v>
       </c>
       <c r="H943" t="n">
-        <v>0</v>
+        <v>198.812</v>
       </c>
       <c r="I943" t="n">
-        <v>0</v>
+        <v>0.956</v>
       </c>
       <c r="J943" t="n">
-        <v>0</v>
+        <v>22.465</v>
       </c>
       <c r="K943" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="L943" t="n">
-        <v>0</v>
+        <v>0.716</v>
       </c>
       <c r="M943" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="N943" t="n">
-        <v>0</v>
+        <v>105.694</v>
       </c>
       <c r="O943" t="n">
-        <v>0</v>
+        <v>291.934</v>
       </c>
       <c r="P943" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="Q943" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R943" t="n">
-        <v>0</v>
+        <v>7.776</v>
       </c>
       <c r="S943" t="n">
-        <v>0</v>
+        <v>43.359</v>
       </c>
       <c r="T943" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="U943" t="n">
-        <v>0</v>
+        <v>0.709</v>
       </c>
       <c r="V943" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="W943" t="n">
-        <v>0</v>
+        <v>1.851</v>
       </c>
       <c r="X943" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y943" t="n">
-        <v>0</v>
+        <v>0.798</v>
       </c>
       <c r="Z943" t="n">
-        <v>0</v>
+        <v>13.332</v>
       </c>
       <c r="AA943" t="n">
-        <v>0</v>
+        <v>1.428</v>
       </c>
       <c r="AB943" t="n">
-        <v>0</v>
+        <v>29.072</v>
       </c>
       <c r="AC943" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -3728,43 +3728,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3275.4</v>
+        <v>3195.8</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>14.59</v>
+        <v>13.85</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>180.8</v>
+        <v>202.2</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>17.3</v>
+        <v>17.35</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>184.2</v>
+        <v>180.27</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3795,55 +3795,55 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3737.2</v>
+        <v>3275.4</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>18.69</v>
+        <v>14.59</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>322.3</v>
+        <v>180.8</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2.33</v>
+        <v>3.13</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.89</v>
+        <v>17.3</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.59</v>
+        <v>3.72</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>241.5</v>
+        <v>184.2</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3856,65 +3856,61 @@
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3541.1</v>
+        <v>3737.2</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>22.12</v>
+        <v>18.69</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>778.4</v>
+        <v>322.3</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>7.46</v>
+        <v>2.33</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>10.74</v>
+        <v>10.89</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.07</v>
+        <v>3.59</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>323.1</v>
+        <v>241.5</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3925,15 +3921,11 @@
       <c r="S47" t="n">
         <v>0</v>
       </c>
-      <c r="T47" t="n">
-        <v>278.65</v>
-      </c>
-      <c r="U47" t="n">
-        <v>-278.65</v>
-      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
@@ -8658,43 +8650,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3275.4</v>
+        <v>3195.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>14.59</v>
+        <v>13.85</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>180.8</v>
+        <v>202.2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>17.3</v>
+        <v>17.35</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -8706,7 +8698,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>184.2</v>
+        <v>180.27</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8725,55 +8717,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3737.2</v>
+        <v>3275.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>18.69</v>
+        <v>14.59</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>322.3</v>
+        <v>180.8</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>3.13</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10.89</v>
+        <v>17.3</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.59</v>
+        <v>3.72</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>241.5</v>
+        <v>184.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8786,65 +8778,61 @@
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3541.1</v>
+        <v>3737.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.12</v>
+        <v>18.69</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>778.4</v>
+        <v>322.3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7.46</v>
+        <v>2.33</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>10.74</v>
+        <v>10.89</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.07</v>
+        <v>3.59</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>323.1</v>
+        <v>241.5</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8855,15 +8843,11 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="n">
-        <v>278.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-278.65</v>
-      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -65912,12 +65896,12 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -65928,7 +65912,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -66005,12 +65989,12 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -66021,7 +66005,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -66098,12 +66082,12 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -66114,14 +66098,14 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F602" t="n">
         <v>-1</v>
       </c>
       <c r="G602" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -66191,12 +66175,12 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -66207,7 +66191,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -66284,12 +66268,12 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -66300,14 +66284,14 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F604" t="n">
         <v>-1</v>
       </c>
       <c r="G604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -66377,27 +66361,27 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C605" t="n">
         <v>2</v>
       </c>
       <c r="D605" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G605" t="n">
         <v>0</v>
@@ -66470,27 +66454,27 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C606" t="n">
         <v>2</v>
       </c>
       <c r="D606" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F606" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G606" t="n">
         <v>0</v>
@@ -66563,12 +66547,12 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -66579,14 +66563,14 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F607" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -66656,12 +66640,12 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -66672,14 +66656,14 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F608" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G608" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -66749,12 +66733,12 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -66765,7 +66749,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F609" t="n">
@@ -66842,12 +66826,12 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -66858,7 +66842,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F610" t="n">
@@ -66935,12 +66919,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -66951,7 +66935,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F611" t="n">
@@ -67028,12 +67012,12 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -67044,7 +67028,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F612" t="n">
@@ -67121,12 +67105,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -67137,14 +67121,14 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F613" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G613" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -67214,12 +67198,12 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -67230,14 +67214,14 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F614" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H614" t="n">
         <v>0</v>
@@ -67307,12 +67291,12 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -67323,7 +67307,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F615" t="n">
@@ -67400,12 +67384,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -67416,11 +67400,11 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F616" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G616" t="n">
         <v>0</v>
@@ -67493,12 +67477,12 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -67509,14 +67493,14 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F617" t="n">
         <v>-1</v>
       </c>
       <c r="G617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -67586,12 +67570,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -67602,7 +67586,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F618" t="n">
@@ -67679,12 +67663,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -67695,14 +67679,14 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F619" t="n">
         <v>-1</v>
       </c>
       <c r="G619" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -67772,12 +67756,12 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -67788,7 +67772,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -67865,12 +67849,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -67881,7 +67865,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F621" t="n">
@@ -67958,12 +67942,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -67974,14 +67958,14 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F622" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G622" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -68051,12 +68035,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -68067,11 +68051,11 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F623" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G623" t="n">
         <v>0</v>
@@ -68144,12 +68128,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -68160,7 +68144,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F624" t="n">
@@ -68237,12 +68221,12 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -68253,7 +68237,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F625" t="n">
@@ -68330,12 +68314,12 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -68346,14 +68330,14 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F626" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G626" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H626" t="n">
         <v>0</v>
@@ -68423,12 +68407,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -68439,14 +68423,14 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F627" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -68516,12 +68500,12 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -68532,11 +68516,11 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F628" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G628" t="n">
         <v>0</v>
@@ -68609,12 +68593,12 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C629" t="n">
@@ -68625,14 +68609,14 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F629" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H629" t="n">
         <v>0</v>
@@ -68702,12 +68686,12 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -68718,7 +68702,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F630" t="n">
@@ -68795,12 +68779,12 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C631" t="n">
@@ -68811,11 +68795,11 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F631" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G631" t="n">
         <v>0</v>
@@ -68888,12 +68872,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -68904,7 +68888,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F632" t="n">
@@ -68981,12 +68965,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -68997,7 +68981,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -69074,12 +69058,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -69090,7 +69074,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -69167,27 +69151,27 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C635" t="n">
         <v>2</v>
       </c>
       <c r="D635" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F635" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G635" t="n">
         <v>0</v>
@@ -69260,27 +69244,27 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C636" t="n">
         <v>2</v>
       </c>
       <c r="D636" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F636" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G636" t="n">
         <v>0</v>
@@ -69353,12 +69337,12 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -69369,7 +69353,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F637" t="n">
@@ -69446,12 +69430,12 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -69462,14 +69446,14 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F638" t="n">
         <v>-1</v>
       </c>
       <c r="G638" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -69539,12 +69523,12 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -69555,7 +69539,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F639" t="n">
@@ -69632,12 +69616,12 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -69648,7 +69632,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -69725,12 +69709,12 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -69741,14 +69725,14 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F641" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -69818,12 +69802,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -69834,14 +69818,14 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="F642" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G642" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H642" t="n">
         <v>0</v>
@@ -69911,12 +69895,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C643" t="n">
@@ -69927,14 +69911,14 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="F643" t="n">
         <v>-1</v>
       </c>
       <c r="G643" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -70004,12 +69988,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -70020,7 +70004,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F644" t="n">

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -2418,74 +2418,74 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3696</v>
+        <v>3784.3</v>
       </c>
       <c r="E27" t="n">
-        <v>3037</v>
+        <v>3105.1</v>
       </c>
       <c r="F27" t="n">
-        <v>23.81</v>
+        <v>21.48</v>
       </c>
       <c r="G27" t="n">
-        <v>19.58</v>
+        <v>17.61</v>
       </c>
       <c r="H27" t="n">
-        <v>290.8</v>
+        <v>187.1</v>
       </c>
       <c r="I27" t="n">
-        <v>239.7</v>
+        <v>155.1</v>
       </c>
       <c r="J27" t="n">
-        <v>2.95</v>
+        <v>2.17</v>
       </c>
       <c r="K27" t="n">
-        <v>2.43</v>
+        <v>1.79</v>
       </c>
       <c r="L27" t="n">
-        <v>12.7</v>
+        <v>9.91</v>
       </c>
       <c r="M27" t="n">
-        <v>10.46</v>
+        <v>8.16</v>
       </c>
       <c r="N27" t="n">
-        <v>3.54</v>
+        <v>3.29</v>
       </c>
       <c r="O27" t="n">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="P27" t="n">
-        <v>257.38</v>
+        <v>242.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>211.59</v>
+        <v>199.15</v>
       </c>
       <c r="R27" t="n">
-        <v>136.67</v>
+        <v>126.01</v>
       </c>
       <c r="S27" t="n">
-        <v>286.78</v>
+        <v>273.75</v>
       </c>
       <c r="T27" t="n">
-        <v>235.78</v>
+        <v>182</v>
       </c>
       <c r="U27" t="n">
-        <v>-24.19</v>
+        <v>17.15</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -2493,74 +2493,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3784.3</v>
+        <v>3602.1</v>
       </c>
       <c r="E28" t="n">
-        <v>3105.1</v>
+        <v>2960.2</v>
       </c>
       <c r="F28" t="n">
-        <v>21.48</v>
+        <v>23.44</v>
       </c>
       <c r="G28" t="n">
-        <v>17.61</v>
+        <v>19.16</v>
       </c>
       <c r="H28" t="n">
-        <v>187.1</v>
+        <v>203.6</v>
       </c>
       <c r="I28" t="n">
-        <v>155.1</v>
+        <v>168.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="K28" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="L28" t="n">
-        <v>9.91</v>
+        <v>13.4</v>
       </c>
       <c r="M28" t="n">
-        <v>8.16</v>
+        <v>11.03</v>
       </c>
       <c r="N28" t="n">
-        <v>3.29</v>
+        <v>3.17</v>
       </c>
       <c r="O28" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="P28" t="n">
-        <v>242.62</v>
+        <v>238.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>199.15</v>
+        <v>195.56</v>
       </c>
       <c r="R28" t="n">
-        <v>126.01</v>
+        <v>122.33</v>
       </c>
       <c r="S28" t="n">
-        <v>273.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>182</v>
-      </c>
-      <c r="U28" t="n">
-        <v>17.15</v>
-      </c>
+        <v>270.64</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
@@ -2568,70 +2564,74 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3602.1</v>
+        <v>3697.7</v>
       </c>
       <c r="E29" t="n">
-        <v>2960.2</v>
+        <v>3040.6</v>
       </c>
       <c r="F29" t="n">
-        <v>23.44</v>
+        <v>22.36</v>
       </c>
       <c r="G29" t="n">
-        <v>19.16</v>
+        <v>18.35</v>
       </c>
       <c r="H29" t="n">
-        <v>203.6</v>
+        <v>115.2</v>
       </c>
       <c r="I29" t="n">
-        <v>168.1</v>
+        <v>95.2</v>
       </c>
       <c r="J29" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="K29" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="L29" t="n">
-        <v>13.4</v>
+        <v>11.7</v>
       </c>
       <c r="M29" t="n">
-        <v>11.03</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="O29" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="P29" t="n">
-        <v>238.38</v>
+        <v>233.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>195.56</v>
+        <v>191.98</v>
       </c>
       <c r="R29" t="n">
-        <v>122.33</v>
+        <v>118.32</v>
       </c>
       <c r="S29" t="n">
-        <v>270.64</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+        <v>267.09</v>
+      </c>
+      <c r="T29" t="n">
+        <v>124.44</v>
+      </c>
+      <c r="U29" t="n">
+        <v>67.54000000000001</v>
+      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -2639,74 +2639,74 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3697.7</v>
+        <v>3567.3</v>
       </c>
       <c r="E30" t="n">
-        <v>3040.6</v>
+        <v>2933.2</v>
       </c>
       <c r="F30" t="n">
-        <v>22.36</v>
+        <v>19.79</v>
       </c>
       <c r="G30" t="n">
-        <v>18.35</v>
+        <v>16.3</v>
       </c>
       <c r="H30" t="n">
-        <v>115.2</v>
+        <v>167.3</v>
       </c>
       <c r="I30" t="n">
-        <v>95.2</v>
+        <v>138</v>
       </c>
       <c r="J30" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="K30" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="L30" t="n">
-        <v>11.7</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>9.630000000000001</v>
+        <v>6.77</v>
       </c>
       <c r="N30" t="n">
-        <v>3.26</v>
+        <v>4.36</v>
       </c>
       <c r="O30" t="n">
-        <v>2.68</v>
+        <v>3.59</v>
       </c>
       <c r="P30" t="n">
-        <v>233.53</v>
+        <v>228.48</v>
       </c>
       <c r="Q30" t="n">
-        <v>191.98</v>
+        <v>188.03</v>
       </c>
       <c r="R30" t="n">
-        <v>118.32</v>
+        <v>113.02</v>
       </c>
       <c r="S30" t="n">
-        <v>267.09</v>
+        <v>262.61</v>
       </c>
       <c r="T30" t="n">
-        <v>124.44</v>
+        <v>212.14</v>
       </c>
       <c r="U30" t="n">
-        <v>67.54000000000001</v>
+        <v>-24.11</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
@@ -2714,74 +2714,74 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3567.3</v>
+        <v>3696</v>
       </c>
       <c r="E31" t="n">
-        <v>2933.2</v>
+        <v>2377.8</v>
       </c>
       <c r="F31" t="n">
-        <v>19.79</v>
+        <v>23.81</v>
       </c>
       <c r="G31" t="n">
-        <v>16.3</v>
+        <v>15.33</v>
       </c>
       <c r="H31" t="n">
-        <v>167.3</v>
+        <v>290.8</v>
       </c>
       <c r="I31" t="n">
-        <v>138</v>
+        <v>188.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2.51</v>
+        <v>2.95</v>
       </c>
       <c r="K31" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="L31" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M31" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="M31" t="n">
-        <v>6.77</v>
-      </c>
       <c r="N31" t="n">
-        <v>4.36</v>
+        <v>3.54</v>
       </c>
       <c r="O31" t="n">
-        <v>3.59</v>
+        <v>2.29</v>
       </c>
       <c r="P31" t="n">
-        <v>228.48</v>
+        <v>257.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>188.03</v>
+        <v>165.7</v>
       </c>
       <c r="R31" t="n">
-        <v>113.02</v>
+        <v>107.03</v>
       </c>
       <c r="S31" t="n">
-        <v>262.61</v>
+        <v>224.58</v>
       </c>
       <c r="T31" t="n">
-        <v>212.14</v>
+        <v>235.78</v>
       </c>
       <c r="U31" t="n">
-        <v>-24.11</v>
+        <v>-70.08</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -3160,135 +3160,131 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3517.9</v>
+        <v>3147.6</v>
       </c>
       <c r="E37" t="n">
-        <v>198.8</v>
+        <v>562.4</v>
       </c>
       <c r="F37" t="n">
-        <v>16.98</v>
+        <v>14.72</v>
       </c>
       <c r="G37" t="n">
-        <v>0.96</v>
+        <v>2.64</v>
       </c>
       <c r="H37" t="n">
-        <v>379.2</v>
+        <v>183.6</v>
       </c>
       <c r="I37" t="n">
-        <v>22.5</v>
+        <v>32.5</v>
       </c>
       <c r="J37" t="n">
-        <v>3.26</v>
+        <v>2.93</v>
       </c>
       <c r="K37" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="L37" t="n">
-        <v>12.16</v>
+        <v>21.54</v>
       </c>
       <c r="M37" t="n">
-        <v>0.72</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>3.48</v>
+        <v>5.33</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P37" t="n">
-        <v>234.84</v>
+        <v>166.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>13.34</v>
+        <v>29.83</v>
       </c>
       <c r="R37" t="n">
-        <v>8.15</v>
+        <v>13.58</v>
       </c>
       <c r="S37" t="n">
-        <v>18.51</v>
+        <v>46.16</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Andy Dalton</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3413.2</v>
+        <v>3517.9</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>198.8</v>
       </c>
       <c r="F38" t="n">
-        <v>22.06</v>
+        <v>16.98</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="H38" t="n">
-        <v>101.3</v>
+        <v>379.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1.66</v>
+        <v>3.26</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="L38" t="n">
-        <v>10.61</v>
+        <v>12.16</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="N38" t="n">
-        <v>2.87</v>
+        <v>3.48</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P38" t="n">
-        <v>217.9</v>
+        <v>234.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>13.34</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>18.51</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -3302,55 +3298,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Andy Dalton</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3494.7</v>
+        <v>3413.2</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>17</v>
+        <v>22.06</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>828.9</v>
+        <v>101.3</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>7.93</v>
+        <v>1.66</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>13.85</v>
+        <v>10.61</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.65</v>
+        <v>2.87</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>301.26</v>
+        <v>217.9</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3373,55 +3369,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3232.1</v>
+        <v>3494.7</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>14.01</v>
+        <v>17</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>188.3</v>
+        <v>828.9</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>17.37</v>
+        <v>13.85</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.71</v>
+        <v>4.65</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>180.47</v>
+        <v>301.26</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3432,12 +3428,8 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="U40" t="n">
-        <v>-19.76</v>
-      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>50</t>
@@ -3448,55 +3440,55 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3403</v>
+        <v>3232.1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>21.41</v>
+        <v>14.01</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>231.2</v>
+        <v>188.3</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2.16</v>
+        <v>3.08</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>13.14</v>
+        <v>17.37</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.59</v>
+        <v>3.71</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>224.38</v>
+        <v>180.47</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3507,63 +3499,71 @@
       <c r="S41" t="n">
         <v>0</v>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-19.76</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3511.4</v>
+        <v>3403</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>20.61</v>
+        <v>21.41</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>142.6</v>
+        <v>231.2</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>12.37</v>
+        <v>13.14</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.24</v>
+        <v>3.59</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>217.52</v>
+        <v>224.38</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3576,65 +3576,61 @@
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3477.4</v>
+        <v>3511.4</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>19</v>
+        <v>20.61</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>261</v>
+        <v>142.6</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2.67</v>
+        <v>1.93</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>11.11</v>
+        <v>12.37</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>229.7</v>
+        <v>217.52</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3657,55 +3653,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3429.8</v>
+        <v>3477.4</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>15.7</v>
+        <v>19</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>111.9</v>
+        <v>261</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>11.26</v>
+        <v>11.11</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>192.64</v>
+        <v>229.7</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3728,55 +3724,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3237.3</v>
+        <v>3429.8</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>14.08</v>
+        <v>15.7</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>201.9</v>
+        <v>111.9</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>17.29</v>
+        <v>11.26</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>182.94</v>
+        <v>192.64</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3789,61 +3785,65 @@
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3147.6</v>
+        <v>3439.4</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>14.72</v>
+        <v>16.89</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>183.6</v>
+        <v>271.6</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2.93</v>
+        <v>3.75</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>21.54</v>
+        <v>10.35</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>5.33</v>
+        <v>4.25</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>166.98</v>
+        <v>225.6</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3854,9 +3854,17 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-24.46</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -7209,74 +7217,74 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3696</v>
+        <v>3784.3</v>
       </c>
       <c r="E27" t="n">
-        <v>3037</v>
+        <v>3105.1</v>
       </c>
       <c r="F27" t="n">
-        <v>23.81</v>
+        <v>21.48</v>
       </c>
       <c r="G27" t="n">
-        <v>19.58</v>
+        <v>17.61</v>
       </c>
       <c r="H27" t="n">
-        <v>290.8</v>
+        <v>187.1</v>
       </c>
       <c r="I27" t="n">
-        <v>239.7</v>
+        <v>155.1</v>
       </c>
       <c r="J27" t="n">
-        <v>2.95</v>
+        <v>2.17</v>
       </c>
       <c r="K27" t="n">
-        <v>2.43</v>
+        <v>1.79</v>
       </c>
       <c r="L27" t="n">
-        <v>12.7</v>
+        <v>9.91</v>
       </c>
       <c r="M27" t="n">
-        <v>10.46</v>
+        <v>8.16</v>
       </c>
       <c r="N27" t="n">
-        <v>3.54</v>
+        <v>3.29</v>
       </c>
       <c r="O27" t="n">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="P27" t="n">
-        <v>257.38</v>
+        <v>242.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>211.59</v>
+        <v>199.15</v>
       </c>
       <c r="R27" t="n">
-        <v>136.67</v>
+        <v>126.01</v>
       </c>
       <c r="S27" t="n">
-        <v>286.78</v>
+        <v>273.75</v>
       </c>
       <c r="T27" t="n">
-        <v>235.78</v>
+        <v>182</v>
       </c>
       <c r="U27" t="n">
-        <v>-24.19</v>
+        <v>17.15</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -7284,74 +7292,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3784.3</v>
+        <v>3602.1</v>
       </c>
       <c r="E28" t="n">
-        <v>3105.1</v>
+        <v>2960.2</v>
       </c>
       <c r="F28" t="n">
-        <v>21.48</v>
+        <v>23.44</v>
       </c>
       <c r="G28" t="n">
-        <v>17.61</v>
+        <v>19.16</v>
       </c>
       <c r="H28" t="n">
-        <v>187.1</v>
+        <v>203.6</v>
       </c>
       <c r="I28" t="n">
-        <v>155.1</v>
+        <v>168.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="K28" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="L28" t="n">
-        <v>9.91</v>
+        <v>13.4</v>
       </c>
       <c r="M28" t="n">
-        <v>8.16</v>
+        <v>11.03</v>
       </c>
       <c r="N28" t="n">
-        <v>3.29</v>
+        <v>3.17</v>
       </c>
       <c r="O28" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="P28" t="n">
-        <v>242.62</v>
+        <v>238.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>199.15</v>
+        <v>195.56</v>
       </c>
       <c r="R28" t="n">
-        <v>126.01</v>
+        <v>122.33</v>
       </c>
       <c r="S28" t="n">
-        <v>273.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>182</v>
-      </c>
-      <c r="U28" t="n">
-        <v>17.15</v>
-      </c>
+        <v>270.64</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
@@ -7359,70 +7363,74 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3602.1</v>
+        <v>3697.7</v>
       </c>
       <c r="E29" t="n">
-        <v>2960.2</v>
+        <v>3040.6</v>
       </c>
       <c r="F29" t="n">
-        <v>23.44</v>
+        <v>22.36</v>
       </c>
       <c r="G29" t="n">
-        <v>19.16</v>
+        <v>18.35</v>
       </c>
       <c r="H29" t="n">
-        <v>203.6</v>
+        <v>115.2</v>
       </c>
       <c r="I29" t="n">
-        <v>168.1</v>
+        <v>95.2</v>
       </c>
       <c r="J29" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="K29" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="L29" t="n">
-        <v>13.4</v>
+        <v>11.7</v>
       </c>
       <c r="M29" t="n">
-        <v>11.03</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="O29" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="P29" t="n">
-        <v>238.38</v>
+        <v>233.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>195.56</v>
+        <v>191.98</v>
       </c>
       <c r="R29" t="n">
-        <v>122.33</v>
+        <v>118.32</v>
       </c>
       <c r="S29" t="n">
-        <v>270.64</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+        <v>267.09</v>
+      </c>
+      <c r="T29" t="n">
+        <v>124.44</v>
+      </c>
+      <c r="U29" t="n">
+        <v>67.54000000000001</v>
+      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -7430,74 +7438,74 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3697.7</v>
+        <v>3567.3</v>
       </c>
       <c r="E30" t="n">
-        <v>3040.6</v>
+        <v>2933.2</v>
       </c>
       <c r="F30" t="n">
-        <v>22.36</v>
+        <v>19.79</v>
       </c>
       <c r="G30" t="n">
-        <v>18.35</v>
+        <v>16.3</v>
       </c>
       <c r="H30" t="n">
-        <v>115.2</v>
+        <v>167.3</v>
       </c>
       <c r="I30" t="n">
-        <v>95.2</v>
+        <v>138</v>
       </c>
       <c r="J30" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="K30" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="L30" t="n">
-        <v>11.7</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>9.630000000000001</v>
+        <v>6.77</v>
       </c>
       <c r="N30" t="n">
-        <v>3.26</v>
+        <v>4.36</v>
       </c>
       <c r="O30" t="n">
-        <v>2.68</v>
+        <v>3.59</v>
       </c>
       <c r="P30" t="n">
-        <v>233.53</v>
+        <v>228.48</v>
       </c>
       <c r="Q30" t="n">
-        <v>191.98</v>
+        <v>188.03</v>
       </c>
       <c r="R30" t="n">
-        <v>118.32</v>
+        <v>113.02</v>
       </c>
       <c r="S30" t="n">
-        <v>267.09</v>
+        <v>262.61</v>
       </c>
       <c r="T30" t="n">
-        <v>124.44</v>
+        <v>212.14</v>
       </c>
       <c r="U30" t="n">
-        <v>67.54000000000001</v>
+        <v>-24.11</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
@@ -7505,74 +7513,74 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3567.3</v>
+        <v>3696</v>
       </c>
       <c r="E31" t="n">
-        <v>2933.2</v>
+        <v>2377.8</v>
       </c>
       <c r="F31" t="n">
-        <v>19.79</v>
+        <v>23.81</v>
       </c>
       <c r="G31" t="n">
-        <v>16.3</v>
+        <v>15.33</v>
       </c>
       <c r="H31" t="n">
-        <v>167.3</v>
+        <v>290.8</v>
       </c>
       <c r="I31" t="n">
-        <v>138</v>
+        <v>188.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2.51</v>
+        <v>2.95</v>
       </c>
       <c r="K31" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="L31" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M31" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="M31" t="n">
-        <v>6.77</v>
-      </c>
       <c r="N31" t="n">
-        <v>4.36</v>
+        <v>3.54</v>
       </c>
       <c r="O31" t="n">
-        <v>3.59</v>
+        <v>2.29</v>
       </c>
       <c r="P31" t="n">
-        <v>228.48</v>
+        <v>257.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>188.03</v>
+        <v>165.7</v>
       </c>
       <c r="R31" t="n">
-        <v>113.02</v>
+        <v>107.03</v>
       </c>
       <c r="S31" t="n">
-        <v>262.61</v>
+        <v>224.58</v>
       </c>
       <c r="T31" t="n">
-        <v>212.14</v>
+        <v>235.78</v>
       </c>
       <c r="U31" t="n">
-        <v>-24.11</v>
+        <v>-70.08</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -8082,135 +8090,131 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3517.9</v>
+        <v>3147.6</v>
       </c>
       <c r="E5" t="n">
-        <v>198.8</v>
+        <v>562.4</v>
       </c>
       <c r="F5" t="n">
-        <v>16.98</v>
+        <v>14.72</v>
       </c>
       <c r="G5" t="n">
-        <v>0.96</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>379.2</v>
+        <v>183.6</v>
       </c>
       <c r="I5" t="n">
-        <v>22.5</v>
+        <v>32.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.26</v>
+        <v>2.93</v>
       </c>
       <c r="K5" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>12.16</v>
+        <v>21.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0.72</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.48</v>
+        <v>5.33</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>234.84</v>
+        <v>166.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.34</v>
+        <v>29.83</v>
       </c>
       <c r="R5" t="n">
-        <v>8.15</v>
+        <v>13.58</v>
       </c>
       <c r="S5" t="n">
-        <v>18.51</v>
+        <v>46.16</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Andy Dalton</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3413.2</v>
+        <v>3517.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>198.8</v>
       </c>
       <c r="F6" t="n">
-        <v>22.06</v>
+        <v>16.98</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="H6" t="n">
-        <v>101.3</v>
+        <v>379.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.66</v>
+        <v>3.26</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="L6" t="n">
-        <v>10.61</v>
+        <v>12.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P6" t="n">
-        <v>217.9</v>
+        <v>234.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>13.34</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>18.51</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -8224,55 +8228,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Andy Dalton</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3494.7</v>
+        <v>3413.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>22.06</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>828.9</v>
+        <v>101.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7.93</v>
+        <v>1.66</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13.85</v>
+        <v>10.61</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.65</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>301.26</v>
+        <v>217.9</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -8295,55 +8299,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3232.1</v>
+        <v>3494.7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>14.01</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>188.3</v>
+        <v>828.9</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17.37</v>
+        <v>13.85</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.71</v>
+        <v>4.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>180.47</v>
+        <v>301.26</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -8354,12 +8358,8 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-19.76</v>
-      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>50</t>
@@ -8370,55 +8370,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3403</v>
+        <v>3232.1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>21.41</v>
+        <v>14.01</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>231.2</v>
+        <v>188.3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.16</v>
+        <v>3.08</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13.14</v>
+        <v>17.37</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.59</v>
+        <v>3.71</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>224.38</v>
+        <v>180.47</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8429,63 +8429,71 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-19.76</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3511.4</v>
+        <v>3403</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>20.61</v>
+        <v>21.41</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>142.6</v>
+        <v>231.2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12.37</v>
+        <v>13.14</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.24</v>
+        <v>3.59</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>217.52</v>
+        <v>224.38</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8498,65 +8506,61 @@
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3477.4</v>
+        <v>3511.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>20.61</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>261</v>
+        <v>142.6</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67</v>
+        <v>1.93</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11.11</v>
+        <v>12.37</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>229.7</v>
+        <v>217.52</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8579,55 +8583,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3429.8</v>
+        <v>3477.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>15.7</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>111.9</v>
+        <v>261</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>11.26</v>
+        <v>11.11</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>192.64</v>
+        <v>229.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8650,55 +8654,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3237.3</v>
+        <v>3429.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>14.08</v>
+        <v>15.7</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>201.9</v>
+        <v>111.9</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>17.29</v>
+        <v>11.26</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>182.94</v>
+        <v>192.64</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8711,61 +8715,65 @@
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3147.6</v>
+        <v>3439.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>14.72</v>
+        <v>16.89</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>183.6</v>
+        <v>271.6</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.93</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>21.54</v>
+        <v>10.35</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.33</v>
+        <v>4.25</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>166.98</v>
+        <v>225.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8776,9 +8784,17 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-24.46</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -11610,67 +11626,67 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>220.101</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.356</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>17.189</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.177</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.747</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.206</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>126.977</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>313.224</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.469</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>38.081</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.695</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.883</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.802</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.099</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.547</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>30.887</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="inlineStr"/>
     </row>
@@ -11703,67 +11719,67 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>226.206</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.488</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>16.873</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.173</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.748</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>133.085</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>319.325</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.515</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.892</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>37.768</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.883</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.803</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.942</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>31.604</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="inlineStr"/>
     </row>
@@ -11796,67 +11812,67 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>212.911</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.408</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>17.319</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.748</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.206</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>119.794</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>306.034</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.487</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.813</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>5.995</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>38.21</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6889999999999999</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.883</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.802</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.997</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.324</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>30.785</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="inlineStr"/>
     </row>
@@ -62641,7 +62657,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -62734,7 +62750,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -62827,7 +62843,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -62920,7 +62936,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -63013,7 +63029,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -63106,7 +63122,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -63199,7 +63215,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -63292,7 +63308,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -63385,7 +63401,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -63478,7 +63494,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -63571,7 +63587,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -63664,7 +63680,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -63757,7 +63773,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -63850,7 +63866,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Jake Haener</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -63969,67 +63985,67 @@
         <v>0</v>
       </c>
       <c r="H579" t="n">
-        <v>0</v>
+        <v>187.844</v>
       </c>
       <c r="I579" t="n">
-        <v>0</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="J579" t="n">
-        <v>0</v>
+        <v>10.885</v>
       </c>
       <c r="K579" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="L579" t="n">
-        <v>0</v>
+        <v>1.268</v>
       </c>
       <c r="M579" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="N579" t="n">
-        <v>0</v>
+        <v>94.72499999999999</v>
       </c>
       <c r="O579" t="n">
-        <v>0</v>
+        <v>280.965</v>
       </c>
       <c r="P579" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="Q579" t="n">
-        <v>0</v>
+        <v>2.223</v>
       </c>
       <c r="R579" t="n">
-        <v>0</v>
+        <v>3.768</v>
       </c>
       <c r="S579" t="n">
-        <v>0</v>
+        <v>31.779</v>
       </c>
       <c r="T579" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="U579" t="n">
-        <v>0</v>
+        <v>0.671</v>
       </c>
       <c r="V579" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="W579" t="n">
-        <v>0</v>
+        <v>2.403</v>
       </c>
       <c r="X579" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="Y579" t="n">
-        <v>0</v>
+        <v>0.906</v>
       </c>
       <c r="Z579" t="n">
-        <v>0</v>
+        <v>9.635</v>
       </c>
       <c r="AA579" t="n">
-        <v>0</v>
+        <v>-1.003</v>
       </c>
       <c r="AB579" t="n">
-        <v>0</v>
+        <v>26.241</v>
       </c>
       <c r="AC579" t="inlineStr"/>
     </row>
@@ -64062,67 +64078,67 @@
         <v>1</v>
       </c>
       <c r="H580" t="n">
-        <v>0</v>
+        <v>193.95</v>
       </c>
       <c r="I580" t="n">
-        <v>0</v>
+        <v>0.951</v>
       </c>
       <c r="J580" t="n">
-        <v>0</v>
+        <v>10.568</v>
       </c>
       <c r="K580" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="L580" t="n">
-        <v>0</v>
+        <v>1.268</v>
       </c>
       <c r="M580" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="N580" t="n">
-        <v>0</v>
+        <v>100.826</v>
       </c>
       <c r="O580" t="n">
-        <v>0</v>
+        <v>287.073</v>
       </c>
       <c r="P580" t="n">
-        <v>0</v>
+        <v>0.329</v>
       </c>
       <c r="Q580" t="n">
-        <v>0</v>
+        <v>2.356</v>
       </c>
       <c r="R580" t="n">
-        <v>0</v>
+        <v>3.658</v>
       </c>
       <c r="S580" t="n">
-        <v>0</v>
+        <v>31.46</v>
       </c>
       <c r="T580" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="U580" t="n">
-        <v>0</v>
+        <v>0.697</v>
       </c>
       <c r="V580" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="W580" t="n">
-        <v>0</v>
+        <v>2.403</v>
       </c>
       <c r="X580" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="Y580" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="Z580" t="n">
-        <v>0</v>
+        <v>10.508</v>
       </c>
       <c r="AA580" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="AB580" t="n">
-        <v>0</v>
+        <v>27.133</v>
       </c>
       <c r="AC580" t="inlineStr"/>
     </row>
@@ -64155,67 +64171,67 @@
         <v>0</v>
       </c>
       <c r="H581" t="n">
-        <v>0</v>
+        <v>180.655</v>
       </c>
       <c r="I581" t="n">
-        <v>0</v>
+        <v>0.871</v>
       </c>
       <c r="J581" t="n">
-        <v>0</v>
+        <v>11.014</v>
       </c>
       <c r="K581" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="L581" t="n">
-        <v>0</v>
+        <v>1.268</v>
       </c>
       <c r="M581" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="N581" t="n">
-        <v>0</v>
+        <v>87.535</v>
       </c>
       <c r="O581" t="n">
-        <v>0</v>
+        <v>273.775</v>
       </c>
       <c r="P581" t="n">
-        <v>0</v>
+        <v>0.302</v>
       </c>
       <c r="Q581" t="n">
-        <v>0</v>
+        <v>2.276</v>
       </c>
       <c r="R581" t="n">
-        <v>0</v>
+        <v>3.812</v>
       </c>
       <c r="S581" t="n">
-        <v>0</v>
+        <v>31.909</v>
       </c>
       <c r="T581" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="U581" t="n">
-        <v>0</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="V581" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="W581" t="n">
-        <v>0</v>
+        <v>2.403</v>
       </c>
       <c r="X581" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="Y581" t="n">
-        <v>0</v>
+        <v>0.906</v>
       </c>
       <c r="Z581" t="n">
-        <v>0</v>
+        <v>9.664</v>
       </c>
       <c r="AA581" t="n">
-        <v>0</v>
+        <v>-1.181</v>
       </c>
       <c r="AB581" t="n">
-        <v>0</v>
+        <v>26.27</v>
       </c>
       <c r="AC581" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -681,70 +681,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3752.8</v>
+        <v>3735.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2872.5</v>
+        <v>2848.3</v>
       </c>
       <c r="F4" t="n">
-        <v>27.65</v>
+        <v>24.96</v>
       </c>
       <c r="G4" t="n">
-        <v>21.05</v>
+        <v>19.03</v>
       </c>
       <c r="H4" t="n">
-        <v>651.9</v>
+        <v>812.5</v>
       </c>
       <c r="I4" t="n">
-        <v>499.5</v>
+        <v>622.2</v>
       </c>
       <c r="J4" t="n">
-        <v>5.67</v>
+        <v>6.03</v>
       </c>
       <c r="K4" t="n">
-        <v>4.35</v>
+        <v>4.61</v>
       </c>
       <c r="L4" t="n">
-        <v>7.93</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>6.06</v>
+        <v>6.85</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>2.17</v>
       </c>
       <c r="O4" t="n">
-        <v>2.33</v>
+        <v>1.66</v>
       </c>
       <c r="P4" t="n">
-        <v>337.96</v>
+        <v>344.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>258.37</v>
+        <v>262.91</v>
       </c>
       <c r="R4" t="n">
-        <v>188.54</v>
+        <v>193.38</v>
       </c>
       <c r="S4" t="n">
-        <v>327.96</v>
+        <v>331.73</v>
       </c>
       <c r="T4" t="n">
-        <v>251.97</v>
+        <v>252.43</v>
       </c>
       <c r="U4" t="n">
-        <v>6.4</v>
+        <v>10.48</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -752,70 +752,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4289.6</v>
+        <v>3752.8</v>
       </c>
       <c r="E5" t="n">
-        <v>3267.6</v>
+        <v>2872.5</v>
       </c>
       <c r="F5" t="n">
-        <v>33.75</v>
+        <v>27.65</v>
       </c>
       <c r="G5" t="n">
-        <v>25.64</v>
+        <v>21.05</v>
       </c>
       <c r="H5" t="n">
-        <v>337.3</v>
+        <v>651.9</v>
       </c>
       <c r="I5" t="n">
-        <v>257.7</v>
+        <v>499.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.44</v>
+        <v>5.67</v>
       </c>
       <c r="K5" t="n">
-        <v>2.65</v>
+        <v>4.35</v>
       </c>
       <c r="L5" t="n">
-        <v>8.449999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="M5" t="n">
-        <v>6.46</v>
+        <v>6.06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>338.31</v>
+        <v>337.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>257.61</v>
+        <v>258.37</v>
       </c>
       <c r="R5" t="n">
-        <v>188.22</v>
+        <v>188.54</v>
       </c>
       <c r="S5" t="n">
-        <v>327.09</v>
+        <v>327.96</v>
       </c>
       <c r="T5" t="n">
-        <v>244.32</v>
+        <v>251.97</v>
       </c>
       <c r="U5" t="n">
-        <v>13.29</v>
+        <v>6.4</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -823,70 +823,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4553</v>
+        <v>4289.6</v>
       </c>
       <c r="E6" t="n">
-        <v>3483.2</v>
+        <v>3267.6</v>
       </c>
       <c r="F6" t="n">
-        <v>36.16</v>
+        <v>33.75</v>
       </c>
       <c r="G6" t="n">
-        <v>27.62</v>
+        <v>25.64</v>
       </c>
       <c r="H6" t="n">
-        <v>201</v>
+        <v>337.3</v>
       </c>
       <c r="I6" t="n">
-        <v>153.7</v>
+        <v>257.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.63</v>
+        <v>3.44</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="L6" t="n">
-        <v>10.95</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>8.369999999999999</v>
+        <v>6.46</v>
       </c>
       <c r="N6" t="n">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>334.78</v>
+        <v>338.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>255.88</v>
+        <v>257.61</v>
       </c>
       <c r="R6" t="n">
-        <v>186.24</v>
+        <v>188.22</v>
       </c>
       <c r="S6" t="n">
-        <v>325.65</v>
+        <v>327.09</v>
       </c>
       <c r="T6" t="n">
-        <v>246.92</v>
+        <v>244.32</v>
       </c>
       <c r="U6" t="n">
-        <v>8.960000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -894,70 +894,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3986.1</v>
+        <v>4553</v>
       </c>
       <c r="E7" t="n">
-        <v>3056.4</v>
+        <v>3483.2</v>
       </c>
       <c r="F7" t="n">
-        <v>26.27</v>
+        <v>36.16</v>
       </c>
       <c r="G7" t="n">
-        <v>20.16</v>
+        <v>27.62</v>
       </c>
       <c r="H7" t="n">
-        <v>552.8</v>
+        <v>201</v>
       </c>
       <c r="I7" t="n">
-        <v>424.2</v>
+        <v>153.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4.88</v>
+        <v>2.63</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>11.15</v>
+        <v>10.95</v>
       </c>
       <c r="M7" t="n">
-        <v>8.529999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>4.11</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="P7" t="n">
-        <v>318.56</v>
+        <v>334.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>244.48</v>
+        <v>255.88</v>
       </c>
       <c r="R7" t="n">
-        <v>174.31</v>
+        <v>186.24</v>
       </c>
       <c r="S7" t="n">
-        <v>314.28</v>
+        <v>325.65</v>
       </c>
       <c r="T7" t="n">
-        <v>257.25</v>
+        <v>246.92</v>
       </c>
       <c r="U7" t="n">
-        <v>-12.77</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -965,70 +965,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Drake Maye</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4268.7</v>
+        <v>3986.1</v>
       </c>
       <c r="E8" t="n">
-        <v>3245.6</v>
+        <v>3056.4</v>
       </c>
       <c r="F8" t="n">
-        <v>30.65</v>
+        <v>26.27</v>
       </c>
       <c r="G8" t="n">
-        <v>23.4</v>
+        <v>20.16</v>
       </c>
       <c r="H8" t="n">
-        <v>287.5</v>
+        <v>552.8</v>
       </c>
       <c r="I8" t="n">
-        <v>220.8</v>
+        <v>424.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.07</v>
+        <v>4.88</v>
       </c>
       <c r="K8" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>8.02</v>
+        <v>11.15</v>
       </c>
       <c r="M8" t="n">
-        <v>6.13</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N8" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="O8" t="n">
         <v>3.14</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.4</v>
-      </c>
       <c r="P8" t="n">
-        <v>318.2</v>
+        <v>318.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>242.6</v>
+        <v>244.48</v>
       </c>
       <c r="R8" t="n">
-        <v>172.93</v>
+        <v>174.31</v>
       </c>
       <c r="S8" t="n">
-        <v>311.98</v>
+        <v>314.28</v>
       </c>
       <c r="T8" t="n">
-        <v>233.62</v>
+        <v>257.25</v>
       </c>
       <c r="U8" t="n">
-        <v>8.98</v>
+        <v>-12.77</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
@@ -1036,70 +1036,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4437.6</v>
+        <v>4268.7</v>
       </c>
       <c r="E9" t="n">
-        <v>3399.2</v>
+        <v>3245.6</v>
       </c>
       <c r="F9" t="n">
-        <v>33.3</v>
+        <v>30.65</v>
       </c>
       <c r="G9" t="n">
-        <v>25.49</v>
+        <v>23.4</v>
       </c>
       <c r="H9" t="n">
-        <v>159.8</v>
+        <v>287.5</v>
       </c>
       <c r="I9" t="n">
-        <v>122.7</v>
+        <v>220.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.28</v>
+        <v>3.07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="L9" t="n">
-        <v>10.48</v>
+        <v>8.02</v>
       </c>
       <c r="M9" t="n">
-        <v>8.02</v>
+        <v>6.13</v>
       </c>
       <c r="N9" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>312.94</v>
+        <v>318.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>239.78</v>
+        <v>242.6</v>
       </c>
       <c r="R9" t="n">
-        <v>171.34</v>
+        <v>172.93</v>
       </c>
       <c r="S9" t="n">
-        <v>309.39</v>
+        <v>311.98</v>
       </c>
       <c r="T9" t="n">
-        <v>253.88</v>
+        <v>233.62</v>
       </c>
       <c r="U9" t="n">
-        <v>-14.1</v>
+        <v>8.98</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -1107,70 +1107,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4571.4</v>
+        <v>4437.6</v>
       </c>
       <c r="E10" t="n">
-        <v>3495</v>
+        <v>3399.2</v>
       </c>
       <c r="F10" t="n">
-        <v>36.09</v>
+        <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>28.04</v>
+        <v>25.49</v>
       </c>
       <c r="H10" t="n">
-        <v>42.9</v>
+        <v>159.8</v>
       </c>
       <c r="I10" t="n">
-        <v>33.5</v>
+        <v>122.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>1.76</v>
       </c>
       <c r="L10" t="n">
-        <v>13.58</v>
+        <v>10.48</v>
       </c>
       <c r="M10" t="n">
-        <v>10.38</v>
+        <v>8.02</v>
       </c>
       <c r="N10" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="O10" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="P10" t="n">
-        <v>306.31</v>
+        <v>312.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>236.09</v>
+        <v>239.78</v>
       </c>
       <c r="R10" t="n">
-        <v>177.87</v>
+        <v>171.34</v>
       </c>
       <c r="S10" t="n">
-        <v>306.07</v>
+        <v>309.39</v>
       </c>
       <c r="T10" t="n">
-        <v>223.45</v>
+        <v>253.88</v>
       </c>
       <c r="U10" t="n">
-        <v>12.64</v>
+        <v>-14.1</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -1178,70 +1178,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4008.4</v>
+        <v>4571.4</v>
       </c>
       <c r="E11" t="n">
-        <v>3072.1</v>
+        <v>3495</v>
       </c>
       <c r="F11" t="n">
-        <v>31.11</v>
+        <v>36.09</v>
       </c>
       <c r="G11" t="n">
-        <v>23.71</v>
+        <v>28.04</v>
       </c>
       <c r="H11" t="n">
-        <v>282</v>
+        <v>42.9</v>
       </c>
       <c r="I11" t="n">
-        <v>216.3</v>
+        <v>33.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.73</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.87</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>11.95</v>
+        <v>13.58</v>
       </c>
       <c r="M11" t="n">
-        <v>9.140000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
-        <v>2.86</v>
+        <v>2.23</v>
       </c>
       <c r="P11" t="n">
-        <v>303.98</v>
+        <v>306.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>232.57</v>
+        <v>236.09</v>
       </c>
       <c r="R11" t="n">
-        <v>163.02</v>
+        <v>177.87</v>
       </c>
       <c r="S11" t="n">
-        <v>302.55</v>
+        <v>306.07</v>
       </c>
       <c r="T11" t="n">
-        <v>246.62</v>
+        <v>223.45</v>
       </c>
       <c r="U11" t="n">
-        <v>-14.05</v>
+        <v>12.64</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1249,70 +1249,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4185.4</v>
+        <v>4008.4</v>
       </c>
       <c r="E12" t="n">
-        <v>3189</v>
+        <v>3072.1</v>
       </c>
       <c r="F12" t="n">
-        <v>26.32</v>
+        <v>31.11</v>
       </c>
       <c r="G12" t="n">
-        <v>20.06</v>
+        <v>23.71</v>
       </c>
       <c r="H12" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I12" t="n">
-        <v>222.4</v>
+        <v>216.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="K12" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="L12" t="n">
-        <v>11.67</v>
+        <v>11.95</v>
       </c>
       <c r="M12" t="n">
-        <v>8.93</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>4.43</v>
+        <v>3.74</v>
       </c>
       <c r="O12" t="n">
-        <v>3.38</v>
+        <v>2.86</v>
       </c>
       <c r="P12" t="n">
-        <v>291.1</v>
+        <v>303.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>221.98</v>
+        <v>232.57</v>
       </c>
       <c r="R12" t="n">
-        <v>152.78</v>
+        <v>163.02</v>
       </c>
       <c r="S12" t="n">
-        <v>291.4</v>
+        <v>302.55</v>
       </c>
       <c r="T12" t="n">
-        <v>222.53</v>
+        <v>246.62</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.55</v>
+        <v>-14.05</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -1320,70 +1320,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3735.3</v>
+        <v>4185.4</v>
       </c>
       <c r="E13" t="n">
-        <v>2403.8</v>
+        <v>3189</v>
       </c>
       <c r="F13" t="n">
-        <v>24.96</v>
+        <v>26.32</v>
       </c>
       <c r="G13" t="n">
-        <v>16.02</v>
+        <v>20.06</v>
       </c>
       <c r="H13" t="n">
-        <v>812.5</v>
+        <v>290</v>
       </c>
       <c r="I13" t="n">
-        <v>526.9</v>
+        <v>222.4</v>
       </c>
       <c r="J13" t="n">
-        <v>6.03</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="L13" t="n">
-        <v>8.960000000000001</v>
+        <v>11.67</v>
       </c>
       <c r="M13" t="n">
-        <v>5.79</v>
+        <v>8.93</v>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>4.43</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>3.38</v>
       </c>
       <c r="P13" t="n">
-        <v>344.42</v>
+        <v>291.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>221.92</v>
+        <v>221.98</v>
       </c>
       <c r="R13" t="n">
-        <v>163.23</v>
+        <v>152.78</v>
       </c>
       <c r="S13" t="n">
-        <v>280.01</v>
+        <v>291.4</v>
       </c>
       <c r="T13" t="n">
-        <v>252.43</v>
+        <v>222.53</v>
       </c>
       <c r="U13" t="n">
-        <v>-30.51</v>
+        <v>-0.55</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -2949,64 +2949,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3675.1</v>
+        <v>3197.9</v>
       </c>
       <c r="E36" t="n">
-        <v>437.5</v>
+        <v>378.5</v>
       </c>
       <c r="F36" t="n">
-        <v>24.65</v>
+        <v>14.54</v>
       </c>
       <c r="G36" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="H36" t="n">
-        <v>581.1</v>
+        <v>221.2</v>
       </c>
       <c r="I36" t="n">
-        <v>68.09999999999999</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="L36" t="n">
-        <v>14.5</v>
+        <v>15.18</v>
       </c>
       <c r="M36" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="N36" t="n">
-        <v>3.64</v>
+        <v>5.29</v>
       </c>
       <c r="O36" t="n">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="P36" t="n">
-        <v>289.39</v>
+        <v>191.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>34.19</v>
+        <v>22.92</v>
       </c>
       <c r="R36" t="n">
-        <v>23.42</v>
+        <v>12.04</v>
       </c>
       <c r="S36" t="n">
-        <v>44.97</v>
+        <v>33.82</v>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -3016,64 +3016,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3197.9</v>
+        <v>3334.1</v>
       </c>
       <c r="E37" t="n">
-        <v>378.5</v>
+        <v>201.5</v>
       </c>
       <c r="F37" t="n">
-        <v>14.54</v>
+        <v>16.68</v>
       </c>
       <c r="G37" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="H37" t="n">
-        <v>221.2</v>
+        <v>269.5</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>15.4</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="K37" t="n">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="L37" t="n">
-        <v>15.18</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>1.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>5.29</v>
+        <v>2.44</v>
       </c>
       <c r="O37" t="n">
-        <v>0.63</v>
+        <v>0.14</v>
       </c>
       <c r="P37" t="n">
-        <v>191.26</v>
+        <v>221.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>22.92</v>
+        <v>13.4</v>
       </c>
       <c r="R37" t="n">
-        <v>12.04</v>
+        <v>7.9</v>
       </c>
       <c r="S37" t="n">
-        <v>33.82</v>
+        <v>18.87</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3083,64 +3083,64 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3334.1</v>
+        <v>3496</v>
       </c>
       <c r="E38" t="n">
-        <v>201.5</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>16.68</v>
+        <v>17.14</v>
       </c>
       <c r="G38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>269.5</v>
+        <v>828.8</v>
       </c>
       <c r="I38" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>3.12</v>
+        <v>7.93</v>
       </c>
       <c r="K38" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>9.460000000000001</v>
+        <v>13.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.44</v>
+        <v>4.31</v>
       </c>
       <c r="O38" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>221.95</v>
+        <v>303.12</v>
       </c>
       <c r="Q38" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>18.87</v>
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -3150,55 +3150,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3496</v>
+        <v>3245.4</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>17.14</v>
+        <v>14.43</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>828.8</v>
+        <v>188.6</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>7.93</v>
+        <v>3.08</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>13.56</v>
+        <v>17.41</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.31</v>
+        <v>3.71</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>303.12</v>
+        <v>182.64</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3209,63 +3209,67 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-18.35</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3245.4</v>
+        <v>3444.7</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>14.43</v>
+        <v>21.78</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>188.6</v>
+        <v>230.9</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3.08</v>
+        <v>2.17</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>17.41</v>
+        <v>12.09</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>182.64</v>
+        <v>229.88</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3276,67 +3280,63 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="U40" t="n">
-        <v>-18.35</v>
-      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3444.7</v>
+        <v>3597.8</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>21.78</v>
+        <v>20.69</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>230.9</v>
+        <v>142.3</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>12.09</v>
+        <v>12.54</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.48</v>
+        <v>3.31</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>229.88</v>
+        <v>220.66</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3355,55 +3355,55 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3597.8</v>
+        <v>3429.8</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>20.69</v>
+        <v>19.19</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>142.3</v>
+        <v>261.6</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.91</v>
+        <v>2.67</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>12.54</v>
+        <v>11.07</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.31</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>220.66</v>
+        <v>228.69</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3422,55 +3422,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3429.8</v>
+        <v>3394</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>19.19</v>
+        <v>15.58</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>261.6</v>
+        <v>110</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2.67</v>
+        <v>1.83</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>11.07</v>
+        <v>10.37</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>228.69</v>
+        <v>192.52</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3489,55 +3489,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3394</v>
+        <v>3465.6</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>15.58</v>
+        <v>16.89</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>110</v>
+        <v>272.3</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1.83</v>
+        <v>3.77</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>10.37</v>
+        <v>10.99</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>4.22</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>192.52</v>
+        <v>225.61</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3548,63 +3548,67 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-22.71</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3465.6</v>
+        <v>3722.3</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>16.89</v>
+        <v>18.82</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>272.3</v>
+        <v>322.8</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3.77</v>
+        <v>2.33</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>10.99</v>
+        <v>10.91</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.22</v>
+        <v>3.09</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>225.61</v>
+        <v>242.43</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3615,67 +3619,63 @@
       <c r="S45" t="n">
         <v>0</v>
       </c>
-      <c r="T45" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="U45" t="n">
-        <v>-22.71</v>
-      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3722.3</v>
+        <v>3623.4</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>18.82</v>
+        <v>25.51</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>322.8</v>
+        <v>33.3</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.91</v>
+        <v>11.45</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.09</v>
+        <v>3.51</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>242.43</v>
+        <v>230.89</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3694,55 +3694,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3623.4</v>
+        <v>3454.9</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>25.51</v>
+        <v>17.97</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>33.3</v>
+        <v>550.7</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1.75</v>
+        <v>4.93</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>11.45</v>
+        <v>11.1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>230.89</v>
+        <v>265.93</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3761,55 +3761,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3454.9</v>
+        <v>3282.8</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>17.97</v>
+        <v>18.4</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>550.7</v>
+        <v>840.9</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4.93</v>
+        <v>7.25</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>11.1</v>
+        <v>8.76</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>265.93</v>
+        <v>307.9</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3828,55 +3828,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3282.8</v>
+        <v>3364.3</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>18.4</v>
+        <v>16.39</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>840.9</v>
+        <v>188.9</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>7.25</v>
+        <v>1.88</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>8.76</v>
+        <v>11.86</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.54</v>
+        <v>3.23</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>307.9</v>
+        <v>200.12</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3895,55 +3895,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3364.3</v>
+        <v>3479.9</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>16.39</v>
+        <v>18.11</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>188.9</v>
+        <v>182.6</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>11.86</v>
+        <v>13.28</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.23</v>
+        <v>3.39</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>200.12</v>
+        <v>211.56</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3962,55 +3962,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3479.9</v>
+        <v>3223.8</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>18.11</v>
+        <v>14.1</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>182.6</v>
+        <v>182.7</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>2.5</v>
+        <v>3.09</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>13.28</v>
+        <v>17.31</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.39</v>
+        <v>3.72</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>211.56</v>
+        <v>180.1</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4029,55 +4029,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3223.8</v>
+        <v>3652</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>14.1</v>
+        <v>22.6</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>182.7</v>
+        <v>175.8</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>3.09</v>
+        <v>2.16</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>17.31</v>
+        <v>10.67</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.72</v>
+        <v>2.59</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>180.1</v>
+        <v>240.5</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4096,55 +4096,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3652</v>
+        <v>3675.1</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>22.6</v>
+        <v>24.65</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>175.8</v>
+        <v>581.1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>2.16</v>
+        <v>3.66</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10.67</v>
+        <v>14.5</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.59</v>
+        <v>3.64</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>240.5</v>
+        <v>289.39</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -5244,70 +5244,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3752.8</v>
+        <v>3735.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2872.5</v>
+        <v>2848.3</v>
       </c>
       <c r="F4" t="n">
-        <v>27.65</v>
+        <v>24.96</v>
       </c>
       <c r="G4" t="n">
-        <v>21.05</v>
+        <v>19.03</v>
       </c>
       <c r="H4" t="n">
-        <v>651.9</v>
+        <v>812.5</v>
       </c>
       <c r="I4" t="n">
-        <v>499.5</v>
+        <v>622.2</v>
       </c>
       <c r="J4" t="n">
-        <v>5.67</v>
+        <v>6.03</v>
       </c>
       <c r="K4" t="n">
-        <v>4.35</v>
+        <v>4.61</v>
       </c>
       <c r="L4" t="n">
-        <v>7.93</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>6.06</v>
+        <v>6.85</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>2.17</v>
       </c>
       <c r="O4" t="n">
-        <v>2.33</v>
+        <v>1.66</v>
       </c>
       <c r="P4" t="n">
-        <v>337.96</v>
+        <v>344.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>258.37</v>
+        <v>262.91</v>
       </c>
       <c r="R4" t="n">
-        <v>188.54</v>
+        <v>193.38</v>
       </c>
       <c r="S4" t="n">
-        <v>327.96</v>
+        <v>331.73</v>
       </c>
       <c r="T4" t="n">
-        <v>251.97</v>
+        <v>252.43</v>
       </c>
       <c r="U4" t="n">
-        <v>6.4</v>
+        <v>10.48</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -5315,70 +5315,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4289.6</v>
+        <v>3752.8</v>
       </c>
       <c r="E5" t="n">
-        <v>3267.6</v>
+        <v>2872.5</v>
       </c>
       <c r="F5" t="n">
-        <v>33.75</v>
+        <v>27.65</v>
       </c>
       <c r="G5" t="n">
-        <v>25.64</v>
+        <v>21.05</v>
       </c>
       <c r="H5" t="n">
-        <v>337.3</v>
+        <v>651.9</v>
       </c>
       <c r="I5" t="n">
-        <v>257.7</v>
+        <v>499.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.44</v>
+        <v>5.67</v>
       </c>
       <c r="K5" t="n">
-        <v>2.65</v>
+        <v>4.35</v>
       </c>
       <c r="L5" t="n">
-        <v>8.449999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="M5" t="n">
-        <v>6.46</v>
+        <v>6.06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>338.31</v>
+        <v>337.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>257.61</v>
+        <v>258.37</v>
       </c>
       <c r="R5" t="n">
-        <v>188.22</v>
+        <v>188.54</v>
       </c>
       <c r="S5" t="n">
-        <v>327.09</v>
+        <v>327.96</v>
       </c>
       <c r="T5" t="n">
-        <v>244.32</v>
+        <v>251.97</v>
       </c>
       <c r="U5" t="n">
-        <v>13.29</v>
+        <v>6.4</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -5386,70 +5386,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4553</v>
+        <v>4289.6</v>
       </c>
       <c r="E6" t="n">
-        <v>3483.2</v>
+        <v>3267.6</v>
       </c>
       <c r="F6" t="n">
-        <v>36.16</v>
+        <v>33.75</v>
       </c>
       <c r="G6" t="n">
-        <v>27.62</v>
+        <v>25.64</v>
       </c>
       <c r="H6" t="n">
-        <v>201</v>
+        <v>337.3</v>
       </c>
       <c r="I6" t="n">
-        <v>153.7</v>
+        <v>257.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.63</v>
+        <v>3.44</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="L6" t="n">
-        <v>10.95</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>8.369999999999999</v>
+        <v>6.46</v>
       </c>
       <c r="N6" t="n">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>334.78</v>
+        <v>338.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>255.88</v>
+        <v>257.61</v>
       </c>
       <c r="R6" t="n">
-        <v>186.24</v>
+        <v>188.22</v>
       </c>
       <c r="S6" t="n">
-        <v>325.65</v>
+        <v>327.09</v>
       </c>
       <c r="T6" t="n">
-        <v>246.92</v>
+        <v>244.32</v>
       </c>
       <c r="U6" t="n">
-        <v>8.960000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -5457,70 +5457,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3986.1</v>
+        <v>4553</v>
       </c>
       <c r="E7" t="n">
-        <v>3056.4</v>
+        <v>3483.2</v>
       </c>
       <c r="F7" t="n">
-        <v>26.27</v>
+        <v>36.16</v>
       </c>
       <c r="G7" t="n">
-        <v>20.16</v>
+        <v>27.62</v>
       </c>
       <c r="H7" t="n">
-        <v>552.8</v>
+        <v>201</v>
       </c>
       <c r="I7" t="n">
-        <v>424.2</v>
+        <v>153.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4.88</v>
+        <v>2.63</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>11.15</v>
+        <v>10.95</v>
       </c>
       <c r="M7" t="n">
-        <v>8.529999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>4.11</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="P7" t="n">
-        <v>318.56</v>
+        <v>334.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>244.48</v>
+        <v>255.88</v>
       </c>
       <c r="R7" t="n">
-        <v>174.31</v>
+        <v>186.24</v>
       </c>
       <c r="S7" t="n">
-        <v>314.28</v>
+        <v>325.65</v>
       </c>
       <c r="T7" t="n">
-        <v>257.25</v>
+        <v>246.92</v>
       </c>
       <c r="U7" t="n">
-        <v>-12.77</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -5528,70 +5528,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Drake Maye</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4268.7</v>
+        <v>3986.1</v>
       </c>
       <c r="E8" t="n">
-        <v>3245.6</v>
+        <v>3056.4</v>
       </c>
       <c r="F8" t="n">
-        <v>30.65</v>
+        <v>26.27</v>
       </c>
       <c r="G8" t="n">
-        <v>23.4</v>
+        <v>20.16</v>
       </c>
       <c r="H8" t="n">
-        <v>287.5</v>
+        <v>552.8</v>
       </c>
       <c r="I8" t="n">
-        <v>220.8</v>
+        <v>424.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.07</v>
+        <v>4.88</v>
       </c>
       <c r="K8" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>8.02</v>
+        <v>11.15</v>
       </c>
       <c r="M8" t="n">
-        <v>6.13</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N8" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="O8" t="n">
         <v>3.14</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.4</v>
-      </c>
       <c r="P8" t="n">
-        <v>318.2</v>
+        <v>318.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>242.6</v>
+        <v>244.48</v>
       </c>
       <c r="R8" t="n">
-        <v>172.93</v>
+        <v>174.31</v>
       </c>
       <c r="S8" t="n">
-        <v>311.98</v>
+        <v>314.28</v>
       </c>
       <c r="T8" t="n">
-        <v>233.62</v>
+        <v>257.25</v>
       </c>
       <c r="U8" t="n">
-        <v>8.98</v>
+        <v>-12.77</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
@@ -5599,70 +5599,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4437.6</v>
+        <v>4268.7</v>
       </c>
       <c r="E9" t="n">
-        <v>3399.2</v>
+        <v>3245.6</v>
       </c>
       <c r="F9" t="n">
-        <v>33.3</v>
+        <v>30.65</v>
       </c>
       <c r="G9" t="n">
-        <v>25.49</v>
+        <v>23.4</v>
       </c>
       <c r="H9" t="n">
-        <v>159.8</v>
+        <v>287.5</v>
       </c>
       <c r="I9" t="n">
-        <v>122.7</v>
+        <v>220.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.28</v>
+        <v>3.07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="L9" t="n">
-        <v>10.48</v>
+        <v>8.02</v>
       </c>
       <c r="M9" t="n">
-        <v>8.02</v>
+        <v>6.13</v>
       </c>
       <c r="N9" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>312.94</v>
+        <v>318.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>239.78</v>
+        <v>242.6</v>
       </c>
       <c r="R9" t="n">
-        <v>171.34</v>
+        <v>172.93</v>
       </c>
       <c r="S9" t="n">
-        <v>309.39</v>
+        <v>311.98</v>
       </c>
       <c r="T9" t="n">
-        <v>253.88</v>
+        <v>233.62</v>
       </c>
       <c r="U9" t="n">
-        <v>-14.1</v>
+        <v>8.98</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -5670,70 +5670,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4571.4</v>
+        <v>4437.6</v>
       </c>
       <c r="E10" t="n">
-        <v>3495</v>
+        <v>3399.2</v>
       </c>
       <c r="F10" t="n">
-        <v>36.09</v>
+        <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>28.04</v>
+        <v>25.49</v>
       </c>
       <c r="H10" t="n">
-        <v>42.9</v>
+        <v>159.8</v>
       </c>
       <c r="I10" t="n">
-        <v>33.5</v>
+        <v>122.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>1.76</v>
       </c>
       <c r="L10" t="n">
-        <v>13.58</v>
+        <v>10.48</v>
       </c>
       <c r="M10" t="n">
-        <v>10.38</v>
+        <v>8.02</v>
       </c>
       <c r="N10" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="O10" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="P10" t="n">
-        <v>306.31</v>
+        <v>312.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>236.09</v>
+        <v>239.78</v>
       </c>
       <c r="R10" t="n">
-        <v>177.87</v>
+        <v>171.34</v>
       </c>
       <c r="S10" t="n">
-        <v>306.07</v>
+        <v>309.39</v>
       </c>
       <c r="T10" t="n">
-        <v>223.45</v>
+        <v>253.88</v>
       </c>
       <c r="U10" t="n">
-        <v>12.64</v>
+        <v>-14.1</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -5741,70 +5741,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4008.4</v>
+        <v>4571.4</v>
       </c>
       <c r="E11" t="n">
-        <v>3072.1</v>
+        <v>3495</v>
       </c>
       <c r="F11" t="n">
-        <v>31.11</v>
+        <v>36.09</v>
       </c>
       <c r="G11" t="n">
-        <v>23.71</v>
+        <v>28.04</v>
       </c>
       <c r="H11" t="n">
-        <v>282</v>
+        <v>42.9</v>
       </c>
       <c r="I11" t="n">
-        <v>216.3</v>
+        <v>33.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.73</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.87</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>11.95</v>
+        <v>13.58</v>
       </c>
       <c r="M11" t="n">
-        <v>9.140000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
-        <v>2.86</v>
+        <v>2.23</v>
       </c>
       <c r="P11" t="n">
-        <v>303.98</v>
+        <v>306.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>232.57</v>
+        <v>236.09</v>
       </c>
       <c r="R11" t="n">
-        <v>163.02</v>
+        <v>177.87</v>
       </c>
       <c r="S11" t="n">
-        <v>302.55</v>
+        <v>306.07</v>
       </c>
       <c r="T11" t="n">
-        <v>246.62</v>
+        <v>223.45</v>
       </c>
       <c r="U11" t="n">
-        <v>-14.05</v>
+        <v>12.64</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -5812,70 +5812,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4185.4</v>
+        <v>4008.4</v>
       </c>
       <c r="E12" t="n">
-        <v>3189</v>
+        <v>3072.1</v>
       </c>
       <c r="F12" t="n">
-        <v>26.32</v>
+        <v>31.11</v>
       </c>
       <c r="G12" t="n">
-        <v>20.06</v>
+        <v>23.71</v>
       </c>
       <c r="H12" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I12" t="n">
-        <v>222.4</v>
+        <v>216.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="K12" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="L12" t="n">
-        <v>11.67</v>
+        <v>11.95</v>
       </c>
       <c r="M12" t="n">
-        <v>8.93</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>4.43</v>
+        <v>3.74</v>
       </c>
       <c r="O12" t="n">
-        <v>3.38</v>
+        <v>2.86</v>
       </c>
       <c r="P12" t="n">
-        <v>291.1</v>
+        <v>303.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>221.98</v>
+        <v>232.57</v>
       </c>
       <c r="R12" t="n">
-        <v>152.78</v>
+        <v>163.02</v>
       </c>
       <c r="S12" t="n">
-        <v>291.4</v>
+        <v>302.55</v>
       </c>
       <c r="T12" t="n">
-        <v>222.53</v>
+        <v>246.62</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.55</v>
+        <v>-14.05</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -5883,70 +5883,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3735.3</v>
+        <v>4185.4</v>
       </c>
       <c r="E13" t="n">
-        <v>2403.8</v>
+        <v>3189</v>
       </c>
       <c r="F13" t="n">
-        <v>24.96</v>
+        <v>26.32</v>
       </c>
       <c r="G13" t="n">
-        <v>16.02</v>
+        <v>20.06</v>
       </c>
       <c r="H13" t="n">
-        <v>812.5</v>
+        <v>290</v>
       </c>
       <c r="I13" t="n">
-        <v>526.9</v>
+        <v>222.4</v>
       </c>
       <c r="J13" t="n">
-        <v>6.03</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="L13" t="n">
-        <v>8.960000000000001</v>
+        <v>11.67</v>
       </c>
       <c r="M13" t="n">
-        <v>5.79</v>
+        <v>8.93</v>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>4.43</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>3.38</v>
       </c>
       <c r="P13" t="n">
-        <v>344.42</v>
+        <v>291.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>221.92</v>
+        <v>221.98</v>
       </c>
       <c r="R13" t="n">
-        <v>163.23</v>
+        <v>152.78</v>
       </c>
       <c r="S13" t="n">
-        <v>280.01</v>
+        <v>291.4</v>
       </c>
       <c r="T13" t="n">
-        <v>252.43</v>
+        <v>222.53</v>
       </c>
       <c r="U13" t="n">
-        <v>-30.51</v>
+        <v>-0.55</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -7643,64 +7643,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3675.1</v>
+        <v>3197.9</v>
       </c>
       <c r="E4" t="n">
-        <v>437.5</v>
+        <v>378.5</v>
       </c>
       <c r="F4" t="n">
-        <v>24.65</v>
+        <v>14.54</v>
       </c>
       <c r="G4" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>581.1</v>
+        <v>221.2</v>
       </c>
       <c r="I4" t="n">
-        <v>68.09999999999999</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="L4" t="n">
-        <v>14.5</v>
+        <v>15.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="N4" t="n">
-        <v>3.64</v>
+        <v>5.29</v>
       </c>
       <c r="O4" t="n">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="P4" t="n">
-        <v>289.39</v>
+        <v>191.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>34.19</v>
+        <v>22.92</v>
       </c>
       <c r="R4" t="n">
-        <v>23.42</v>
+        <v>12.04</v>
       </c>
       <c r="S4" t="n">
-        <v>44.97</v>
+        <v>33.82</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -7710,64 +7710,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3197.9</v>
+        <v>3334.1</v>
       </c>
       <c r="E5" t="n">
-        <v>378.5</v>
+        <v>201.5</v>
       </c>
       <c r="F5" t="n">
-        <v>14.54</v>
+        <v>16.68</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="H5" t="n">
-        <v>221.2</v>
+        <v>269.5</v>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>15.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="K5" t="n">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="L5" t="n">
-        <v>15.18</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>1.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>5.29</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>0.63</v>
+        <v>0.14</v>
       </c>
       <c r="P5" t="n">
-        <v>191.26</v>
+        <v>221.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.92</v>
+        <v>13.4</v>
       </c>
       <c r="R5" t="n">
-        <v>12.04</v>
+        <v>7.9</v>
       </c>
       <c r="S5" t="n">
-        <v>33.82</v>
+        <v>18.87</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -7777,64 +7777,64 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3334.1</v>
+        <v>3496</v>
       </c>
       <c r="E6" t="n">
-        <v>201.5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>16.68</v>
+        <v>17.14</v>
       </c>
       <c r="G6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>269.5</v>
+        <v>828.8</v>
       </c>
       <c r="I6" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.12</v>
+        <v>7.93</v>
       </c>
       <c r="K6" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9.460000000000001</v>
+        <v>13.56</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.44</v>
+        <v>4.31</v>
       </c>
       <c r="O6" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>221.95</v>
+        <v>303.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>18.87</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -7844,55 +7844,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3496</v>
+        <v>3245.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>17.14</v>
+        <v>14.43</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>828.8</v>
+        <v>188.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7.93</v>
+        <v>3.08</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13.56</v>
+        <v>17.41</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.31</v>
+        <v>3.71</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>303.12</v>
+        <v>182.64</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -7903,63 +7903,67 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-18.35</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3245.4</v>
+        <v>3444.7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>14.43</v>
+        <v>21.78</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>188.6</v>
+        <v>230.9</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.08</v>
+        <v>2.17</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17.41</v>
+        <v>12.09</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>182.64</v>
+        <v>229.88</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -7970,67 +7974,63 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-18.35</v>
-      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3444.7</v>
+        <v>3597.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>21.78</v>
+        <v>20.69</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>230.9</v>
+        <v>142.3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>12.09</v>
+        <v>12.54</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.48</v>
+        <v>3.31</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>229.88</v>
+        <v>220.66</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8049,55 +8049,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3597.8</v>
+        <v>3429.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>20.69</v>
+        <v>19.19</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>142.3</v>
+        <v>261.6</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.91</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12.54</v>
+        <v>11.07</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.31</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>220.66</v>
+        <v>228.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8116,55 +8116,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3429.8</v>
+        <v>3394</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>19.19</v>
+        <v>15.58</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>261.6</v>
+        <v>110</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67</v>
+        <v>1.83</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11.07</v>
+        <v>10.37</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>228.69</v>
+        <v>192.52</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8183,55 +8183,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3394</v>
+        <v>3465.6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>15.58</v>
+        <v>16.89</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>110</v>
+        <v>272.3</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.83</v>
+        <v>3.77</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10.37</v>
+        <v>10.99</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>4.22</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>192.52</v>
+        <v>225.61</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8242,63 +8242,67 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-22.71</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3465.6</v>
+        <v>3722.3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>16.89</v>
+        <v>18.82</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>272.3</v>
+        <v>322.8</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.77</v>
+        <v>2.33</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.99</v>
+        <v>10.91</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.22</v>
+        <v>3.09</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>225.61</v>
+        <v>242.43</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8309,67 +8313,63 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-22.71</v>
-      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3722.3</v>
+        <v>3623.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>18.82</v>
+        <v>25.51</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>322.8</v>
+        <v>33.3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10.91</v>
+        <v>11.45</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.09</v>
+        <v>3.51</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>242.43</v>
+        <v>230.89</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8388,55 +8388,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3623.4</v>
+        <v>3454.9</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>25.51</v>
+        <v>17.97</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>33.3</v>
+        <v>550.7</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.75</v>
+        <v>4.93</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>11.45</v>
+        <v>11.1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>230.89</v>
+        <v>265.93</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8455,55 +8455,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3454.9</v>
+        <v>3282.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>17.97</v>
+        <v>18.4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>550.7</v>
+        <v>840.9</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.93</v>
+        <v>7.25</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>11.1</v>
+        <v>8.76</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>265.93</v>
+        <v>307.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -8522,55 +8522,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3282.8</v>
+        <v>3364.3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>18.4</v>
+        <v>16.39</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>840.9</v>
+        <v>188.9</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7.25</v>
+        <v>1.88</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8.76</v>
+        <v>11.86</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.54</v>
+        <v>3.23</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>307.9</v>
+        <v>200.12</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -8589,55 +8589,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3364.3</v>
+        <v>3479.9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>16.39</v>
+        <v>18.11</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>188.9</v>
+        <v>182.6</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>11.86</v>
+        <v>13.28</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.23</v>
+        <v>3.39</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>200.12</v>
+        <v>211.56</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -8656,55 +8656,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3479.9</v>
+        <v>3223.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>18.11</v>
+        <v>14.1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>182.6</v>
+        <v>182.7</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>3.09</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>13.28</v>
+        <v>17.31</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.39</v>
+        <v>3.72</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>211.56</v>
+        <v>180.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -8723,55 +8723,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3223.8</v>
+        <v>3652</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>14.1</v>
+        <v>22.6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>182.7</v>
+        <v>175.8</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.09</v>
+        <v>2.16</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>17.31</v>
+        <v>10.67</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.72</v>
+        <v>2.59</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>180.1</v>
+        <v>240.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -8790,55 +8790,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3652</v>
+        <v>3675.1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>22.6</v>
+        <v>24.65</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>175.8</v>
+        <v>581.1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.16</v>
+        <v>3.66</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>10.67</v>
+        <v>14.5</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.59</v>
+        <v>3.64</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>240.5</v>
+        <v>289.39</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -30405,67 +30405,67 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>0</v>
+        <v>222.133</v>
       </c>
       <c r="I223" t="n">
-        <v>0</v>
+        <v>1.501</v>
       </c>
       <c r="J223" t="n">
-        <v>0</v>
+        <v>47.942</v>
       </c>
       <c r="K223" t="n">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>129.014</v>
       </c>
       <c r="O223" t="n">
-        <v>0</v>
+        <v>315.254</v>
       </c>
       <c r="P223" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="Q223" t="n">
-        <v>0</v>
+        <v>2.906</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>27.05</v>
       </c>
       <c r="S223" t="n">
-        <v>0</v>
+        <v>68.83199999999999</v>
       </c>
       <c r="T223" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="U223" t="n">
-        <v>0</v>
+        <v>0.876</v>
       </c>
       <c r="V223" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="W223" t="n">
-        <v>0</v>
+        <v>1.663</v>
       </c>
       <c r="X223" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="Y223" t="n">
-        <v>0</v>
+        <v>0.724</v>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>20.521</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>5.914</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>35.917</v>
       </c>
       <c r="AC223" t="inlineStr"/>
     </row>
@@ -30498,67 +30498,67 @@
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>0</v>
+        <v>222.433</v>
       </c>
       <c r="I224" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="J224" t="n">
-        <v>0</v>
+        <v>47.372</v>
       </c>
       <c r="K224" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>0.527</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>129.314</v>
       </c>
       <c r="O224" t="n">
-        <v>0</v>
+        <v>315.554</v>
       </c>
       <c r="P224" t="n">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>26.48</v>
       </c>
       <c r="S224" t="n">
-        <v>0</v>
+        <v>68.262</v>
       </c>
       <c r="T224" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="U224" t="n">
-        <v>0</v>
+        <v>0.879</v>
       </c>
       <c r="V224" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="W224" t="n">
-        <v>0</v>
+        <v>1.663</v>
       </c>
       <c r="X224" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="Y224" t="n">
-        <v>0</v>
+        <v>0.724</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>20.51</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>5.881</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>35.909</v>
       </c>
       <c r="AC224" t="inlineStr"/>
     </row>
@@ -69093,67 +69093,67 @@
         <v>0</v>
       </c>
       <c r="H639" t="n">
-        <v>218.595</v>
+        <v>0</v>
       </c>
       <c r="I639" t="n">
-        <v>1.438</v>
+        <v>0</v>
       </c>
       <c r="J639" t="n">
-        <v>34.33</v>
+        <v>0</v>
       </c>
       <c r="K639" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>0.853</v>
+        <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="N639" t="n">
-        <v>125.475</v>
+        <v>0</v>
       </c>
       <c r="O639" t="n">
-        <v>311.715</v>
+        <v>0</v>
       </c>
       <c r="P639" t="n">
-        <v>0.498</v>
+        <v>0</v>
       </c>
       <c r="Q639" t="n">
-        <v>2.843</v>
+        <v>0</v>
       </c>
       <c r="R639" t="n">
-        <v>13.439</v>
+        <v>0</v>
       </c>
       <c r="S639" t="n">
-        <v>55.221</v>
+        <v>0</v>
       </c>
       <c r="T639" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="U639" t="n">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="V639" t="n">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="W639" t="n">
-        <v>1.989</v>
+        <v>0</v>
       </c>
       <c r="X639" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="Y639" t="n">
-        <v>0.8090000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z639" t="n">
-        <v>17.101</v>
+        <v>0</v>
       </c>
       <c r="AA639" t="n">
-        <v>3.209</v>
+        <v>0</v>
       </c>
       <c r="AB639" t="n">
-        <v>33.039</v>
+        <v>0</v>
       </c>
       <c r="AC639" t="inlineStr"/>
     </row>
@@ -69186,67 +69186,67 @@
         <v>0</v>
       </c>
       <c r="H640" t="n">
-        <v>218.896</v>
+        <v>0</v>
       </c>
       <c r="I640" t="n">
-        <v>1.443</v>
+        <v>0</v>
       </c>
       <c r="J640" t="n">
-        <v>33.76</v>
+        <v>0</v>
       </c>
       <c r="K640" t="n">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="L640" t="n">
-        <v>0.853</v>
+        <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="N640" t="n">
-        <v>125.775</v>
+        <v>0</v>
       </c>
       <c r="O640" t="n">
-        <v>312.015</v>
+        <v>0</v>
       </c>
       <c r="P640" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q640" t="n">
-        <v>2.848</v>
+        <v>0</v>
       </c>
       <c r="R640" t="n">
-        <v>12.869</v>
+        <v>0</v>
       </c>
       <c r="S640" t="n">
-        <v>54.651</v>
+        <v>0</v>
       </c>
       <c r="T640" t="n">
-        <v>0.076</v>
+        <v>0</v>
       </c>
       <c r="U640" t="n">
-        <v>0.739</v>
+        <v>0</v>
       </c>
       <c r="V640" t="n">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="W640" t="n">
-        <v>1.989</v>
+        <v>0</v>
       </c>
       <c r="X640" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="Y640" t="n">
-        <v>0.8090000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z640" t="n">
-        <v>17.096</v>
+        <v>0</v>
       </c>
       <c r="AA640" t="n">
-        <v>3.178</v>
+        <v>0</v>
       </c>
       <c r="AB640" t="n">
-        <v>33.033</v>
+        <v>0</v>
       </c>
       <c r="AC640" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -610,70 +610,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lamar Jackson</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3869.1</v>
+        <v>3729.7</v>
       </c>
       <c r="E3" t="n">
-        <v>2932.9</v>
+        <v>2842.8</v>
       </c>
       <c r="F3" t="n">
-        <v>29.79</v>
+        <v>24.96</v>
       </c>
       <c r="G3" t="n">
-        <v>22.61</v>
+        <v>19.03</v>
       </c>
       <c r="H3" t="n">
-        <v>770.8</v>
+        <v>812.5</v>
       </c>
       <c r="I3" t="n">
-        <v>590.1</v>
+        <v>622.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.31</v>
+        <v>6.03</v>
       </c>
       <c r="K3" t="n">
-        <v>3.33</v>
+        <v>4.61</v>
       </c>
       <c r="L3" t="n">
-        <v>7.88</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>6.02</v>
+        <v>6.85</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.17</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="P3" t="n">
-        <v>355.74</v>
+        <v>344.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>270.61</v>
+        <v>262.69</v>
       </c>
       <c r="R3" t="n">
-        <v>201.36</v>
+        <v>193.17</v>
       </c>
       <c r="S3" t="n">
-        <v>340</v>
+        <v>331.5</v>
       </c>
       <c r="T3" t="n">
-        <v>256.79</v>
+        <v>252.43</v>
       </c>
       <c r="U3" t="n">
-        <v>13.82</v>
+        <v>10.26</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -681,70 +681,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3729.7</v>
+        <v>3747.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2842.8</v>
+        <v>2868.1</v>
       </c>
       <c r="F4" t="n">
-        <v>24.96</v>
+        <v>27.63</v>
       </c>
       <c r="G4" t="n">
-        <v>19.03</v>
+        <v>21.03</v>
       </c>
       <c r="H4" t="n">
-        <v>812.5</v>
+        <v>651.9</v>
       </c>
       <c r="I4" t="n">
-        <v>622.2</v>
+        <v>499.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6.03</v>
+        <v>5.67</v>
       </c>
       <c r="K4" t="n">
-        <v>4.61</v>
+        <v>4.35</v>
       </c>
       <c r="L4" t="n">
-        <v>8.960000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="M4" t="n">
-        <v>6.85</v>
+        <v>6.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.17</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.66</v>
+        <v>2.33</v>
       </c>
       <c r="P4" t="n">
-        <v>344.2</v>
+        <v>337.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>262.69</v>
+        <v>258.11</v>
       </c>
       <c r="R4" t="n">
-        <v>193.17</v>
+        <v>188.35</v>
       </c>
       <c r="S4" t="n">
-        <v>331.5</v>
+        <v>327.76</v>
       </c>
       <c r="T4" t="n">
-        <v>252.43</v>
+        <v>251.97</v>
       </c>
       <c r="U4" t="n">
-        <v>10.26</v>
+        <v>6.14</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -752,70 +752,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3747.3</v>
+        <v>4285.1</v>
       </c>
       <c r="E5" t="n">
-        <v>2868.1</v>
+        <v>3264.3</v>
       </c>
       <c r="F5" t="n">
-        <v>27.63</v>
+        <v>33.75</v>
       </c>
       <c r="G5" t="n">
-        <v>21.03</v>
+        <v>25.65</v>
       </c>
       <c r="H5" t="n">
-        <v>651.9</v>
+        <v>337.3</v>
       </c>
       <c r="I5" t="n">
-        <v>499.5</v>
+        <v>257.7</v>
       </c>
       <c r="J5" t="n">
-        <v>5.67</v>
+        <v>3.44</v>
       </c>
       <c r="K5" t="n">
-        <v>4.35</v>
+        <v>2.65</v>
       </c>
       <c r="L5" t="n">
-        <v>7.93</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>6.06</v>
+        <v>6.46</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>337.66</v>
+        <v>338.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>258.11</v>
+        <v>257.52</v>
       </c>
       <c r="R5" t="n">
-        <v>188.35</v>
+        <v>188.12</v>
       </c>
       <c r="S5" t="n">
-        <v>327.76</v>
+        <v>327.01</v>
       </c>
       <c r="T5" t="n">
-        <v>251.97</v>
+        <v>244.32</v>
       </c>
       <c r="U5" t="n">
-        <v>6.14</v>
+        <v>13.2</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -823,70 +823,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Lamar Jackson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4285.1</v>
+        <v>3869.1</v>
       </c>
       <c r="E6" t="n">
-        <v>3264.3</v>
+        <v>2706.4</v>
       </c>
       <c r="F6" t="n">
-        <v>33.75</v>
+        <v>29.79</v>
       </c>
       <c r="G6" t="n">
-        <v>25.65</v>
+        <v>20.85</v>
       </c>
       <c r="H6" t="n">
-        <v>337.3</v>
+        <v>770.8</v>
       </c>
       <c r="I6" t="n">
-        <v>257.7</v>
+        <v>545.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.44</v>
+        <v>4.31</v>
       </c>
       <c r="K6" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.449999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="M6" t="n">
-        <v>6.46</v>
+        <v>5.56</v>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="P6" t="n">
-        <v>338.13</v>
+        <v>355.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>257.52</v>
+        <v>249.77</v>
       </c>
       <c r="R6" t="n">
-        <v>188.12</v>
+        <v>185.85</v>
       </c>
       <c r="S6" t="n">
-        <v>327.01</v>
+        <v>313.81</v>
       </c>
       <c r="T6" t="n">
-        <v>244.32</v>
+        <v>256.79</v>
       </c>
       <c r="U6" t="n">
-        <v>13.2</v>
+        <v>-7.02</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1178,70 +1178,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4006.2</v>
+        <v>3793</v>
       </c>
       <c r="E11" t="n">
-        <v>3069.9</v>
+        <v>2894.9</v>
       </c>
       <c r="F11" t="n">
-        <v>31.1</v>
+        <v>27.16</v>
       </c>
       <c r="G11" t="n">
-        <v>23.7</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>282</v>
+        <v>484.2</v>
       </c>
       <c r="I11" t="n">
-        <v>216.3</v>
+        <v>370.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.73</v>
+        <v>4.03</v>
       </c>
       <c r="K11" t="n">
-        <v>2.87</v>
+        <v>3.11</v>
       </c>
       <c r="L11" t="n">
-        <v>11.95</v>
+        <v>11.29</v>
       </c>
       <c r="M11" t="n">
-        <v>9.140000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="O11" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="P11" t="n">
-        <v>303.85</v>
+        <v>303.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>232.45</v>
+        <v>232.84</v>
       </c>
       <c r="R11" t="n">
-        <v>162.94</v>
+        <v>162.96</v>
       </c>
       <c r="S11" t="n">
-        <v>302.15</v>
+        <v>302.98</v>
       </c>
       <c r="T11" t="n">
-        <v>246.62</v>
+        <v>248.22</v>
       </c>
       <c r="U11" t="n">
-        <v>-14.17</v>
+        <v>-15.38</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1249,70 +1249,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4621.9</v>
+        <v>4006.2</v>
       </c>
       <c r="E12" t="n">
-        <v>3261.8</v>
+        <v>3069.9</v>
       </c>
       <c r="F12" t="n">
-        <v>34.98</v>
+        <v>31.1</v>
       </c>
       <c r="G12" t="n">
-        <v>24.64</v>
+        <v>23.7</v>
       </c>
       <c r="H12" t="n">
-        <v>183.6</v>
+        <v>282</v>
       </c>
       <c r="I12" t="n">
-        <v>129.7</v>
+        <v>216.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.52</v>
+        <v>3.73</v>
       </c>
       <c r="K12" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="L12" t="n">
-        <v>12.19</v>
+        <v>11.95</v>
       </c>
       <c r="M12" t="n">
-        <v>8.6</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="O12" t="n">
-        <v>2.16</v>
+        <v>2.86</v>
       </c>
       <c r="P12" t="n">
-        <v>327.78</v>
+        <v>303.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>231.1</v>
+        <v>232.45</v>
       </c>
       <c r="R12" t="n">
-        <v>166.9</v>
+        <v>162.94</v>
       </c>
       <c r="S12" t="n">
-        <v>295.48</v>
+        <v>302.15</v>
       </c>
       <c r="T12" t="n">
-        <v>227.93</v>
+        <v>246.62</v>
       </c>
       <c r="U12" t="n">
-        <v>3.17</v>
+        <v>-14.17</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -1320,70 +1320,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4184.8</v>
+        <v>4621.9</v>
       </c>
       <c r="E13" t="n">
-        <v>3188.4</v>
+        <v>3261.8</v>
       </c>
       <c r="F13" t="n">
-        <v>26.33</v>
+        <v>34.98</v>
       </c>
       <c r="G13" t="n">
-        <v>20.07</v>
+        <v>24.64</v>
       </c>
       <c r="H13" t="n">
-        <v>290</v>
+        <v>183.6</v>
       </c>
       <c r="I13" t="n">
-        <v>222.4</v>
+        <v>129.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="K13" t="n">
-        <v>2.76</v>
+        <v>1.77</v>
       </c>
       <c r="L13" t="n">
-        <v>11.67</v>
+        <v>12.19</v>
       </c>
       <c r="M13" t="n">
-        <v>8.93</v>
+        <v>8.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.43</v>
+        <v>3.06</v>
       </c>
       <c r="O13" t="n">
-        <v>3.38</v>
+        <v>2.16</v>
       </c>
       <c r="P13" t="n">
-        <v>291.11</v>
+        <v>327.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>222</v>
+        <v>231.1</v>
       </c>
       <c r="R13" t="n">
-        <v>152.77</v>
+        <v>166.9</v>
       </c>
       <c r="S13" t="n">
-        <v>291.4</v>
+        <v>295.48</v>
       </c>
       <c r="T13" t="n">
-        <v>222.53</v>
+        <v>227.93</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.53</v>
+        <v>3.17</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -1391,70 +1391,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4429.5</v>
+        <v>4184.8</v>
       </c>
       <c r="E14" t="n">
-        <v>3387.4</v>
+        <v>3188.4</v>
       </c>
       <c r="F14" t="n">
-        <v>31.33</v>
+        <v>26.33</v>
       </c>
       <c r="G14" t="n">
-        <v>23.95</v>
+        <v>20.07</v>
       </c>
       <c r="H14" t="n">
-        <v>26.8</v>
+        <v>290</v>
       </c>
       <c r="I14" t="n">
-        <v>21.1</v>
+        <v>222.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.34</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="L14" t="n">
-        <v>9.41</v>
+        <v>11.67</v>
       </c>
       <c r="M14" t="n">
-        <v>7.19</v>
+        <v>8.93</v>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>4.43</v>
       </c>
       <c r="O14" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="P14" t="n">
-        <v>287.76</v>
+        <v>291.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>220.19</v>
+        <v>222</v>
       </c>
       <c r="R14" t="n">
-        <v>163.5</v>
+        <v>152.77</v>
       </c>
       <c r="S14" t="n">
-        <v>290.01</v>
+        <v>291.4</v>
       </c>
       <c r="T14" t="n">
-        <v>231.48</v>
+        <v>222.53</v>
       </c>
       <c r="U14" t="n">
-        <v>-11.29</v>
+        <v>-0.53</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -1462,70 +1462,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4000.1</v>
+        <v>4429.5</v>
       </c>
       <c r="E15" t="n">
-        <v>3065.6</v>
+        <v>3387.4</v>
       </c>
       <c r="F15" t="n">
-        <v>25.96</v>
+        <v>31.33</v>
       </c>
       <c r="G15" t="n">
-        <v>19.89</v>
+        <v>23.95</v>
       </c>
       <c r="H15" t="n">
-        <v>276.7</v>
+        <v>26.8</v>
       </c>
       <c r="I15" t="n">
-        <v>212.4</v>
+        <v>21.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.29</v>
+        <v>1.34</v>
       </c>
       <c r="K15" t="n">
-        <v>2.53</v>
+        <v>1.04</v>
       </c>
       <c r="L15" t="n">
-        <v>9.26</v>
+        <v>9.41</v>
       </c>
       <c r="M15" t="n">
-        <v>7.08</v>
+        <v>7.19</v>
       </c>
       <c r="N15" t="n">
-        <v>3.49</v>
+        <v>3.32</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="P15" t="n">
-        <v>285.75</v>
+        <v>287.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>219.1</v>
+        <v>220.19</v>
       </c>
       <c r="R15" t="n">
-        <v>148.99</v>
+        <v>163.5</v>
       </c>
       <c r="S15" t="n">
-        <v>288.82</v>
+        <v>290.01</v>
       </c>
       <c r="T15" t="n">
-        <v>232.09</v>
+        <v>231.48</v>
       </c>
       <c r="U15" t="n">
-        <v>-12.99</v>
+        <v>-11.29</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -1533,70 +1533,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3669.6</v>
+        <v>4000.1</v>
       </c>
       <c r="E16" t="n">
-        <v>2785.1</v>
+        <v>3065.6</v>
       </c>
       <c r="F16" t="n">
-        <v>21.59</v>
+        <v>25.96</v>
       </c>
       <c r="G16" t="n">
-        <v>16.44</v>
+        <v>19.89</v>
       </c>
       <c r="H16" t="n">
-        <v>521.5</v>
+        <v>276.7</v>
       </c>
       <c r="I16" t="n">
-        <v>399.3</v>
+        <v>212.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="K16" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="L16" t="n">
-        <v>8.81</v>
+        <v>9.26</v>
       </c>
       <c r="M16" t="n">
-        <v>6.74</v>
+        <v>7.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.83</v>
+        <v>3.49</v>
       </c>
       <c r="O16" t="n">
-        <v>2.17</v>
+        <v>2.67</v>
       </c>
       <c r="P16" t="n">
-        <v>283.31</v>
+        <v>285.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>215.59</v>
+        <v>219.1</v>
       </c>
       <c r="R16" t="n">
-        <v>146.01</v>
+        <v>148.99</v>
       </c>
       <c r="S16" t="n">
-        <v>284.81</v>
+        <v>288.82</v>
       </c>
       <c r="T16" t="n">
-        <v>245.55</v>
+        <v>232.09</v>
       </c>
       <c r="U16" t="n">
-        <v>-29.96</v>
+        <v>-12.99</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
@@ -1604,70 +1604,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4040.9</v>
+        <v>3669.6</v>
       </c>
       <c r="E17" t="n">
-        <v>3083.4</v>
+        <v>2785.1</v>
       </c>
       <c r="F17" t="n">
-        <v>26.29</v>
+        <v>21.59</v>
       </c>
       <c r="G17" t="n">
-        <v>20.13</v>
+        <v>16.44</v>
       </c>
       <c r="H17" t="n">
-        <v>224.6</v>
+        <v>521.5</v>
       </c>
       <c r="I17" t="n">
-        <v>172.5</v>
+        <v>399.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.17</v>
       </c>
-      <c r="L17" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="M17" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.93</v>
-      </c>
       <c r="P17" t="n">
-        <v>282.38</v>
+        <v>283.31</v>
       </c>
       <c r="Q17" t="n">
-        <v>215.55</v>
+        <v>215.59</v>
       </c>
       <c r="R17" t="n">
-        <v>146.03</v>
+        <v>146.01</v>
       </c>
       <c r="S17" t="n">
-        <v>284.43</v>
+        <v>284.81</v>
       </c>
       <c r="T17" t="n">
-        <v>206.7</v>
+        <v>245.55</v>
       </c>
       <c r="U17" t="n">
-        <v>8.85</v>
+        <v>-29.96</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -1675,70 +1675,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3793</v>
+        <v>4040.9</v>
       </c>
       <c r="E18" t="n">
-        <v>2666.5</v>
+        <v>3083.4</v>
       </c>
       <c r="F18" t="n">
-        <v>27.16</v>
+        <v>26.29</v>
       </c>
       <c r="G18" t="n">
-        <v>19.39</v>
+        <v>20.13</v>
       </c>
       <c r="H18" t="n">
-        <v>484.2</v>
+        <v>224.6</v>
       </c>
       <c r="I18" t="n">
-        <v>342.6</v>
+        <v>172.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.03</v>
+        <v>2.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="L18" t="n">
-        <v>11.29</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>7.97</v>
+        <v>7.36</v>
       </c>
       <c r="N18" t="n">
-        <v>3.54</v>
+        <v>2.51</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="P18" t="n">
-        <v>303.3</v>
+        <v>282.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>214.76</v>
+        <v>215.55</v>
       </c>
       <c r="R18" t="n">
-        <v>150.3</v>
+        <v>146.03</v>
       </c>
       <c r="S18" t="n">
-        <v>279.45</v>
+        <v>284.43</v>
       </c>
       <c r="T18" t="n">
-        <v>248.22</v>
+        <v>206.7</v>
       </c>
       <c r="U18" t="n">
-        <v>-33.46</v>
+        <v>8.85</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
@@ -2949,64 +2949,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3334.8</v>
+        <v>3328.3</v>
       </c>
       <c r="E36" t="n">
-        <v>201.5</v>
+        <v>194.7</v>
       </c>
       <c r="F36" t="n">
-        <v>16.71</v>
+        <v>18.88</v>
       </c>
       <c r="G36" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="H36" t="n">
-        <v>269.5</v>
+        <v>722.9</v>
       </c>
       <c r="I36" t="n">
-        <v>15.4</v>
+        <v>42.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3.12</v>
+        <v>4.04</v>
       </c>
       <c r="K36" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="L36" t="n">
-        <v>9.460000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="N36" t="n">
-        <v>2.44</v>
+        <v>2.87</v>
       </c>
       <c r="O36" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="P36" t="n">
-        <v>222.1</v>
+        <v>281.48</v>
       </c>
       <c r="Q36" t="n">
-        <v>13.4</v>
+        <v>16.57</v>
       </c>
       <c r="R36" t="n">
-        <v>7.92</v>
+        <v>11.2</v>
       </c>
       <c r="S36" t="n">
-        <v>18.89</v>
+        <v>21.94</v>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -4837,55 +4837,55 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>3328.3</v>
+        <v>3590.2</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>18.88</v>
+        <v>22.85</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>722.9</v>
+        <v>545.3</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>4.04</v>
+        <v>4.16</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>8.98</v>
+        <v>10.53</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>281.48</v>
+        <v>287.66</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -4904,55 +4904,55 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>3590.2</v>
+        <v>3334.8</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>22.85</v>
+        <v>16.71</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>545.3</v>
+        <v>269.5</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>4.16</v>
+        <v>3.12</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>10.53</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>287.66</v>
+        <v>222.1</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5173,70 +5173,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lamar Jackson</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3869.1</v>
+        <v>3729.7</v>
       </c>
       <c r="E3" t="n">
-        <v>2932.9</v>
+        <v>2842.8</v>
       </c>
       <c r="F3" t="n">
-        <v>29.79</v>
+        <v>24.96</v>
       </c>
       <c r="G3" t="n">
-        <v>22.61</v>
+        <v>19.03</v>
       </c>
       <c r="H3" t="n">
-        <v>770.8</v>
+        <v>812.5</v>
       </c>
       <c r="I3" t="n">
-        <v>590.1</v>
+        <v>622.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.31</v>
+        <v>6.03</v>
       </c>
       <c r="K3" t="n">
-        <v>3.33</v>
+        <v>4.61</v>
       </c>
       <c r="L3" t="n">
-        <v>7.88</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>6.02</v>
+        <v>6.85</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.17</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="P3" t="n">
-        <v>355.74</v>
+        <v>344.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>270.61</v>
+        <v>262.69</v>
       </c>
       <c r="R3" t="n">
-        <v>201.36</v>
+        <v>193.17</v>
       </c>
       <c r="S3" t="n">
-        <v>340</v>
+        <v>331.5</v>
       </c>
       <c r="T3" t="n">
-        <v>256.79</v>
+        <v>252.43</v>
       </c>
       <c r="U3" t="n">
-        <v>13.82</v>
+        <v>10.26</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -5244,70 +5244,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3729.7</v>
+        <v>3747.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2842.8</v>
+        <v>2868.1</v>
       </c>
       <c r="F4" t="n">
-        <v>24.96</v>
+        <v>27.63</v>
       </c>
       <c r="G4" t="n">
-        <v>19.03</v>
+        <v>21.03</v>
       </c>
       <c r="H4" t="n">
-        <v>812.5</v>
+        <v>651.9</v>
       </c>
       <c r="I4" t="n">
-        <v>622.2</v>
+        <v>499.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6.03</v>
+        <v>5.67</v>
       </c>
       <c r="K4" t="n">
-        <v>4.61</v>
+        <v>4.35</v>
       </c>
       <c r="L4" t="n">
-        <v>8.960000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="M4" t="n">
-        <v>6.85</v>
+        <v>6.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.17</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.66</v>
+        <v>2.33</v>
       </c>
       <c r="P4" t="n">
-        <v>344.2</v>
+        <v>337.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>262.69</v>
+        <v>258.11</v>
       </c>
       <c r="R4" t="n">
-        <v>193.17</v>
+        <v>188.35</v>
       </c>
       <c r="S4" t="n">
-        <v>331.5</v>
+        <v>327.76</v>
       </c>
       <c r="T4" t="n">
-        <v>252.43</v>
+        <v>251.97</v>
       </c>
       <c r="U4" t="n">
-        <v>10.26</v>
+        <v>6.14</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -5315,70 +5315,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3747.3</v>
+        <v>4285.1</v>
       </c>
       <c r="E5" t="n">
-        <v>2868.1</v>
+        <v>3264.3</v>
       </c>
       <c r="F5" t="n">
-        <v>27.63</v>
+        <v>33.75</v>
       </c>
       <c r="G5" t="n">
-        <v>21.03</v>
+        <v>25.65</v>
       </c>
       <c r="H5" t="n">
-        <v>651.9</v>
+        <v>337.3</v>
       </c>
       <c r="I5" t="n">
-        <v>499.5</v>
+        <v>257.7</v>
       </c>
       <c r="J5" t="n">
-        <v>5.67</v>
+        <v>3.44</v>
       </c>
       <c r="K5" t="n">
-        <v>4.35</v>
+        <v>2.65</v>
       </c>
       <c r="L5" t="n">
-        <v>7.93</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>6.06</v>
+        <v>6.46</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>337.66</v>
+        <v>338.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>258.11</v>
+        <v>257.52</v>
       </c>
       <c r="R5" t="n">
-        <v>188.35</v>
+        <v>188.12</v>
       </c>
       <c r="S5" t="n">
-        <v>327.76</v>
+        <v>327.01</v>
       </c>
       <c r="T5" t="n">
-        <v>251.97</v>
+        <v>244.32</v>
       </c>
       <c r="U5" t="n">
-        <v>6.14</v>
+        <v>13.2</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -5386,70 +5386,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Lamar Jackson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4285.1</v>
+        <v>3869.1</v>
       </c>
       <c r="E6" t="n">
-        <v>3264.3</v>
+        <v>2706.4</v>
       </c>
       <c r="F6" t="n">
-        <v>33.75</v>
+        <v>29.79</v>
       </c>
       <c r="G6" t="n">
-        <v>25.65</v>
+        <v>20.85</v>
       </c>
       <c r="H6" t="n">
-        <v>337.3</v>
+        <v>770.8</v>
       </c>
       <c r="I6" t="n">
-        <v>257.7</v>
+        <v>545.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.44</v>
+        <v>4.31</v>
       </c>
       <c r="K6" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.449999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="M6" t="n">
-        <v>6.46</v>
+        <v>5.56</v>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="P6" t="n">
-        <v>338.13</v>
+        <v>355.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>257.52</v>
+        <v>249.77</v>
       </c>
       <c r="R6" t="n">
-        <v>188.12</v>
+        <v>185.85</v>
       </c>
       <c r="S6" t="n">
-        <v>327.01</v>
+        <v>313.81</v>
       </c>
       <c r="T6" t="n">
-        <v>244.32</v>
+        <v>256.79</v>
       </c>
       <c r="U6" t="n">
-        <v>13.2</v>
+        <v>-7.02</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -5741,70 +5741,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4006.2</v>
+        <v>3793</v>
       </c>
       <c r="E11" t="n">
-        <v>3069.9</v>
+        <v>2894.9</v>
       </c>
       <c r="F11" t="n">
-        <v>31.1</v>
+        <v>27.16</v>
       </c>
       <c r="G11" t="n">
-        <v>23.7</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>282</v>
+        <v>484.2</v>
       </c>
       <c r="I11" t="n">
-        <v>216.3</v>
+        <v>370.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.73</v>
+        <v>4.03</v>
       </c>
       <c r="K11" t="n">
-        <v>2.87</v>
+        <v>3.11</v>
       </c>
       <c r="L11" t="n">
-        <v>11.95</v>
+        <v>11.29</v>
       </c>
       <c r="M11" t="n">
-        <v>9.140000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="O11" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="P11" t="n">
-        <v>303.85</v>
+        <v>303.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>232.45</v>
+        <v>232.84</v>
       </c>
       <c r="R11" t="n">
-        <v>162.94</v>
+        <v>162.96</v>
       </c>
       <c r="S11" t="n">
-        <v>302.15</v>
+        <v>302.98</v>
       </c>
       <c r="T11" t="n">
-        <v>246.62</v>
+        <v>248.22</v>
       </c>
       <c r="U11" t="n">
-        <v>-14.17</v>
+        <v>-15.38</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -5812,70 +5812,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4621.9</v>
+        <v>4006.2</v>
       </c>
       <c r="E12" t="n">
-        <v>3261.8</v>
+        <v>3069.9</v>
       </c>
       <c r="F12" t="n">
-        <v>34.98</v>
+        <v>31.1</v>
       </c>
       <c r="G12" t="n">
-        <v>24.64</v>
+        <v>23.7</v>
       </c>
       <c r="H12" t="n">
-        <v>183.6</v>
+        <v>282</v>
       </c>
       <c r="I12" t="n">
-        <v>129.7</v>
+        <v>216.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.52</v>
+        <v>3.73</v>
       </c>
       <c r="K12" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="L12" t="n">
-        <v>12.19</v>
+        <v>11.95</v>
       </c>
       <c r="M12" t="n">
-        <v>8.6</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="O12" t="n">
-        <v>2.16</v>
+        <v>2.86</v>
       </c>
       <c r="P12" t="n">
-        <v>327.78</v>
+        <v>303.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>231.1</v>
+        <v>232.45</v>
       </c>
       <c r="R12" t="n">
-        <v>166.9</v>
+        <v>162.94</v>
       </c>
       <c r="S12" t="n">
-        <v>295.48</v>
+        <v>302.15</v>
       </c>
       <c r="T12" t="n">
-        <v>227.93</v>
+        <v>246.62</v>
       </c>
       <c r="U12" t="n">
-        <v>3.17</v>
+        <v>-14.17</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -5883,70 +5883,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4184.8</v>
+        <v>4621.9</v>
       </c>
       <c r="E13" t="n">
-        <v>3188.4</v>
+        <v>3261.8</v>
       </c>
       <c r="F13" t="n">
-        <v>26.33</v>
+        <v>34.98</v>
       </c>
       <c r="G13" t="n">
-        <v>20.07</v>
+        <v>24.64</v>
       </c>
       <c r="H13" t="n">
-        <v>290</v>
+        <v>183.6</v>
       </c>
       <c r="I13" t="n">
-        <v>222.4</v>
+        <v>129.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="K13" t="n">
-        <v>2.76</v>
+        <v>1.77</v>
       </c>
       <c r="L13" t="n">
-        <v>11.67</v>
+        <v>12.19</v>
       </c>
       <c r="M13" t="n">
-        <v>8.93</v>
+        <v>8.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.43</v>
+        <v>3.06</v>
       </c>
       <c r="O13" t="n">
-        <v>3.38</v>
+        <v>2.16</v>
       </c>
       <c r="P13" t="n">
-        <v>291.11</v>
+        <v>327.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>222</v>
+        <v>231.1</v>
       </c>
       <c r="R13" t="n">
-        <v>152.77</v>
+        <v>166.9</v>
       </c>
       <c r="S13" t="n">
-        <v>291.4</v>
+        <v>295.48</v>
       </c>
       <c r="T13" t="n">
-        <v>222.53</v>
+        <v>227.93</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.53</v>
+        <v>3.17</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -5954,70 +5954,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4429.5</v>
+        <v>4184.8</v>
       </c>
       <c r="E14" t="n">
-        <v>3387.4</v>
+        <v>3188.4</v>
       </c>
       <c r="F14" t="n">
-        <v>31.33</v>
+        <v>26.33</v>
       </c>
       <c r="G14" t="n">
-        <v>23.95</v>
+        <v>20.07</v>
       </c>
       <c r="H14" t="n">
-        <v>26.8</v>
+        <v>290</v>
       </c>
       <c r="I14" t="n">
-        <v>21.1</v>
+        <v>222.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.34</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="L14" t="n">
-        <v>9.41</v>
+        <v>11.67</v>
       </c>
       <c r="M14" t="n">
-        <v>7.19</v>
+        <v>8.93</v>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>4.43</v>
       </c>
       <c r="O14" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="P14" t="n">
-        <v>287.76</v>
+        <v>291.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>220.19</v>
+        <v>222</v>
       </c>
       <c r="R14" t="n">
-        <v>163.5</v>
+        <v>152.77</v>
       </c>
       <c r="S14" t="n">
-        <v>290.01</v>
+        <v>291.4</v>
       </c>
       <c r="T14" t="n">
-        <v>231.48</v>
+        <v>222.53</v>
       </c>
       <c r="U14" t="n">
-        <v>-11.29</v>
+        <v>-0.53</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -6025,70 +6025,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4000.1</v>
+        <v>4429.5</v>
       </c>
       <c r="E15" t="n">
-        <v>3065.6</v>
+        <v>3387.4</v>
       </c>
       <c r="F15" t="n">
-        <v>25.96</v>
+        <v>31.33</v>
       </c>
       <c r="G15" t="n">
-        <v>19.89</v>
+        <v>23.95</v>
       </c>
       <c r="H15" t="n">
-        <v>276.7</v>
+        <v>26.8</v>
       </c>
       <c r="I15" t="n">
-        <v>212.4</v>
+        <v>21.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.29</v>
+        <v>1.34</v>
       </c>
       <c r="K15" t="n">
-        <v>2.53</v>
+        <v>1.04</v>
       </c>
       <c r="L15" t="n">
-        <v>9.26</v>
+        <v>9.41</v>
       </c>
       <c r="M15" t="n">
-        <v>7.08</v>
+        <v>7.19</v>
       </c>
       <c r="N15" t="n">
-        <v>3.49</v>
+        <v>3.32</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="P15" t="n">
-        <v>285.75</v>
+        <v>287.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>219.1</v>
+        <v>220.19</v>
       </c>
       <c r="R15" t="n">
-        <v>148.99</v>
+        <v>163.5</v>
       </c>
       <c r="S15" t="n">
-        <v>288.82</v>
+        <v>290.01</v>
       </c>
       <c r="T15" t="n">
-        <v>232.09</v>
+        <v>231.48</v>
       </c>
       <c r="U15" t="n">
-        <v>-12.99</v>
+        <v>-11.29</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -6096,70 +6096,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3669.6</v>
+        <v>4000.1</v>
       </c>
       <c r="E16" t="n">
-        <v>2785.1</v>
+        <v>3065.6</v>
       </c>
       <c r="F16" t="n">
-        <v>21.59</v>
+        <v>25.96</v>
       </c>
       <c r="G16" t="n">
-        <v>16.44</v>
+        <v>19.89</v>
       </c>
       <c r="H16" t="n">
-        <v>521.5</v>
+        <v>276.7</v>
       </c>
       <c r="I16" t="n">
-        <v>399.3</v>
+        <v>212.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="K16" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="L16" t="n">
-        <v>8.81</v>
+        <v>9.26</v>
       </c>
       <c r="M16" t="n">
-        <v>6.74</v>
+        <v>7.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.83</v>
+        <v>3.49</v>
       </c>
       <c r="O16" t="n">
-        <v>2.17</v>
+        <v>2.67</v>
       </c>
       <c r="P16" t="n">
-        <v>283.31</v>
+        <v>285.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>215.59</v>
+        <v>219.1</v>
       </c>
       <c r="R16" t="n">
-        <v>146.01</v>
+        <v>148.99</v>
       </c>
       <c r="S16" t="n">
-        <v>284.81</v>
+        <v>288.82</v>
       </c>
       <c r="T16" t="n">
-        <v>245.55</v>
+        <v>232.09</v>
       </c>
       <c r="U16" t="n">
-        <v>-29.96</v>
+        <v>-12.99</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
@@ -6167,70 +6167,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4040.9</v>
+        <v>3669.6</v>
       </c>
       <c r="E17" t="n">
-        <v>3083.4</v>
+        <v>2785.1</v>
       </c>
       <c r="F17" t="n">
-        <v>26.29</v>
+        <v>21.59</v>
       </c>
       <c r="G17" t="n">
-        <v>20.13</v>
+        <v>16.44</v>
       </c>
       <c r="H17" t="n">
-        <v>224.6</v>
+        <v>521.5</v>
       </c>
       <c r="I17" t="n">
-        <v>172.5</v>
+        <v>399.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.17</v>
       </c>
-      <c r="L17" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="M17" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.93</v>
-      </c>
       <c r="P17" t="n">
-        <v>282.38</v>
+        <v>283.31</v>
       </c>
       <c r="Q17" t="n">
-        <v>215.55</v>
+        <v>215.59</v>
       </c>
       <c r="R17" t="n">
-        <v>146.03</v>
+        <v>146.01</v>
       </c>
       <c r="S17" t="n">
-        <v>284.43</v>
+        <v>284.81</v>
       </c>
       <c r="T17" t="n">
-        <v>206.7</v>
+        <v>245.55</v>
       </c>
       <c r="U17" t="n">
-        <v>8.85</v>
+        <v>-29.96</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -6238,70 +6238,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3793</v>
+        <v>4040.9</v>
       </c>
       <c r="E18" t="n">
-        <v>2666.5</v>
+        <v>3083.4</v>
       </c>
       <c r="F18" t="n">
-        <v>27.16</v>
+        <v>26.29</v>
       </c>
       <c r="G18" t="n">
-        <v>19.39</v>
+        <v>20.13</v>
       </c>
       <c r="H18" t="n">
-        <v>484.2</v>
+        <v>224.6</v>
       </c>
       <c r="I18" t="n">
-        <v>342.6</v>
+        <v>172.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.03</v>
+        <v>2.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="L18" t="n">
-        <v>11.29</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>7.97</v>
+        <v>7.36</v>
       </c>
       <c r="N18" t="n">
-        <v>3.54</v>
+        <v>2.51</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="P18" t="n">
-        <v>303.3</v>
+        <v>282.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>214.76</v>
+        <v>215.55</v>
       </c>
       <c r="R18" t="n">
-        <v>150.3</v>
+        <v>146.03</v>
       </c>
       <c r="S18" t="n">
-        <v>279.45</v>
+        <v>284.43</v>
       </c>
       <c r="T18" t="n">
-        <v>248.22</v>
+        <v>206.7</v>
       </c>
       <c r="U18" t="n">
-        <v>-33.46</v>
+        <v>8.85</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
@@ -7643,64 +7643,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3334.8</v>
+        <v>3328.3</v>
       </c>
       <c r="E4" t="n">
-        <v>201.5</v>
+        <v>194.7</v>
       </c>
       <c r="F4" t="n">
-        <v>16.71</v>
+        <v>18.88</v>
       </c>
       <c r="G4" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="H4" t="n">
-        <v>269.5</v>
+        <v>722.9</v>
       </c>
       <c r="I4" t="n">
-        <v>15.4</v>
+        <v>42.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.12</v>
+        <v>4.04</v>
       </c>
       <c r="K4" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="L4" t="n">
-        <v>9.460000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="P4" t="n">
-        <v>222.1</v>
+        <v>281.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.4</v>
+        <v>16.57</v>
       </c>
       <c r="R4" t="n">
-        <v>7.92</v>
+        <v>11.2</v>
       </c>
       <c r="S4" t="n">
-        <v>18.89</v>
+        <v>21.94</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -9531,55 +9531,55 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3328.3</v>
+        <v>3590.2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>18.88</v>
+        <v>22.85</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>722.9</v>
+        <v>545.3</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>4.04</v>
+        <v>4.16</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>8.98</v>
+        <v>10.53</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>281.48</v>
+        <v>287.66</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -9598,55 +9598,55 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>3590.2</v>
+        <v>3334.8</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>22.85</v>
+        <v>16.71</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>545.3</v>
+        <v>269.5</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>4.16</v>
+        <v>3.12</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>10.53</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>287.66</v>
+        <v>222.1</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -17013,67 +17013,67 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>228.415</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1.612</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>28.049</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>135.295</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>321.535</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.017</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>9.709</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>48.941</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>0.757</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>0.803</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>18.078</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>3.904</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>33.758</v>
       </c>
       <c r="AC79" t="inlineStr"/>
     </row>
@@ -38682,67 +38682,67 @@
         <v>1</v>
       </c>
       <c r="H312" t="n">
-        <v>226.46</v>
+        <v>0</v>
       </c>
       <c r="I312" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="J312" t="n">
-        <v>44.98</v>
+        <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="N312" t="n">
-        <v>133.337</v>
+        <v>0</v>
       </c>
       <c r="O312" t="n">
-        <v>319.583</v>
+        <v>0</v>
       </c>
       <c r="P312" t="n">
-        <v>0.609</v>
+        <v>0</v>
       </c>
       <c r="Q312" t="n">
-        <v>3.164</v>
+        <v>0</v>
       </c>
       <c r="R312" t="n">
-        <v>24.089</v>
+        <v>0</v>
       </c>
       <c r="S312" t="n">
-        <v>65.871</v>
+        <v>0</v>
       </c>
       <c r="T312" t="n">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="U312" t="n">
-        <v>0.766</v>
+        <v>0</v>
       </c>
       <c r="V312" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="W312" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X312" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="Y312" t="n">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="Z312" t="n">
-        <v>20.832</v>
+        <v>0</v>
       </c>
       <c r="AA312" t="n">
-        <v>5.979</v>
+        <v>0</v>
       </c>
       <c r="AB312" t="n">
-        <v>36.19</v>
+        <v>0</v>
       </c>
       <c r="AC312" t="inlineStr"/>
     </row>
@@ -83229,67 +83229,67 @@
         <v>1</v>
       </c>
       <c r="H791" t="n">
-        <v>0</v>
+        <v>194.651</v>
       </c>
       <c r="I791" t="n">
-        <v>0</v>
+        <v>1.127</v>
       </c>
       <c r="J791" t="n">
-        <v>0</v>
+        <v>42.164</v>
       </c>
       <c r="K791" t="n">
-        <v>0</v>
+        <v>0.244</v>
       </c>
       <c r="L791" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="M791" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="N791" t="n">
-        <v>0</v>
+        <v>101.533</v>
       </c>
       <c r="O791" t="n">
-        <v>0</v>
+        <v>287.774</v>
       </c>
       <c r="P791" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="Q791" t="n">
-        <v>0</v>
+        <v>2.531</v>
       </c>
       <c r="R791" t="n">
-        <v>0</v>
+        <v>21.27</v>
       </c>
       <c r="S791" t="n">
-        <v>0</v>
+        <v>63.059</v>
       </c>
       <c r="T791" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="U791" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="V791" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="W791" t="n">
-        <v>0</v>
+        <v>1.664</v>
       </c>
       <c r="X791" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="Y791" t="n">
-        <v>0</v>
+        <v>0.766</v>
       </c>
       <c r="Z791" t="n">
-        <v>0</v>
+        <v>16.573</v>
       </c>
       <c r="AA791" t="n">
-        <v>0</v>
+        <v>3.394</v>
       </c>
       <c r="AB791" t="n">
-        <v>0</v>
+        <v>32.029</v>
       </c>
       <c r="AC791" t="inlineStr"/>
     </row>
@@ -85647,67 +85647,67 @@
         <v>0</v>
       </c>
       <c r="H817" t="n">
-        <v>201.465</v>
+        <v>0</v>
       </c>
       <c r="I817" t="n">
-        <v>1.032</v>
+        <v>0</v>
       </c>
       <c r="J817" t="n">
-        <v>15.418</v>
+        <v>0</v>
       </c>
       <c r="K817" t="n">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="L817" t="n">
-        <v>0.5570000000000001</v>
+        <v>0</v>
       </c>
       <c r="M817" t="n">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="N817" t="n">
-        <v>108.345</v>
+        <v>0</v>
       </c>
       <c r="O817" t="n">
-        <v>294.585</v>
+        <v>0</v>
       </c>
       <c r="P817" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="Q817" t="n">
-        <v>2.437</v>
+        <v>0</v>
       </c>
       <c r="R817" t="n">
-        <v>5.337</v>
+        <v>0</v>
       </c>
       <c r="S817" t="n">
-        <v>36.31</v>
+        <v>0</v>
       </c>
       <c r="T817" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="U817" t="n">
-        <v>0.694</v>
+        <v>0</v>
       </c>
       <c r="V817" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="W817" t="n">
-        <v>1.692</v>
+        <v>0</v>
       </c>
       <c r="X817" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="Y817" t="n">
-        <v>0.738</v>
+        <v>0</v>
       </c>
       <c r="Z817" t="n">
-        <v>13.386</v>
+        <v>0</v>
       </c>
       <c r="AA817" t="n">
-        <v>1.801</v>
+        <v>0</v>
       </c>
       <c r="AB817" t="n">
-        <v>28.842</v>
+        <v>0</v>
       </c>
       <c r="AC817" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -1178,70 +1178,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3793</v>
+        <v>4621.9</v>
       </c>
       <c r="E11" t="n">
-        <v>2894.9</v>
+        <v>3261.8</v>
       </c>
       <c r="F11" t="n">
-        <v>27.16</v>
+        <v>34.98</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>24.64</v>
       </c>
       <c r="H11" t="n">
-        <v>484.2</v>
+        <v>183.6</v>
       </c>
       <c r="I11" t="n">
-        <v>370.6</v>
+        <v>129.7</v>
       </c>
       <c r="J11" t="n">
-        <v>4.03</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="n">
-        <v>3.11</v>
+        <v>1.77</v>
       </c>
       <c r="L11" t="n">
-        <v>11.29</v>
+        <v>12.19</v>
       </c>
       <c r="M11" t="n">
-        <v>8.630000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.54</v>
+        <v>3.06</v>
       </c>
       <c r="O11" t="n">
-        <v>2.71</v>
+        <v>2.16</v>
       </c>
       <c r="P11" t="n">
-        <v>303.3</v>
+        <v>327.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>232.84</v>
+        <v>231.1</v>
       </c>
       <c r="R11" t="n">
-        <v>162.96</v>
+        <v>166.9</v>
       </c>
       <c r="S11" t="n">
-        <v>302.98</v>
+        <v>295.48</v>
       </c>
       <c r="T11" t="n">
-        <v>248.22</v>
+        <v>227.93</v>
       </c>
       <c r="U11" t="n">
-        <v>-15.38</v>
+        <v>3.17</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1249,70 +1249,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4621.9</v>
+        <v>4184.8</v>
       </c>
       <c r="E12" t="n">
-        <v>3261.8</v>
+        <v>3188.4</v>
       </c>
       <c r="F12" t="n">
-        <v>34.98</v>
+        <v>26.33</v>
       </c>
       <c r="G12" t="n">
-        <v>24.64</v>
+        <v>20.07</v>
       </c>
       <c r="H12" t="n">
-        <v>183.6</v>
+        <v>290</v>
       </c>
       <c r="I12" t="n">
-        <v>129.7</v>
+        <v>222.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>1.77</v>
+        <v>2.76</v>
       </c>
       <c r="L12" t="n">
-        <v>12.19</v>
+        <v>11.67</v>
       </c>
       <c r="M12" t="n">
-        <v>8.6</v>
+        <v>8.93</v>
       </c>
       <c r="N12" t="n">
-        <v>3.06</v>
+        <v>4.43</v>
       </c>
       <c r="O12" t="n">
-        <v>2.16</v>
+        <v>3.38</v>
       </c>
       <c r="P12" t="n">
-        <v>327.78</v>
+        <v>291.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>231.1</v>
+        <v>222</v>
       </c>
       <c r="R12" t="n">
-        <v>166.9</v>
+        <v>152.77</v>
       </c>
       <c r="S12" t="n">
-        <v>295.48</v>
+        <v>291.4</v>
       </c>
       <c r="T12" t="n">
-        <v>227.93</v>
+        <v>222.53</v>
       </c>
       <c r="U12" t="n">
-        <v>3.17</v>
+        <v>-0.53</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -1320,70 +1320,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4184.8</v>
+        <v>4429.5</v>
       </c>
       <c r="E13" t="n">
-        <v>3188.4</v>
+        <v>3387.4</v>
       </c>
       <c r="F13" t="n">
-        <v>26.33</v>
+        <v>31.33</v>
       </c>
       <c r="G13" t="n">
-        <v>20.07</v>
+        <v>23.95</v>
       </c>
       <c r="H13" t="n">
-        <v>290</v>
+        <v>26.8</v>
       </c>
       <c r="I13" t="n">
-        <v>222.4</v>
+        <v>21.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>1.34</v>
       </c>
       <c r="K13" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="L13" t="n">
-        <v>11.67</v>
+        <v>9.41</v>
       </c>
       <c r="M13" t="n">
-        <v>8.93</v>
+        <v>7.19</v>
       </c>
       <c r="N13" t="n">
-        <v>4.43</v>
+        <v>3.32</v>
       </c>
       <c r="O13" t="n">
-        <v>3.38</v>
+        <v>2.54</v>
       </c>
       <c r="P13" t="n">
-        <v>291.11</v>
+        <v>287.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>222</v>
+        <v>220.19</v>
       </c>
       <c r="R13" t="n">
-        <v>152.77</v>
+        <v>163.5</v>
       </c>
       <c r="S13" t="n">
-        <v>291.4</v>
+        <v>290.01</v>
       </c>
       <c r="T13" t="n">
-        <v>222.53</v>
+        <v>231.48</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.53</v>
+        <v>-11.29</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -1391,70 +1391,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4429.5</v>
+        <v>4000.1</v>
       </c>
       <c r="E14" t="n">
-        <v>3387.4</v>
+        <v>3065.6</v>
       </c>
       <c r="F14" t="n">
-        <v>31.33</v>
+        <v>25.96</v>
       </c>
       <c r="G14" t="n">
-        <v>23.95</v>
+        <v>19.89</v>
       </c>
       <c r="H14" t="n">
-        <v>26.8</v>
+        <v>276.7</v>
       </c>
       <c r="I14" t="n">
-        <v>21.1</v>
+        <v>212.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.34</v>
+        <v>3.29</v>
       </c>
       <c r="K14" t="n">
-        <v>1.04</v>
+        <v>2.53</v>
       </c>
       <c r="L14" t="n">
-        <v>9.41</v>
+        <v>9.26</v>
       </c>
       <c r="M14" t="n">
-        <v>7.19</v>
+        <v>7.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>3.49</v>
       </c>
       <c r="O14" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="P14" t="n">
-        <v>287.76</v>
+        <v>285.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>220.19</v>
+        <v>219.1</v>
       </c>
       <c r="R14" t="n">
-        <v>163.5</v>
+        <v>148.99</v>
       </c>
       <c r="S14" t="n">
-        <v>290.01</v>
+        <v>288.82</v>
       </c>
       <c r="T14" t="n">
-        <v>231.48</v>
+        <v>232.09</v>
       </c>
       <c r="U14" t="n">
-        <v>-11.29</v>
+        <v>-12.99</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -1462,70 +1462,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4000.1</v>
+        <v>3669.6</v>
       </c>
       <c r="E15" t="n">
-        <v>3065.6</v>
+        <v>2785.1</v>
       </c>
       <c r="F15" t="n">
-        <v>25.96</v>
+        <v>21.59</v>
       </c>
       <c r="G15" t="n">
-        <v>19.89</v>
+        <v>16.44</v>
       </c>
       <c r="H15" t="n">
-        <v>276.7</v>
+        <v>521.5</v>
       </c>
       <c r="I15" t="n">
-        <v>212.4</v>
+        <v>399.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="L15" t="n">
-        <v>9.26</v>
+        <v>8.81</v>
       </c>
       <c r="M15" t="n">
-        <v>7.08</v>
+        <v>6.74</v>
       </c>
       <c r="N15" t="n">
-        <v>3.49</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>285.75</v>
+        <v>283.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>219.1</v>
+        <v>215.59</v>
       </c>
       <c r="R15" t="n">
-        <v>148.99</v>
+        <v>146.01</v>
       </c>
       <c r="S15" t="n">
-        <v>288.82</v>
+        <v>284.81</v>
       </c>
       <c r="T15" t="n">
-        <v>232.09</v>
+        <v>245.55</v>
       </c>
       <c r="U15" t="n">
-        <v>-12.99</v>
+        <v>-29.96</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -1533,70 +1533,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3669.6</v>
+        <v>4040.9</v>
       </c>
       <c r="E16" t="n">
-        <v>2785.1</v>
+        <v>3083.4</v>
       </c>
       <c r="F16" t="n">
-        <v>21.59</v>
+        <v>26.29</v>
       </c>
       <c r="G16" t="n">
-        <v>16.44</v>
+        <v>20.13</v>
       </c>
       <c r="H16" t="n">
-        <v>521.5</v>
+        <v>224.6</v>
       </c>
       <c r="I16" t="n">
-        <v>399.3</v>
+        <v>172.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="L16" t="n">
-        <v>8.81</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>6.74</v>
+        <v>7.36</v>
       </c>
       <c r="N16" t="n">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="O16" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="P16" t="n">
-        <v>283.31</v>
+        <v>282.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>215.59</v>
+        <v>215.55</v>
       </c>
       <c r="R16" t="n">
-        <v>146.01</v>
+        <v>146.03</v>
       </c>
       <c r="S16" t="n">
-        <v>284.81</v>
+        <v>284.43</v>
       </c>
       <c r="T16" t="n">
-        <v>245.55</v>
+        <v>206.7</v>
       </c>
       <c r="U16" t="n">
-        <v>-29.96</v>
+        <v>8.85</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
@@ -1604,70 +1604,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4040.9</v>
+        <v>4006.2</v>
       </c>
       <c r="E17" t="n">
-        <v>3083.4</v>
+        <v>2833.8</v>
       </c>
       <c r="F17" t="n">
-        <v>26.29</v>
+        <v>31.1</v>
       </c>
       <c r="G17" t="n">
-        <v>20.13</v>
+        <v>21.93</v>
       </c>
       <c r="H17" t="n">
-        <v>224.6</v>
+        <v>282</v>
       </c>
       <c r="I17" t="n">
-        <v>172.5</v>
+        <v>199.4</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9</v>
+        <v>3.73</v>
       </c>
       <c r="K17" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="L17" t="n">
-        <v>9.630000000000001</v>
+        <v>11.95</v>
       </c>
       <c r="M17" t="n">
-        <v>7.36</v>
+        <v>8.43</v>
       </c>
       <c r="N17" t="n">
-        <v>2.51</v>
+        <v>3.74</v>
       </c>
       <c r="O17" t="n">
-        <v>1.93</v>
+        <v>2.64</v>
       </c>
       <c r="P17" t="n">
-        <v>282.38</v>
+        <v>303.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>215.55</v>
+        <v>214.77</v>
       </c>
       <c r="R17" t="n">
-        <v>146.03</v>
+        <v>150.54</v>
       </c>
       <c r="S17" t="n">
-        <v>284.43</v>
+        <v>279.17</v>
       </c>
       <c r="T17" t="n">
-        <v>206.7</v>
+        <v>227.65</v>
       </c>
       <c r="U17" t="n">
-        <v>8.85</v>
+        <v>-12.88</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -1675,70 +1675,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4006.2</v>
+        <v>3793</v>
       </c>
       <c r="E18" t="n">
-        <v>2833.8</v>
+        <v>2666.5</v>
       </c>
       <c r="F18" t="n">
-        <v>31.1</v>
+        <v>27.16</v>
       </c>
       <c r="G18" t="n">
-        <v>21.93</v>
+        <v>19.39</v>
       </c>
       <c r="H18" t="n">
-        <v>282</v>
+        <v>484.2</v>
       </c>
       <c r="I18" t="n">
-        <v>199.4</v>
+        <v>342.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.73</v>
+        <v>4.03</v>
       </c>
       <c r="K18" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="L18" t="n">
-        <v>11.95</v>
+        <v>11.29</v>
       </c>
       <c r="M18" t="n">
-        <v>8.43</v>
+        <v>7.97</v>
       </c>
       <c r="N18" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="O18" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>303.85</v>
+        <v>303.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>214.77</v>
+        <v>214.76</v>
       </c>
       <c r="R18" t="n">
-        <v>150.54</v>
+        <v>150.3</v>
       </c>
       <c r="S18" t="n">
-        <v>279.17</v>
+        <v>279.45</v>
       </c>
       <c r="T18" t="n">
-        <v>227.65</v>
+        <v>248.22</v>
       </c>
       <c r="U18" t="n">
-        <v>-12.88</v>
+        <v>-33.46</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
@@ -3016,64 +3016,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3493.8</v>
+        <v>3334.8</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>201.5</v>
       </c>
       <c r="F37" t="n">
-        <v>17.15</v>
+        <v>16.71</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="H37" t="n">
-        <v>828.8</v>
+        <v>269.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="J37" t="n">
-        <v>7.93</v>
+        <v>3.12</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="L37" t="n">
-        <v>13.56</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>4.31</v>
+        <v>2.44</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="P37" t="n">
-        <v>303.07</v>
+        <v>222.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.92</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>18.89</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3083,55 +3083,55 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3245.4</v>
+        <v>3493.8</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>14.44</v>
+        <v>17.15</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>188.6</v>
+        <v>828.8</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>17.41</v>
+        <v>13.56</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.71</v>
+        <v>4.31</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>182.68</v>
+        <v>303.07</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3142,67 +3142,63 @@
       <c r="S38" t="n">
         <v>0</v>
       </c>
-      <c r="T38" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="U38" t="n">
-        <v>-18.35</v>
-      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3445.5</v>
+        <v>3245.4</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>21.77</v>
+        <v>14.44</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>230.9</v>
+        <v>188.6</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>12.09</v>
+        <v>17.41</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>229.87</v>
+        <v>182.68</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3213,63 +3209,67 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-18.35</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3192</v>
+        <v>3445.5</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>13.87</v>
+        <v>21.77</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>185.8</v>
+        <v>230.9</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>17.33</v>
+        <v>12.09</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>178.2</v>
+        <v>229.87</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3288,55 +3288,55 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3595.6</v>
+        <v>3192</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>20.68</v>
+        <v>13.87</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>142.3</v>
+        <v>185.8</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1.91</v>
+        <v>3.09</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>12.54</v>
+        <v>17.33</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.31</v>
+        <v>3.71</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>220.53</v>
+        <v>178.2</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3355,55 +3355,55 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3425.4</v>
+        <v>3595.6</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>19.18</v>
+        <v>20.68</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>261.6</v>
+        <v>142.3</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2.67</v>
+        <v>1.91</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>11.07</v>
+        <v>12.54</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>3.31</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>228.48</v>
+        <v>220.53</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3422,55 +3422,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3389.5</v>
+        <v>3425.4</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>15.54</v>
+        <v>19.18</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>110</v>
+        <v>261.6</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.37</v>
+        <v>11.07</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>192.18</v>
+        <v>228.48</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3489,55 +3489,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3464.5</v>
+        <v>3389.5</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>16.87</v>
+        <v>15.54</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>272.3</v>
+        <v>110</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>3.77</v>
+        <v>1.83</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>10.99</v>
+        <v>10.37</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>225.49</v>
+        <v>192.18</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3548,67 +3548,63 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
-      <c r="T44" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="U44" t="n">
-        <v>-22.71</v>
-      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3458.5</v>
+        <v>3464.5</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>18.35</v>
+        <v>16.87</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>493.8</v>
+        <v>272.3</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>4.24</v>
+        <v>3.77</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>10.92</v>
+        <v>10.99</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.68</v>
+        <v>4.22</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>259.36</v>
+        <v>225.49</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3619,63 +3615,67 @@
       <c r="S45" t="n">
         <v>0</v>
       </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="T45" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="U45" t="n">
+        <v>-22.71</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3721.2</v>
+        <v>3458.5</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>18.82</v>
+        <v>18.35</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>322.8</v>
+        <v>493.8</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2.33</v>
+        <v>4.24</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.09</v>
+        <v>2.68</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>242.39</v>
+        <v>259.36</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3694,55 +3694,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3624.2</v>
+        <v>3721.2</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>25.51</v>
+        <v>18.82</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>33.3</v>
+        <v>322.8</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>11.45</v>
+        <v>10.91</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.51</v>
+        <v>3.09</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>230.92</v>
+        <v>242.39</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3761,55 +3761,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3453.5</v>
+        <v>3624.2</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>18</v>
+        <v>25.51</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>550.7</v>
+        <v>33.3</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4.93</v>
+        <v>1.75</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>11.1</v>
+        <v>11.45</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>265.99</v>
+        <v>230.92</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3828,55 +3828,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3281.7</v>
+        <v>3453.5</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>840.9</v>
+        <v>550.7</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>7.25</v>
+        <v>4.93</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>8.76</v>
+        <v>11.1</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>307.86</v>
+        <v>265.99</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3895,55 +3895,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3365.9</v>
+        <v>3281.7</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>16.39</v>
+        <v>18.4</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>188.9</v>
+        <v>840.9</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.88</v>
+        <v>7.25</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>11.86</v>
+        <v>8.76</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.23</v>
+        <v>3.54</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>200.19</v>
+        <v>307.86</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3962,55 +3962,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3478.8</v>
+        <v>3365.9</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>18.13</v>
+        <v>16.39</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>182.6</v>
+        <v>188.9</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>13.28</v>
+        <v>11.86</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.39</v>
+        <v>3.23</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>211.59</v>
+        <v>200.19</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4029,55 +4029,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3223.8</v>
+        <v>3478.8</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>14.11</v>
+        <v>18.13</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>182.7</v>
+        <v>182.6</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>17.31</v>
+        <v>13.28</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.72</v>
+        <v>3.39</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>180.14</v>
+        <v>211.59</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4096,55 +4096,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3647.5</v>
+        <v>3223.8</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>22.6</v>
+        <v>14.11</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>175.8</v>
+        <v>182.7</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>2.16</v>
+        <v>3.09</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10.67</v>
+        <v>17.31</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.59</v>
+        <v>3.72</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>240.32</v>
+        <v>180.14</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4163,55 +4163,55 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3669.6</v>
+        <v>3647.5</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>24.64</v>
+        <v>22.6</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>581.1</v>
+        <v>175.8</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>3.66</v>
+        <v>2.16</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>14.5</v>
+        <v>10.67</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.64</v>
+        <v>2.59</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>289.13</v>
+        <v>240.32</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4230,55 +4230,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3468.7</v>
+        <v>3669.6</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>20.51</v>
+        <v>24.64</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>148.9</v>
+        <v>581.1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1.85</v>
+        <v>3.66</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>9.44</v>
+        <v>14.5</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.23</v>
+        <v>3.64</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>221.44</v>
+        <v>289.13</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4297,55 +4297,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3603.6</v>
+        <v>3468.7</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>22.1</v>
+        <v>20.51</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>203.3</v>
+        <v>148.9</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>3.03</v>
+        <v>1.85</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>10.18</v>
+        <v>9.44</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.21</v>
+        <v>3.23</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>246.27</v>
+        <v>221.44</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4364,55 +4364,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3335.3</v>
+        <v>3603.6</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>17.6</v>
+        <v>22.1</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>150.5</v>
+        <v>203.3</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>12.98</v>
+        <v>10.18</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.81</v>
+        <v>2.21</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>199.68</v>
+        <v>246.27</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4431,55 +4431,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3347.6</v>
+        <v>3335.3</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>15.23</v>
+        <v>17.6</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>204.2</v>
+        <v>150.5</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>17.3</v>
+        <v>12.98</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.76</v>
+        <v>3.81</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>192.08</v>
+        <v>199.68</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4498,55 +4498,55 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>3425.1</v>
+        <v>3347.6</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>17.04</v>
+        <v>15.23</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>287.1</v>
+        <v>204.2</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>11.42</v>
+        <v>17.3</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.11</v>
+        <v>3.76</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>218.23</v>
+        <v>192.08</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4565,55 +4565,55 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3396.1</v>
+        <v>3425.1</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>15.86</v>
+        <v>17.04</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>182.8</v>
+        <v>287.1</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>15.84</v>
+        <v>11.42</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5.59</v>
+        <v>4.11</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>190.72</v>
+        <v>218.23</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4632,55 +4632,55 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tanner McKee</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3662.1</v>
+        <v>3396.1</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>23.48</v>
+        <v>15.86</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>58.1</v>
+        <v>182.8</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>12.28</v>
+        <v>15.84</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.76</v>
+        <v>5.59</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>229.99</v>
+        <v>190.72</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4699,55 +4699,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>3207.7</v>
+        <v>3662.1</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>15.48</v>
+        <v>23.48</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>447</v>
+        <v>58.1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>3.3</v>
+        <v>2.31</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>11.3</v>
+        <v>12.28</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.86</v>
+        <v>2.76</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>224.41</v>
+        <v>229.99</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4766,55 +4766,55 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>3462.3</v>
+        <v>3207.7</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>21.84</v>
+        <v>15.48</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>41.9</v>
+        <v>447</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>10.28</v>
+        <v>11.3</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.42</v>
+        <v>3.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>212.36</v>
+        <v>224.41</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -4825,67 +4825,63 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="n">
-        <v>61.64</v>
-      </c>
-      <c r="U63" t="n">
-        <v>-61.64</v>
-      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>3590.2</v>
+        <v>3462.3</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>22.85</v>
+        <v>21.84</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>545.3</v>
+        <v>41.9</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>4.16</v>
+        <v>1.62</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>10.53</v>
+        <v>10.28</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.89</v>
+        <v>3.42</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>287.66</v>
+        <v>212.36</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -4896,63 +4892,67 @@
       <c r="S64" t="n">
         <v>0</v>
       </c>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
+      <c r="T64" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="U64" t="n">
+        <v>-61.64</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>3334.8</v>
+        <v>3590.2</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>16.71</v>
+        <v>22.85</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>269.5</v>
+        <v>545.3</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>3.12</v>
+        <v>4.16</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>9.460000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.44</v>
+        <v>2.89</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>222.1</v>
+        <v>287.66</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5741,70 +5741,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3793</v>
+        <v>4621.9</v>
       </c>
       <c r="E11" t="n">
-        <v>2894.9</v>
+        <v>3261.8</v>
       </c>
       <c r="F11" t="n">
-        <v>27.16</v>
+        <v>34.98</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>24.64</v>
       </c>
       <c r="H11" t="n">
-        <v>484.2</v>
+        <v>183.6</v>
       </c>
       <c r="I11" t="n">
-        <v>370.6</v>
+        <v>129.7</v>
       </c>
       <c r="J11" t="n">
-        <v>4.03</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="n">
-        <v>3.11</v>
+        <v>1.77</v>
       </c>
       <c r="L11" t="n">
-        <v>11.29</v>
+        <v>12.19</v>
       </c>
       <c r="M11" t="n">
-        <v>8.630000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.54</v>
+        <v>3.06</v>
       </c>
       <c r="O11" t="n">
-        <v>2.71</v>
+        <v>2.16</v>
       </c>
       <c r="P11" t="n">
-        <v>303.3</v>
+        <v>327.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>232.84</v>
+        <v>231.1</v>
       </c>
       <c r="R11" t="n">
-        <v>162.96</v>
+        <v>166.9</v>
       </c>
       <c r="S11" t="n">
-        <v>302.98</v>
+        <v>295.48</v>
       </c>
       <c r="T11" t="n">
-        <v>248.22</v>
+        <v>227.93</v>
       </c>
       <c r="U11" t="n">
-        <v>-15.38</v>
+        <v>3.17</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -5812,70 +5812,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4621.9</v>
+        <v>4184.8</v>
       </c>
       <c r="E12" t="n">
-        <v>3261.8</v>
+        <v>3188.4</v>
       </c>
       <c r="F12" t="n">
-        <v>34.98</v>
+        <v>26.33</v>
       </c>
       <c r="G12" t="n">
-        <v>24.64</v>
+        <v>20.07</v>
       </c>
       <c r="H12" t="n">
-        <v>183.6</v>
+        <v>290</v>
       </c>
       <c r="I12" t="n">
-        <v>129.7</v>
+        <v>222.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>1.77</v>
+        <v>2.76</v>
       </c>
       <c r="L12" t="n">
-        <v>12.19</v>
+        <v>11.67</v>
       </c>
       <c r="M12" t="n">
-        <v>8.6</v>
+        <v>8.93</v>
       </c>
       <c r="N12" t="n">
-        <v>3.06</v>
+        <v>4.43</v>
       </c>
       <c r="O12" t="n">
-        <v>2.16</v>
+        <v>3.38</v>
       </c>
       <c r="P12" t="n">
-        <v>327.78</v>
+        <v>291.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>231.1</v>
+        <v>222</v>
       </c>
       <c r="R12" t="n">
-        <v>166.9</v>
+        <v>152.77</v>
       </c>
       <c r="S12" t="n">
-        <v>295.48</v>
+        <v>291.4</v>
       </c>
       <c r="T12" t="n">
-        <v>227.93</v>
+        <v>222.53</v>
       </c>
       <c r="U12" t="n">
-        <v>3.17</v>
+        <v>-0.53</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -5883,70 +5883,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4184.8</v>
+        <v>4429.5</v>
       </c>
       <c r="E13" t="n">
-        <v>3188.4</v>
+        <v>3387.4</v>
       </c>
       <c r="F13" t="n">
-        <v>26.33</v>
+        <v>31.33</v>
       </c>
       <c r="G13" t="n">
-        <v>20.07</v>
+        <v>23.95</v>
       </c>
       <c r="H13" t="n">
-        <v>290</v>
+        <v>26.8</v>
       </c>
       <c r="I13" t="n">
-        <v>222.4</v>
+        <v>21.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>1.34</v>
       </c>
       <c r="K13" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="L13" t="n">
-        <v>11.67</v>
+        <v>9.41</v>
       </c>
       <c r="M13" t="n">
-        <v>8.93</v>
+        <v>7.19</v>
       </c>
       <c r="N13" t="n">
-        <v>4.43</v>
+        <v>3.32</v>
       </c>
       <c r="O13" t="n">
-        <v>3.38</v>
+        <v>2.54</v>
       </c>
       <c r="P13" t="n">
-        <v>291.11</v>
+        <v>287.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>222</v>
+        <v>220.19</v>
       </c>
       <c r="R13" t="n">
-        <v>152.77</v>
+        <v>163.5</v>
       </c>
       <c r="S13" t="n">
-        <v>291.4</v>
+        <v>290.01</v>
       </c>
       <c r="T13" t="n">
-        <v>222.53</v>
+        <v>231.48</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.53</v>
+        <v>-11.29</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -5954,70 +5954,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4429.5</v>
+        <v>4000.1</v>
       </c>
       <c r="E14" t="n">
-        <v>3387.4</v>
+        <v>3065.6</v>
       </c>
       <c r="F14" t="n">
-        <v>31.33</v>
+        <v>25.96</v>
       </c>
       <c r="G14" t="n">
-        <v>23.95</v>
+        <v>19.89</v>
       </c>
       <c r="H14" t="n">
-        <v>26.8</v>
+        <v>276.7</v>
       </c>
       <c r="I14" t="n">
-        <v>21.1</v>
+        <v>212.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.34</v>
+        <v>3.29</v>
       </c>
       <c r="K14" t="n">
-        <v>1.04</v>
+        <v>2.53</v>
       </c>
       <c r="L14" t="n">
-        <v>9.41</v>
+        <v>9.26</v>
       </c>
       <c r="M14" t="n">
-        <v>7.19</v>
+        <v>7.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>3.49</v>
       </c>
       <c r="O14" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="P14" t="n">
-        <v>287.76</v>
+        <v>285.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>220.19</v>
+        <v>219.1</v>
       </c>
       <c r="R14" t="n">
-        <v>163.5</v>
+        <v>148.99</v>
       </c>
       <c r="S14" t="n">
-        <v>290.01</v>
+        <v>288.82</v>
       </c>
       <c r="T14" t="n">
-        <v>231.48</v>
+        <v>232.09</v>
       </c>
       <c r="U14" t="n">
-        <v>-11.29</v>
+        <v>-12.99</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -6025,70 +6025,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4000.1</v>
+        <v>3669.6</v>
       </c>
       <c r="E15" t="n">
-        <v>3065.6</v>
+        <v>2785.1</v>
       </c>
       <c r="F15" t="n">
-        <v>25.96</v>
+        <v>21.59</v>
       </c>
       <c r="G15" t="n">
-        <v>19.89</v>
+        <v>16.44</v>
       </c>
       <c r="H15" t="n">
-        <v>276.7</v>
+        <v>521.5</v>
       </c>
       <c r="I15" t="n">
-        <v>212.4</v>
+        <v>399.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="L15" t="n">
-        <v>9.26</v>
+        <v>8.81</v>
       </c>
       <c r="M15" t="n">
-        <v>7.08</v>
+        <v>6.74</v>
       </c>
       <c r="N15" t="n">
-        <v>3.49</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>285.75</v>
+        <v>283.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>219.1</v>
+        <v>215.59</v>
       </c>
       <c r="R15" t="n">
-        <v>148.99</v>
+        <v>146.01</v>
       </c>
       <c r="S15" t="n">
-        <v>288.82</v>
+        <v>284.81</v>
       </c>
       <c r="T15" t="n">
-        <v>232.09</v>
+        <v>245.55</v>
       </c>
       <c r="U15" t="n">
-        <v>-12.99</v>
+        <v>-29.96</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -6096,70 +6096,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3669.6</v>
+        <v>4040.9</v>
       </c>
       <c r="E16" t="n">
-        <v>2785.1</v>
+        <v>3083.4</v>
       </c>
       <c r="F16" t="n">
-        <v>21.59</v>
+        <v>26.29</v>
       </c>
       <c r="G16" t="n">
-        <v>16.44</v>
+        <v>20.13</v>
       </c>
       <c r="H16" t="n">
-        <v>521.5</v>
+        <v>224.6</v>
       </c>
       <c r="I16" t="n">
-        <v>399.3</v>
+        <v>172.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="L16" t="n">
-        <v>8.81</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>6.74</v>
+        <v>7.36</v>
       </c>
       <c r="N16" t="n">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="O16" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="P16" t="n">
-        <v>283.31</v>
+        <v>282.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>215.59</v>
+        <v>215.55</v>
       </c>
       <c r="R16" t="n">
-        <v>146.01</v>
+        <v>146.03</v>
       </c>
       <c r="S16" t="n">
-        <v>284.81</v>
+        <v>284.43</v>
       </c>
       <c r="T16" t="n">
-        <v>245.55</v>
+        <v>206.7</v>
       </c>
       <c r="U16" t="n">
-        <v>-29.96</v>
+        <v>8.85</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
@@ -6167,70 +6167,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4040.9</v>
+        <v>4006.2</v>
       </c>
       <c r="E17" t="n">
-        <v>3083.4</v>
+        <v>2833.8</v>
       </c>
       <c r="F17" t="n">
-        <v>26.29</v>
+        <v>31.1</v>
       </c>
       <c r="G17" t="n">
-        <v>20.13</v>
+        <v>21.93</v>
       </c>
       <c r="H17" t="n">
-        <v>224.6</v>
+        <v>282</v>
       </c>
       <c r="I17" t="n">
-        <v>172.5</v>
+        <v>199.4</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9</v>
+        <v>3.73</v>
       </c>
       <c r="K17" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="L17" t="n">
-        <v>9.630000000000001</v>
+        <v>11.95</v>
       </c>
       <c r="M17" t="n">
-        <v>7.36</v>
+        <v>8.43</v>
       </c>
       <c r="N17" t="n">
-        <v>2.51</v>
+        <v>3.74</v>
       </c>
       <c r="O17" t="n">
-        <v>1.93</v>
+        <v>2.64</v>
       </c>
       <c r="P17" t="n">
-        <v>282.38</v>
+        <v>303.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>215.55</v>
+        <v>214.77</v>
       </c>
       <c r="R17" t="n">
-        <v>146.03</v>
+        <v>150.54</v>
       </c>
       <c r="S17" t="n">
-        <v>284.43</v>
+        <v>279.17</v>
       </c>
       <c r="T17" t="n">
-        <v>206.7</v>
+        <v>227.65</v>
       </c>
       <c r="U17" t="n">
-        <v>8.85</v>
+        <v>-12.88</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -6238,70 +6238,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4006.2</v>
+        <v>3793</v>
       </c>
       <c r="E18" t="n">
-        <v>2833.8</v>
+        <v>2666.5</v>
       </c>
       <c r="F18" t="n">
-        <v>31.1</v>
+        <v>27.16</v>
       </c>
       <c r="G18" t="n">
-        <v>21.93</v>
+        <v>19.39</v>
       </c>
       <c r="H18" t="n">
-        <v>282</v>
+        <v>484.2</v>
       </c>
       <c r="I18" t="n">
-        <v>199.4</v>
+        <v>342.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.73</v>
+        <v>4.03</v>
       </c>
       <c r="K18" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="L18" t="n">
-        <v>11.95</v>
+        <v>11.29</v>
       </c>
       <c r="M18" t="n">
-        <v>8.43</v>
+        <v>7.97</v>
       </c>
       <c r="N18" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="O18" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>303.85</v>
+        <v>303.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>214.77</v>
+        <v>214.76</v>
       </c>
       <c r="R18" t="n">
-        <v>150.54</v>
+        <v>150.3</v>
       </c>
       <c r="S18" t="n">
-        <v>279.17</v>
+        <v>279.45</v>
       </c>
       <c r="T18" t="n">
-        <v>227.65</v>
+        <v>248.22</v>
       </c>
       <c r="U18" t="n">
-        <v>-12.88</v>
+        <v>-33.46</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
@@ -7710,64 +7710,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3493.8</v>
+        <v>3334.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>201.5</v>
       </c>
       <c r="F5" t="n">
-        <v>17.15</v>
+        <v>16.71</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="H5" t="n">
-        <v>828.8</v>
+        <v>269.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="J5" t="n">
-        <v>7.93</v>
+        <v>3.12</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="L5" t="n">
-        <v>13.56</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>4.31</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="P5" t="n">
-        <v>303.07</v>
+        <v>222.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>7.92</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>18.89</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -7777,55 +7777,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3245.4</v>
+        <v>3493.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>14.44</v>
+        <v>17.15</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>188.6</v>
+        <v>828.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>17.41</v>
+        <v>13.56</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.71</v>
+        <v>4.31</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>182.68</v>
+        <v>303.07</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -7836,67 +7836,63 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-18.35</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3445.5</v>
+        <v>3245.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>21.77</v>
+        <v>14.44</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>230.9</v>
+        <v>188.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>12.09</v>
+        <v>17.41</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>229.87</v>
+        <v>182.68</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -7907,63 +7903,67 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-18.35</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3192</v>
+        <v>3445.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>13.87</v>
+        <v>21.77</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>185.8</v>
+        <v>230.9</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17.33</v>
+        <v>12.09</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>178.2</v>
+        <v>229.87</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -7982,55 +7982,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3595.6</v>
+        <v>3192</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>20.68</v>
+        <v>13.87</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>142.3</v>
+        <v>185.8</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.91</v>
+        <v>3.09</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>12.54</v>
+        <v>17.33</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.31</v>
+        <v>3.71</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>220.53</v>
+        <v>178.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8049,55 +8049,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3425.4</v>
+        <v>3595.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>19.18</v>
+        <v>20.68</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>261.6</v>
+        <v>142.3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>1.91</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11.07</v>
+        <v>12.54</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>3.31</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>228.48</v>
+        <v>220.53</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8116,55 +8116,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3389.5</v>
+        <v>3425.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>15.54</v>
+        <v>19.18</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>110</v>
+        <v>261.6</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10.37</v>
+        <v>11.07</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>192.18</v>
+        <v>228.48</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8183,55 +8183,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3464.5</v>
+        <v>3389.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>16.87</v>
+        <v>15.54</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>272.3</v>
+        <v>110</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3.77</v>
+        <v>1.83</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10.99</v>
+        <v>10.37</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>225.49</v>
+        <v>192.18</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8242,67 +8242,63 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-22.71</v>
-      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3458.5</v>
+        <v>3464.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>18.35</v>
+        <v>16.87</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>493.8</v>
+        <v>272.3</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>4.24</v>
+        <v>3.77</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.92</v>
+        <v>10.99</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.68</v>
+        <v>4.22</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>259.36</v>
+        <v>225.49</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8313,63 +8309,67 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-22.71</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3721.2</v>
+        <v>3458.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>18.82</v>
+        <v>18.35</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>322.8</v>
+        <v>493.8</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>4.24</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.09</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>242.39</v>
+        <v>259.36</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8388,55 +8388,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3624.2</v>
+        <v>3721.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>25.51</v>
+        <v>18.82</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>33.3</v>
+        <v>322.8</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>11.45</v>
+        <v>10.91</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.51</v>
+        <v>3.09</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>230.92</v>
+        <v>242.39</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8455,55 +8455,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3453.5</v>
+        <v>3624.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>25.51</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>550.7</v>
+        <v>33.3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.93</v>
+        <v>1.75</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>11.1</v>
+        <v>11.45</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>265.99</v>
+        <v>230.92</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -8522,55 +8522,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3281.7</v>
+        <v>3453.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>840.9</v>
+        <v>550.7</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7.25</v>
+        <v>4.93</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8.76</v>
+        <v>11.1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>307.86</v>
+        <v>265.99</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -8589,55 +8589,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3365.9</v>
+        <v>3281.7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>16.39</v>
+        <v>18.4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>188.9</v>
+        <v>840.9</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.88</v>
+        <v>7.25</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>11.86</v>
+        <v>8.76</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.23</v>
+        <v>3.54</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>200.19</v>
+        <v>307.86</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -8656,55 +8656,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3478.8</v>
+        <v>3365.9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>18.13</v>
+        <v>16.39</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>182.6</v>
+        <v>188.9</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>13.28</v>
+        <v>11.86</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.39</v>
+        <v>3.23</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>211.59</v>
+        <v>200.19</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -8723,55 +8723,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3223.8</v>
+        <v>3478.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>14.11</v>
+        <v>18.13</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>182.7</v>
+        <v>182.6</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>17.31</v>
+        <v>13.28</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.72</v>
+        <v>3.39</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>180.14</v>
+        <v>211.59</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -8790,55 +8790,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3647.5</v>
+        <v>3223.8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>22.6</v>
+        <v>14.11</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>175.8</v>
+        <v>182.7</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.16</v>
+        <v>3.09</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>10.67</v>
+        <v>17.31</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.59</v>
+        <v>3.72</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>240.32</v>
+        <v>180.14</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -8857,55 +8857,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3669.6</v>
+        <v>3647.5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>24.64</v>
+        <v>22.6</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>581.1</v>
+        <v>175.8</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3.66</v>
+        <v>2.16</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>14.5</v>
+        <v>10.67</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.64</v>
+        <v>2.59</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>289.13</v>
+        <v>240.32</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -8924,55 +8924,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3468.7</v>
+        <v>3669.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>20.51</v>
+        <v>24.64</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>148.9</v>
+        <v>581.1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.85</v>
+        <v>3.66</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>9.44</v>
+        <v>14.5</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.23</v>
+        <v>3.64</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>221.44</v>
+        <v>289.13</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -8991,55 +8991,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3603.6</v>
+        <v>3468.7</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>22.1</v>
+        <v>20.51</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>203.3</v>
+        <v>148.9</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3.03</v>
+        <v>1.85</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>10.18</v>
+        <v>9.44</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.21</v>
+        <v>3.23</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>246.27</v>
+        <v>221.44</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -9058,55 +9058,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3335.3</v>
+        <v>3603.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>17.6</v>
+        <v>22.1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>150.5</v>
+        <v>203.3</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>12.98</v>
+        <v>10.18</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.81</v>
+        <v>2.21</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>199.68</v>
+        <v>246.27</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -9125,55 +9125,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3347.6</v>
+        <v>3335.3</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>15.23</v>
+        <v>17.6</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>204.2</v>
+        <v>150.5</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>17.3</v>
+        <v>12.98</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.76</v>
+        <v>3.81</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>192.08</v>
+        <v>199.68</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -9192,55 +9192,55 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3425.1</v>
+        <v>3347.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>17.04</v>
+        <v>15.23</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>287.1</v>
+        <v>204.2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>11.42</v>
+        <v>17.3</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.11</v>
+        <v>3.76</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>218.23</v>
+        <v>192.08</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -9259,55 +9259,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3396.1</v>
+        <v>3425.1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>15.86</v>
+        <v>17.04</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>182.8</v>
+        <v>287.1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>15.84</v>
+        <v>11.42</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.59</v>
+        <v>4.11</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>190.72</v>
+        <v>218.23</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -9326,55 +9326,55 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tanner McKee</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3662.1</v>
+        <v>3396.1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>23.48</v>
+        <v>15.86</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>58.1</v>
+        <v>182.8</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>12.28</v>
+        <v>15.84</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.76</v>
+        <v>5.59</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>229.99</v>
+        <v>190.72</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -9393,55 +9393,55 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3207.7</v>
+        <v>3662.1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>15.48</v>
+        <v>23.48</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>447</v>
+        <v>58.1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>3.3</v>
+        <v>2.31</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>11.3</v>
+        <v>12.28</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.86</v>
+        <v>2.76</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>224.41</v>
+        <v>229.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -9460,55 +9460,55 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3462.3</v>
+        <v>3207.7</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>21.84</v>
+        <v>15.48</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>41.9</v>
+        <v>447</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.28</v>
+        <v>11.3</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.42</v>
+        <v>3.86</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>212.36</v>
+        <v>224.41</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -9519,67 +9519,63 @@
       <c r="S31" t="n">
         <v>0</v>
       </c>
-      <c r="T31" t="n">
-        <v>61.64</v>
-      </c>
-      <c r="U31" t="n">
-        <v>-61.64</v>
-      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tyrod Taylor</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3590.2</v>
+        <v>3462.3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>22.85</v>
+        <v>21.84</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>545.3</v>
+        <v>41.9</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>4.16</v>
+        <v>1.62</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>10.53</v>
+        <v>10.28</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.89</v>
+        <v>3.42</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>287.66</v>
+        <v>212.36</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -9590,63 +9586,67 @@
       <c r="S32" t="n">
         <v>0</v>
       </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-61.64</v>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Tyrod Taylor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>3334.8</v>
+        <v>3590.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>16.71</v>
+        <v>22.85</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>269.5</v>
+        <v>545.3</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3.12</v>
+        <v>4.16</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>9.460000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.44</v>
+        <v>2.89</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>222.1</v>
+        <v>287.66</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -17013,67 +17013,67 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>228.415</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1.612</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>28.049</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.239</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0.664</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>0.207</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>135.295</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>321.535</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>0.5580000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.017</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>9.709</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>48.941</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.803</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>18.078</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>3.904</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>33.758</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="inlineStr"/>
     </row>
@@ -85275,67 +85275,67 @@
         <v>0</v>
       </c>
       <c r="H813" t="n">
-        <v>0</v>
+        <v>201.465</v>
       </c>
       <c r="I813" t="n">
-        <v>0</v>
+        <v>1.032</v>
       </c>
       <c r="J813" t="n">
-        <v>0</v>
+        <v>15.418</v>
       </c>
       <c r="K813" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="L813" t="n">
-        <v>0</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="M813" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="N813" t="n">
-        <v>0</v>
+        <v>108.345</v>
       </c>
       <c r="O813" t="n">
-        <v>0</v>
+        <v>294.585</v>
       </c>
       <c r="P813" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="Q813" t="n">
-        <v>0</v>
+        <v>2.437</v>
       </c>
       <c r="R813" t="n">
-        <v>0</v>
+        <v>5.337</v>
       </c>
       <c r="S813" t="n">
-        <v>0</v>
+        <v>36.31</v>
       </c>
       <c r="T813" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="U813" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="V813" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="W813" t="n">
-        <v>0</v>
+        <v>1.692</v>
       </c>
       <c r="X813" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="Y813" t="n">
-        <v>0</v>
+        <v>0.738</v>
       </c>
       <c r="Z813" t="n">
-        <v>0</v>
+        <v>13.386</v>
       </c>
       <c r="AA813" t="n">
-        <v>0</v>
+        <v>1.801</v>
       </c>
       <c r="AB813" t="n">
-        <v>0</v>
+        <v>28.842</v>
       </c>
       <c r="AC813" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -2030,70 +2030,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3711</v>
+        <v>3362.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>2359.3</v>
       </c>
       <c r="F23" t="n">
-        <v>24.01</v>
+        <v>19.45</v>
       </c>
       <c r="G23" t="n">
-        <v>16.95</v>
+        <v>13.69</v>
       </c>
       <c r="H23" t="n">
-        <v>293.1</v>
+        <v>602.9</v>
       </c>
       <c r="I23" t="n">
-        <v>207.2</v>
+        <v>426.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.95</v>
+        <v>3.94</v>
       </c>
       <c r="K23" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="L23" t="n">
-        <v>11.91</v>
+        <v>14.25</v>
       </c>
       <c r="M23" t="n">
-        <v>8.41</v>
+        <v>10.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.53</v>
+        <v>4.06</v>
       </c>
       <c r="O23" t="n">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="P23" t="n">
-        <v>260.61</v>
+        <v>259.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>183.44</v>
+        <v>182.61</v>
       </c>
       <c r="R23" t="n">
-        <v>119.32</v>
+        <v>118.51</v>
       </c>
       <c r="S23" t="n">
-        <v>247.68</v>
+        <v>246.79</v>
       </c>
       <c r="T23" t="n">
-        <v>202.09</v>
+        <v>192.85</v>
       </c>
       <c r="U23" t="n">
-        <v>-18.65</v>
+        <v>-10.24</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
@@ -2101,70 +2101,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3362.7</v>
+        <v>3802.6</v>
       </c>
       <c r="E24" t="n">
-        <v>2359.3</v>
+        <v>2685.3</v>
       </c>
       <c r="F24" t="n">
-        <v>19.45</v>
+        <v>21.99</v>
       </c>
       <c r="G24" t="n">
-        <v>13.69</v>
+        <v>15.47</v>
       </c>
       <c r="H24" t="n">
-        <v>602.9</v>
+        <v>282.6</v>
       </c>
       <c r="I24" t="n">
-        <v>426.2</v>
+        <v>200</v>
       </c>
       <c r="J24" t="n">
-        <v>3.94</v>
+        <v>2.93</v>
       </c>
       <c r="K24" t="n">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="L24" t="n">
-        <v>14.25</v>
+        <v>11.01</v>
       </c>
       <c r="M24" t="n">
-        <v>10.06</v>
+        <v>7.77</v>
       </c>
       <c r="N24" t="n">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="O24" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="P24" t="n">
-        <v>259.62</v>
+        <v>255.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>182.61</v>
+        <v>180.37</v>
       </c>
       <c r="R24" t="n">
-        <v>118.51</v>
+        <v>116.23</v>
       </c>
       <c r="S24" t="n">
-        <v>246.79</v>
+        <v>244.65</v>
       </c>
       <c r="T24" t="n">
-        <v>192.85</v>
+        <v>192.14</v>
       </c>
       <c r="U24" t="n">
-        <v>-10.24</v>
+        <v>-11.77</v>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
@@ -2172,70 +2172,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3802.6</v>
+        <v>3747.9</v>
       </c>
       <c r="E25" t="n">
-        <v>2685.3</v>
+        <v>2632.3</v>
       </c>
       <c r="F25" t="n">
-        <v>21.99</v>
+        <v>23.28</v>
       </c>
       <c r="G25" t="n">
-        <v>15.47</v>
+        <v>16.43</v>
       </c>
       <c r="H25" t="n">
-        <v>282.6</v>
+        <v>239</v>
       </c>
       <c r="I25" t="n">
-        <v>200</v>
+        <v>169.1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="K25" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="L25" t="n">
-        <v>11.01</v>
+        <v>10.64</v>
       </c>
       <c r="M25" t="n">
-        <v>7.77</v>
+        <v>7.51</v>
       </c>
       <c r="N25" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="O25" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>255.6</v>
+        <v>253.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>180.37</v>
+        <v>178.44</v>
       </c>
       <c r="R25" t="n">
-        <v>116.23</v>
+        <v>114.1</v>
       </c>
       <c r="S25" t="n">
-        <v>244.65</v>
+        <v>242.57</v>
       </c>
       <c r="T25" t="n">
-        <v>192.14</v>
+        <v>143.44</v>
       </c>
       <c r="U25" t="n">
-        <v>-11.77</v>
+        <v>35</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
@@ -2243,208 +2243,208 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3747.9</v>
+        <v>3761.5</v>
       </c>
       <c r="E26" t="n">
-        <v>2632.3</v>
+        <v>2640.3</v>
       </c>
       <c r="F26" t="n">
-        <v>23.28</v>
+        <v>25.84</v>
       </c>
       <c r="G26" t="n">
-        <v>16.43</v>
+        <v>17.96</v>
       </c>
       <c r="H26" t="n">
-        <v>239</v>
+        <v>201.2</v>
       </c>
       <c r="I26" t="n">
-        <v>169.1</v>
+        <v>142.8</v>
       </c>
       <c r="J26" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="K26" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="L26" t="n">
-        <v>10.64</v>
+        <v>14.05</v>
       </c>
       <c r="M26" t="n">
-        <v>7.51</v>
+        <v>9.92</v>
       </c>
       <c r="N26" t="n">
-        <v>4.11</v>
+        <v>3.54</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>253.34</v>
+        <v>252.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>178.44</v>
+        <v>176.37</v>
       </c>
       <c r="R26" t="n">
-        <v>114.1</v>
+        <v>113.96</v>
       </c>
       <c r="S26" t="n">
-        <v>242.57</v>
-      </c>
-      <c r="T26" t="n">
-        <v>143.44</v>
-      </c>
-      <c r="U26" t="n">
-        <v>35</v>
-      </c>
+        <v>240.28</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3761.5</v>
+        <v>3932.2</v>
       </c>
       <c r="E27" t="n">
-        <v>2640.3</v>
+        <v>2756.7</v>
       </c>
       <c r="F27" t="n">
-        <v>25.84</v>
+        <v>24.37</v>
       </c>
       <c r="G27" t="n">
-        <v>17.96</v>
+        <v>17.11</v>
       </c>
       <c r="H27" t="n">
-        <v>201.2</v>
+        <v>94.2</v>
       </c>
       <c r="I27" t="n">
-        <v>142.8</v>
+        <v>67</v>
       </c>
       <c r="J27" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="K27" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="L27" t="n">
-        <v>14.05</v>
+        <v>10.84</v>
       </c>
       <c r="M27" t="n">
-        <v>9.92</v>
+        <v>7.65</v>
       </c>
       <c r="N27" t="n">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>252.14</v>
+        <v>249.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>176.37</v>
+        <v>175.17</v>
       </c>
       <c r="R27" t="n">
-        <v>113.96</v>
+        <v>114.38</v>
       </c>
       <c r="S27" t="n">
-        <v>240.28</v>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+        <v>238.84</v>
+      </c>
+      <c r="T27" t="n">
+        <v>106.66</v>
+      </c>
+      <c r="U27" t="n">
+        <v>68.51000000000001</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3932.2</v>
+        <v>3638.5</v>
       </c>
       <c r="E28" t="n">
-        <v>2756.7</v>
+        <v>2552.3</v>
       </c>
       <c r="F28" t="n">
-        <v>24.37</v>
+        <v>25.55</v>
       </c>
       <c r="G28" t="n">
-        <v>17.11</v>
+        <v>17.81</v>
       </c>
       <c r="H28" t="n">
-        <v>94.2</v>
+        <v>141.6</v>
       </c>
       <c r="I28" t="n">
-        <v>67</v>
+        <v>100.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="K28" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="L28" t="n">
-        <v>10.84</v>
+        <v>8.69</v>
       </c>
       <c r="M28" t="n">
-        <v>7.65</v>
+        <v>6.13</v>
       </c>
       <c r="N28" t="n">
-        <v>3.26</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="P28" t="n">
-        <v>249.79</v>
+        <v>248.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>175.17</v>
+        <v>173.8</v>
       </c>
       <c r="R28" t="n">
-        <v>114.38</v>
+        <v>112.92</v>
       </c>
       <c r="S28" t="n">
-        <v>238.84</v>
+        <v>237.73</v>
       </c>
       <c r="T28" t="n">
-        <v>106.66</v>
+        <v>179.01</v>
       </c>
       <c r="U28" t="n">
-        <v>68.51000000000001</v>
+        <v>-5.21</v>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
@@ -2452,70 +2452,70 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3638.5</v>
+        <v>3711</v>
       </c>
       <c r="E29" t="n">
-        <v>2552.3</v>
+        <v>2387.4</v>
       </c>
       <c r="F29" t="n">
-        <v>25.55</v>
+        <v>24.01</v>
       </c>
       <c r="G29" t="n">
-        <v>17.81</v>
+        <v>15.55</v>
       </c>
       <c r="H29" t="n">
-        <v>141.6</v>
+        <v>293.1</v>
       </c>
       <c r="I29" t="n">
-        <v>100.5</v>
+        <v>189.7</v>
       </c>
       <c r="J29" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="K29" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="L29" t="n">
-        <v>8.69</v>
+        <v>11.91</v>
       </c>
       <c r="M29" t="n">
-        <v>6.13</v>
+        <v>7.7</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>3.53</v>
       </c>
       <c r="O29" t="n">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="P29" t="n">
-        <v>248.12</v>
+        <v>260.61</v>
       </c>
       <c r="Q29" t="n">
-        <v>173.8</v>
+        <v>168.15</v>
       </c>
       <c r="R29" t="n">
-        <v>112.92</v>
+        <v>109.37</v>
       </c>
       <c r="S29" t="n">
-        <v>237.73</v>
+        <v>227.04</v>
       </c>
       <c r="T29" t="n">
-        <v>179.01</v>
+        <v>202.09</v>
       </c>
       <c r="U29" t="n">
-        <v>-5.21</v>
+        <v>-33.94</v>
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
@@ -2949,64 +2949,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3454</v>
+        <v>3439.8</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>202.6</v>
       </c>
       <c r="F36" t="n">
-        <v>17.15</v>
+        <v>18.36</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="H36" t="n">
-        <v>828.4</v>
+        <v>493.8</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="J36" t="n">
-        <v>7.93</v>
+        <v>4.24</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="L36" t="n">
-        <v>13.69</v>
+        <v>10.92</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="N36" t="n">
-        <v>4.48</v>
+        <v>2.68</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="P36" t="n">
-        <v>300.84</v>
+        <v>258.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>15.15</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>9.81</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>20.48</v>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -3016,55 +3016,55 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3169.6</v>
+        <v>3454</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>14.24</v>
+        <v>17.15</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>187.4</v>
+        <v>828.4</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>17.31</v>
+        <v>13.69</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.71</v>
+        <v>4.48</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>178.92</v>
+        <v>300.84</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3075,67 +3075,63 @@
       <c r="S37" t="n">
         <v>0</v>
       </c>
-      <c r="T37" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="U37" t="n">
-        <v>-16.94</v>
-      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3417.5</v>
+        <v>3169.6</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>21.65</v>
+        <v>14.24</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>230.4</v>
+        <v>187.4</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>10.45</v>
+        <v>17.31</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>231.7</v>
+        <v>178.92</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3146,63 +3142,67 @@
       <c r="S38" t="n">
         <v>0</v>
       </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-16.94</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3052</v>
+        <v>3417.5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>14.48</v>
+        <v>21.65</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>182.8</v>
+        <v>230.4</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>17.4</v>
+        <v>10.45</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>174.6</v>
+        <v>231.7</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3221,55 +3221,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3546.8</v>
+        <v>3052</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>20.76</v>
+        <v>14.48</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>143.7</v>
+        <v>182.8</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>12.54</v>
+        <v>17.4</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>219</v>
+        <v>174.6</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3288,55 +3288,55 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3427.7</v>
+        <v>3546.8</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>19.25</v>
+        <v>20.76</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>258</v>
+        <v>143.7</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>11.24</v>
+        <v>12.54</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>228.61</v>
+        <v>219</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3355,55 +3355,55 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3356.1</v>
+        <v>3427.7</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>15.53</v>
+        <v>19.25</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>110.3</v>
+        <v>258</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>10.42</v>
+        <v>11.24</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>190.73</v>
+        <v>228.61</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3422,55 +3422,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3536.7</v>
+        <v>3356.1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>16.69</v>
+        <v>15.53</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>271.4</v>
+        <v>110.3</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>3.69</v>
+        <v>1.83</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.72</v>
+        <v>10.42</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>229.17</v>
+        <v>190.73</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3481,67 +3481,63 @@
       <c r="S43" t="n">
         <v>0</v>
       </c>
-      <c r="T43" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="U43" t="n">
-        <v>-20.96</v>
-      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3439.8</v>
+        <v>3536.7</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>18.36</v>
+        <v>16.69</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>493.8</v>
+        <v>271.4</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>4.24</v>
+        <v>3.69</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>10.92</v>
+        <v>10.72</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>258.65</v>
+        <v>229.17</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3552,8 +3548,12 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-20.96</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
     </row>
@@ -6593,70 +6593,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3711</v>
+        <v>3362.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>2359.3</v>
       </c>
       <c r="F23" t="n">
-        <v>24.01</v>
+        <v>19.45</v>
       </c>
       <c r="G23" t="n">
-        <v>16.95</v>
+        <v>13.69</v>
       </c>
       <c r="H23" t="n">
-        <v>293.1</v>
+        <v>602.9</v>
       </c>
       <c r="I23" t="n">
-        <v>207.2</v>
+        <v>426.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.95</v>
+        <v>3.94</v>
       </c>
       <c r="K23" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="L23" t="n">
-        <v>11.91</v>
+        <v>14.25</v>
       </c>
       <c r="M23" t="n">
-        <v>8.41</v>
+        <v>10.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.53</v>
+        <v>4.06</v>
       </c>
       <c r="O23" t="n">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="P23" t="n">
-        <v>260.61</v>
+        <v>259.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>183.44</v>
+        <v>182.61</v>
       </c>
       <c r="R23" t="n">
-        <v>119.32</v>
+        <v>118.51</v>
       </c>
       <c r="S23" t="n">
-        <v>247.68</v>
+        <v>246.79</v>
       </c>
       <c r="T23" t="n">
-        <v>202.09</v>
+        <v>192.85</v>
       </c>
       <c r="U23" t="n">
-        <v>-18.65</v>
+        <v>-10.24</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
@@ -6664,70 +6664,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3362.7</v>
+        <v>3802.6</v>
       </c>
       <c r="E24" t="n">
-        <v>2359.3</v>
+        <v>2685.3</v>
       </c>
       <c r="F24" t="n">
-        <v>19.45</v>
+        <v>21.99</v>
       </c>
       <c r="G24" t="n">
-        <v>13.69</v>
+        <v>15.47</v>
       </c>
       <c r="H24" t="n">
-        <v>602.9</v>
+        <v>282.6</v>
       </c>
       <c r="I24" t="n">
-        <v>426.2</v>
+        <v>200</v>
       </c>
       <c r="J24" t="n">
-        <v>3.94</v>
+        <v>2.93</v>
       </c>
       <c r="K24" t="n">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="L24" t="n">
-        <v>14.25</v>
+        <v>11.01</v>
       </c>
       <c r="M24" t="n">
-        <v>10.06</v>
+        <v>7.77</v>
       </c>
       <c r="N24" t="n">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="O24" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="P24" t="n">
-        <v>259.62</v>
+        <v>255.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>182.61</v>
+        <v>180.37</v>
       </c>
       <c r="R24" t="n">
-        <v>118.51</v>
+        <v>116.23</v>
       </c>
       <c r="S24" t="n">
-        <v>246.79</v>
+        <v>244.65</v>
       </c>
       <c r="T24" t="n">
-        <v>192.85</v>
+        <v>192.14</v>
       </c>
       <c r="U24" t="n">
-        <v>-10.24</v>
+        <v>-11.77</v>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
@@ -6735,70 +6735,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3802.6</v>
+        <v>3747.9</v>
       </c>
       <c r="E25" t="n">
-        <v>2685.3</v>
+        <v>2632.3</v>
       </c>
       <c r="F25" t="n">
-        <v>21.99</v>
+        <v>23.28</v>
       </c>
       <c r="G25" t="n">
-        <v>15.47</v>
+        <v>16.43</v>
       </c>
       <c r="H25" t="n">
-        <v>282.6</v>
+        <v>239</v>
       </c>
       <c r="I25" t="n">
-        <v>200</v>
+        <v>169.1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="K25" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="L25" t="n">
-        <v>11.01</v>
+        <v>10.64</v>
       </c>
       <c r="M25" t="n">
-        <v>7.77</v>
+        <v>7.51</v>
       </c>
       <c r="N25" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="O25" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>255.6</v>
+        <v>253.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>180.37</v>
+        <v>178.44</v>
       </c>
       <c r="R25" t="n">
-        <v>116.23</v>
+        <v>114.1</v>
       </c>
       <c r="S25" t="n">
-        <v>244.65</v>
+        <v>242.57</v>
       </c>
       <c r="T25" t="n">
-        <v>192.14</v>
+        <v>143.44</v>
       </c>
       <c r="U25" t="n">
-        <v>-11.77</v>
+        <v>35</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
@@ -6806,208 +6806,208 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3747.9</v>
+        <v>3761.5</v>
       </c>
       <c r="E26" t="n">
-        <v>2632.3</v>
+        <v>2640.3</v>
       </c>
       <c r="F26" t="n">
-        <v>23.28</v>
+        <v>25.84</v>
       </c>
       <c r="G26" t="n">
-        <v>16.43</v>
+        <v>17.96</v>
       </c>
       <c r="H26" t="n">
-        <v>239</v>
+        <v>201.2</v>
       </c>
       <c r="I26" t="n">
-        <v>169.1</v>
+        <v>142.8</v>
       </c>
       <c r="J26" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="K26" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="L26" t="n">
-        <v>10.64</v>
+        <v>14.05</v>
       </c>
       <c r="M26" t="n">
-        <v>7.51</v>
+        <v>9.92</v>
       </c>
       <c r="N26" t="n">
-        <v>4.11</v>
+        <v>3.54</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>253.34</v>
+        <v>252.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>178.44</v>
+        <v>176.37</v>
       </c>
       <c r="R26" t="n">
-        <v>114.1</v>
+        <v>113.96</v>
       </c>
       <c r="S26" t="n">
-        <v>242.57</v>
-      </c>
-      <c r="T26" t="n">
-        <v>143.44</v>
-      </c>
-      <c r="U26" t="n">
-        <v>35</v>
-      </c>
+        <v>240.28</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3761.5</v>
+        <v>3932.2</v>
       </c>
       <c r="E27" t="n">
-        <v>2640.3</v>
+        <v>2756.7</v>
       </c>
       <c r="F27" t="n">
-        <v>25.84</v>
+        <v>24.37</v>
       </c>
       <c r="G27" t="n">
-        <v>17.96</v>
+        <v>17.11</v>
       </c>
       <c r="H27" t="n">
-        <v>201.2</v>
+        <v>94.2</v>
       </c>
       <c r="I27" t="n">
-        <v>142.8</v>
+        <v>67</v>
       </c>
       <c r="J27" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="K27" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="L27" t="n">
-        <v>14.05</v>
+        <v>10.84</v>
       </c>
       <c r="M27" t="n">
-        <v>9.92</v>
+        <v>7.65</v>
       </c>
       <c r="N27" t="n">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>252.14</v>
+        <v>249.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>176.37</v>
+        <v>175.17</v>
       </c>
       <c r="R27" t="n">
-        <v>113.96</v>
+        <v>114.38</v>
       </c>
       <c r="S27" t="n">
-        <v>240.28</v>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+        <v>238.84</v>
+      </c>
+      <c r="T27" t="n">
+        <v>106.66</v>
+      </c>
+      <c r="U27" t="n">
+        <v>68.51000000000001</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3932.2</v>
+        <v>3638.5</v>
       </c>
       <c r="E28" t="n">
-        <v>2756.7</v>
+        <v>2552.3</v>
       </c>
       <c r="F28" t="n">
-        <v>24.37</v>
+        <v>25.55</v>
       </c>
       <c r="G28" t="n">
-        <v>17.11</v>
+        <v>17.81</v>
       </c>
       <c r="H28" t="n">
-        <v>94.2</v>
+        <v>141.6</v>
       </c>
       <c r="I28" t="n">
-        <v>67</v>
+        <v>100.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="K28" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="L28" t="n">
-        <v>10.84</v>
+        <v>8.69</v>
       </c>
       <c r="M28" t="n">
-        <v>7.65</v>
+        <v>6.13</v>
       </c>
       <c r="N28" t="n">
-        <v>3.26</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="P28" t="n">
-        <v>249.79</v>
+        <v>248.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>175.17</v>
+        <v>173.8</v>
       </c>
       <c r="R28" t="n">
-        <v>114.38</v>
+        <v>112.92</v>
       </c>
       <c r="S28" t="n">
-        <v>238.84</v>
+        <v>237.73</v>
       </c>
       <c r="T28" t="n">
-        <v>106.66</v>
+        <v>179.01</v>
       </c>
       <c r="U28" t="n">
-        <v>68.51000000000001</v>
+        <v>-5.21</v>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
@@ -7015,70 +7015,70 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3638.5</v>
+        <v>3711</v>
       </c>
       <c r="E29" t="n">
-        <v>2552.3</v>
+        <v>2387.4</v>
       </c>
       <c r="F29" t="n">
-        <v>25.55</v>
+        <v>24.01</v>
       </c>
       <c r="G29" t="n">
-        <v>17.81</v>
+        <v>15.55</v>
       </c>
       <c r="H29" t="n">
-        <v>141.6</v>
+        <v>293.1</v>
       </c>
       <c r="I29" t="n">
-        <v>100.5</v>
+        <v>189.7</v>
       </c>
       <c r="J29" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="K29" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="L29" t="n">
-        <v>8.69</v>
+        <v>11.91</v>
       </c>
       <c r="M29" t="n">
-        <v>6.13</v>
+        <v>7.7</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>3.53</v>
       </c>
       <c r="O29" t="n">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="P29" t="n">
-        <v>248.12</v>
+        <v>260.61</v>
       </c>
       <c r="Q29" t="n">
-        <v>173.8</v>
+        <v>168.15</v>
       </c>
       <c r="R29" t="n">
-        <v>112.92</v>
+        <v>109.37</v>
       </c>
       <c r="S29" t="n">
-        <v>237.73</v>
+        <v>227.04</v>
       </c>
       <c r="T29" t="n">
-        <v>179.01</v>
+        <v>202.09</v>
       </c>
       <c r="U29" t="n">
-        <v>-5.21</v>
+        <v>-33.94</v>
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
@@ -7643,64 +7643,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3454</v>
+        <v>3439.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>202.6</v>
       </c>
       <c r="F4" t="n">
-        <v>17.15</v>
+        <v>18.36</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="H4" t="n">
-        <v>828.4</v>
+        <v>493.8</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="J4" t="n">
-        <v>7.93</v>
+        <v>4.24</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="L4" t="n">
-        <v>13.69</v>
+        <v>10.92</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="N4" t="n">
-        <v>4.48</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="P4" t="n">
-        <v>300.84</v>
+        <v>258.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>15.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>9.81</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>20.48</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -7710,55 +7710,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3169.6</v>
+        <v>3454</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>14.24</v>
+        <v>17.15</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>187.4</v>
+        <v>828.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>17.31</v>
+        <v>13.69</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.71</v>
+        <v>4.48</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>178.92</v>
+        <v>300.84</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -7769,67 +7769,63 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-16.94</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3417.5</v>
+        <v>3169.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>21.65</v>
+        <v>14.24</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>230.4</v>
+        <v>187.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10.45</v>
+        <v>17.31</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>231.7</v>
+        <v>178.92</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -7840,63 +7836,67 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-16.94</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3052</v>
+        <v>3417.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>14.48</v>
+        <v>21.65</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>182.8</v>
+        <v>230.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>17.4</v>
+        <v>10.45</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>174.6</v>
+        <v>231.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -7915,55 +7915,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3546.8</v>
+        <v>3052</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>20.76</v>
+        <v>14.48</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>143.7</v>
+        <v>182.8</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>12.54</v>
+        <v>17.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>219</v>
+        <v>174.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -7982,55 +7982,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3427.7</v>
+        <v>3546.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>19.25</v>
+        <v>20.76</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>258</v>
+        <v>143.7</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>11.24</v>
+        <v>12.54</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>228.61</v>
+        <v>219</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8049,55 +8049,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3356.1</v>
+        <v>3427.7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>15.53</v>
+        <v>19.25</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>110.3</v>
+        <v>258</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>10.42</v>
+        <v>11.24</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>190.73</v>
+        <v>228.61</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8116,55 +8116,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3536.7</v>
+        <v>3356.1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>16.69</v>
+        <v>15.53</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>271.4</v>
+        <v>110.3</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.69</v>
+        <v>1.83</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10.72</v>
+        <v>10.42</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>229.17</v>
+        <v>190.73</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8175,67 +8175,63 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-20.96</v>
-      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3439.8</v>
+        <v>3536.7</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>18.36</v>
+        <v>16.69</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>493.8</v>
+        <v>271.4</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>4.24</v>
+        <v>3.69</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10.92</v>
+        <v>10.72</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>258.65</v>
+        <v>229.17</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8246,8 +8242,12 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-20.96</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
@@ -10968,67 +10968,67 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>218.571</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>17.451</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.701</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>125.453</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>311.694</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.805</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>6.041</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>38.341</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.243</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.837</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.801</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.302</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.639</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>31.033</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="inlineStr"/>
     </row>
@@ -55980,67 +55980,67 @@
         <v>0</v>
       </c>
       <c r="H498" t="n">
-        <v>0</v>
+        <v>202.62</v>
       </c>
       <c r="I498" t="n">
-        <v>0</v>
+        <v>1.067</v>
       </c>
       <c r="J498" t="n">
-        <v>0</v>
+        <v>29.258</v>
       </c>
       <c r="K498" t="n">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="L498" t="n">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="M498" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="N498" t="n">
-        <v>0</v>
+        <v>109.497</v>
       </c>
       <c r="O498" t="n">
-        <v>0</v>
+        <v>295.743</v>
       </c>
       <c r="P498" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="Q498" t="n">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="R498" t="n">
-        <v>0</v>
+        <v>10.127</v>
       </c>
       <c r="S498" t="n">
-        <v>0</v>
+        <v>50.15</v>
       </c>
       <c r="T498" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U498" t="n">
-        <v>0</v>
+        <v>0.763</v>
       </c>
       <c r="V498" t="n">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="W498" t="n">
-        <v>0</v>
+        <v>1.778</v>
       </c>
       <c r="X498" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="Y498" t="n">
-        <v>0</v>
+        <v>0.754</v>
       </c>
       <c r="Z498" t="n">
-        <v>0</v>
+        <v>15.164</v>
       </c>
       <c r="AA498" t="n">
-        <v>0</v>
+        <v>2.313</v>
       </c>
       <c r="AB498" t="n">
-        <v>0</v>
+        <v>30.753</v>
       </c>
       <c r="AC498" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -965,70 +965,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3690.1</v>
+        <v>3996.4</v>
       </c>
       <c r="E8" t="n">
-        <v>2611.4</v>
+        <v>2814.4</v>
       </c>
       <c r="F8" t="n">
-        <v>27.42</v>
+        <v>33.65</v>
       </c>
       <c r="G8" t="n">
-        <v>19.3</v>
+        <v>23.72</v>
       </c>
       <c r="H8" t="n">
-        <v>631.5</v>
+        <v>338.2</v>
       </c>
       <c r="I8" t="n">
-        <v>447.1</v>
+        <v>238.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.79</v>
+        <v>3.44</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="L8" t="n">
-        <v>8.82</v>
+        <v>10.67</v>
       </c>
       <c r="M8" t="n">
-        <v>6.22</v>
+        <v>7.53</v>
       </c>
       <c r="N8" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>325.51</v>
+        <v>321.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>230.07</v>
+        <v>226.52</v>
       </c>
       <c r="R8" t="n">
-        <v>165.49</v>
+        <v>162.31</v>
       </c>
       <c r="S8" t="n">
-        <v>294.39</v>
+        <v>290.87</v>
       </c>
       <c r="T8" t="n">
-        <v>232.59</v>
+        <v>225.53</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.52</v>
+        <v>0.99</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
@@ -1036,70 +1036,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3996.4</v>
+        <v>4376.1</v>
       </c>
       <c r="E9" t="n">
-        <v>2814.4</v>
+        <v>3080.4</v>
       </c>
       <c r="F9" t="n">
-        <v>33.65</v>
+        <v>33.34</v>
       </c>
       <c r="G9" t="n">
-        <v>23.72</v>
+        <v>23.55</v>
       </c>
       <c r="H9" t="n">
-        <v>338.2</v>
+        <v>171.3</v>
       </c>
       <c r="I9" t="n">
-        <v>238.8</v>
+        <v>121.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.44</v>
+        <v>2.24</v>
       </c>
       <c r="K9" t="n">
-        <v>2.44</v>
+        <v>1.59</v>
       </c>
       <c r="L9" t="n">
-        <v>10.67</v>
+        <v>9.56</v>
       </c>
       <c r="M9" t="n">
-        <v>7.53</v>
+        <v>6.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="P9" t="n">
-        <v>321.38</v>
+        <v>314.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>226.52</v>
+        <v>221.91</v>
       </c>
       <c r="R9" t="n">
-        <v>162.31</v>
+        <v>158.94</v>
       </c>
       <c r="S9" t="n">
-        <v>290.87</v>
+        <v>286.21</v>
       </c>
       <c r="T9" t="n">
-        <v>225.53</v>
+        <v>234.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0.99</v>
+        <v>-12.44</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -1107,70 +1107,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4376.1</v>
+        <v>4661.4</v>
       </c>
       <c r="E10" t="n">
-        <v>3080.4</v>
+        <v>3292.9</v>
       </c>
       <c r="F10" t="n">
-        <v>33.34</v>
+        <v>36.38</v>
       </c>
       <c r="G10" t="n">
-        <v>23.55</v>
+        <v>26.18</v>
       </c>
       <c r="H10" t="n">
-        <v>171.3</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
-        <v>121.9</v>
+        <v>25.2</v>
       </c>
       <c r="J10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="O10" t="n">
         <v>2.24</v>
       </c>
-      <c r="K10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.87</v>
-      </c>
       <c r="P10" t="n">
-        <v>314.55</v>
+        <v>308.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>221.91</v>
+        <v>219.9</v>
       </c>
       <c r="R10" t="n">
-        <v>158.94</v>
+        <v>166.77</v>
       </c>
       <c r="S10" t="n">
-        <v>286.21</v>
+        <v>284.86</v>
       </c>
       <c r="T10" t="n">
-        <v>234.35</v>
+        <v>206.26</v>
       </c>
       <c r="U10" t="n">
-        <v>-12.44</v>
+        <v>13.64</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -1178,70 +1178,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4661.4</v>
+        <v>3805.5</v>
       </c>
       <c r="E11" t="n">
-        <v>3292.9</v>
+        <v>2669.4</v>
       </c>
       <c r="F11" t="n">
-        <v>36.38</v>
+        <v>26.65</v>
       </c>
       <c r="G11" t="n">
-        <v>26.18</v>
+        <v>18.98</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>481.7</v>
       </c>
       <c r="I11" t="n">
-        <v>25.2</v>
+        <v>340.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.25</v>
+        <v>4.03</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9</v>
+        <v>2.87</v>
       </c>
       <c r="L11" t="n">
-        <v>14.15</v>
+        <v>10.23</v>
       </c>
       <c r="M11" t="n">
-        <v>9.99</v>
+        <v>7.22</v>
       </c>
       <c r="N11" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.24</v>
+        <v>2.51</v>
       </c>
       <c r="P11" t="n">
-        <v>308.32</v>
+        <v>303.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>219.9</v>
+        <v>214.54</v>
       </c>
       <c r="R11" t="n">
-        <v>166.77</v>
+        <v>150.16</v>
       </c>
       <c r="S11" t="n">
-        <v>284.86</v>
+        <v>279.04</v>
       </c>
       <c r="T11" t="n">
-        <v>206.26</v>
+        <v>229.13</v>
       </c>
       <c r="U11" t="n">
-        <v>13.64</v>
+        <v>-14.59</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1249,70 +1249,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3805.5</v>
+        <v>3923.2</v>
       </c>
       <c r="E12" t="n">
-        <v>2669.4</v>
+        <v>2773.6</v>
       </c>
       <c r="F12" t="n">
-        <v>26.65</v>
+        <v>30.91</v>
       </c>
       <c r="G12" t="n">
-        <v>18.98</v>
+        <v>21.91</v>
       </c>
       <c r="H12" t="n">
-        <v>481.7</v>
+        <v>292.2</v>
       </c>
       <c r="I12" t="n">
-        <v>340.8</v>
+        <v>206.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.03</v>
+        <v>3.71</v>
       </c>
       <c r="K12" t="n">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="L12" t="n">
-        <v>10.23</v>
+        <v>11.37</v>
       </c>
       <c r="M12" t="n">
-        <v>7.22</v>
+        <v>8.02</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="O12" t="n">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="P12" t="n">
-        <v>303.61</v>
+        <v>301.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>214.54</v>
+        <v>213.82</v>
       </c>
       <c r="R12" t="n">
-        <v>150.16</v>
+        <v>149.56</v>
       </c>
       <c r="S12" t="n">
-        <v>279.04</v>
+        <v>278.71</v>
       </c>
       <c r="T12" t="n">
-        <v>229.13</v>
+        <v>227.65</v>
       </c>
       <c r="U12" t="n">
-        <v>-14.59</v>
+        <v>-13.83</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -1320,70 +1320,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3923.2</v>
+        <v>4103.8</v>
       </c>
       <c r="E13" t="n">
-        <v>2773.6</v>
+        <v>3134.4</v>
       </c>
       <c r="F13" t="n">
-        <v>30.91</v>
+        <v>25.82</v>
       </c>
       <c r="G13" t="n">
-        <v>21.91</v>
+        <v>19.62</v>
       </c>
       <c r="H13" t="n">
-        <v>292.2</v>
+        <v>223.1</v>
       </c>
       <c r="I13" t="n">
-        <v>206.6</v>
+        <v>171.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.71</v>
+        <v>2.95</v>
       </c>
       <c r="K13" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="L13" t="n">
-        <v>11.37</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.02</v>
+        <v>7.42</v>
       </c>
       <c r="N13" t="n">
-        <v>3.66</v>
+        <v>4.07</v>
       </c>
       <c r="O13" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="P13" t="n">
-        <v>301.99</v>
+        <v>279.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>213.82</v>
+        <v>213.64</v>
       </c>
       <c r="R13" t="n">
-        <v>149.56</v>
+        <v>144.06</v>
       </c>
       <c r="S13" t="n">
-        <v>278.71</v>
+        <v>283.28</v>
       </c>
       <c r="T13" t="n">
-        <v>227.65</v>
+        <v>183.68</v>
       </c>
       <c r="U13" t="n">
-        <v>-13.83</v>
+        <v>29.96</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -1391,70 +1391,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4103.8</v>
+        <v>3690.1</v>
       </c>
       <c r="E14" t="n">
-        <v>3134.4</v>
+        <v>2389.6</v>
       </c>
       <c r="F14" t="n">
-        <v>25.82</v>
+        <v>27.42</v>
       </c>
       <c r="G14" t="n">
-        <v>19.62</v>
+        <v>17.67</v>
       </c>
       <c r="H14" t="n">
-        <v>223.1</v>
+        <v>631.5</v>
       </c>
       <c r="I14" t="n">
-        <v>171.6</v>
+        <v>409.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.95</v>
+        <v>4.79</v>
       </c>
       <c r="K14" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
-        <v>9.710000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="M14" t="n">
-        <v>7.42</v>
+        <v>5.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.07</v>
+        <v>3.01</v>
       </c>
       <c r="O14" t="n">
-        <v>3.11</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
-        <v>279.88</v>
+        <v>325.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>213.64</v>
+        <v>210.54</v>
       </c>
       <c r="R14" t="n">
-        <v>144.06</v>
+        <v>151.44</v>
       </c>
       <c r="S14" t="n">
-        <v>283.28</v>
+        <v>269.4</v>
       </c>
       <c r="T14" t="n">
-        <v>183.68</v>
+        <v>232.59</v>
       </c>
       <c r="U14" t="n">
-        <v>29.96</v>
+        <v>-22.05</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -3016,64 +3016,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3454</v>
+        <v>3609.1</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="F37" t="n">
-        <v>17.15</v>
+        <v>23.69</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="H37" t="n">
-        <v>828.4</v>
+        <v>57.9</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
-        <v>7.93</v>
+        <v>2.29</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="L37" t="n">
-        <v>13.69</v>
+        <v>11.86</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N37" t="n">
-        <v>4.48</v>
+        <v>2.83</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="P37" t="n">
-        <v>300.84</v>
+        <v>229.27</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>13.82</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>19.29</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3083,55 +3083,55 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3191.5</v>
+        <v>3454</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>14.26</v>
+        <v>17.15</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>187.4</v>
+        <v>828.4</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>17.31</v>
+        <v>13.69</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.71</v>
+        <v>4.48</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>179.88</v>
+        <v>300.84</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3142,67 +3142,63 @@
       <c r="S38" t="n">
         <v>0</v>
       </c>
-      <c r="T38" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="U38" t="n">
-        <v>-16.94</v>
-      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3428.5</v>
+        <v>3191.5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>21.66</v>
+        <v>14.26</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>230.4</v>
+        <v>187.4</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>10.45</v>
+        <v>17.31</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>232.18</v>
+        <v>179.88</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3213,63 +3209,67 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-16.94</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3072.2</v>
+        <v>3428.5</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>14.53</v>
+        <v>21.66</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>182.8</v>
+        <v>230.4</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>17.4</v>
+        <v>10.45</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>175.61</v>
+        <v>232.18</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3288,55 +3288,55 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3557.8</v>
+        <v>3072.2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>20.77</v>
+        <v>14.53</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>143.7</v>
+        <v>182.8</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>12.54</v>
+        <v>17.4</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>219.48</v>
+        <v>175.61</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3355,55 +3355,55 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3446.1</v>
+        <v>3557.8</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>19.33</v>
+        <v>20.77</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>258</v>
+        <v>143.7</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>11.24</v>
+        <v>12.54</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>229.66</v>
+        <v>219.48</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3422,55 +3422,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3374.5</v>
+        <v>3446.1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>15.61</v>
+        <v>19.33</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>110.3</v>
+        <v>258</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.42</v>
+        <v>11.24</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>191.79</v>
+        <v>229.66</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3489,55 +3489,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3545.9</v>
+        <v>3374.5</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>16.73</v>
+        <v>15.61</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>271.4</v>
+        <v>110.3</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>3.69</v>
+        <v>1.83</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>10.72</v>
+        <v>10.42</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>229.7</v>
+        <v>191.79</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3548,67 +3548,63 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
-      <c r="T44" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="U44" t="n">
-        <v>-20.96</v>
-      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3702.9</v>
+        <v>3545.9</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>19.24</v>
+        <v>16.73</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>322.3</v>
+        <v>271.4</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2.32</v>
+        <v>3.69</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>10.9</v>
+        <v>10.72</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>243.03</v>
+        <v>229.7</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3619,63 +3615,67 @@
       <c r="S45" t="n">
         <v>0</v>
       </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="T45" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="U45" t="n">
+        <v>-20.96</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3596.8</v>
+        <v>3702.9</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>25.54</v>
+        <v>19.24</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>33.5</v>
+        <v>322.3</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>11.54</v>
+        <v>10.9</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>229.78</v>
+        <v>243.03</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3694,55 +3694,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3434.3</v>
+        <v>3596.8</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>17.8</v>
+        <v>25.54</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>550.2</v>
+        <v>33.5</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>4.94</v>
+        <v>1.75</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>11.09</v>
+        <v>11.54</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>264.59</v>
+        <v>229.78</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3761,55 +3761,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3277.5</v>
+        <v>3434.3</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>18.61</v>
+        <v>17.8</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>841.3</v>
+        <v>550.2</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>7.25</v>
+        <v>4.94</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>8.65</v>
+        <v>11.09</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>308.61</v>
+        <v>264.59</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3828,55 +3828,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3341.5</v>
+        <v>3277.5</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>16.38</v>
+        <v>18.61</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>188.9</v>
+        <v>841.3</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1.88</v>
+        <v>7.25</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>11.86</v>
+        <v>8.65</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>199.17</v>
+        <v>308.61</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3895,55 +3895,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3453.9</v>
+        <v>3341.5</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>18</v>
+        <v>16.38</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>183.4</v>
+        <v>188.9</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>12.93</v>
+        <v>11.86</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>210.74</v>
+        <v>199.17</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3962,55 +3962,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3254.1</v>
+        <v>3453.9</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>14.14</v>
+        <v>18</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>182.3</v>
+        <v>183.4</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>17.38</v>
+        <v>12.93</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>181.29</v>
+        <v>210.74</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4029,55 +4029,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3594.1</v>
+        <v>3254.1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>22.73</v>
+        <v>14.14</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>174.5</v>
+        <v>182.3</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2.17</v>
+        <v>3.09</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>10.7</v>
+        <v>17.38</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.59</v>
+        <v>3.72</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>238.57</v>
+        <v>181.29</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4096,55 +4096,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3645</v>
+        <v>3594.1</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>25.12</v>
+        <v>22.73</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>582.3</v>
+        <v>174.5</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>14.49</v>
+        <v>10.7</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.33</v>
+        <v>2.59</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>290.77</v>
+        <v>238.57</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4163,55 +4163,55 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3419.1</v>
+        <v>3645</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>20.18</v>
+        <v>25.12</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>149.2</v>
+        <v>582.3</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>9.380000000000001</v>
+        <v>14.49</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>217.94</v>
+        <v>290.77</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4230,55 +4230,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3540.7</v>
+        <v>3419.1</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>22.31</v>
+        <v>20.18</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>201.9</v>
+        <v>149.2</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>3.03</v>
+        <v>1.78</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>10.94</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.17</v>
+        <v>3.19</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>243.02</v>
+        <v>217.94</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4297,55 +4297,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3276.6</v>
+        <v>3540.7</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>17.46</v>
+        <v>22.31</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>153.2</v>
+        <v>201.9</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>12.86</v>
+        <v>10.94</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.11</v>
+        <v>2.17</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>196.68</v>
+        <v>243.02</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4364,55 +4364,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3326.2</v>
+        <v>3276.6</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>15.33</v>
+        <v>17.46</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>204.2</v>
+        <v>153.2</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>17.3</v>
+        <v>12.86</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>191.63</v>
+        <v>196.68</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4431,55 +4431,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3392.4</v>
+        <v>3326.2</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>16.8</v>
+        <v>15.33</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>287</v>
+        <v>204.2</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>11.42</v>
+        <v>17.3</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>215.88</v>
+        <v>191.63</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4498,55 +4498,55 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>3391.3</v>
+        <v>3392.4</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>16.05</v>
+        <v>16.8</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>184</v>
+        <v>287</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>15.75</v>
+        <v>11.42</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>5.75</v>
+        <v>4.15</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>191.21</v>
+        <v>215.88</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4565,55 +4565,55 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tanner McKee</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3609.1</v>
+        <v>3391.3</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>23.69</v>
+        <v>16.05</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>57.9</v>
+        <v>184</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.29</v>
+        <v>2.66</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>11.86</v>
+        <v>15.75</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.83</v>
+        <v>5.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>229.27</v>
+        <v>191.21</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -5528,70 +5528,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3690.1</v>
+        <v>3996.4</v>
       </c>
       <c r="E8" t="n">
-        <v>2611.4</v>
+        <v>2814.4</v>
       </c>
       <c r="F8" t="n">
-        <v>27.42</v>
+        <v>33.65</v>
       </c>
       <c r="G8" t="n">
-        <v>19.3</v>
+        <v>23.72</v>
       </c>
       <c r="H8" t="n">
-        <v>631.5</v>
+        <v>338.2</v>
       </c>
       <c r="I8" t="n">
-        <v>447.1</v>
+        <v>238.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.79</v>
+        <v>3.44</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="L8" t="n">
-        <v>8.82</v>
+        <v>10.67</v>
       </c>
       <c r="M8" t="n">
-        <v>6.22</v>
+        <v>7.53</v>
       </c>
       <c r="N8" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>325.51</v>
+        <v>321.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>230.07</v>
+        <v>226.52</v>
       </c>
       <c r="R8" t="n">
-        <v>165.49</v>
+        <v>162.31</v>
       </c>
       <c r="S8" t="n">
-        <v>294.39</v>
+        <v>290.87</v>
       </c>
       <c r="T8" t="n">
-        <v>232.59</v>
+        <v>225.53</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.52</v>
+        <v>0.99</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
@@ -5599,70 +5599,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3996.4</v>
+        <v>4376.1</v>
       </c>
       <c r="E9" t="n">
-        <v>2814.4</v>
+        <v>3080.4</v>
       </c>
       <c r="F9" t="n">
-        <v>33.65</v>
+        <v>33.34</v>
       </c>
       <c r="G9" t="n">
-        <v>23.72</v>
+        <v>23.55</v>
       </c>
       <c r="H9" t="n">
-        <v>338.2</v>
+        <v>171.3</v>
       </c>
       <c r="I9" t="n">
-        <v>238.8</v>
+        <v>121.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.44</v>
+        <v>2.24</v>
       </c>
       <c r="K9" t="n">
-        <v>2.44</v>
+        <v>1.59</v>
       </c>
       <c r="L9" t="n">
-        <v>10.67</v>
+        <v>9.56</v>
       </c>
       <c r="M9" t="n">
-        <v>7.53</v>
+        <v>6.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="P9" t="n">
-        <v>321.38</v>
+        <v>314.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>226.52</v>
+        <v>221.91</v>
       </c>
       <c r="R9" t="n">
-        <v>162.31</v>
+        <v>158.94</v>
       </c>
       <c r="S9" t="n">
-        <v>290.87</v>
+        <v>286.21</v>
       </c>
       <c r="T9" t="n">
-        <v>225.53</v>
+        <v>234.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0.99</v>
+        <v>-12.44</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -5670,70 +5670,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4376.1</v>
+        <v>4661.4</v>
       </c>
       <c r="E10" t="n">
-        <v>3080.4</v>
+        <v>3292.9</v>
       </c>
       <c r="F10" t="n">
-        <v>33.34</v>
+        <v>36.38</v>
       </c>
       <c r="G10" t="n">
-        <v>23.55</v>
+        <v>26.18</v>
       </c>
       <c r="H10" t="n">
-        <v>171.3</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
-        <v>121.9</v>
+        <v>25.2</v>
       </c>
       <c r="J10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="O10" t="n">
         <v>2.24</v>
       </c>
-      <c r="K10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.87</v>
-      </c>
       <c r="P10" t="n">
-        <v>314.55</v>
+        <v>308.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>221.91</v>
+        <v>219.9</v>
       </c>
       <c r="R10" t="n">
-        <v>158.94</v>
+        <v>166.77</v>
       </c>
       <c r="S10" t="n">
-        <v>286.21</v>
+        <v>284.86</v>
       </c>
       <c r="T10" t="n">
-        <v>234.35</v>
+        <v>206.26</v>
       </c>
       <c r="U10" t="n">
-        <v>-12.44</v>
+        <v>13.64</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -5741,70 +5741,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4661.4</v>
+        <v>3805.5</v>
       </c>
       <c r="E11" t="n">
-        <v>3292.9</v>
+        <v>2669.4</v>
       </c>
       <c r="F11" t="n">
-        <v>36.38</v>
+        <v>26.65</v>
       </c>
       <c r="G11" t="n">
-        <v>26.18</v>
+        <v>18.98</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>481.7</v>
       </c>
       <c r="I11" t="n">
-        <v>25.2</v>
+        <v>340.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.25</v>
+        <v>4.03</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9</v>
+        <v>2.87</v>
       </c>
       <c r="L11" t="n">
-        <v>14.15</v>
+        <v>10.23</v>
       </c>
       <c r="M11" t="n">
-        <v>9.99</v>
+        <v>7.22</v>
       </c>
       <c r="N11" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.24</v>
+        <v>2.51</v>
       </c>
       <c r="P11" t="n">
-        <v>308.32</v>
+        <v>303.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>219.9</v>
+        <v>214.54</v>
       </c>
       <c r="R11" t="n">
-        <v>166.77</v>
+        <v>150.16</v>
       </c>
       <c r="S11" t="n">
-        <v>284.86</v>
+        <v>279.04</v>
       </c>
       <c r="T11" t="n">
-        <v>206.26</v>
+        <v>229.13</v>
       </c>
       <c r="U11" t="n">
-        <v>13.64</v>
+        <v>-14.59</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -5812,70 +5812,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3805.5</v>
+        <v>3923.2</v>
       </c>
       <c r="E12" t="n">
-        <v>2669.4</v>
+        <v>2773.6</v>
       </c>
       <c r="F12" t="n">
-        <v>26.65</v>
+        <v>30.91</v>
       </c>
       <c r="G12" t="n">
-        <v>18.98</v>
+        <v>21.91</v>
       </c>
       <c r="H12" t="n">
-        <v>481.7</v>
+        <v>292.2</v>
       </c>
       <c r="I12" t="n">
-        <v>340.8</v>
+        <v>206.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.03</v>
+        <v>3.71</v>
       </c>
       <c r="K12" t="n">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="L12" t="n">
-        <v>10.23</v>
+        <v>11.37</v>
       </c>
       <c r="M12" t="n">
-        <v>7.22</v>
+        <v>8.02</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="O12" t="n">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="P12" t="n">
-        <v>303.61</v>
+        <v>301.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>214.54</v>
+        <v>213.82</v>
       </c>
       <c r="R12" t="n">
-        <v>150.16</v>
+        <v>149.56</v>
       </c>
       <c r="S12" t="n">
-        <v>279.04</v>
+        <v>278.71</v>
       </c>
       <c r="T12" t="n">
-        <v>229.13</v>
+        <v>227.65</v>
       </c>
       <c r="U12" t="n">
-        <v>-14.59</v>
+        <v>-13.83</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -5883,70 +5883,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3923.2</v>
+        <v>4103.8</v>
       </c>
       <c r="E13" t="n">
-        <v>2773.6</v>
+        <v>3134.4</v>
       </c>
       <c r="F13" t="n">
-        <v>30.91</v>
+        <v>25.82</v>
       </c>
       <c r="G13" t="n">
-        <v>21.91</v>
+        <v>19.62</v>
       </c>
       <c r="H13" t="n">
-        <v>292.2</v>
+        <v>223.1</v>
       </c>
       <c r="I13" t="n">
-        <v>206.6</v>
+        <v>171.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.71</v>
+        <v>2.95</v>
       </c>
       <c r="K13" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="L13" t="n">
-        <v>11.37</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.02</v>
+        <v>7.42</v>
       </c>
       <c r="N13" t="n">
-        <v>3.66</v>
+        <v>4.07</v>
       </c>
       <c r="O13" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="P13" t="n">
-        <v>301.99</v>
+        <v>279.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>213.82</v>
+        <v>213.64</v>
       </c>
       <c r="R13" t="n">
-        <v>149.56</v>
+        <v>144.06</v>
       </c>
       <c r="S13" t="n">
-        <v>278.71</v>
+        <v>283.28</v>
       </c>
       <c r="T13" t="n">
-        <v>227.65</v>
+        <v>183.68</v>
       </c>
       <c r="U13" t="n">
-        <v>-13.83</v>
+        <v>29.96</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -5954,70 +5954,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4103.8</v>
+        <v>3690.1</v>
       </c>
       <c r="E14" t="n">
-        <v>3134.4</v>
+        <v>2389.6</v>
       </c>
       <c r="F14" t="n">
-        <v>25.82</v>
+        <v>27.42</v>
       </c>
       <c r="G14" t="n">
-        <v>19.62</v>
+        <v>17.67</v>
       </c>
       <c r="H14" t="n">
-        <v>223.1</v>
+        <v>631.5</v>
       </c>
       <c r="I14" t="n">
-        <v>171.6</v>
+        <v>409.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.95</v>
+        <v>4.79</v>
       </c>
       <c r="K14" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
-        <v>9.710000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="M14" t="n">
-        <v>7.42</v>
+        <v>5.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.07</v>
+        <v>3.01</v>
       </c>
       <c r="O14" t="n">
-        <v>3.11</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
-        <v>279.88</v>
+        <v>325.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>213.64</v>
+        <v>210.54</v>
       </c>
       <c r="R14" t="n">
-        <v>144.06</v>
+        <v>151.44</v>
       </c>
       <c r="S14" t="n">
-        <v>283.28</v>
+        <v>269.4</v>
       </c>
       <c r="T14" t="n">
-        <v>183.68</v>
+        <v>232.59</v>
       </c>
       <c r="U14" t="n">
-        <v>29.96</v>
+        <v>-22.05</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -7710,64 +7710,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3454</v>
+        <v>3609.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="F5" t="n">
-        <v>17.15</v>
+        <v>23.69</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="H5" t="n">
-        <v>828.4</v>
+        <v>57.9</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
-        <v>7.93</v>
+        <v>2.29</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="L5" t="n">
-        <v>13.69</v>
+        <v>11.86</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="n">
-        <v>4.48</v>
+        <v>2.83</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="P5" t="n">
-        <v>300.84</v>
+        <v>229.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>13.82</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>19.29</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -7777,55 +7777,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3191.5</v>
+        <v>3454</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>14.26</v>
+        <v>17.15</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>187.4</v>
+        <v>828.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>17.31</v>
+        <v>13.69</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.71</v>
+        <v>4.48</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>179.88</v>
+        <v>300.84</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -7836,67 +7836,63 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-16.94</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3428.5</v>
+        <v>3191.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>21.66</v>
+        <v>14.26</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>230.4</v>
+        <v>187.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10.45</v>
+        <v>17.31</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>232.18</v>
+        <v>179.88</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -7907,63 +7903,67 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-16.94</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3072.2</v>
+        <v>3428.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>14.53</v>
+        <v>21.66</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>182.8</v>
+        <v>230.4</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17.4</v>
+        <v>10.45</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>175.61</v>
+        <v>232.18</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -7982,55 +7982,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3557.8</v>
+        <v>3072.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>20.77</v>
+        <v>14.53</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>143.7</v>
+        <v>182.8</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>12.54</v>
+        <v>17.4</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>219.48</v>
+        <v>175.61</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8049,55 +8049,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3446.1</v>
+        <v>3557.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>19.33</v>
+        <v>20.77</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>258</v>
+        <v>143.7</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11.24</v>
+        <v>12.54</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>229.66</v>
+        <v>219.48</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8116,55 +8116,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3374.5</v>
+        <v>3446.1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>15.61</v>
+        <v>19.33</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>110.3</v>
+        <v>258</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10.42</v>
+        <v>11.24</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>191.79</v>
+        <v>229.66</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8183,55 +8183,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3545.9</v>
+        <v>3374.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>16.73</v>
+        <v>15.61</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>271.4</v>
+        <v>110.3</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3.69</v>
+        <v>1.83</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10.72</v>
+        <v>10.42</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>229.7</v>
+        <v>191.79</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8242,67 +8242,63 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-20.96</v>
-      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3702.9</v>
+        <v>3545.9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>19.24</v>
+        <v>16.73</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>322.3</v>
+        <v>271.4</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.32</v>
+        <v>3.69</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.9</v>
+        <v>10.72</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>243.03</v>
+        <v>229.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8313,63 +8309,67 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-20.96</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3596.8</v>
+        <v>3702.9</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>25.54</v>
+        <v>19.24</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>33.5</v>
+        <v>322.3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11.54</v>
+        <v>10.9</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>229.78</v>
+        <v>243.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8388,55 +8388,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3434.3</v>
+        <v>3596.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>17.8</v>
+        <v>25.54</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>550.2</v>
+        <v>33.5</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>4.94</v>
+        <v>1.75</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>11.09</v>
+        <v>11.54</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>264.59</v>
+        <v>229.78</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8455,55 +8455,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3277.5</v>
+        <v>3434.3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>18.61</v>
+        <v>17.8</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>841.3</v>
+        <v>550.2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>7.25</v>
+        <v>4.94</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8.65</v>
+        <v>11.09</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>308.61</v>
+        <v>264.59</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -8522,55 +8522,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3341.5</v>
+        <v>3277.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16.38</v>
+        <v>18.61</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>188.9</v>
+        <v>841.3</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.88</v>
+        <v>7.25</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>11.86</v>
+        <v>8.65</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>199.17</v>
+        <v>308.61</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -8589,55 +8589,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3453.9</v>
+        <v>3341.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>16.38</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>183.4</v>
+        <v>188.9</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>12.93</v>
+        <v>11.86</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>210.74</v>
+        <v>199.17</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -8656,55 +8656,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3254.1</v>
+        <v>3453.9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14.14</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>182.3</v>
+        <v>183.4</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>17.38</v>
+        <v>12.93</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>181.29</v>
+        <v>210.74</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -8723,55 +8723,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3594.1</v>
+        <v>3254.1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>22.73</v>
+        <v>14.14</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>174.5</v>
+        <v>182.3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.17</v>
+        <v>3.09</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>10.7</v>
+        <v>17.38</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.59</v>
+        <v>3.72</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>238.57</v>
+        <v>181.29</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -8790,55 +8790,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3645</v>
+        <v>3594.1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>25.12</v>
+        <v>22.73</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>582.3</v>
+        <v>174.5</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>14.49</v>
+        <v>10.7</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.33</v>
+        <v>2.59</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>290.77</v>
+        <v>238.57</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -8857,55 +8857,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3419.1</v>
+        <v>3645</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>20.18</v>
+        <v>25.12</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>149.2</v>
+        <v>582.3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>9.380000000000001</v>
+        <v>14.49</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>217.94</v>
+        <v>290.77</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -8924,55 +8924,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3540.7</v>
+        <v>3419.1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>22.31</v>
+        <v>20.18</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>201.9</v>
+        <v>149.2</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.03</v>
+        <v>1.78</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>10.94</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.17</v>
+        <v>3.19</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>243.02</v>
+        <v>217.94</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -8991,55 +8991,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3276.6</v>
+        <v>3540.7</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>17.46</v>
+        <v>22.31</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>153.2</v>
+        <v>201.9</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>12.86</v>
+        <v>10.94</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.11</v>
+        <v>2.17</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>196.68</v>
+        <v>243.02</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -9058,55 +9058,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3326.2</v>
+        <v>3276.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>15.33</v>
+        <v>17.46</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>204.2</v>
+        <v>153.2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>17.3</v>
+        <v>12.86</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>191.63</v>
+        <v>196.68</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -9125,55 +9125,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3392.4</v>
+        <v>3326.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>16.8</v>
+        <v>15.33</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>287</v>
+        <v>204.2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>11.42</v>
+        <v>17.3</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>215.88</v>
+        <v>191.63</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -9192,55 +9192,55 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3391.3</v>
+        <v>3392.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>16.05</v>
+        <v>16.8</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>184</v>
+        <v>287</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>15.75</v>
+        <v>11.42</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5.75</v>
+        <v>4.15</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>191.21</v>
+        <v>215.88</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -9259,55 +9259,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tanner McKee</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3609.1</v>
+        <v>3391.3</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>23.69</v>
+        <v>16.05</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>57.9</v>
+        <v>184</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2.29</v>
+        <v>2.66</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>11.86</v>
+        <v>15.75</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>5.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>229.27</v>
+        <v>191.21</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -25569,67 +25569,67 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>221.744</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>1.633</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>37.3</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>128.625</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>314.865</v>
+        <v>0</v>
       </c>
       <c r="P171" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.037</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>16.409</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
-        <v>58.191</v>
+        <v>0</v>
       </c>
       <c r="T171" t="n">
-        <v>0.101</v>
+        <v>0</v>
       </c>
       <c r="U171" t="n">
-        <v>0.8090000000000001</v>
+        <v>0</v>
       </c>
       <c r="V171" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="W171" t="n">
-        <v>1.655</v>
+        <v>0</v>
       </c>
       <c r="X171" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="Z171" t="n">
-        <v>19.482</v>
+        <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>4.795</v>
+        <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>34.933</v>
+        <v>0</v>
       </c>
       <c r="AC171" t="inlineStr"/>
     </row>
@@ -74952,67 +74952,67 @@
         <v>0</v>
       </c>
       <c r="H702" t="n">
-        <v>0</v>
+        <v>216.983</v>
       </c>
       <c r="I702" t="n">
-        <v>0</v>
+        <v>1.417</v>
       </c>
       <c r="J702" t="n">
-        <v>0</v>
+        <v>3.557</v>
       </c>
       <c r="K702" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="L702" t="n">
-        <v>0</v>
+        <v>0.698</v>
       </c>
       <c r="M702" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N702" t="n">
-        <v>0</v>
+        <v>123.864</v>
       </c>
       <c r="O702" t="n">
-        <v>0</v>
+        <v>310.104</v>
       </c>
       <c r="P702" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="Q702" t="n">
-        <v>0</v>
+        <v>2.822</v>
       </c>
       <c r="R702" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="S702" t="n">
-        <v>0</v>
+        <v>24.45</v>
       </c>
       <c r="T702" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="U702" t="n">
-        <v>0</v>
+        <v>0.657</v>
       </c>
       <c r="V702" t="n">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="W702" t="n">
-        <v>0</v>
+        <v>1.834</v>
       </c>
       <c r="X702" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="Y702" t="n">
-        <v>0</v>
+        <v>0.763</v>
       </c>
       <c r="Z702" t="n">
-        <v>0</v>
+        <v>13.801</v>
       </c>
       <c r="AA702" t="n">
-        <v>0</v>
+        <v>2.132</v>
       </c>
       <c r="AB702" t="n">
-        <v>0</v>
+        <v>29.475</v>
       </c>
       <c r="AC702" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -610,70 +610,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lamar Jackson</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3851</v>
+        <v>3717.2</v>
       </c>
       <c r="E3" t="n">
-        <v>2696.9</v>
+        <v>2621.4</v>
       </c>
       <c r="F3" t="n">
-        <v>29.91</v>
+        <v>25.36</v>
       </c>
       <c r="G3" t="n">
-        <v>20.82</v>
+        <v>17.79</v>
       </c>
       <c r="H3" t="n">
-        <v>767.3</v>
+        <v>886.1</v>
       </c>
       <c r="I3" t="n">
-        <v>542.7</v>
+        <v>626.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.32</v>
+        <v>7.11</v>
       </c>
       <c r="K3" t="n">
-        <v>3.08</v>
+        <v>5.02</v>
       </c>
       <c r="L3" t="n">
-        <v>7.55</v>
+        <v>10.08</v>
       </c>
       <c r="M3" t="n">
-        <v>5.33</v>
+        <v>7.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>4.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.89</v>
+        <v>2.86</v>
       </c>
       <c r="P3" t="n">
-        <v>355.87</v>
+        <v>353.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>249.47</v>
+        <v>248.8</v>
       </c>
       <c r="R3" t="n">
-        <v>185.78</v>
+        <v>184.73</v>
       </c>
       <c r="S3" t="n">
-        <v>313.55</v>
+        <v>313.23</v>
       </c>
       <c r="T3" t="n">
-        <v>237.04</v>
+        <v>233.01</v>
       </c>
       <c r="U3" t="n">
-        <v>12.43</v>
+        <v>15.79</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -681,70 +681,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Drake Maye</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3717.2</v>
+        <v>4325.5</v>
       </c>
       <c r="E4" t="n">
-        <v>2621.4</v>
+        <v>3048.8</v>
       </c>
       <c r="F4" t="n">
-        <v>25.36</v>
+        <v>28.49</v>
       </c>
       <c r="G4" t="n">
-        <v>17.79</v>
+        <v>20.07</v>
       </c>
       <c r="H4" t="n">
-        <v>886.1</v>
+        <v>529.9</v>
       </c>
       <c r="I4" t="n">
-        <v>626.2</v>
+        <v>375.5</v>
       </c>
       <c r="J4" t="n">
-        <v>7.11</v>
+        <v>4.89</v>
       </c>
       <c r="K4" t="n">
-        <v>5.02</v>
+        <v>3.47</v>
       </c>
       <c r="L4" t="n">
-        <v>10.08</v>
+        <v>9.1</v>
       </c>
       <c r="M4" t="n">
-        <v>7.12</v>
+        <v>6.42</v>
       </c>
       <c r="N4" t="n">
-        <v>4.05</v>
+        <v>3.81</v>
       </c>
       <c r="O4" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="P4" t="n">
-        <v>353.14</v>
+        <v>343.49</v>
       </c>
       <c r="Q4" t="n">
-        <v>248.8</v>
+        <v>242.38</v>
       </c>
       <c r="R4" t="n">
-        <v>184.73</v>
+        <v>177.67</v>
       </c>
       <c r="S4" t="n">
-        <v>313.23</v>
+        <v>306.52</v>
       </c>
       <c r="T4" t="n">
-        <v>233.01</v>
+        <v>237.46</v>
       </c>
       <c r="U4" t="n">
-        <v>15.79</v>
+        <v>4.92</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -752,70 +752,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4325.5</v>
+        <v>4244.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3048.8</v>
+        <v>3239.1</v>
       </c>
       <c r="F5" t="n">
-        <v>28.49</v>
+        <v>30.55</v>
       </c>
       <c r="G5" t="n">
-        <v>20.07</v>
+        <v>23.23</v>
       </c>
       <c r="H5" t="n">
-        <v>529.9</v>
+        <v>287.6</v>
       </c>
       <c r="I5" t="n">
-        <v>375.5</v>
+        <v>220.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4.89</v>
+        <v>3.07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.47</v>
+        <v>2.36</v>
       </c>
       <c r="L5" t="n">
-        <v>9.1</v>
+        <v>8.02</v>
       </c>
       <c r="M5" t="n">
-        <v>6.42</v>
+        <v>6.13</v>
       </c>
       <c r="N5" t="n">
-        <v>3.81</v>
+        <v>3.14</v>
       </c>
       <c r="O5" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>343.49</v>
+        <v>316.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>242.38</v>
+        <v>241.66</v>
       </c>
       <c r="R5" t="n">
-        <v>177.67</v>
+        <v>171.97</v>
       </c>
       <c r="S5" t="n">
-        <v>306.52</v>
+        <v>311.06</v>
       </c>
       <c r="T5" t="n">
-        <v>237.46</v>
+        <v>233.62</v>
       </c>
       <c r="U5" t="n">
-        <v>4.92</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -823,70 +823,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4244.6</v>
+        <v>4600.2</v>
       </c>
       <c r="E6" t="n">
-        <v>3239.1</v>
+        <v>3246.5</v>
       </c>
       <c r="F6" t="n">
-        <v>30.55</v>
+        <v>35.06</v>
       </c>
       <c r="G6" t="n">
-        <v>23.23</v>
+        <v>24.68</v>
       </c>
       <c r="H6" t="n">
-        <v>287.6</v>
+        <v>183.6</v>
       </c>
       <c r="I6" t="n">
-        <v>220.8</v>
+        <v>129.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.07</v>
+        <v>2.52</v>
       </c>
       <c r="K6" t="n">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="L6" t="n">
-        <v>8.02</v>
+        <v>12.19</v>
       </c>
       <c r="M6" t="n">
-        <v>6.13</v>
+        <v>8.6</v>
       </c>
       <c r="N6" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="P6" t="n">
-        <v>316.84</v>
+        <v>327.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>241.66</v>
+        <v>230.65</v>
       </c>
       <c r="R6" t="n">
-        <v>171.97</v>
+        <v>166.53</v>
       </c>
       <c r="S6" t="n">
-        <v>311.06</v>
+        <v>295.08</v>
       </c>
       <c r="T6" t="n">
-        <v>233.62</v>
+        <v>227.93</v>
       </c>
       <c r="U6" t="n">
-        <v>8.039999999999999</v>
+        <v>2.72</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -894,70 +894,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Lamar Jackson</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4600.2</v>
+        <v>3851</v>
       </c>
       <c r="E7" t="n">
-        <v>3246.5</v>
+        <v>2475.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.06</v>
+        <v>29.91</v>
       </c>
       <c r="G7" t="n">
-        <v>24.68</v>
+        <v>19.09</v>
       </c>
       <c r="H7" t="n">
-        <v>183.6</v>
+        <v>767.3</v>
       </c>
       <c r="I7" t="n">
-        <v>129.7</v>
+        <v>497.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.52</v>
+        <v>4.32</v>
       </c>
       <c r="K7" t="n">
-        <v>1.77</v>
+        <v>2.82</v>
       </c>
       <c r="L7" t="n">
-        <v>12.19</v>
+        <v>7.55</v>
       </c>
       <c r="M7" t="n">
-        <v>8.6</v>
+        <v>4.88</v>
       </c>
       <c r="N7" t="n">
-        <v>3.06</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="P7" t="n">
-        <v>327.23</v>
+        <v>355.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>230.65</v>
+        <v>228.87</v>
       </c>
       <c r="R7" t="n">
-        <v>166.53</v>
+        <v>170.44</v>
       </c>
       <c r="S7" t="n">
-        <v>295.08</v>
+        <v>287.66</v>
       </c>
       <c r="T7" t="n">
-        <v>227.93</v>
+        <v>237.04</v>
       </c>
       <c r="U7" t="n">
-        <v>2.72</v>
+        <v>-8.17</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -2949,64 +2949,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3442.3</v>
+        <v>3257.6</v>
       </c>
       <c r="E36" t="n">
-        <v>202.6</v>
+        <v>186.4</v>
       </c>
       <c r="F36" t="n">
-        <v>18.26</v>
+        <v>18.84</v>
       </c>
       <c r="G36" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H36" t="n">
-        <v>493.8</v>
+        <v>683.5</v>
       </c>
       <c r="I36" t="n">
-        <v>29.3</v>
+        <v>39.9</v>
       </c>
       <c r="J36" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="K36" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="L36" t="n">
-        <v>10.92</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="N36" t="n">
-        <v>2.68</v>
+        <v>3.67</v>
       </c>
       <c r="O36" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="P36" t="n">
-        <v>258.35</v>
+        <v>275.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>15.15</v>
+        <v>15.91</v>
       </c>
       <c r="R36" t="n">
-        <v>9.800000000000001</v>
+        <v>10.63</v>
       </c>
       <c r="S36" t="n">
-        <v>20.49</v>
+        <v>21.18</v>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -3016,64 +3016,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tanner McKee</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3608.3</v>
+        <v>3442.3</v>
       </c>
       <c r="E37" t="n">
-        <v>217</v>
+        <v>202.6</v>
       </c>
       <c r="F37" t="n">
-        <v>23.67</v>
+        <v>18.26</v>
       </c>
       <c r="G37" t="n">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="H37" t="n">
-        <v>57.9</v>
+        <v>493.8</v>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>29.3</v>
       </c>
       <c r="J37" t="n">
-        <v>2.29</v>
+        <v>4.24</v>
       </c>
       <c r="K37" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="L37" t="n">
-        <v>11.86</v>
+        <v>10.92</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="N37" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="O37" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="P37" t="n">
-        <v>229.16</v>
+        <v>258.35</v>
       </c>
       <c r="Q37" t="n">
-        <v>13.82</v>
+        <v>15.15</v>
       </c>
       <c r="R37" t="n">
-        <v>8.82</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S37" t="n">
-        <v>19.3</v>
+        <v>20.49</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3083,64 +3083,64 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3454</v>
+        <v>3608.3</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="F38" t="n">
-        <v>17.15</v>
+        <v>23.67</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="H38" t="n">
-        <v>828.4</v>
+        <v>57.9</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
-        <v>7.93</v>
+        <v>2.29</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="L38" t="n">
-        <v>13.69</v>
+        <v>11.86</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N38" t="n">
-        <v>4.48</v>
+        <v>2.83</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="P38" t="n">
-        <v>300.84</v>
+        <v>229.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>13.82</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -3150,55 +3150,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3182.6</v>
+        <v>3454</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>14.11</v>
+        <v>17.15</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>187.4</v>
+        <v>828.4</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>17.31</v>
+        <v>13.69</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.71</v>
+        <v>4.48</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>178.92</v>
+        <v>300.84</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3209,67 +3209,63 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="U39" t="n">
-        <v>-16.94</v>
-      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3429.1</v>
+        <v>3182.6</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>21.66</v>
+        <v>14.11</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>230.4</v>
+        <v>187.4</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.45</v>
+        <v>17.31</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>232.2</v>
+        <v>178.92</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3280,63 +3276,67 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-16.94</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3067.5</v>
+        <v>3429.1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>14.5</v>
+        <v>21.66</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>182.8</v>
+        <v>230.4</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>17.4</v>
+        <v>10.45</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>175.3</v>
+        <v>232.2</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3355,55 +3355,55 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3551</v>
+        <v>3067.5</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>20.63</v>
+        <v>14.5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>143.7</v>
+        <v>182.8</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>12.54</v>
+        <v>17.4</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>218.65</v>
+        <v>175.3</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3422,55 +3422,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3475</v>
+        <v>3551</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>19.12</v>
+        <v>20.63</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>255.3</v>
+        <v>143.7</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>11.58</v>
+        <v>12.54</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>229.07</v>
+        <v>218.65</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3489,55 +3489,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3363.7</v>
+        <v>3475</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>15.43</v>
+        <v>19.12</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>110.3</v>
+        <v>255.3</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>10.42</v>
+        <v>11.58</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>190.64</v>
+        <v>229.07</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3556,55 +3556,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3545</v>
+        <v>3363.7</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>16.71</v>
+        <v>15.43</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>271.4</v>
+        <v>110.3</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3.69</v>
+        <v>1.83</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>10.72</v>
+        <v>10.42</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>229.58</v>
+        <v>190.64</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3615,67 +3615,63 @@
       <c r="S45" t="n">
         <v>0</v>
       </c>
-      <c r="T45" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="U45" t="n">
-        <v>-20.96</v>
-      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3676.3</v>
+        <v>3545</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>19.16</v>
+        <v>16.71</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>322.3</v>
+        <v>271.4</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2.33</v>
+        <v>3.69</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>11.74</v>
+        <v>10.72</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>239.78</v>
+        <v>229.58</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3686,63 +3682,67 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-20.96</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3597.4</v>
+        <v>3676.3</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>25.54</v>
+        <v>19.16</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>33.5</v>
+        <v>322.3</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>11.54</v>
+        <v>11.74</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.51</v>
+        <v>3.32</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>229.81</v>
+        <v>239.78</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3761,55 +3761,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3434.9</v>
+        <v>3597.4</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>17.79</v>
+        <v>25.54</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>550.2</v>
+        <v>33.5</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4.94</v>
+        <v>1.75</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>11.09</v>
+        <v>11.54</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>264.58</v>
+        <v>229.81</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3828,55 +3828,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3258.7</v>
+        <v>3434.9</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>18.3</v>
+        <v>17.79</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>841.3</v>
+        <v>550.2</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>7.25</v>
+        <v>4.94</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>8.65</v>
+        <v>11.09</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>306.62</v>
+        <v>264.58</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3895,55 +3895,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3339.6</v>
+        <v>3258.7</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>16.36</v>
+        <v>18.3</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>188.9</v>
+        <v>841.3</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.88</v>
+        <v>7.25</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>11.86</v>
+        <v>8.65</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>199.01</v>
+        <v>306.62</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3962,55 +3962,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3444.9</v>
+        <v>3339.6</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>17.86</v>
+        <v>16.36</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>183.4</v>
+        <v>188.9</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>12.93</v>
+        <v>11.86</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>209.82</v>
+        <v>199.01</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4029,55 +4029,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3245.2</v>
+        <v>3444.9</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>17.86</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>182.3</v>
+        <v>183.4</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>17.38</v>
+        <v>12.93</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>180.38</v>
+        <v>209.82</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4096,55 +4096,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3583.4</v>
+        <v>3245.2</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>22.54</v>
+        <v>14</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>174.5</v>
+        <v>182.3</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>2.17</v>
+        <v>3.09</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10.7</v>
+        <v>17.38</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.59</v>
+        <v>3.72</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>237.39</v>
+        <v>180.38</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4163,55 +4163,55 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3644.1</v>
+        <v>3583.4</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>25.09</v>
+        <v>22.54</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>582.3</v>
+        <v>174.5</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>14.49</v>
+        <v>10.7</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.33</v>
+        <v>2.59</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>290.61</v>
+        <v>237.39</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4230,55 +4230,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3417.5</v>
+        <v>3644.1</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>20.18</v>
+        <v>25.09</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>149.2</v>
+        <v>582.3</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>9.380000000000001</v>
+        <v>14.49</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>217.88</v>
+        <v>290.61</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4297,55 +4297,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3540.7</v>
+        <v>3417.5</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>22.31</v>
+        <v>20.18</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>201.9</v>
+        <v>149.2</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>3.03</v>
+        <v>1.78</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>10.94</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.17</v>
+        <v>3.19</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>243.02</v>
+        <v>217.88</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4364,55 +4364,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3274.4</v>
+        <v>3540.7</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>17.46</v>
+        <v>22.31</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>153.2</v>
+        <v>201.9</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>12.86</v>
+        <v>10.94</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.11</v>
+        <v>2.17</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>196.6</v>
+        <v>243.02</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4431,55 +4431,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3326</v>
+        <v>3274.4</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>15.3</v>
+        <v>17.46</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>204.2</v>
+        <v>153.2</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>17.3</v>
+        <v>12.86</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>191.5</v>
+        <v>196.6</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4498,55 +4498,55 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>3393.6</v>
+        <v>3326</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>16.79</v>
+        <v>15.3</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>287</v>
+        <v>204.2</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>11.42</v>
+        <v>17.3</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>215.88</v>
+        <v>191.5</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4565,55 +4565,55 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3381.2</v>
+        <v>3393.6</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>15.85</v>
+        <v>16.79</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>184</v>
+        <v>287</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>15.75</v>
+        <v>11.42</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5.75</v>
+        <v>4.15</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>190.01</v>
+        <v>215.88</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4632,55 +4632,55 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3224.6</v>
+        <v>3381.2</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>15.34</v>
+        <v>15.85</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>443.2</v>
+        <v>184</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>10.63</v>
+        <v>15.75</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>225.58</v>
+        <v>190.01</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4699,55 +4699,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>3569.9</v>
+        <v>3224.6</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>21.31</v>
+        <v>15.34</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>40.1</v>
+        <v>443.2</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>9.66</v>
+        <v>10.63</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.98</v>
+        <v>3.81</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>216.43</v>
+        <v>225.58</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4758,67 +4758,63 @@
       <c r="S62" t="n">
         <v>0</v>
       </c>
-      <c r="T62" t="n">
-        <v>56.89</v>
-      </c>
-      <c r="U62" t="n">
-        <v>-56.89</v>
-      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>3257.6</v>
+        <v>3569.9</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>18.84</v>
+        <v>21.31</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>683.5</v>
+        <v>40.1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>4.19</v>
+        <v>1.61</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>8.380000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.67</v>
+        <v>2.98</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>275.05</v>
+        <v>216.43</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -4829,8 +4825,12 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
+      <c r="T63" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="U63" t="n">
+        <v>-56.89</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
     </row>
@@ -5173,70 +5173,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lamar Jackson</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3851</v>
+        <v>3717.2</v>
       </c>
       <c r="E3" t="n">
-        <v>2696.9</v>
+        <v>2621.4</v>
       </c>
       <c r="F3" t="n">
-        <v>29.91</v>
+        <v>25.36</v>
       </c>
       <c r="G3" t="n">
-        <v>20.82</v>
+        <v>17.79</v>
       </c>
       <c r="H3" t="n">
-        <v>767.3</v>
+        <v>886.1</v>
       </c>
       <c r="I3" t="n">
-        <v>542.7</v>
+        <v>626.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.32</v>
+        <v>7.11</v>
       </c>
       <c r="K3" t="n">
-        <v>3.08</v>
+        <v>5.02</v>
       </c>
       <c r="L3" t="n">
-        <v>7.55</v>
+        <v>10.08</v>
       </c>
       <c r="M3" t="n">
-        <v>5.33</v>
+        <v>7.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>4.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.89</v>
+        <v>2.86</v>
       </c>
       <c r="P3" t="n">
-        <v>355.87</v>
+        <v>353.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>249.47</v>
+        <v>248.8</v>
       </c>
       <c r="R3" t="n">
-        <v>185.78</v>
+        <v>184.73</v>
       </c>
       <c r="S3" t="n">
-        <v>313.55</v>
+        <v>313.23</v>
       </c>
       <c r="T3" t="n">
-        <v>237.04</v>
+        <v>233.01</v>
       </c>
       <c r="U3" t="n">
-        <v>12.43</v>
+        <v>15.79</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -5244,70 +5244,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Drake Maye</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3717.2</v>
+        <v>4325.5</v>
       </c>
       <c r="E4" t="n">
-        <v>2621.4</v>
+        <v>3048.8</v>
       </c>
       <c r="F4" t="n">
-        <v>25.36</v>
+        <v>28.49</v>
       </c>
       <c r="G4" t="n">
-        <v>17.79</v>
+        <v>20.07</v>
       </c>
       <c r="H4" t="n">
-        <v>886.1</v>
+        <v>529.9</v>
       </c>
       <c r="I4" t="n">
-        <v>626.2</v>
+        <v>375.5</v>
       </c>
       <c r="J4" t="n">
-        <v>7.11</v>
+        <v>4.89</v>
       </c>
       <c r="K4" t="n">
-        <v>5.02</v>
+        <v>3.47</v>
       </c>
       <c r="L4" t="n">
-        <v>10.08</v>
+        <v>9.1</v>
       </c>
       <c r="M4" t="n">
-        <v>7.12</v>
+        <v>6.42</v>
       </c>
       <c r="N4" t="n">
-        <v>4.05</v>
+        <v>3.81</v>
       </c>
       <c r="O4" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="P4" t="n">
-        <v>353.14</v>
+        <v>343.49</v>
       </c>
       <c r="Q4" t="n">
-        <v>248.8</v>
+        <v>242.38</v>
       </c>
       <c r="R4" t="n">
-        <v>184.73</v>
+        <v>177.67</v>
       </c>
       <c r="S4" t="n">
-        <v>313.23</v>
+        <v>306.52</v>
       </c>
       <c r="T4" t="n">
-        <v>233.01</v>
+        <v>237.46</v>
       </c>
       <c r="U4" t="n">
-        <v>15.79</v>
+        <v>4.92</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -5315,70 +5315,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4325.5</v>
+        <v>4244.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3048.8</v>
+        <v>3239.1</v>
       </c>
       <c r="F5" t="n">
-        <v>28.49</v>
+        <v>30.55</v>
       </c>
       <c r="G5" t="n">
-        <v>20.07</v>
+        <v>23.23</v>
       </c>
       <c r="H5" t="n">
-        <v>529.9</v>
+        <v>287.6</v>
       </c>
       <c r="I5" t="n">
-        <v>375.5</v>
+        <v>220.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4.89</v>
+        <v>3.07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.47</v>
+        <v>2.36</v>
       </c>
       <c r="L5" t="n">
-        <v>9.1</v>
+        <v>8.02</v>
       </c>
       <c r="M5" t="n">
-        <v>6.42</v>
+        <v>6.13</v>
       </c>
       <c r="N5" t="n">
-        <v>3.81</v>
+        <v>3.14</v>
       </c>
       <c r="O5" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>343.49</v>
+        <v>316.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>242.38</v>
+        <v>241.66</v>
       </c>
       <c r="R5" t="n">
-        <v>177.67</v>
+        <v>171.97</v>
       </c>
       <c r="S5" t="n">
-        <v>306.52</v>
+        <v>311.06</v>
       </c>
       <c r="T5" t="n">
-        <v>237.46</v>
+        <v>233.62</v>
       </c>
       <c r="U5" t="n">
-        <v>4.92</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -5386,70 +5386,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4244.6</v>
+        <v>4600.2</v>
       </c>
       <c r="E6" t="n">
-        <v>3239.1</v>
+        <v>3246.5</v>
       </c>
       <c r="F6" t="n">
-        <v>30.55</v>
+        <v>35.06</v>
       </c>
       <c r="G6" t="n">
-        <v>23.23</v>
+        <v>24.68</v>
       </c>
       <c r="H6" t="n">
-        <v>287.6</v>
+        <v>183.6</v>
       </c>
       <c r="I6" t="n">
-        <v>220.8</v>
+        <v>129.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.07</v>
+        <v>2.52</v>
       </c>
       <c r="K6" t="n">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="L6" t="n">
-        <v>8.02</v>
+        <v>12.19</v>
       </c>
       <c r="M6" t="n">
-        <v>6.13</v>
+        <v>8.6</v>
       </c>
       <c r="N6" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="P6" t="n">
-        <v>316.84</v>
+        <v>327.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>241.66</v>
+        <v>230.65</v>
       </c>
       <c r="R6" t="n">
-        <v>171.97</v>
+        <v>166.53</v>
       </c>
       <c r="S6" t="n">
-        <v>311.06</v>
+        <v>295.08</v>
       </c>
       <c r="T6" t="n">
-        <v>233.62</v>
+        <v>227.93</v>
       </c>
       <c r="U6" t="n">
-        <v>8.039999999999999</v>
+        <v>2.72</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -5457,70 +5457,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Lamar Jackson</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4600.2</v>
+        <v>3851</v>
       </c>
       <c r="E7" t="n">
-        <v>3246.5</v>
+        <v>2475.5</v>
       </c>
       <c r="F7" t="n">
-        <v>35.06</v>
+        <v>29.91</v>
       </c>
       <c r="G7" t="n">
-        <v>24.68</v>
+        <v>19.09</v>
       </c>
       <c r="H7" t="n">
-        <v>183.6</v>
+        <v>767.3</v>
       </c>
       <c r="I7" t="n">
-        <v>129.7</v>
+        <v>497.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.52</v>
+        <v>4.32</v>
       </c>
       <c r="K7" t="n">
-        <v>1.77</v>
+        <v>2.82</v>
       </c>
       <c r="L7" t="n">
-        <v>12.19</v>
+        <v>7.55</v>
       </c>
       <c r="M7" t="n">
-        <v>8.6</v>
+        <v>4.88</v>
       </c>
       <c r="N7" t="n">
-        <v>3.06</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="P7" t="n">
-        <v>327.23</v>
+        <v>355.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>230.65</v>
+        <v>228.87</v>
       </c>
       <c r="R7" t="n">
-        <v>166.53</v>
+        <v>170.44</v>
       </c>
       <c r="S7" t="n">
-        <v>295.08</v>
+        <v>287.66</v>
       </c>
       <c r="T7" t="n">
-        <v>227.93</v>
+        <v>237.04</v>
       </c>
       <c r="U7" t="n">
-        <v>2.72</v>
+        <v>-8.17</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -7643,64 +7643,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3442.3</v>
+        <v>3257.6</v>
       </c>
       <c r="E4" t="n">
-        <v>202.6</v>
+        <v>186.4</v>
       </c>
       <c r="F4" t="n">
-        <v>18.26</v>
+        <v>18.84</v>
       </c>
       <c r="G4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H4" t="n">
-        <v>493.8</v>
+        <v>683.5</v>
       </c>
       <c r="I4" t="n">
-        <v>29.3</v>
+        <v>39.9</v>
       </c>
       <c r="J4" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="K4" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="L4" t="n">
-        <v>10.92</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>3.67</v>
       </c>
       <c r="O4" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="P4" t="n">
-        <v>258.35</v>
+        <v>275.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.15</v>
+        <v>15.91</v>
       </c>
       <c r="R4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.63</v>
       </c>
       <c r="S4" t="n">
-        <v>20.49</v>
+        <v>21.18</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -7710,64 +7710,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tanner McKee</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3608.3</v>
+        <v>3442.3</v>
       </c>
       <c r="E5" t="n">
-        <v>217</v>
+        <v>202.6</v>
       </c>
       <c r="F5" t="n">
-        <v>23.67</v>
+        <v>18.26</v>
       </c>
       <c r="G5" t="n">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="H5" t="n">
-        <v>57.9</v>
+        <v>493.8</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6</v>
+        <v>29.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.29</v>
+        <v>4.24</v>
       </c>
       <c r="K5" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="L5" t="n">
-        <v>11.86</v>
+        <v>10.92</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="N5" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="P5" t="n">
-        <v>229.16</v>
+        <v>258.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.82</v>
+        <v>15.15</v>
       </c>
       <c r="R5" t="n">
-        <v>8.82</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>19.3</v>
+        <v>20.49</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -7777,64 +7777,64 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3454</v>
+        <v>3608.3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="F6" t="n">
-        <v>17.15</v>
+        <v>23.67</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="H6" t="n">
-        <v>828.4</v>
+        <v>57.9</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
-        <v>7.93</v>
+        <v>2.29</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="L6" t="n">
-        <v>13.69</v>
+        <v>11.86</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N6" t="n">
-        <v>4.48</v>
+        <v>2.83</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="P6" t="n">
-        <v>300.84</v>
+        <v>229.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>13.82</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -7844,55 +7844,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3182.6</v>
+        <v>3454</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>14.11</v>
+        <v>17.15</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>187.4</v>
+        <v>828.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>17.31</v>
+        <v>13.69</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.71</v>
+        <v>4.48</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>178.92</v>
+        <v>300.84</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -7903,67 +7903,63 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-16.94</v>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3429.1</v>
+        <v>3182.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>21.66</v>
+        <v>14.11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>230.4</v>
+        <v>187.4</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10.45</v>
+        <v>17.31</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>232.2</v>
+        <v>178.92</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -7974,63 +7970,67 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-16.94</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3067.5</v>
+        <v>3429.1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>14.5</v>
+        <v>21.66</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>182.8</v>
+        <v>230.4</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>17.4</v>
+        <v>10.45</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>175.3</v>
+        <v>232.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8049,55 +8049,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3551</v>
+        <v>3067.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>20.63</v>
+        <v>14.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>143.7</v>
+        <v>182.8</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12.54</v>
+        <v>17.4</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>218.65</v>
+        <v>175.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8116,55 +8116,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3475</v>
+        <v>3551</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>19.12</v>
+        <v>20.63</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>255.3</v>
+        <v>143.7</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11.58</v>
+        <v>12.54</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>229.07</v>
+        <v>218.65</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8183,55 +8183,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3363.7</v>
+        <v>3475</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>15.43</v>
+        <v>19.12</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>110.3</v>
+        <v>255.3</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10.42</v>
+        <v>11.58</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>190.64</v>
+        <v>229.07</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8250,55 +8250,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3545</v>
+        <v>3363.7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>16.71</v>
+        <v>15.43</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>271.4</v>
+        <v>110.3</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.69</v>
+        <v>1.83</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.72</v>
+        <v>10.42</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>229.58</v>
+        <v>190.64</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8309,67 +8309,63 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-20.96</v>
-      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3676.3</v>
+        <v>3545</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>19.16</v>
+        <v>16.71</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>322.3</v>
+        <v>271.4</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>3.69</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11.74</v>
+        <v>10.72</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>239.78</v>
+        <v>229.58</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8380,63 +8376,67 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-20.96</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3597.4</v>
+        <v>3676.3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>25.54</v>
+        <v>19.16</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>33.5</v>
+        <v>322.3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>11.54</v>
+        <v>11.74</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.51</v>
+        <v>3.32</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>229.81</v>
+        <v>239.78</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8455,55 +8455,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3434.9</v>
+        <v>3597.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>17.79</v>
+        <v>25.54</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>550.2</v>
+        <v>33.5</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.94</v>
+        <v>1.75</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>11.09</v>
+        <v>11.54</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>264.58</v>
+        <v>229.81</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -8522,55 +8522,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3258.7</v>
+        <v>3434.9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>18.3</v>
+        <v>17.79</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>841.3</v>
+        <v>550.2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7.25</v>
+        <v>4.94</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>8.65</v>
+        <v>11.09</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>306.62</v>
+        <v>264.58</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -8589,55 +8589,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3339.6</v>
+        <v>3258.7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>16.36</v>
+        <v>18.3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>188.9</v>
+        <v>841.3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.88</v>
+        <v>7.25</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>11.86</v>
+        <v>8.65</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>199.01</v>
+        <v>306.62</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -8656,55 +8656,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3444.9</v>
+        <v>3339.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>17.86</v>
+        <v>16.36</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>183.4</v>
+        <v>188.9</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>12.93</v>
+        <v>11.86</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>209.82</v>
+        <v>199.01</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -8723,55 +8723,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3245.2</v>
+        <v>3444.9</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>17.86</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>182.3</v>
+        <v>183.4</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>17.38</v>
+        <v>12.93</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>180.38</v>
+        <v>209.82</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -8790,55 +8790,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3583.4</v>
+        <v>3245.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>22.54</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>174.5</v>
+        <v>182.3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.17</v>
+        <v>3.09</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>10.7</v>
+        <v>17.38</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.59</v>
+        <v>3.72</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>237.39</v>
+        <v>180.38</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -8857,55 +8857,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3644.1</v>
+        <v>3583.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>25.09</v>
+        <v>22.54</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>582.3</v>
+        <v>174.5</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>14.49</v>
+        <v>10.7</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.33</v>
+        <v>2.59</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>290.61</v>
+        <v>237.39</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -8924,55 +8924,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3417.5</v>
+        <v>3644.1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>20.18</v>
+        <v>25.09</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>149.2</v>
+        <v>582.3</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>9.380000000000001</v>
+        <v>14.49</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>217.88</v>
+        <v>290.61</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -8991,55 +8991,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3540.7</v>
+        <v>3417.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>22.31</v>
+        <v>20.18</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>201.9</v>
+        <v>149.2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3.03</v>
+        <v>1.78</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>10.94</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.17</v>
+        <v>3.19</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>243.02</v>
+        <v>217.88</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -9058,55 +9058,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3274.4</v>
+        <v>3540.7</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>17.46</v>
+        <v>22.31</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>153.2</v>
+        <v>201.9</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>12.86</v>
+        <v>10.94</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.11</v>
+        <v>2.17</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>196.6</v>
+        <v>243.02</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -9125,55 +9125,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3326</v>
+        <v>3274.4</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>15.3</v>
+        <v>17.46</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>204.2</v>
+        <v>153.2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>17.3</v>
+        <v>12.86</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>191.5</v>
+        <v>196.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -9192,55 +9192,55 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3393.6</v>
+        <v>3326</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>16.79</v>
+        <v>15.3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>287</v>
+        <v>204.2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>11.42</v>
+        <v>17.3</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>215.88</v>
+        <v>191.5</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -9259,55 +9259,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3381.2</v>
+        <v>3393.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>15.85</v>
+        <v>16.79</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>184</v>
+        <v>287</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>15.75</v>
+        <v>11.42</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.75</v>
+        <v>4.15</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>190.01</v>
+        <v>215.88</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -9326,55 +9326,55 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3224.6</v>
+        <v>3381.2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>15.34</v>
+        <v>15.85</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>443.2</v>
+        <v>184</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>10.63</v>
+        <v>15.75</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>225.58</v>
+        <v>190.01</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -9393,55 +9393,55 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3569.9</v>
+        <v>3224.6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>21.31</v>
+        <v>15.34</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>40.1</v>
+        <v>443.2</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>9.66</v>
+        <v>10.63</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>3.81</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>216.43</v>
+        <v>225.58</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -9452,67 +9452,63 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="T30" t="n">
-        <v>56.89</v>
-      </c>
-      <c r="U30" t="n">
-        <v>-56.89</v>
-      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3257.6</v>
+        <v>3569.9</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>18.84</v>
+        <v>21.31</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>683.5</v>
+        <v>40.1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4.19</v>
+        <v>1.61</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>8.380000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.67</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>275.05</v>
+        <v>216.43</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -9523,8 +9519,12 @@
       <c r="S31" t="n">
         <v>0</v>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-56.89</v>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
     </row>
@@ -36636,67 +36636,67 @@
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>221.333</v>
+        <v>0</v>
       </c>
       <c r="I290" t="n">
-        <v>1.736</v>
+        <v>0</v>
       </c>
       <c r="J290" t="n">
-        <v>44.797</v>
+        <v>0</v>
       </c>
       <c r="K290" t="n">
-        <v>0.262</v>
+        <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>0.157</v>
+        <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>128.214</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
-        <v>314.455</v>
+        <v>0</v>
       </c>
       <c r="P290" t="n">
-        <v>0.601</v>
+        <v>0</v>
       </c>
       <c r="Q290" t="n">
-        <v>3.141</v>
+        <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>23.901</v>
+        <v>0</v>
       </c>
       <c r="S290" t="n">
-        <v>65.69</v>
+        <v>0</v>
       </c>
       <c r="T290" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="U290" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="V290" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="W290" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X290" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>0.753</v>
+        <v>0</v>
       </c>
       <c r="Z290" t="n">
-        <v>20.646</v>
+        <v>0</v>
       </c>
       <c r="AA290" t="n">
-        <v>5.801</v>
+        <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>35.975</v>
+        <v>0</v>
       </c>
       <c r="AC290" t="inlineStr"/>
     </row>
@@ -77928,67 +77928,67 @@
         <v>0</v>
       </c>
       <c r="H734" t="n">
-        <v>0</v>
+        <v>186.427</v>
       </c>
       <c r="I734" t="n">
-        <v>0</v>
+        <v>1.094</v>
       </c>
       <c r="J734" t="n">
-        <v>0</v>
+        <v>39.871</v>
       </c>
       <c r="K734" t="n">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>0.494</v>
       </c>
       <c r="M734" t="n">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="N734" t="n">
-        <v>0</v>
+        <v>93.306</v>
       </c>
       <c r="O734" t="n">
-        <v>0</v>
+        <v>279.546</v>
       </c>
       <c r="P734" t="n">
-        <v>0</v>
+        <v>0.379</v>
       </c>
       <c r="Q734" t="n">
-        <v>0</v>
+        <v>2.498</v>
       </c>
       <c r="R734" t="n">
-        <v>0</v>
+        <v>18.979</v>
       </c>
       <c r="S734" t="n">
-        <v>0</v>
+        <v>60.761</v>
       </c>
       <c r="T734" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U734" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="V734" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="W734" t="n">
-        <v>0</v>
+        <v>1.629</v>
       </c>
       <c r="X734" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="Y734" t="n">
-        <v>0</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="Z734" t="n">
-        <v>0</v>
+        <v>15.884</v>
       </c>
       <c r="AA734" t="n">
-        <v>0</v>
+        <v>2.778</v>
       </c>
       <c r="AB734" t="n">
-        <v>0</v>
+        <v>31.351</v>
       </c>
       <c r="AC734" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -622,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3882</v>
+        <v>3882.6</v>
       </c>
       <c r="E3" t="n">
         <v>2505.6</v>
@@ -658,13 +658,13 @@
         <v>1.79</v>
       </c>
       <c r="P3" t="n">
-        <v>357.24</v>
+        <v>357.26</v>
       </c>
       <c r="Q3" t="n">
         <v>230.62</v>
       </c>
       <c r="R3" t="n">
-        <v>171.74</v>
+        <v>171.75</v>
       </c>
       <c r="S3" t="n">
         <v>289.48</v>
@@ -681,70 +681,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3697</v>
+        <v>4377.9</v>
       </c>
       <c r="E4" t="n">
-        <v>2382.2</v>
+        <v>3081.6</v>
       </c>
       <c r="F4" t="n">
-        <v>25.41</v>
+        <v>33.35</v>
       </c>
       <c r="G4" t="n">
-        <v>16.31</v>
+        <v>23.39</v>
       </c>
       <c r="H4" t="n">
-        <v>886.1</v>
+        <v>171.3</v>
       </c>
       <c r="I4" t="n">
-        <v>574.5</v>
+        <v>121.9</v>
       </c>
       <c r="J4" t="n">
-        <v>7.11</v>
+        <v>2.24</v>
       </c>
       <c r="K4" t="n">
-        <v>4.59</v>
+        <v>1.59</v>
       </c>
       <c r="L4" t="n">
-        <v>10.08</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>6.52</v>
+        <v>6.72</v>
       </c>
       <c r="N4" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="P4" t="n">
-        <v>352.53</v>
+        <v>314.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>227.24</v>
+        <v>221.37</v>
       </c>
       <c r="R4" t="n">
-        <v>168.75</v>
+        <v>158.51</v>
       </c>
       <c r="S4" t="n">
-        <v>286.32</v>
+        <v>285.4</v>
       </c>
       <c r="T4" t="n">
-        <v>213.59</v>
+        <v>234.35</v>
       </c>
       <c r="U4" t="n">
-        <v>13.65</v>
+        <v>-12.98</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -764,7 +764,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4157</v>
+        <v>4165.3</v>
       </c>
       <c r="E5" t="n">
         <v>2672.8</v>
@@ -800,16 +800,16 @@
         <v>1.77</v>
       </c>
       <c r="P5" t="n">
-        <v>343.5</v>
+        <v>343.83</v>
       </c>
       <c r="Q5" t="n">
         <v>221.26</v>
       </c>
       <c r="R5" t="n">
-        <v>162.5</v>
+        <v>162.55</v>
       </c>
       <c r="S5" t="n">
-        <v>279.98</v>
+        <v>279.93</v>
       </c>
       <c r="T5" t="n">
         <v>217.67</v>
@@ -823,70 +823,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4361.6</v>
+        <v>3715.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3065.3</v>
+        <v>2387.3</v>
       </c>
       <c r="F6" t="n">
-        <v>33.27</v>
+        <v>24.38</v>
       </c>
       <c r="G6" t="n">
-        <v>23.31</v>
+        <v>15.65</v>
       </c>
       <c r="H6" t="n">
-        <v>171.3</v>
+        <v>779.2</v>
       </c>
       <c r="I6" t="n">
-        <v>121.9</v>
+        <v>505.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.24</v>
+        <v>6.46</v>
       </c>
       <c r="K6" t="n">
-        <v>1.59</v>
+        <v>4.17</v>
       </c>
       <c r="L6" t="n">
-        <v>9.529999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="M6" t="n">
-        <v>6.72</v>
+        <v>6.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>3.33</v>
       </c>
       <c r="O6" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="P6" t="n">
-        <v>313.75</v>
+        <v>337.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>220.4</v>
+        <v>217.16</v>
       </c>
       <c r="R6" t="n">
-        <v>157.57</v>
+        <v>158.29</v>
       </c>
       <c r="S6" t="n">
-        <v>284.3</v>
+        <v>275.7</v>
       </c>
       <c r="T6" t="n">
-        <v>234.35</v>
+        <v>213.59</v>
       </c>
       <c r="U6" t="n">
-        <v>-13.95</v>
+        <v>3.57</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -894,70 +894,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4221.7</v>
+        <v>4142.4</v>
       </c>
       <c r="E7" t="n">
-        <v>2971.4</v>
+        <v>2666.4</v>
       </c>
       <c r="F7" t="n">
-        <v>28.65</v>
+        <v>34.45</v>
       </c>
       <c r="G7" t="n">
-        <v>20.01</v>
+        <v>22.1</v>
       </c>
       <c r="H7" t="n">
-        <v>270.4</v>
+        <v>349.1</v>
       </c>
       <c r="I7" t="n">
-        <v>191.6</v>
+        <v>225.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="L7" t="n">
-        <v>10.11</v>
+        <v>8.09</v>
       </c>
       <c r="M7" t="n">
-        <v>7.13</v>
+        <v>5.23</v>
       </c>
       <c r="N7" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="O7" t="n">
-        <v>2.21</v>
+        <v>1.96</v>
       </c>
       <c r="P7" t="n">
-        <v>302.03</v>
+        <v>337.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>212.16</v>
+        <v>217.06</v>
       </c>
       <c r="R7" t="n">
-        <v>148.25</v>
+        <v>158.46</v>
       </c>
       <c r="S7" t="n">
-        <v>275.95</v>
+        <v>275.77</v>
       </c>
       <c r="T7" t="n">
-        <v>215.65</v>
+        <v>206.74</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.49</v>
+        <v>10.32</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -965,70 +965,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4552</v>
+        <v>4227.9</v>
       </c>
       <c r="E8" t="n">
-        <v>3179.4</v>
+        <v>2977</v>
       </c>
       <c r="F8" t="n">
-        <v>31.27</v>
+        <v>28.63</v>
       </c>
       <c r="G8" t="n">
-        <v>21.91</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>29.7</v>
+        <v>270.4</v>
       </c>
       <c r="I8" t="n">
-        <v>21.6</v>
+        <v>191.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.47</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.05</v>
+        <v>2.13</v>
       </c>
       <c r="L8" t="n">
-        <v>8.949999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="M8" t="n">
-        <v>6.32</v>
+        <v>7.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.47</v>
+        <v>3.13</v>
       </c>
       <c r="O8" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="P8" t="n">
-        <v>296.11</v>
+        <v>302.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>207.14</v>
+        <v>212.34</v>
       </c>
       <c r="R8" t="n">
-        <v>154.51</v>
+        <v>148.47</v>
       </c>
       <c r="S8" t="n">
-        <v>270.42</v>
+        <v>276.21</v>
       </c>
       <c r="T8" t="n">
-        <v>213.67</v>
+        <v>215.65</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.53</v>
+        <v>-3.31</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
@@ -1036,70 +1036,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3989</v>
+        <v>4690.5</v>
       </c>
       <c r="E9" t="n">
-        <v>2576.2</v>
+        <v>3040.6</v>
       </c>
       <c r="F9" t="n">
-        <v>33.72</v>
+        <v>36.53</v>
       </c>
       <c r="G9" t="n">
-        <v>21.67</v>
+        <v>24.03</v>
       </c>
       <c r="H9" t="n">
-        <v>338.2</v>
+        <v>41</v>
       </c>
       <c r="I9" t="n">
-        <v>218.7</v>
+        <v>26.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.44</v>
+        <v>1.23</v>
       </c>
       <c r="K9" t="n">
-        <v>2.23</v>
+        <v>0.82</v>
       </c>
       <c r="L9" t="n">
-        <v>10.67</v>
+        <v>10.84</v>
       </c>
       <c r="M9" t="n">
-        <v>6.91</v>
+        <v>7.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>321.36</v>
+        <v>318.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>207.12</v>
+        <v>208.32</v>
       </c>
       <c r="R9" t="n">
-        <v>148.49</v>
+        <v>159.47</v>
       </c>
       <c r="S9" t="n">
-        <v>266.04</v>
+        <v>267.46</v>
       </c>
       <c r="T9" t="n">
-        <v>206.74</v>
+        <v>189.07</v>
       </c>
       <c r="U9" t="n">
-        <v>0.38</v>
+        <v>19.25</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -1107,70 +1107,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4653.5</v>
+        <v>4534.6</v>
       </c>
       <c r="E10" t="n">
-        <v>3011</v>
+        <v>2931.2</v>
       </c>
       <c r="F10" t="n">
-        <v>36.49</v>
+        <v>34.62</v>
       </c>
       <c r="G10" t="n">
-        <v>23.98</v>
+        <v>22.39</v>
       </c>
       <c r="H10" t="n">
-        <v>41</v>
+        <v>173.2</v>
       </c>
       <c r="I10" t="n">
-        <v>26.8</v>
+        <v>112.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.23</v>
+        <v>2.52</v>
       </c>
       <c r="K10" t="n">
-        <v>0.82</v>
+        <v>1.64</v>
       </c>
       <c r="L10" t="n">
-        <v>10.84</v>
+        <v>12.24</v>
       </c>
       <c r="M10" t="n">
-        <v>7.01</v>
+        <v>7.92</v>
       </c>
       <c r="N10" t="n">
-        <v>2.32</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="P10" t="n">
-        <v>317.26</v>
+        <v>321.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>206.94</v>
+        <v>208</v>
       </c>
       <c r="R10" t="n">
-        <v>158.27</v>
+        <v>149.2</v>
       </c>
       <c r="S10" t="n">
-        <v>265.84</v>
+        <v>267.17</v>
       </c>
       <c r="T10" t="n">
-        <v>189.07</v>
+        <v>208.94</v>
       </c>
       <c r="U10" t="n">
-        <v>17.87</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -1190,16 +1190,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4149.1</v>
+        <v>4176</v>
       </c>
       <c r="E11" t="n">
-        <v>2705.7</v>
+        <v>2723.5</v>
       </c>
       <c r="F11" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="G11" t="n">
-        <v>21.1</v>
+        <v>21.18</v>
       </c>
       <c r="H11" t="n">
         <v>286</v>
@@ -1226,22 +1226,22 @@
         <v>2.31</v>
       </c>
       <c r="P11" t="n">
-        <v>317.26</v>
+        <v>318.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>206.64</v>
+        <v>207.67</v>
       </c>
       <c r="R11" t="n">
-        <v>147.48</v>
+        <v>148.54</v>
       </c>
       <c r="S11" t="n">
-        <v>266.27</v>
+        <v>267.41</v>
       </c>
       <c r="T11" t="n">
         <v>208.68</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.04</v>
+        <v>-1.01</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1249,70 +1249,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4476.9</v>
+        <v>4552.9</v>
       </c>
       <c r="E12" t="n">
-        <v>2890.1</v>
+        <v>3180.4</v>
       </c>
       <c r="F12" t="n">
-        <v>34.49</v>
+        <v>31.27</v>
       </c>
       <c r="G12" t="n">
-        <v>22.34</v>
+        <v>21.91</v>
       </c>
       <c r="H12" t="n">
-        <v>173.2</v>
+        <v>29.7</v>
       </c>
       <c r="I12" t="n">
-        <v>112.1</v>
+        <v>21.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.52</v>
+        <v>1.47</v>
       </c>
       <c r="K12" t="n">
-        <v>1.64</v>
+        <v>1.05</v>
       </c>
       <c r="L12" t="n">
-        <v>12.24</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>7.92</v>
+        <v>6.32</v>
       </c>
       <c r="N12" t="n">
-        <v>3.11</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>318.78</v>
+        <v>296.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>206.15</v>
+        <v>207.18</v>
       </c>
       <c r="R12" t="n">
-        <v>147.18</v>
+        <v>154.55</v>
       </c>
       <c r="S12" t="n">
-        <v>265.13</v>
+        <v>270.46</v>
       </c>
       <c r="T12" t="n">
-        <v>208.94</v>
+        <v>213.67</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.79</v>
+        <v>-6.49</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4065.9</v>
+        <v>4083.3</v>
       </c>
       <c r="E13" t="n">
-        <v>2880.9</v>
+        <v>2889.2</v>
       </c>
       <c r="F13" t="n">
         <v>26.45</v>
@@ -1368,22 +1368,22 @@
         <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>279.52</v>
+        <v>280.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>198.22</v>
+        <v>198.55</v>
       </c>
       <c r="R13" t="n">
-        <v>133.48</v>
+        <v>133.87</v>
       </c>
       <c r="S13" t="n">
-        <v>262.82</v>
+        <v>263.1</v>
       </c>
       <c r="T13" t="n">
         <v>169.55</v>
       </c>
       <c r="U13" t="n">
-        <v>28.67</v>
+        <v>29</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -1403,16 +1403,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3535.9</v>
+        <v>3549.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2476.8</v>
+        <v>2490.4</v>
       </c>
       <c r="F14" t="n">
-        <v>21.49</v>
+        <v>21.54</v>
       </c>
       <c r="G14" t="n">
-        <v>14.95</v>
+        <v>15.01</v>
       </c>
       <c r="H14" t="n">
         <v>532.5</v>
@@ -1439,22 +1439,22 @@
         <v>2.34</v>
       </c>
       <c r="P14" t="n">
-        <v>278.75</v>
+        <v>279.49</v>
       </c>
       <c r="Q14" t="n">
-        <v>195.22</v>
+        <v>196.01</v>
       </c>
       <c r="R14" t="n">
-        <v>131.44</v>
+        <v>132.28</v>
       </c>
       <c r="S14" t="n">
-        <v>259.17</v>
+        <v>260.19</v>
       </c>
       <c r="T14" t="n">
         <v>226.66</v>
       </c>
       <c r="U14" t="n">
-        <v>-31.44</v>
+        <v>-30.65</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3688</v>
+        <v>3705.4</v>
       </c>
       <c r="E16" t="n">
-        <v>2358.1</v>
+        <v>2366.4</v>
       </c>
       <c r="F16" t="n">
         <v>27.3</v>
@@ -1581,22 +1581,22 @@
         <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>296.67</v>
+        <v>297.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>191.54</v>
+        <v>191.88</v>
       </c>
       <c r="R16" t="n">
-        <v>132.84</v>
+        <v>133.21</v>
       </c>
       <c r="S16" t="n">
-        <v>250.32</v>
+        <v>250.63</v>
       </c>
       <c r="T16" t="n">
         <v>210.04</v>
       </c>
       <c r="U16" t="n">
-        <v>-18.5</v>
+        <v>-18.16</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
@@ -1616,16 +1616,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4337.6</v>
+        <v>4364.6</v>
       </c>
       <c r="E17" t="n">
-        <v>2782.9</v>
+        <v>2809.2</v>
       </c>
       <c r="F17" t="n">
-        <v>28.14</v>
+        <v>28.22</v>
       </c>
       <c r="G17" t="n">
-        <v>18.21</v>
+        <v>18.28</v>
       </c>
       <c r="H17" t="n">
         <v>234.1</v>
@@ -1652,22 +1652,22 @@
         <v>2.16</v>
       </c>
       <c r="P17" t="n">
-        <v>294.73</v>
+        <v>296.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>189.66</v>
+        <v>190.99</v>
       </c>
       <c r="R17" t="n">
-        <v>131.17</v>
+        <v>132.42</v>
       </c>
       <c r="S17" t="n">
-        <v>248.16</v>
+        <v>249.67</v>
       </c>
       <c r="T17" t="n">
         <v>174.9</v>
       </c>
       <c r="U17" t="n">
-        <v>14.76</v>
+        <v>16.09</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -1687,13 +1687,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3371.5</v>
+        <v>3369.4</v>
       </c>
       <c r="E18" t="n">
-        <v>2367.9</v>
+        <v>2368.5</v>
       </c>
       <c r="F18" t="n">
-        <v>19.38</v>
+        <v>19.37</v>
       </c>
       <c r="G18" t="n">
         <v>13.61</v>
@@ -1723,22 +1723,22 @@
         <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>259.69</v>
+        <v>259.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>182.64</v>
+        <v>182.66</v>
       </c>
       <c r="R18" t="n">
-        <v>118.46</v>
+        <v>118.47</v>
       </c>
       <c r="S18" t="n">
-        <v>246.72</v>
+        <v>246.81</v>
       </c>
       <c r="T18" t="n">
         <v>192.85</v>
       </c>
       <c r="U18" t="n">
-        <v>-10.21</v>
+        <v>-10.19</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
@@ -1758,10 +1758,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3501</v>
+        <v>3502.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2237.4</v>
+        <v>2239</v>
       </c>
       <c r="F19" t="n">
         <v>20.43</v>
@@ -1794,22 +1794,22 @@
         <v>2.74</v>
       </c>
       <c r="P19" t="n">
-        <v>280.34</v>
+        <v>280.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>181.18</v>
+        <v>181.24</v>
       </c>
       <c r="R19" t="n">
-        <v>122.14</v>
+        <v>122.19</v>
       </c>
       <c r="S19" t="n">
-        <v>240.01</v>
+        <v>240.08</v>
       </c>
       <c r="T19" t="n">
         <v>67.42</v>
       </c>
       <c r="U19" t="n">
-        <v>113.76</v>
+        <v>113.82</v>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
@@ -1829,13 +1829,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3842.8</v>
+        <v>3848.4</v>
       </c>
       <c r="E20" t="n">
         <v>2492.8</v>
       </c>
       <c r="F20" t="n">
-        <v>25.18</v>
+        <v>25.16</v>
       </c>
       <c r="G20" t="n">
         <v>16.37</v>
@@ -1853,10 +1853,10 @@
         <v>1.97</v>
       </c>
       <c r="L20" t="n">
-        <v>11.06</v>
+        <v>11.18</v>
       </c>
       <c r="M20" t="n">
-        <v>7.15</v>
+        <v>7.23</v>
       </c>
       <c r="N20" t="n">
         <v>3.15</v>
@@ -1865,22 +1865,22 @@
         <v>2.04</v>
       </c>
       <c r="P20" t="n">
-        <v>272.35</v>
+        <v>272.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>176.93</v>
+        <v>176.77</v>
       </c>
       <c r="R20" t="n">
-        <v>117.71</v>
+        <v>117.66</v>
       </c>
       <c r="S20" t="n">
-        <v>236.19</v>
+        <v>236.07</v>
       </c>
       <c r="T20" t="n">
         <v>196.38</v>
       </c>
       <c r="U20" t="n">
-        <v>-19.45</v>
+        <v>-19.61</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3791.8</v>
+        <v>3801.6</v>
       </c>
       <c r="E21" t="n">
-        <v>2443.1</v>
+        <v>2452.2</v>
       </c>
       <c r="F21" t="n">
         <v>29.82</v>
@@ -1936,22 +1936,22 @@
         <v>1.83</v>
       </c>
       <c r="P21" t="n">
-        <v>268.26</v>
+        <v>268.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>174.32</v>
+        <v>174.69</v>
       </c>
       <c r="R21" t="n">
-        <v>118.5</v>
+        <v>118.83</v>
       </c>
       <c r="S21" t="n">
-        <v>233.81</v>
+        <v>234.22</v>
       </c>
       <c r="T21" t="n">
         <v>165.13</v>
       </c>
       <c r="U21" t="n">
-        <v>9.19</v>
+        <v>9.56</v>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3768.4</v>
+        <v>3769.3</v>
       </c>
       <c r="E22" t="n">
         <v>2450.3</v>
@@ -2007,13 +2007,13 @@
         <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>264.34</v>
+        <v>264.37</v>
       </c>
       <c r="Q22" t="n">
         <v>171.66</v>
       </c>
       <c r="R22" t="n">
-        <v>112.39</v>
+        <v>112.4</v>
       </c>
       <c r="S22" t="n">
         <v>230.57</v>
@@ -2042,13 +2042,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3903.2</v>
+        <v>3928.9</v>
       </c>
       <c r="E23" t="n">
-        <v>2522.5</v>
+        <v>2532.6</v>
       </c>
       <c r="F23" t="n">
-        <v>22.54</v>
+        <v>22.61</v>
       </c>
       <c r="G23" t="n">
         <v>14.51</v>
@@ -2078,22 +2078,22 @@
         <v>2.26</v>
       </c>
       <c r="P23" t="n">
-        <v>262.82</v>
+        <v>264.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>169.8</v>
+        <v>170.2</v>
       </c>
       <c r="R23" t="n">
-        <v>110.85</v>
+        <v>111.48</v>
       </c>
       <c r="S23" t="n">
-        <v>228.69</v>
+        <v>229.01</v>
       </c>
       <c r="T23" t="n">
         <v>176.13</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.33</v>
+        <v>-5.93</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
@@ -2184,16 +2184,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3808.8</v>
+        <v>3845.8</v>
       </c>
       <c r="E25" t="n">
-        <v>2462.7</v>
+        <v>2493.1</v>
       </c>
       <c r="F25" t="n">
-        <v>23.04</v>
+        <v>23.08</v>
       </c>
       <c r="G25" t="n">
-        <v>14.91</v>
+        <v>14.97</v>
       </c>
       <c r="H25" t="n">
         <v>211.7</v>
@@ -2220,22 +2220,22 @@
         <v>2.52</v>
       </c>
       <c r="P25" t="n">
-        <v>251.1</v>
+        <v>252.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>162.63</v>
+        <v>164.08</v>
       </c>
       <c r="R25" t="n">
-        <v>103.59</v>
+        <v>104.79</v>
       </c>
       <c r="S25" t="n">
-        <v>221.71</v>
+        <v>223.19</v>
       </c>
       <c r="T25" t="n">
         <v>131.48</v>
       </c>
       <c r="U25" t="n">
-        <v>31.15</v>
+        <v>32.6</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
@@ -2255,16 +2255,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3761.1</v>
+        <v>3781.4</v>
       </c>
       <c r="E26" t="n">
-        <v>2432.7</v>
+        <v>2440.1</v>
       </c>
       <c r="F26" t="n">
-        <v>24.74</v>
+        <v>24.77</v>
       </c>
       <c r="G26" t="n">
-        <v>15.95</v>
+        <v>15.93</v>
       </c>
       <c r="H26" t="n">
         <v>163.3</v>
@@ -2291,22 +2291,22 @@
         <v>2.35</v>
       </c>
       <c r="P26" t="n">
-        <v>251.05</v>
+        <v>251.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>162.42</v>
+        <v>162.63</v>
       </c>
       <c r="R26" t="n">
-        <v>105.79</v>
+        <v>106.05</v>
       </c>
       <c r="S26" t="n">
-        <v>221.46</v>
+        <v>221.44</v>
       </c>
       <c r="T26" t="n">
         <v>164.09</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.67</v>
+        <v>-1.46</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
@@ -2326,16 +2326,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3187.9</v>
+        <v>3193.5</v>
       </c>
       <c r="E27" t="n">
-        <v>2059.7</v>
+        <v>2056.9</v>
       </c>
       <c r="F27" t="n">
-        <v>22.85</v>
+        <v>22.83</v>
       </c>
       <c r="G27" t="n">
-        <v>14.85</v>
+        <v>14.83</v>
       </c>
       <c r="H27" t="n">
         <v>386.1</v>
@@ -2362,22 +2362,22 @@
         <v>2.04</v>
       </c>
       <c r="P27" t="n">
-        <v>249.89</v>
+        <v>250.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>162.01</v>
+        <v>161.82</v>
       </c>
       <c r="R27" t="n">
-        <v>102.85</v>
+        <v>102.81</v>
       </c>
       <c r="S27" t="n">
-        <v>221.08</v>
+        <v>220.84</v>
       </c>
       <c r="T27" t="n">
         <v>208.48</v>
       </c>
       <c r="U27" t="n">
-        <v>-46.47</v>
+        <v>-46.66</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
@@ -2397,16 +2397,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3997.6</v>
+        <v>4010.6</v>
       </c>
       <c r="E28" t="n">
-        <v>2563.7</v>
+        <v>2576.6</v>
       </c>
       <c r="F28" t="n">
-        <v>24.49</v>
+        <v>24.54</v>
       </c>
       <c r="G28" t="n">
-        <v>15.66</v>
+        <v>15.71</v>
       </c>
       <c r="H28" t="n">
         <v>94.2</v>
@@ -2433,22 +2433,22 @@
         <v>2.18</v>
       </c>
       <c r="P28" t="n">
-        <v>251.32</v>
+        <v>252.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>160.91</v>
+        <v>161.62</v>
       </c>
       <c r="R28" t="n">
-        <v>105.58</v>
+        <v>106.33</v>
       </c>
       <c r="S28" t="n">
-        <v>219.2</v>
+        <v>220.12</v>
       </c>
       <c r="T28" t="n">
         <v>97.77</v>
       </c>
       <c r="U28" t="n">
-        <v>63.14</v>
+        <v>63.85</v>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
@@ -2468,16 +2468,16 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3729.9</v>
+        <v>3785.7</v>
       </c>
       <c r="E29" t="n">
-        <v>2380.4</v>
+        <v>2420.5</v>
       </c>
       <c r="F29" t="n">
-        <v>24.92</v>
+        <v>25.04</v>
       </c>
       <c r="G29" t="n">
-        <v>15.78</v>
+        <v>15.83</v>
       </c>
       <c r="H29" t="n">
         <v>190.7</v>
@@ -2504,16 +2504,16 @@
         <v>2.52</v>
       </c>
       <c r="P29" t="n">
-        <v>246.65</v>
+        <v>249.36</v>
       </c>
       <c r="Q29" t="n">
-        <v>157.02</v>
+        <v>158.82</v>
       </c>
       <c r="R29" t="n">
-        <v>100.27</v>
+        <v>102</v>
       </c>
       <c r="S29" t="n">
-        <v>215.23</v>
+        <v>217.01</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -2606,16 +2606,16 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3684.2</v>
+        <v>3723.6</v>
       </c>
       <c r="E31" t="n">
-        <v>2375</v>
+        <v>2398.7</v>
       </c>
       <c r="F31" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G31" t="n">
-        <v>15.66</v>
+        <v>15.72</v>
       </c>
       <c r="H31" t="n">
         <v>54.7</v>
@@ -2642,16 +2642,16 @@
         <v>2.16</v>
       </c>
       <c r="P31" t="n">
-        <v>229.74</v>
+        <v>231.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>147.84</v>
+        <v>149.03</v>
       </c>
       <c r="R31" t="n">
-        <v>94.86</v>
+        <v>96.03</v>
       </c>
       <c r="S31" t="n">
-        <v>206.52</v>
+        <v>207.58</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -2673,16 +2673,16 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>3533.6</v>
+        <v>3560.5</v>
       </c>
       <c r="E32" t="n">
-        <v>2274.5</v>
+        <v>2290.8</v>
       </c>
       <c r="F32" t="n">
-        <v>18.61</v>
+        <v>18.68</v>
       </c>
       <c r="G32" t="n">
-        <v>11.99</v>
+        <v>12.06</v>
       </c>
       <c r="H32" t="n">
         <v>174.7</v>
@@ -2709,22 +2709,22 @@
         <v>2.22</v>
       </c>
       <c r="P32" t="n">
-        <v>221.99</v>
+        <v>223.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>143.12</v>
+        <v>144.05</v>
       </c>
       <c r="R32" t="n">
-        <v>85.22</v>
+        <v>85.95</v>
       </c>
       <c r="S32" t="n">
-        <v>202.02</v>
+        <v>202.79</v>
       </c>
       <c r="T32" t="n">
         <v>166.68</v>
       </c>
       <c r="U32" t="n">
-        <v>-23.56</v>
+        <v>-22.63</v>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
@@ -2744,13 +2744,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3736.5</v>
+        <v>3742.1</v>
       </c>
       <c r="E33" t="n">
         <v>457.1</v>
       </c>
       <c r="F33" t="n">
-        <v>27.95</v>
+        <v>27.93</v>
       </c>
       <c r="G33" t="n">
         <v>3.52</v>
@@ -2780,16 +2780,16 @@
         <v>0.39</v>
       </c>
       <c r="P33" t="n">
-        <v>241.38</v>
+        <v>241.52</v>
       </c>
       <c r="Q33" t="n">
         <v>30.04</v>
       </c>
       <c r="R33" t="n">
-        <v>20.7</v>
+        <v>20.72</v>
       </c>
       <c r="S33" t="n">
-        <v>41.4</v>
+        <v>41.41</v>
       </c>
       <c r="T33" t="n">
         <v>32.03</v>
@@ -2815,16 +2815,16 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>3868.1</v>
+        <v>3875.1</v>
       </c>
       <c r="E34" t="n">
-        <v>2014.7</v>
+        <v>2021.8</v>
       </c>
       <c r="F34" t="n">
-        <v>19.59</v>
+        <v>19.56</v>
       </c>
       <c r="G34" t="n">
-        <v>9.92</v>
+        <v>9.9</v>
       </c>
       <c r="H34" t="n">
         <v>229.6</v>
@@ -2851,22 +2851,22 @@
         <v>1.96</v>
       </c>
       <c r="P34" t="n">
-        <v>245.12</v>
+        <v>245.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>126.51</v>
+        <v>126.71</v>
       </c>
       <c r="R34" t="n">
-        <v>79.31999999999999</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="S34" t="n">
-        <v>173.45</v>
+        <v>173.76</v>
       </c>
       <c r="T34" t="n">
         <v>124.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
@@ -2886,13 +2886,13 @@
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3450.2</v>
+        <v>3476</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>17.1</v>
+        <v>17.17</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>300.19</v>
+        <v>301.5</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3024,13 +3024,13 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3403.1</v>
+        <v>3416.6</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>229.96</v>
+        <v>230.74</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3091,13 +3091,13 @@
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3277.7</v>
+        <v>3317.1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>14.75</v>
+        <v>14.87</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>185.77</v>
+        <v>187.82</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3055</v>
+        <v>3060.6</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>14.16</v>
+        <v>14.14</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>173.6</v>
+        <v>173.74</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3225,13 +3225,13 @@
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3561.5</v>
+        <v>3588.5</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>21.07</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>219.6</v>
+        <v>220.96</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3292,13 +3292,13 @@
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3488.4</v>
+        <v>3508.7</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>19.26</v>
+        <v>19.3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>230.59</v>
+        <v>231.56</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3353.2</v>
+        <v>3390.1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>15.48</v>
+        <v>15.52</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3395,7 +3395,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>187.71</v>
+        <v>189.34</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3426,13 +3426,13 @@
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3407.9</v>
+        <v>3463.8</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>18.01</v>
+        <v>18.14</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>237.35</v>
+        <v>240.1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3564,13 +3564,13 @@
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3704.8</v>
+        <v>3710.4</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>19.71</v>
+        <v>19.69</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>242.86</v>
+        <v>243.01</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3631,13 +3631,13 @@
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3582.4</v>
+        <v>3598.7</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>25.43</v>
+        <v>25.51</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>228.85</v>
+        <v>229.82</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3436.5</v>
+        <v>3437.4</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -3734,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>264.41</v>
+        <v>264.45</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3247.8</v>
+        <v>3254</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>18.34</v>
+        <v>18.32</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>306</v>
+        <v>306.17</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3301.7</v>
+        <v>3319.2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>199.05</v>
+        <v>199.75</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>184</v>
+        <v>184.3</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>209.06</v>
+        <v>209.09</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3240.9</v>
+        <v>3238.9</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>14.05</v>
+        <v>14.03</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>180.41</v>
+        <v>180.25</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4033,19 +4033,19 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3586.8</v>
+        <v>3641.2</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>22.8</v>
+        <v>22.94</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>174.5</v>
+        <v>176.6</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -4057,19 +4057,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>238.56</v>
+        <v>241.27</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4100,19 +4100,19 @@
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3624</v>
+        <v>3654.2</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>25.14</v>
+        <v>25.16</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>582.3</v>
+        <v>581.6</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -4124,19 +4124,19 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>14.49</v>
+        <v>14.88</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.33</v>
+        <v>3.47</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>290.01</v>
+        <v>290.17</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3456.2</v>
+        <v>3465.9</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -4203,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>218.24</v>
+        <v>218.61</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4234,13 +4234,13 @@
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3484</v>
+        <v>3510.9</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>22.21</v>
+        <v>22.29</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>239.19</v>
+        <v>240.59</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4301,13 +4301,13 @@
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3326.2</v>
+        <v>3353.2</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>17.24</v>
+        <v>17.32</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>197.77</v>
+        <v>199.17</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4368,13 +4368,13 @@
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3333</v>
+        <v>3390.7</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>15.29</v>
+        <v>15.42</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>191.8</v>
+        <v>194.63</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4435,7 +4435,7 @@
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3293.7</v>
+        <v>3295.2</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>213.67</v>
+        <v>213.73</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4506,7 +4506,7 @@
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>3352.8</v>
+        <v>3353.7</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -4542,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>213.62</v>
+        <v>213.66</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4573,19 +4573,19 @@
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3380.6</v>
+        <v>3417.5</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>16.02</v>
+        <v>16.05</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>183.8</v>
+        <v>183.5</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -4597,19 +4597,19 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>15.78</v>
+        <v>16.17</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5.65</v>
+        <v>5.63</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>190.72</v>
+        <v>191.55</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3241.2</v>
+        <v>3249.5</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>227.45</v>
+        <v>227.78</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4707,13 +4707,13 @@
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>3655.2</v>
+        <v>3668.2</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>21.05</v>
+        <v>21.1</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>218.94</v>
+        <v>219.66</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>3411.8</v>
+        <v>3412.4</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>283.39</v>
+        <v>283.42</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -4912,7 +4912,7 @@
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>3234.9</v>
+        <v>3252.4</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>207.4</v>
+        <v>208.1</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3882</v>
+        <v>3882.6</v>
       </c>
       <c r="E3" t="n">
         <v>2505.6</v>
@@ -5217,13 +5217,13 @@
         <v>1.79</v>
       </c>
       <c r="P3" t="n">
-        <v>357.24</v>
+        <v>357.26</v>
       </c>
       <c r="Q3" t="n">
         <v>230.62</v>
       </c>
       <c r="R3" t="n">
-        <v>171.74</v>
+        <v>171.75</v>
       </c>
       <c r="S3" t="n">
         <v>289.48</v>
@@ -5240,70 +5240,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3697</v>
+        <v>4377.9</v>
       </c>
       <c r="E4" t="n">
-        <v>2382.2</v>
+        <v>3081.6</v>
       </c>
       <c r="F4" t="n">
-        <v>25.41</v>
+        <v>33.35</v>
       </c>
       <c r="G4" t="n">
-        <v>16.31</v>
+        <v>23.39</v>
       </c>
       <c r="H4" t="n">
-        <v>886.1</v>
+        <v>171.3</v>
       </c>
       <c r="I4" t="n">
-        <v>574.5</v>
+        <v>121.9</v>
       </c>
       <c r="J4" t="n">
-        <v>7.11</v>
+        <v>2.24</v>
       </c>
       <c r="K4" t="n">
-        <v>4.59</v>
+        <v>1.59</v>
       </c>
       <c r="L4" t="n">
-        <v>10.08</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>6.52</v>
+        <v>6.72</v>
       </c>
       <c r="N4" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="P4" t="n">
-        <v>352.53</v>
+        <v>314.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>227.24</v>
+        <v>221.37</v>
       </c>
       <c r="R4" t="n">
-        <v>168.75</v>
+        <v>158.51</v>
       </c>
       <c r="S4" t="n">
-        <v>286.32</v>
+        <v>285.4</v>
       </c>
       <c r="T4" t="n">
-        <v>213.59</v>
+        <v>234.35</v>
       </c>
       <c r="U4" t="n">
-        <v>13.65</v>
+        <v>-12.98</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -5323,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4157</v>
+        <v>4165.3</v>
       </c>
       <c r="E5" t="n">
         <v>2672.8</v>
@@ -5359,16 +5359,16 @@
         <v>1.77</v>
       </c>
       <c r="P5" t="n">
-        <v>343.5</v>
+        <v>343.83</v>
       </c>
       <c r="Q5" t="n">
         <v>221.26</v>
       </c>
       <c r="R5" t="n">
-        <v>162.5</v>
+        <v>162.55</v>
       </c>
       <c r="S5" t="n">
-        <v>279.98</v>
+        <v>279.93</v>
       </c>
       <c r="T5" t="n">
         <v>217.67</v>
@@ -5382,70 +5382,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4361.6</v>
+        <v>3715.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3065.3</v>
+        <v>2387.3</v>
       </c>
       <c r="F6" t="n">
-        <v>33.27</v>
+        <v>24.38</v>
       </c>
       <c r="G6" t="n">
-        <v>23.31</v>
+        <v>15.65</v>
       </c>
       <c r="H6" t="n">
-        <v>171.3</v>
+        <v>779.2</v>
       </c>
       <c r="I6" t="n">
-        <v>121.9</v>
+        <v>505.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.24</v>
+        <v>6.46</v>
       </c>
       <c r="K6" t="n">
-        <v>1.59</v>
+        <v>4.17</v>
       </c>
       <c r="L6" t="n">
-        <v>9.529999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="M6" t="n">
-        <v>6.72</v>
+        <v>6.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>3.33</v>
       </c>
       <c r="O6" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="P6" t="n">
-        <v>313.75</v>
+        <v>337.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>220.4</v>
+        <v>217.16</v>
       </c>
       <c r="R6" t="n">
-        <v>157.57</v>
+        <v>158.29</v>
       </c>
       <c r="S6" t="n">
-        <v>284.3</v>
+        <v>275.7</v>
       </c>
       <c r="T6" t="n">
-        <v>234.35</v>
+        <v>213.59</v>
       </c>
       <c r="U6" t="n">
-        <v>-13.95</v>
+        <v>3.57</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -5453,70 +5453,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4221.7</v>
+        <v>4142.4</v>
       </c>
       <c r="E7" t="n">
-        <v>2971.4</v>
+        <v>2666.4</v>
       </c>
       <c r="F7" t="n">
-        <v>28.65</v>
+        <v>34.45</v>
       </c>
       <c r="G7" t="n">
-        <v>20.01</v>
+        <v>22.1</v>
       </c>
       <c r="H7" t="n">
-        <v>270.4</v>
+        <v>349.1</v>
       </c>
       <c r="I7" t="n">
-        <v>191.6</v>
+        <v>225.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="L7" t="n">
-        <v>10.11</v>
+        <v>8.09</v>
       </c>
       <c r="M7" t="n">
-        <v>7.13</v>
+        <v>5.23</v>
       </c>
       <c r="N7" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="O7" t="n">
-        <v>2.21</v>
+        <v>1.96</v>
       </c>
       <c r="P7" t="n">
-        <v>302.03</v>
+        <v>337.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>212.16</v>
+        <v>217.06</v>
       </c>
       <c r="R7" t="n">
-        <v>148.25</v>
+        <v>158.46</v>
       </c>
       <c r="S7" t="n">
-        <v>275.95</v>
+        <v>275.77</v>
       </c>
       <c r="T7" t="n">
-        <v>215.65</v>
+        <v>206.74</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.49</v>
+        <v>10.32</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -5524,70 +5524,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4552</v>
+        <v>4227.9</v>
       </c>
       <c r="E8" t="n">
-        <v>3179.4</v>
+        <v>2977</v>
       </c>
       <c r="F8" t="n">
-        <v>31.27</v>
+        <v>28.63</v>
       </c>
       <c r="G8" t="n">
-        <v>21.91</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>29.7</v>
+        <v>270.4</v>
       </c>
       <c r="I8" t="n">
-        <v>21.6</v>
+        <v>191.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.47</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.05</v>
+        <v>2.13</v>
       </c>
       <c r="L8" t="n">
-        <v>8.949999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="M8" t="n">
-        <v>6.32</v>
+        <v>7.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.47</v>
+        <v>3.13</v>
       </c>
       <c r="O8" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="P8" t="n">
-        <v>296.11</v>
+        <v>302.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>207.14</v>
+        <v>212.34</v>
       </c>
       <c r="R8" t="n">
-        <v>154.51</v>
+        <v>148.47</v>
       </c>
       <c r="S8" t="n">
-        <v>270.42</v>
+        <v>276.21</v>
       </c>
       <c r="T8" t="n">
-        <v>213.67</v>
+        <v>215.65</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.53</v>
+        <v>-3.31</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
@@ -5595,70 +5595,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3989</v>
+        <v>4690.5</v>
       </c>
       <c r="E9" t="n">
-        <v>2576.2</v>
+        <v>3040.6</v>
       </c>
       <c r="F9" t="n">
-        <v>33.72</v>
+        <v>36.53</v>
       </c>
       <c r="G9" t="n">
-        <v>21.67</v>
+        <v>24.03</v>
       </c>
       <c r="H9" t="n">
-        <v>338.2</v>
+        <v>41</v>
       </c>
       <c r="I9" t="n">
-        <v>218.7</v>
+        <v>26.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.44</v>
+        <v>1.23</v>
       </c>
       <c r="K9" t="n">
-        <v>2.23</v>
+        <v>0.82</v>
       </c>
       <c r="L9" t="n">
-        <v>10.67</v>
+        <v>10.84</v>
       </c>
       <c r="M9" t="n">
-        <v>6.91</v>
+        <v>7.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>321.36</v>
+        <v>318.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>207.12</v>
+        <v>208.32</v>
       </c>
       <c r="R9" t="n">
-        <v>148.49</v>
+        <v>159.47</v>
       </c>
       <c r="S9" t="n">
-        <v>266.04</v>
+        <v>267.46</v>
       </c>
       <c r="T9" t="n">
-        <v>206.74</v>
+        <v>189.07</v>
       </c>
       <c r="U9" t="n">
-        <v>0.38</v>
+        <v>19.25</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -5666,70 +5666,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4653.5</v>
+        <v>4534.6</v>
       </c>
       <c r="E10" t="n">
-        <v>3011</v>
+        <v>2931.2</v>
       </c>
       <c r="F10" t="n">
-        <v>36.49</v>
+        <v>34.62</v>
       </c>
       <c r="G10" t="n">
-        <v>23.98</v>
+        <v>22.39</v>
       </c>
       <c r="H10" t="n">
-        <v>41</v>
+        <v>173.2</v>
       </c>
       <c r="I10" t="n">
-        <v>26.8</v>
+        <v>112.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.23</v>
+        <v>2.52</v>
       </c>
       <c r="K10" t="n">
-        <v>0.82</v>
+        <v>1.64</v>
       </c>
       <c r="L10" t="n">
-        <v>10.84</v>
+        <v>12.24</v>
       </c>
       <c r="M10" t="n">
-        <v>7.01</v>
+        <v>7.92</v>
       </c>
       <c r="N10" t="n">
-        <v>2.32</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="P10" t="n">
-        <v>317.26</v>
+        <v>321.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>206.94</v>
+        <v>208</v>
       </c>
       <c r="R10" t="n">
-        <v>158.27</v>
+        <v>149.2</v>
       </c>
       <c r="S10" t="n">
-        <v>265.84</v>
+        <v>267.17</v>
       </c>
       <c r="T10" t="n">
-        <v>189.07</v>
+        <v>208.94</v>
       </c>
       <c r="U10" t="n">
-        <v>17.87</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -5749,16 +5749,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4149.1</v>
+        <v>4176</v>
       </c>
       <c r="E11" t="n">
-        <v>2705.7</v>
+        <v>2723.5</v>
       </c>
       <c r="F11" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="G11" t="n">
-        <v>21.1</v>
+        <v>21.18</v>
       </c>
       <c r="H11" t="n">
         <v>286</v>
@@ -5785,22 +5785,22 @@
         <v>2.31</v>
       </c>
       <c r="P11" t="n">
-        <v>317.26</v>
+        <v>318.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>206.64</v>
+        <v>207.67</v>
       </c>
       <c r="R11" t="n">
-        <v>147.48</v>
+        <v>148.54</v>
       </c>
       <c r="S11" t="n">
-        <v>266.27</v>
+        <v>267.41</v>
       </c>
       <c r="T11" t="n">
         <v>208.68</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.04</v>
+        <v>-1.01</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -5808,70 +5808,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4476.9</v>
+        <v>4552.9</v>
       </c>
       <c r="E12" t="n">
-        <v>2890.1</v>
+        <v>3180.4</v>
       </c>
       <c r="F12" t="n">
-        <v>34.49</v>
+        <v>31.27</v>
       </c>
       <c r="G12" t="n">
-        <v>22.34</v>
+        <v>21.91</v>
       </c>
       <c r="H12" t="n">
-        <v>173.2</v>
+        <v>29.7</v>
       </c>
       <c r="I12" t="n">
-        <v>112.1</v>
+        <v>21.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.52</v>
+        <v>1.47</v>
       </c>
       <c r="K12" t="n">
-        <v>1.64</v>
+        <v>1.05</v>
       </c>
       <c r="L12" t="n">
-        <v>12.24</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>7.92</v>
+        <v>6.32</v>
       </c>
       <c r="N12" t="n">
-        <v>3.11</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>318.78</v>
+        <v>296.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>206.15</v>
+        <v>207.18</v>
       </c>
       <c r="R12" t="n">
-        <v>147.18</v>
+        <v>154.55</v>
       </c>
       <c r="S12" t="n">
-        <v>265.13</v>
+        <v>270.46</v>
       </c>
       <c r="T12" t="n">
-        <v>208.94</v>
+        <v>213.67</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.79</v>
+        <v>-6.49</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4065.9</v>
+        <v>4083.3</v>
       </c>
       <c r="E13" t="n">
-        <v>2880.9</v>
+        <v>2889.2</v>
       </c>
       <c r="F13" t="n">
         <v>26.45</v>
@@ -5927,22 +5927,22 @@
         <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>279.52</v>
+        <v>280.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>198.22</v>
+        <v>198.55</v>
       </c>
       <c r="R13" t="n">
-        <v>133.48</v>
+        <v>133.87</v>
       </c>
       <c r="S13" t="n">
-        <v>262.82</v>
+        <v>263.1</v>
       </c>
       <c r="T13" t="n">
         <v>169.55</v>
       </c>
       <c r="U13" t="n">
-        <v>28.67</v>
+        <v>29</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -5962,16 +5962,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3535.9</v>
+        <v>3549.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2476.8</v>
+        <v>2490.4</v>
       </c>
       <c r="F14" t="n">
-        <v>21.49</v>
+        <v>21.54</v>
       </c>
       <c r="G14" t="n">
-        <v>14.95</v>
+        <v>15.01</v>
       </c>
       <c r="H14" t="n">
         <v>532.5</v>
@@ -5998,22 +5998,22 @@
         <v>2.34</v>
       </c>
       <c r="P14" t="n">
-        <v>278.75</v>
+        <v>279.49</v>
       </c>
       <c r="Q14" t="n">
-        <v>195.22</v>
+        <v>196.01</v>
       </c>
       <c r="R14" t="n">
-        <v>131.44</v>
+        <v>132.28</v>
       </c>
       <c r="S14" t="n">
-        <v>259.17</v>
+        <v>260.19</v>
       </c>
       <c r="T14" t="n">
         <v>226.66</v>
       </c>
       <c r="U14" t="n">
-        <v>-31.44</v>
+        <v>-30.65</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -6104,10 +6104,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3688</v>
+        <v>3705.4</v>
       </c>
       <c r="E16" t="n">
-        <v>2358.1</v>
+        <v>2366.4</v>
       </c>
       <c r="F16" t="n">
         <v>27.3</v>
@@ -6140,22 +6140,22 @@
         <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>296.67</v>
+        <v>297.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>191.54</v>
+        <v>191.88</v>
       </c>
       <c r="R16" t="n">
-        <v>132.84</v>
+        <v>133.21</v>
       </c>
       <c r="S16" t="n">
-        <v>250.32</v>
+        <v>250.63</v>
       </c>
       <c r="T16" t="n">
         <v>210.04</v>
       </c>
       <c r="U16" t="n">
-        <v>-18.5</v>
+        <v>-18.16</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
@@ -6175,16 +6175,16 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4337.6</v>
+        <v>4364.6</v>
       </c>
       <c r="E17" t="n">
-        <v>2782.9</v>
+        <v>2809.2</v>
       </c>
       <c r="F17" t="n">
-        <v>28.14</v>
+        <v>28.22</v>
       </c>
       <c r="G17" t="n">
-        <v>18.21</v>
+        <v>18.28</v>
       </c>
       <c r="H17" t="n">
         <v>234.1</v>
@@ -6211,22 +6211,22 @@
         <v>2.16</v>
       </c>
       <c r="P17" t="n">
-        <v>294.73</v>
+        <v>296.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>189.66</v>
+        <v>190.99</v>
       </c>
       <c r="R17" t="n">
-        <v>131.17</v>
+        <v>132.42</v>
       </c>
       <c r="S17" t="n">
-        <v>248.16</v>
+        <v>249.67</v>
       </c>
       <c r="T17" t="n">
         <v>174.9</v>
       </c>
       <c r="U17" t="n">
-        <v>14.76</v>
+        <v>16.09</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -6246,13 +6246,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3371.5</v>
+        <v>3369.4</v>
       </c>
       <c r="E18" t="n">
-        <v>2367.9</v>
+        <v>2368.5</v>
       </c>
       <c r="F18" t="n">
-        <v>19.38</v>
+        <v>19.37</v>
       </c>
       <c r="G18" t="n">
         <v>13.61</v>
@@ -6282,22 +6282,22 @@
         <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>259.69</v>
+        <v>259.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>182.64</v>
+        <v>182.66</v>
       </c>
       <c r="R18" t="n">
-        <v>118.46</v>
+        <v>118.47</v>
       </c>
       <c r="S18" t="n">
-        <v>246.72</v>
+        <v>246.81</v>
       </c>
       <c r="T18" t="n">
         <v>192.85</v>
       </c>
       <c r="U18" t="n">
-        <v>-10.21</v>
+        <v>-10.19</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
@@ -6317,10 +6317,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3501</v>
+        <v>3502.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2237.4</v>
+        <v>2239</v>
       </c>
       <c r="F19" t="n">
         <v>20.43</v>
@@ -6353,22 +6353,22 @@
         <v>2.74</v>
       </c>
       <c r="P19" t="n">
-        <v>280.34</v>
+        <v>280.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>181.18</v>
+        <v>181.24</v>
       </c>
       <c r="R19" t="n">
-        <v>122.14</v>
+        <v>122.19</v>
       </c>
       <c r="S19" t="n">
-        <v>240.01</v>
+        <v>240.08</v>
       </c>
       <c r="T19" t="n">
         <v>67.42</v>
       </c>
       <c r="U19" t="n">
-        <v>113.76</v>
+        <v>113.82</v>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
@@ -6388,13 +6388,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3842.8</v>
+        <v>3848.4</v>
       </c>
       <c r="E20" t="n">
         <v>2492.8</v>
       </c>
       <c r="F20" t="n">
-        <v>25.18</v>
+        <v>25.16</v>
       </c>
       <c r="G20" t="n">
         <v>16.37</v>
@@ -6412,10 +6412,10 @@
         <v>1.97</v>
       </c>
       <c r="L20" t="n">
-        <v>11.06</v>
+        <v>11.18</v>
       </c>
       <c r="M20" t="n">
-        <v>7.15</v>
+        <v>7.23</v>
       </c>
       <c r="N20" t="n">
         <v>3.15</v>
@@ -6424,22 +6424,22 @@
         <v>2.04</v>
       </c>
       <c r="P20" t="n">
-        <v>272.35</v>
+        <v>272.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>176.93</v>
+        <v>176.77</v>
       </c>
       <c r="R20" t="n">
-        <v>117.71</v>
+        <v>117.66</v>
       </c>
       <c r="S20" t="n">
-        <v>236.19</v>
+        <v>236.07</v>
       </c>
       <c r="T20" t="n">
         <v>196.38</v>
       </c>
       <c r="U20" t="n">
-        <v>-19.45</v>
+        <v>-19.61</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3791.8</v>
+        <v>3801.6</v>
       </c>
       <c r="E21" t="n">
-        <v>2443.1</v>
+        <v>2452.2</v>
       </c>
       <c r="F21" t="n">
         <v>29.82</v>
@@ -6495,22 +6495,22 @@
         <v>1.83</v>
       </c>
       <c r="P21" t="n">
-        <v>268.26</v>
+        <v>268.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>174.32</v>
+        <v>174.69</v>
       </c>
       <c r="R21" t="n">
-        <v>118.5</v>
+        <v>118.83</v>
       </c>
       <c r="S21" t="n">
-        <v>233.81</v>
+        <v>234.22</v>
       </c>
       <c r="T21" t="n">
         <v>165.13</v>
       </c>
       <c r="U21" t="n">
-        <v>9.19</v>
+        <v>9.56</v>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3768.4</v>
+        <v>3769.3</v>
       </c>
       <c r="E22" t="n">
         <v>2450.3</v>
@@ -6566,13 +6566,13 @@
         <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>264.34</v>
+        <v>264.37</v>
       </c>
       <c r="Q22" t="n">
         <v>171.66</v>
       </c>
       <c r="R22" t="n">
-        <v>112.39</v>
+        <v>112.4</v>
       </c>
       <c r="S22" t="n">
         <v>230.57</v>
@@ -6601,13 +6601,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3903.2</v>
+        <v>3928.9</v>
       </c>
       <c r="E23" t="n">
-        <v>2522.5</v>
+        <v>2532.6</v>
       </c>
       <c r="F23" t="n">
-        <v>22.54</v>
+        <v>22.61</v>
       </c>
       <c r="G23" t="n">
         <v>14.51</v>
@@ -6637,22 +6637,22 @@
         <v>2.26</v>
       </c>
       <c r="P23" t="n">
-        <v>262.82</v>
+        <v>264.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>169.8</v>
+        <v>170.2</v>
       </c>
       <c r="R23" t="n">
-        <v>110.85</v>
+        <v>111.48</v>
       </c>
       <c r="S23" t="n">
-        <v>228.69</v>
+        <v>229.01</v>
       </c>
       <c r="T23" t="n">
         <v>176.13</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.33</v>
+        <v>-5.93</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
@@ -6743,16 +6743,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3808.8</v>
+        <v>3845.8</v>
       </c>
       <c r="E25" t="n">
-        <v>2462.7</v>
+        <v>2493.1</v>
       </c>
       <c r="F25" t="n">
-        <v>23.04</v>
+        <v>23.08</v>
       </c>
       <c r="G25" t="n">
-        <v>14.91</v>
+        <v>14.97</v>
       </c>
       <c r="H25" t="n">
         <v>211.7</v>
@@ -6779,22 +6779,22 @@
         <v>2.52</v>
       </c>
       <c r="P25" t="n">
-        <v>251.1</v>
+        <v>252.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>162.63</v>
+        <v>164.08</v>
       </c>
       <c r="R25" t="n">
-        <v>103.59</v>
+        <v>104.79</v>
       </c>
       <c r="S25" t="n">
-        <v>221.71</v>
+        <v>223.19</v>
       </c>
       <c r="T25" t="n">
         <v>131.48</v>
       </c>
       <c r="U25" t="n">
-        <v>31.15</v>
+        <v>32.6</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
@@ -6814,16 +6814,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3761.1</v>
+        <v>3781.4</v>
       </c>
       <c r="E26" t="n">
-        <v>2432.7</v>
+        <v>2440.1</v>
       </c>
       <c r="F26" t="n">
-        <v>24.74</v>
+        <v>24.77</v>
       </c>
       <c r="G26" t="n">
-        <v>15.95</v>
+        <v>15.93</v>
       </c>
       <c r="H26" t="n">
         <v>163.3</v>
@@ -6850,22 +6850,22 @@
         <v>2.35</v>
       </c>
       <c r="P26" t="n">
-        <v>251.05</v>
+        <v>251.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>162.42</v>
+        <v>162.63</v>
       </c>
       <c r="R26" t="n">
-        <v>105.79</v>
+        <v>106.05</v>
       </c>
       <c r="S26" t="n">
-        <v>221.46</v>
+        <v>221.44</v>
       </c>
       <c r="T26" t="n">
         <v>164.09</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.67</v>
+        <v>-1.46</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
@@ -6885,16 +6885,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3187.9</v>
+        <v>3193.5</v>
       </c>
       <c r="E27" t="n">
-        <v>2059.7</v>
+        <v>2056.9</v>
       </c>
       <c r="F27" t="n">
-        <v>22.85</v>
+        <v>22.83</v>
       </c>
       <c r="G27" t="n">
-        <v>14.85</v>
+        <v>14.83</v>
       </c>
       <c r="H27" t="n">
         <v>386.1</v>
@@ -6921,22 +6921,22 @@
         <v>2.04</v>
       </c>
       <c r="P27" t="n">
-        <v>249.89</v>
+        <v>250.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>162.01</v>
+        <v>161.82</v>
       </c>
       <c r="R27" t="n">
-        <v>102.85</v>
+        <v>102.81</v>
       </c>
       <c r="S27" t="n">
-        <v>221.08</v>
+        <v>220.84</v>
       </c>
       <c r="T27" t="n">
         <v>208.48</v>
       </c>
       <c r="U27" t="n">
-        <v>-46.47</v>
+        <v>-46.66</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
@@ -6956,16 +6956,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3997.6</v>
+        <v>4010.6</v>
       </c>
       <c r="E28" t="n">
-        <v>2563.7</v>
+        <v>2576.6</v>
       </c>
       <c r="F28" t="n">
-        <v>24.49</v>
+        <v>24.54</v>
       </c>
       <c r="G28" t="n">
-        <v>15.66</v>
+        <v>15.71</v>
       </c>
       <c r="H28" t="n">
         <v>94.2</v>
@@ -6992,22 +6992,22 @@
         <v>2.18</v>
       </c>
       <c r="P28" t="n">
-        <v>251.32</v>
+        <v>252.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>160.91</v>
+        <v>161.62</v>
       </c>
       <c r="R28" t="n">
-        <v>105.58</v>
+        <v>106.33</v>
       </c>
       <c r="S28" t="n">
-        <v>219.2</v>
+        <v>220.12</v>
       </c>
       <c r="T28" t="n">
         <v>97.77</v>
       </c>
       <c r="U28" t="n">
-        <v>63.14</v>
+        <v>63.85</v>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
@@ -7027,16 +7027,16 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3729.9</v>
+        <v>3785.7</v>
       </c>
       <c r="E29" t="n">
-        <v>2380.4</v>
+        <v>2420.5</v>
       </c>
       <c r="F29" t="n">
-        <v>24.92</v>
+        <v>25.04</v>
       </c>
       <c r="G29" t="n">
-        <v>15.78</v>
+        <v>15.83</v>
       </c>
       <c r="H29" t="n">
         <v>190.7</v>
@@ -7063,16 +7063,16 @@
         <v>2.52</v>
       </c>
       <c r="P29" t="n">
-        <v>246.65</v>
+        <v>249.36</v>
       </c>
       <c r="Q29" t="n">
-        <v>157.02</v>
+        <v>158.82</v>
       </c>
       <c r="R29" t="n">
-        <v>100.27</v>
+        <v>102</v>
       </c>
       <c r="S29" t="n">
-        <v>215.23</v>
+        <v>217.01</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -7165,16 +7165,16 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3684.2</v>
+        <v>3723.6</v>
       </c>
       <c r="E31" t="n">
-        <v>2375</v>
+        <v>2398.7</v>
       </c>
       <c r="F31" t="n">
-        <v>24.45</v>
+        <v>24.58</v>
       </c>
       <c r="G31" t="n">
-        <v>15.66</v>
+        <v>15.72</v>
       </c>
       <c r="H31" t="n">
         <v>54.7</v>
@@ -7201,16 +7201,16 @@
         <v>2.16</v>
       </c>
       <c r="P31" t="n">
-        <v>229.74</v>
+        <v>231.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>147.84</v>
+        <v>149.03</v>
       </c>
       <c r="R31" t="n">
-        <v>94.86</v>
+        <v>96.03</v>
       </c>
       <c r="S31" t="n">
-        <v>206.52</v>
+        <v>207.58</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -7232,16 +7232,16 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>3533.6</v>
+        <v>3560.5</v>
       </c>
       <c r="E32" t="n">
-        <v>2274.5</v>
+        <v>2290.8</v>
       </c>
       <c r="F32" t="n">
-        <v>18.61</v>
+        <v>18.68</v>
       </c>
       <c r="G32" t="n">
-        <v>11.99</v>
+        <v>12.06</v>
       </c>
       <c r="H32" t="n">
         <v>174.7</v>
@@ -7268,22 +7268,22 @@
         <v>2.22</v>
       </c>
       <c r="P32" t="n">
-        <v>221.99</v>
+        <v>223.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>143.12</v>
+        <v>144.05</v>
       </c>
       <c r="R32" t="n">
-        <v>85.22</v>
+        <v>85.95</v>
       </c>
       <c r="S32" t="n">
-        <v>202.02</v>
+        <v>202.79</v>
       </c>
       <c r="T32" t="n">
         <v>166.68</v>
       </c>
       <c r="U32" t="n">
-        <v>-23.56</v>
+        <v>-22.63</v>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
@@ -7303,13 +7303,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3736.5</v>
+        <v>3742.1</v>
       </c>
       <c r="E33" t="n">
         <v>457.1</v>
       </c>
       <c r="F33" t="n">
-        <v>27.95</v>
+        <v>27.93</v>
       </c>
       <c r="G33" t="n">
         <v>3.52</v>
@@ -7339,16 +7339,16 @@
         <v>0.39</v>
       </c>
       <c r="P33" t="n">
-        <v>241.38</v>
+        <v>241.52</v>
       </c>
       <c r="Q33" t="n">
         <v>30.04</v>
       </c>
       <c r="R33" t="n">
-        <v>20.7</v>
+        <v>20.72</v>
       </c>
       <c r="S33" t="n">
-        <v>41.4</v>
+        <v>41.41</v>
       </c>
       <c r="T33" t="n">
         <v>32.03</v>
@@ -7505,16 +7505,16 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3868.1</v>
+        <v>3875.1</v>
       </c>
       <c r="E2" t="n">
-        <v>2014.7</v>
+        <v>2021.8</v>
       </c>
       <c r="F2" t="n">
-        <v>19.59</v>
+        <v>19.56</v>
       </c>
       <c r="G2" t="n">
-        <v>9.92</v>
+        <v>9.9</v>
       </c>
       <c r="H2" t="n">
         <v>229.6</v>
@@ -7541,22 +7541,22 @@
         <v>1.96</v>
       </c>
       <c r="P2" t="n">
-        <v>245.12</v>
+        <v>245.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>126.51</v>
+        <v>126.71</v>
       </c>
       <c r="R2" t="n">
-        <v>79.31999999999999</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>173.45</v>
+        <v>173.76</v>
       </c>
       <c r="T2" t="n">
         <v>124.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -7576,13 +7576,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3450.2</v>
+        <v>3476</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>17.1</v>
+        <v>17.17</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>300.19</v>
+        <v>301.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3403.1</v>
+        <v>3416.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>229.96</v>
+        <v>230.74</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -7781,13 +7781,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3277.7</v>
+        <v>3317.1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>14.75</v>
+        <v>14.87</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -7817,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>185.77</v>
+        <v>187.82</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -7848,13 +7848,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3055</v>
+        <v>3060.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>14.16</v>
+        <v>14.14</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -7884,7 +7884,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>173.6</v>
+        <v>173.74</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -7915,13 +7915,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3561.5</v>
+        <v>3588.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>21.07</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>219.6</v>
+        <v>220.96</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -7982,13 +7982,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3488.4</v>
+        <v>3508.7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>19.26</v>
+        <v>19.3</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>230.59</v>
+        <v>231.56</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8049,13 +8049,13 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3353.2</v>
+        <v>3390.1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>15.48</v>
+        <v>15.52</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>187.71</v>
+        <v>189.34</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8116,13 +8116,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3407.9</v>
+        <v>3463.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>18.01</v>
+        <v>18.14</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>237.35</v>
+        <v>240.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8254,13 +8254,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3704.8</v>
+        <v>3710.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>19.71</v>
+        <v>19.69</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8290,7 +8290,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>242.86</v>
+        <v>243.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8321,13 +8321,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3582.4</v>
+        <v>3598.7</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>25.43</v>
+        <v>25.51</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8357,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>228.85</v>
+        <v>229.82</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8388,7 +8388,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3436.5</v>
+        <v>3437.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>264.41</v>
+        <v>264.45</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8455,13 +8455,13 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3247.8</v>
+        <v>3254</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>18.34</v>
+        <v>18.32</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8491,7 +8491,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>306</v>
+        <v>306.17</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -8522,7 +8522,7 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3301.7</v>
+        <v>3319.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>199.05</v>
+        <v>199.75</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>184</v>
+        <v>184.3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>209.06</v>
+        <v>209.09</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -8656,13 +8656,13 @@
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3240.9</v>
+        <v>3238.9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14.05</v>
+        <v>14.03</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>180.41</v>
+        <v>180.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -8723,19 +8723,19 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3586.8</v>
+        <v>3641.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>22.8</v>
+        <v>22.94</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>174.5</v>
+        <v>176.6</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -8747,19 +8747,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>238.56</v>
+        <v>241.27</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -8790,19 +8790,19 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3624</v>
+        <v>3654.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>25.14</v>
+        <v>25.16</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>582.3</v>
+        <v>581.6</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -8814,19 +8814,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>14.49</v>
+        <v>14.88</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.33</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>290.01</v>
+        <v>290.17</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -8857,7 +8857,7 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3456.2</v>
+        <v>3465.9</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>218.24</v>
+        <v>218.61</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -8924,13 +8924,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3484</v>
+        <v>3510.9</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>22.21</v>
+        <v>22.29</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>239.19</v>
+        <v>240.59</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -8991,13 +8991,13 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3326.2</v>
+        <v>3353.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>17.24</v>
+        <v>17.32</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>197.77</v>
+        <v>199.17</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -9058,13 +9058,13 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3333</v>
+        <v>3390.7</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>15.29</v>
+        <v>15.42</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -9094,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>191.8</v>
+        <v>194.63</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -9125,7 +9125,7 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3293.7</v>
+        <v>3295.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>213.67</v>
+        <v>213.73</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -9196,7 +9196,7 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3352.8</v>
+        <v>3353.7</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -9232,7 +9232,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>213.62</v>
+        <v>213.66</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -9263,19 +9263,19 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3380.6</v>
+        <v>3417.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>16.02</v>
+        <v>16.05</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>183.8</v>
+        <v>183.5</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -9287,19 +9287,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>15.78</v>
+        <v>16.17</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.65</v>
+        <v>5.63</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>190.72</v>
+        <v>191.55</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3241.2</v>
+        <v>3249.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -9366,7 +9366,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>227.45</v>
+        <v>227.78</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -9397,13 +9397,13 @@
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3655.2</v>
+        <v>3668.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>21.05</v>
+        <v>21.1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>218.94</v>
+        <v>219.66</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -9468,7 +9468,7 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3411.8</v>
+        <v>3412.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>283.39</v>
+        <v>283.42</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -9602,7 +9602,7 @@
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>3234.9</v>
+        <v>3252.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>207.4</v>
+        <v>208.1</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -10123,7 +10123,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>220.318</v>
+        <v>229.462</v>
       </c>
       <c r="I5" t="n">
         <v>1.752</v>
@@ -10141,10 +10141,10 @@
         <v>0.166</v>
       </c>
       <c r="N5" t="n">
-        <v>127.196</v>
+        <v>136.344</v>
       </c>
       <c r="O5" t="n">
-        <v>313.436</v>
+        <v>322.584</v>
       </c>
       <c r="P5" t="n">
         <v>0.606</v>
@@ -10177,13 +10177,13 @@
         <v>0.762</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.603</v>
+        <v>15.969</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.004</v>
+        <v>3.37</v>
       </c>
       <c r="AB5" t="n">
-        <v>31.118</v>
+        <v>31.484</v>
       </c>
       <c r="AC5" t="inlineStr"/>
     </row>
@@ -11902,7 +11902,7 @@
         <v>0.18</v>
       </c>
       <c r="L24" t="n">
-        <v>0.65</v>
+        <v>0.657</v>
       </c>
       <c r="M24" t="n">
         <v>0.191</v>
@@ -11932,10 +11932,10 @@
         <v>0.699</v>
       </c>
       <c r="V24" t="n">
-        <v>0.225</v>
+        <v>0.228</v>
       </c>
       <c r="W24" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="X24" t="n">
         <v>0.066</v>
@@ -11944,13 +11944,13 @@
         <v>0.787</v>
       </c>
       <c r="Z24" t="n">
-        <v>16.825</v>
+        <v>16.811</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.776</v>
+        <v>3.762</v>
       </c>
       <c r="AB24" t="n">
-        <v>32.469</v>
+        <v>32.464</v>
       </c>
       <c r="AC24" t="inlineStr"/>
     </row>
@@ -11995,7 +11995,7 @@
         <v>0.181</v>
       </c>
       <c r="L25" t="n">
-        <v>0.65</v>
+        <v>0.657</v>
       </c>
       <c r="M25" t="n">
         <v>0.184</v>
@@ -12025,10 +12025,10 @@
         <v>0.699</v>
       </c>
       <c r="V25" t="n">
-        <v>0.225</v>
+        <v>0.227</v>
       </c>
       <c r="W25" t="n">
-        <v>1.786</v>
+        <v>1.792</v>
       </c>
       <c r="X25" t="n">
         <v>0.064</v>
@@ -12037,13 +12037,13 @@
         <v>0.78</v>
       </c>
       <c r="Z25" t="n">
-        <v>15.191</v>
+        <v>15.177</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.628</v>
+        <v>2.616</v>
       </c>
       <c r="AB25" t="n">
-        <v>30.822</v>
+        <v>30.817</v>
       </c>
       <c r="AC25" t="inlineStr"/>
     </row>
@@ -12088,7 +12088,7 @@
         <v>0.182</v>
       </c>
       <c r="L26" t="n">
-        <v>0.65</v>
+        <v>0.657</v>
       </c>
       <c r="M26" t="n">
         <v>0.184</v>
@@ -12118,10 +12118,10 @@
         <v>0.7</v>
       </c>
       <c r="V26" t="n">
-        <v>0.225</v>
+        <v>0.227</v>
       </c>
       <c r="W26" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="X26" t="n">
         <v>0.064</v>
@@ -12130,13 +12130,13 @@
         <v>0.78</v>
       </c>
       <c r="Z26" t="n">
-        <v>16.102</v>
+        <v>16.088</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.365</v>
+        <v>3.351</v>
       </c>
       <c r="AB26" t="n">
-        <v>31.735</v>
+        <v>31.73</v>
       </c>
       <c r="AC26" t="inlineStr"/>
     </row>
@@ -12181,7 +12181,7 @@
         <v>0.188</v>
       </c>
       <c r="L27" t="n">
-        <v>0.651</v>
+        <v>0.658</v>
       </c>
       <c r="M27" t="n">
         <v>0.184</v>
@@ -12211,10 +12211,10 @@
         <v>0.707</v>
       </c>
       <c r="V27" t="n">
-        <v>0.225</v>
+        <v>0.228</v>
       </c>
       <c r="W27" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="X27" t="n">
         <v>0.064</v>
@@ -12223,13 +12223,13 @@
         <v>0.78</v>
       </c>
       <c r="Z27" t="n">
-        <v>16.516</v>
+        <v>16.502</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.427</v>
+        <v>3.413</v>
       </c>
       <c r="AB27" t="n">
-        <v>32.15</v>
+        <v>32.145</v>
       </c>
       <c r="AC27" t="inlineStr"/>
     </row>
@@ -12274,7 +12274,7 @@
         <v>0.178</v>
       </c>
       <c r="L28" t="n">
-        <v>0.651</v>
+        <v>0.658</v>
       </c>
       <c r="M28" t="n">
         <v>0.184</v>
@@ -12304,10 +12304,10 @@
         <v>0.696</v>
       </c>
       <c r="V28" t="n">
-        <v>0.225</v>
+        <v>0.228</v>
       </c>
       <c r="W28" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="X28" t="n">
         <v>0.064</v>
@@ -12316,13 +12316,13 @@
         <v>0.78</v>
       </c>
       <c r="Z28" t="n">
-        <v>15.901</v>
+        <v>15.887</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.119</v>
+        <v>3.105</v>
       </c>
       <c r="AB28" t="n">
-        <v>31.536</v>
+        <v>31.531</v>
       </c>
       <c r="AC28" t="inlineStr"/>
     </row>
@@ -12367,7 +12367,7 @@
         <v>0.194</v>
       </c>
       <c r="L29" t="n">
-        <v>0.651</v>
+        <v>0.658</v>
       </c>
       <c r="M29" t="n">
         <v>0.184</v>
@@ -12397,10 +12397,10 @@
         <v>0.712</v>
       </c>
       <c r="V29" t="n">
-        <v>0.225</v>
+        <v>0.228</v>
       </c>
       <c r="W29" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="X29" t="n">
         <v>0.064</v>
@@ -12409,13 +12409,13 @@
         <v>0.78</v>
       </c>
       <c r="Z29" t="n">
-        <v>16.519</v>
+        <v>16.506</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.393</v>
+        <v>3.379</v>
       </c>
       <c r="AB29" t="n">
-        <v>32.153</v>
+        <v>32.148</v>
       </c>
       <c r="AC29" t="inlineStr"/>
     </row>
@@ -12460,7 +12460,7 @@
         <v>0.177</v>
       </c>
       <c r="L30" t="n">
-        <v>0.651</v>
+        <v>0.658</v>
       </c>
       <c r="M30" t="n">
         <v>0.184</v>
@@ -12490,10 +12490,10 @@
         <v>0.696</v>
       </c>
       <c r="V30" t="n">
-        <v>0.225</v>
+        <v>0.228</v>
       </c>
       <c r="W30" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="X30" t="n">
         <v>0.064</v>
@@ -12502,13 +12502,13 @@
         <v>0.78</v>
       </c>
       <c r="Z30" t="n">
-        <v>16.527</v>
+        <v>16.514</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.597</v>
+        <v>3.584</v>
       </c>
       <c r="AB30" t="n">
-        <v>32.162</v>
+        <v>32.158</v>
       </c>
       <c r="AC30" t="inlineStr"/>
     </row>
@@ -12553,7 +12553,7 @@
         <v>0.181</v>
       </c>
       <c r="L31" t="n">
-        <v>0.651</v>
+        <v>0.658</v>
       </c>
       <c r="M31" t="n">
         <v>0.191</v>
@@ -12583,10 +12583,10 @@
         <v>0.699</v>
       </c>
       <c r="V31" t="n">
-        <v>0.225</v>
+        <v>0.228</v>
       </c>
       <c r="W31" t="n">
-        <v>1.786</v>
+        <v>1.793</v>
       </c>
       <c r="X31" t="n">
         <v>0.066</v>
@@ -12595,13 +12595,13 @@
         <v>0.787</v>
       </c>
       <c r="Z31" t="n">
-        <v>16.316</v>
+        <v>16.303</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.321</v>
+        <v>3.307</v>
       </c>
       <c r="AB31" t="n">
-        <v>31.958</v>
+        <v>31.954</v>
       </c>
       <c r="AC31" t="inlineStr"/>
     </row>
@@ -12646,7 +12646,7 @@
         <v>0.175</v>
       </c>
       <c r="L32" t="n">
-        <v>0.65</v>
+        <v>0.657</v>
       </c>
       <c r="M32" t="n">
         <v>0.184</v>
@@ -12676,10 +12676,10 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="V32" t="n">
-        <v>0.225</v>
+        <v>0.227</v>
       </c>
       <c r="W32" t="n">
-        <v>1.785</v>
+        <v>1.792</v>
       </c>
       <c r="X32" t="n">
         <v>0.064</v>
@@ -12688,13 +12688,13 @@
         <v>0.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>15.851</v>
+        <v>15.837</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.063</v>
+        <v>3.049</v>
       </c>
       <c r="AB32" t="n">
-        <v>31.481</v>
+        <v>31.476</v>
       </c>
       <c r="AC32" t="inlineStr"/>
     </row>
@@ -12739,7 +12739,7 @@
         <v>0.169</v>
       </c>
       <c r="L33" t="n">
-        <v>0.65</v>
+        <v>0.656</v>
       </c>
       <c r="M33" t="n">
         <v>0.184</v>
@@ -12769,10 +12769,10 @@
         <v>0.6879999999999999</v>
       </c>
       <c r="V33" t="n">
-        <v>0.225</v>
+        <v>0.227</v>
       </c>
       <c r="W33" t="n">
-        <v>1.785</v>
+        <v>1.792</v>
       </c>
       <c r="X33" t="n">
         <v>0.064</v>
@@ -12781,13 +12781,13 @@
         <v>0.78</v>
       </c>
       <c r="Z33" t="n">
-        <v>15.211</v>
+        <v>15.197</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.518</v>
+        <v>2.504</v>
       </c>
       <c r="AB33" t="n">
-        <v>30.844</v>
+        <v>30.839</v>
       </c>
       <c r="AC33" t="inlineStr"/>
     </row>
@@ -12832,7 +12832,7 @@
         <v>0.17</v>
       </c>
       <c r="L34" t="n">
-        <v>0.649</v>
+        <v>0.656</v>
       </c>
       <c r="M34" t="n">
         <v>0.184</v>
@@ -12862,10 +12862,10 @@
         <v>0.6879999999999999</v>
       </c>
       <c r="V34" t="n">
-        <v>0.225</v>
+        <v>0.227</v>
       </c>
       <c r="W34" t="n">
-        <v>1.785</v>
+        <v>1.791</v>
       </c>
       <c r="X34" t="n">
         <v>0.064</v>
@@ -12874,13 +12874,13 @@
         <v>0.78</v>
       </c>
       <c r="Z34" t="n">
-        <v>16.012</v>
+        <v>15.998</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.156</v>
+        <v>3.144</v>
       </c>
       <c r="AB34" t="n">
-        <v>31.641</v>
+        <v>31.636</v>
       </c>
       <c r="AC34" t="inlineStr"/>
     </row>
@@ -12913,67 +12913,67 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>234.563</v>
+        <v>241.096</v>
       </c>
       <c r="I35" t="n">
-        <v>1.983</v>
+        <v>2.022</v>
       </c>
       <c r="J35" t="n">
-        <v>19.573</v>
+        <v>20.214</v>
       </c>
       <c r="K35" t="n">
-        <v>0.204</v>
+        <v>0.211</v>
       </c>
       <c r="L35" t="n">
-        <v>0.628</v>
+        <v>0.476</v>
       </c>
       <c r="M35" t="n">
-        <v>0.192</v>
+        <v>0.181</v>
       </c>
       <c r="N35" t="n">
-        <v>141.444</v>
+        <v>147.975</v>
       </c>
       <c r="O35" t="n">
-        <v>327.684</v>
+        <v>334.216</v>
       </c>
       <c r="P35" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.388</v>
+        <v>3.426</v>
       </c>
       <c r="R35" t="n">
-        <v>6.775</v>
+        <v>6.997</v>
       </c>
       <c r="S35" t="n">
-        <v>40.468</v>
+        <v>41.109</v>
       </c>
       <c r="T35" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="U35" t="n">
-        <v>0.723</v>
+        <v>0.729</v>
       </c>
       <c r="V35" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W35" t="n">
-        <v>1.763</v>
+        <v>1.611</v>
       </c>
       <c r="X35" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.788</v>
+        <v>0.777</v>
       </c>
       <c r="Z35" t="n">
-        <v>18.859</v>
+        <v>19.701</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.404</v>
+        <v>5.078</v>
       </c>
       <c r="AB35" t="n">
-        <v>34.473</v>
+        <v>35.102</v>
       </c>
       <c r="AC35" t="inlineStr"/>
     </row>
@@ -13006,67 +13006,67 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>241.384</v>
+        <v>247.918</v>
       </c>
       <c r="I36" t="n">
-        <v>2.078</v>
+        <v>2.116</v>
       </c>
       <c r="J36" t="n">
-        <v>19.997</v>
+        <v>20.639</v>
       </c>
       <c r="K36" t="n">
-        <v>0.205</v>
+        <v>0.212</v>
       </c>
       <c r="L36" t="n">
-        <v>0.628</v>
+        <v>0.475</v>
       </c>
       <c r="M36" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="N36" t="n">
-        <v>148.265</v>
+        <v>154.796</v>
       </c>
       <c r="O36" t="n">
-        <v>334.505</v>
+        <v>341.036</v>
       </c>
       <c r="P36" t="n">
-        <v>0.719</v>
+        <v>0.733</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.483</v>
+        <v>3.521</v>
       </c>
       <c r="R36" t="n">
-        <v>6.922</v>
+        <v>7.144</v>
       </c>
       <c r="S36" t="n">
-        <v>40.89</v>
+        <v>41.53</v>
       </c>
       <c r="T36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="U36" t="n">
-        <v>0.724</v>
+        <v>0.73</v>
       </c>
       <c r="V36" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W36" t="n">
-        <v>1.763</v>
+        <v>1.611</v>
       </c>
       <c r="X36" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="Z36" t="n">
-        <v>19.584</v>
+        <v>20.41</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.848</v>
+        <v>5.507</v>
       </c>
       <c r="AB36" t="n">
-        <v>35.182</v>
+        <v>35.806</v>
       </c>
       <c r="AC36" t="inlineStr"/>
     </row>
@@ -13099,67 +13099,67 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>244.709</v>
+        <v>251.243</v>
       </c>
       <c r="I37" t="n">
-        <v>2.043</v>
+        <v>2.081</v>
       </c>
       <c r="J37" t="n">
-        <v>19.664</v>
+        <v>20.305</v>
       </c>
       <c r="K37" t="n">
-        <v>0.202</v>
+        <v>0.208</v>
       </c>
       <c r="L37" t="n">
-        <v>0.628</v>
+        <v>0.476</v>
       </c>
       <c r="M37" t="n">
-        <v>0.192</v>
+        <v>0.181</v>
       </c>
       <c r="N37" t="n">
-        <v>151.586</v>
+        <v>158.124</v>
       </c>
       <c r="O37" t="n">
-        <v>337.833</v>
+        <v>344.364</v>
       </c>
       <c r="P37" t="n">
-        <v>0.707</v>
+        <v>0.72</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.447</v>
+        <v>3.486</v>
       </c>
       <c r="R37" t="n">
-        <v>6.806</v>
+        <v>7.028</v>
       </c>
       <c r="S37" t="n">
-        <v>40.559</v>
+        <v>41.199</v>
       </c>
       <c r="T37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="U37" t="n">
-        <v>0.72</v>
+        <v>0.726</v>
       </c>
       <c r="V37" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W37" t="n">
-        <v>1.764</v>
+        <v>1.612</v>
       </c>
       <c r="X37" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.788</v>
+        <v>0.777</v>
       </c>
       <c r="Z37" t="n">
-        <v>19.495</v>
+        <v>20.337</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.888</v>
+        <v>5.562</v>
       </c>
       <c r="AB37" t="n">
-        <v>35.109</v>
+        <v>35.736</v>
       </c>
       <c r="AC37" t="inlineStr"/>
     </row>
@@ -13192,67 +13192,67 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>231.329</v>
+        <v>237.862</v>
       </c>
       <c r="I38" t="n">
-        <v>1.87</v>
+        <v>1.909</v>
       </c>
       <c r="J38" t="n">
-        <v>20.134</v>
+        <v>20.776</v>
       </c>
       <c r="K38" t="n">
-        <v>0.206</v>
+        <v>0.212</v>
       </c>
       <c r="L38" t="n">
-        <v>0.628</v>
+        <v>0.476</v>
       </c>
       <c r="M38" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="N38" t="n">
-        <v>138.206</v>
+        <v>144.744</v>
       </c>
       <c r="O38" t="n">
-        <v>324.446</v>
+        <v>330.984</v>
       </c>
       <c r="P38" t="n">
-        <v>0.647</v>
+        <v>0.661</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.275</v>
+        <v>3.313</v>
       </c>
       <c r="R38" t="n">
-        <v>6.969</v>
+        <v>7.191</v>
       </c>
       <c r="S38" t="n">
-        <v>41.029</v>
+        <v>41.67</v>
       </c>
       <c r="T38" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="U38" t="n">
-        <v>0.725</v>
+        <v>0.731</v>
       </c>
       <c r="V38" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W38" t="n">
-        <v>1.764</v>
+        <v>1.611</v>
       </c>
       <c r="X38" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="Z38" t="n">
-        <v>18.367</v>
+        <v>19.194</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.162</v>
+        <v>4.823</v>
       </c>
       <c r="AB38" t="n">
-        <v>33.967</v>
+        <v>34.591</v>
       </c>
       <c r="AC38" t="inlineStr"/>
     </row>
@@ -13285,67 +13285,67 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>225.454</v>
+        <v>240.296</v>
       </c>
       <c r="I39" t="n">
-        <v>1.856</v>
+        <v>1.895</v>
       </c>
       <c r="J39" t="n">
-        <v>20.1</v>
+        <v>20.742</v>
       </c>
       <c r="K39" t="n">
-        <v>0.206</v>
+        <v>0.212</v>
       </c>
       <c r="L39" t="n">
-        <v>0.628</v>
+        <v>0.476</v>
       </c>
       <c r="M39" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="N39" t="n">
-        <v>132.334</v>
+        <v>147.175</v>
       </c>
       <c r="O39" t="n">
-        <v>318.575</v>
+        <v>333.415</v>
       </c>
       <c r="P39" t="n">
-        <v>0.643</v>
+        <v>0.656</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.261</v>
+        <v>3.299</v>
       </c>
       <c r="R39" t="n">
-        <v>6.957</v>
+        <v>7.179</v>
       </c>
       <c r="S39" t="n">
-        <v>40.991</v>
+        <v>41.632</v>
       </c>
       <c r="T39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="U39" t="n">
-        <v>0.725</v>
+        <v>0.731</v>
       </c>
       <c r="V39" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W39" t="n">
-        <v>1.764</v>
+        <v>1.611</v>
       </c>
       <c r="X39" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="Z39" t="n">
-        <v>18.074</v>
+        <v>19.233</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.907</v>
+        <v>4.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>33.675</v>
+        <v>34.629</v>
       </c>
       <c r="AC39" t="inlineStr"/>
     </row>
@@ -13378,67 +13378,67 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>227.56</v>
+        <v>235.015</v>
       </c>
       <c r="I40" t="n">
-        <v>1.971</v>
+        <v>2.009</v>
       </c>
       <c r="J40" t="n">
-        <v>19.786</v>
+        <v>20.427</v>
       </c>
       <c r="K40" t="n">
-        <v>0.199</v>
+        <v>0.205</v>
       </c>
       <c r="L40" t="n">
-        <v>0.628</v>
+        <v>0.476</v>
       </c>
       <c r="M40" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="N40" t="n">
-        <v>134.437</v>
+        <v>141.895</v>
       </c>
       <c r="O40" t="n">
-        <v>320.684</v>
+        <v>328.135</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.375</v>
+        <v>3.414</v>
       </c>
       <c r="R40" t="n">
-        <v>6.849</v>
+        <v>7.071</v>
       </c>
       <c r="S40" t="n">
-        <v>40.679</v>
+        <v>41.32</v>
       </c>
       <c r="T40" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U40" t="n">
-        <v>0.717</v>
+        <v>0.723</v>
       </c>
       <c r="V40" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W40" t="n">
-        <v>1.764</v>
+        <v>1.612</v>
       </c>
       <c r="X40" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="Z40" t="n">
-        <v>18.539</v>
+        <v>19.403</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.123</v>
+        <v>4.82</v>
       </c>
       <c r="AB40" t="n">
-        <v>34.138</v>
+        <v>34.799</v>
       </c>
       <c r="AC40" t="inlineStr"/>
     </row>
@@ -13471,67 +13471,67 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>233.712</v>
+        <v>240.246</v>
       </c>
       <c r="I41" t="n">
-        <v>2.046</v>
+        <v>2.084</v>
       </c>
       <c r="J41" t="n">
-        <v>20.186</v>
+        <v>20.827</v>
       </c>
       <c r="K41" t="n">
-        <v>0.209</v>
+        <v>0.216</v>
       </c>
       <c r="L41" t="n">
-        <v>0.628</v>
+        <v>0.476</v>
       </c>
       <c r="M41" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="N41" t="n">
-        <v>140.594</v>
+        <v>147.125</v>
       </c>
       <c r="O41" t="n">
-        <v>326.834</v>
+        <v>333.365</v>
       </c>
       <c r="P41" t="n">
-        <v>0.708</v>
+        <v>0.721</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.45</v>
+        <v>3.489</v>
       </c>
       <c r="R41" t="n">
-        <v>6.987</v>
+        <v>7.209</v>
       </c>
       <c r="S41" t="n">
-        <v>41.08</v>
+        <v>41.72</v>
       </c>
       <c r="T41" t="n">
-        <v>0.073</v>
+        <v>0.075</v>
       </c>
       <c r="U41" t="n">
-        <v>0.728</v>
+        <v>0.734</v>
       </c>
       <c r="V41" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W41" t="n">
-        <v>1.763</v>
+        <v>1.611</v>
       </c>
       <c r="X41" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="Z41" t="n">
-        <v>19.191</v>
+        <v>20.018</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.511</v>
+        <v>5.171</v>
       </c>
       <c r="AB41" t="n">
-        <v>34.79</v>
+        <v>35.414</v>
       </c>
       <c r="AC41" t="inlineStr"/>
     </row>
@@ -13564,67 +13564,67 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>239.214</v>
+        <v>245.748</v>
       </c>
       <c r="I42" t="n">
-        <v>2.049</v>
+        <v>2.087</v>
       </c>
       <c r="J42" t="n">
-        <v>19.758</v>
+        <v>20.399</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2</v>
+        <v>0.206</v>
       </c>
       <c r="L42" t="n">
-        <v>0.628</v>
+        <v>0.476</v>
       </c>
       <c r="M42" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="N42" t="n">
-        <v>146.094</v>
+        <v>152.626</v>
       </c>
       <c r="O42" t="n">
-        <v>332.335</v>
+        <v>338.866</v>
       </c>
       <c r="P42" t="n">
-        <v>0.709</v>
+        <v>0.723</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.454</v>
+        <v>3.492</v>
       </c>
       <c r="R42" t="n">
-        <v>6.839</v>
+        <v>7.061</v>
       </c>
       <c r="S42" t="n">
-        <v>40.65</v>
+        <v>41.291</v>
       </c>
       <c r="T42" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U42" t="n">
-        <v>0.718</v>
+        <v>0.725</v>
       </c>
       <c r="V42" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W42" t="n">
-        <v>1.763</v>
+        <v>1.611</v>
       </c>
       <c r="X42" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="Z42" t="n">
-        <v>19.323</v>
+        <v>20.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.701</v>
+        <v>5.36</v>
       </c>
       <c r="AB42" t="n">
-        <v>34.92</v>
+        <v>35.548</v>
       </c>
       <c r="AC42" t="inlineStr"/>
     </row>
@@ -13657,67 +13657,67 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>224.286</v>
+        <v>230.819</v>
       </c>
       <c r="I43" t="n">
-        <v>1.876</v>
+        <v>1.914</v>
       </c>
       <c r="J43" t="n">
-        <v>19.839</v>
+        <v>20.481</v>
       </c>
       <c r="K43" t="n">
-        <v>0.197</v>
+        <v>0.204</v>
       </c>
       <c r="L43" t="n">
-        <v>0.628</v>
+        <v>0.475</v>
       </c>
       <c r="M43" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="N43" t="n">
-        <v>131.165</v>
+        <v>137.696</v>
       </c>
       <c r="O43" t="n">
-        <v>317.405</v>
+        <v>323.943</v>
       </c>
       <c r="P43" t="n">
-        <v>0.649</v>
+        <v>0.663</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.28</v>
+        <v>3.319</v>
       </c>
       <c r="R43" t="n">
-        <v>6.867</v>
+        <v>7.089</v>
       </c>
       <c r="S43" t="n">
-        <v>40.731</v>
+        <v>41.371</v>
       </c>
       <c r="T43" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U43" t="n">
-        <v>0.716</v>
+        <v>0.722</v>
       </c>
       <c r="V43" t="n">
-        <v>0.217</v>
+        <v>0.165</v>
       </c>
       <c r="W43" t="n">
-        <v>1.763</v>
+        <v>1.611</v>
       </c>
       <c r="X43" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="Z43" t="n">
-        <v>18.026</v>
+        <v>18.853</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.861</v>
+        <v>4.521</v>
       </c>
       <c r="AB43" t="n">
-        <v>33.625</v>
+        <v>34.248</v>
       </c>
       <c r="AC43" t="inlineStr"/>
     </row>
@@ -13750,67 +13750,67 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>229.562</v>
+        <v>245.24</v>
       </c>
       <c r="I44" t="n">
-        <v>1.874</v>
+        <v>1.913</v>
       </c>
       <c r="J44" t="n">
-        <v>20.119</v>
+        <v>20.76</v>
       </c>
       <c r="K44" t="n">
-        <v>0.205</v>
+        <v>0.212</v>
       </c>
       <c r="L44" t="n">
-        <v>0.627</v>
+        <v>0.474</v>
       </c>
       <c r="M44" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="N44" t="n">
-        <v>136.444</v>
+        <v>152.116</v>
       </c>
       <c r="O44" t="n">
-        <v>322.684</v>
+        <v>338.363</v>
       </c>
       <c r="P44" t="n">
-        <v>0.649</v>
+        <v>0.662</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.279</v>
+        <v>3.317</v>
       </c>
       <c r="R44" t="n">
-        <v>6.964</v>
+        <v>7.186</v>
       </c>
       <c r="S44" t="n">
-        <v>41.011</v>
+        <v>41.651</v>
       </c>
       <c r="T44" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="U44" t="n">
-        <v>0.724</v>
+        <v>0.73</v>
       </c>
       <c r="V44" t="n">
-        <v>0.217</v>
+        <v>0.164</v>
       </c>
       <c r="W44" t="n">
-        <v>1.762</v>
+        <v>1.61</v>
       </c>
       <c r="X44" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="Z44" t="n">
-        <v>18.311</v>
+        <v>19.503</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.099</v>
+        <v>5.125</v>
       </c>
       <c r="AB44" t="n">
-        <v>33.909</v>
+        <v>34.896</v>
       </c>
       <c r="AC44" t="inlineStr"/>
     </row>
@@ -13843,67 +13843,67 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>244.409</v>
+        <v>250.943</v>
       </c>
       <c r="I45" t="n">
-        <v>2.026</v>
+        <v>2.065</v>
       </c>
       <c r="J45" t="n">
-        <v>19.58</v>
+        <v>20.221</v>
       </c>
       <c r="K45" t="n">
-        <v>0.197</v>
+        <v>0.203</v>
       </c>
       <c r="L45" t="n">
-        <v>0.627</v>
+        <v>0.475</v>
       </c>
       <c r="M45" t="n">
-        <v>0.192</v>
+        <v>0.181</v>
       </c>
       <c r="N45" t="n">
-        <v>151.286</v>
+        <v>157.824</v>
       </c>
       <c r="O45" t="n">
-        <v>337.527</v>
+        <v>344.064</v>
       </c>
       <c r="P45" t="n">
-        <v>0.701</v>
+        <v>0.715</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.431</v>
+        <v>3.469</v>
       </c>
       <c r="R45" t="n">
-        <v>6.777</v>
+        <v>6.999</v>
       </c>
       <c r="S45" t="n">
-        <v>40.471</v>
+        <v>41.111</v>
       </c>
       <c r="T45" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U45" t="n">
-        <v>0.716</v>
+        <v>0.722</v>
       </c>
       <c r="V45" t="n">
-        <v>0.217</v>
+        <v>0.164</v>
       </c>
       <c r="W45" t="n">
-        <v>1.763</v>
+        <v>1.611</v>
       </c>
       <c r="X45" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.788</v>
+        <v>0.777</v>
       </c>
       <c r="Z45" t="n">
-        <v>19.384</v>
+        <v>20.226</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.843</v>
+        <v>5.517</v>
       </c>
       <c r="AB45" t="n">
-        <v>35</v>
+        <v>35.626</v>
       </c>
       <c r="AC45" t="inlineStr"/>
     </row>
@@ -14866,7 +14866,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>229.239</v>
+        <v>237.547</v>
       </c>
       <c r="I56" t="n">
         <v>1.409</v>
@@ -14884,10 +14884,10 @@
         <v>0.211</v>
       </c>
       <c r="N56" t="n">
-        <v>136.116</v>
+        <v>144.426</v>
       </c>
       <c r="O56" t="n">
-        <v>322.357</v>
+        <v>330.666</v>
       </c>
       <c r="P56" t="n">
         <v>0.488</v>
@@ -14920,13 +14920,13 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="Z56" t="n">
-        <v>15.488</v>
+        <v>15.82</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.127</v>
+        <v>3.459</v>
       </c>
       <c r="AB56" t="n">
-        <v>31.074</v>
+        <v>31.406</v>
       </c>
       <c r="AC56" t="inlineStr"/>
     </row>
@@ -15052,7 +15052,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>248.202</v>
+        <v>249.123</v>
       </c>
       <c r="I58" t="n">
         <v>1.646</v>
@@ -15070,10 +15070,10 @@
         <v>0.196</v>
       </c>
       <c r="N58" t="n">
-        <v>155.084</v>
+        <v>156.004</v>
       </c>
       <c r="O58" t="n">
-        <v>341.324</v>
+        <v>342.245</v>
       </c>
       <c r="P58" t="n">
         <v>0.57</v>
@@ -15106,13 +15106,13 @@
         <v>0.792</v>
       </c>
       <c r="Z58" t="n">
-        <v>17.048</v>
+        <v>17.084</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.946</v>
+        <v>3.982</v>
       </c>
       <c r="AB58" t="n">
-        <v>32.848</v>
+        <v>32.885</v>
       </c>
       <c r="AC58" t="inlineStr"/>
     </row>
@@ -15331,7 +15331,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>258.267</v>
+        <v>258.881</v>
       </c>
       <c r="I61" t="n">
         <v>1.731</v>
@@ -15349,10 +15349,10 @@
         <v>0.196</v>
       </c>
       <c r="N61" t="n">
-        <v>165.146</v>
+        <v>165.757</v>
       </c>
       <c r="O61" t="n">
-        <v>351.386</v>
+        <v>352.004</v>
       </c>
       <c r="P61" t="n">
         <v>0.599</v>
@@ -15385,13 +15385,13 @@
         <v>0.792</v>
       </c>
       <c r="Z61" t="n">
-        <v>17.825</v>
+        <v>17.85</v>
       </c>
       <c r="AA61" t="n">
-        <v>4.476</v>
+        <v>4.501</v>
       </c>
       <c r="AB61" t="n">
-        <v>33.629</v>
+        <v>33.654</v>
       </c>
       <c r="AC61" t="inlineStr"/>
     </row>
@@ -15610,10 +15610,10 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>249.419</v>
+        <v>265.085</v>
       </c>
       <c r="I64" t="n">
-        <v>1.647</v>
+        <v>1.72</v>
       </c>
       <c r="J64" t="n">
         <v>14.071</v>
@@ -15628,16 +15628,16 @@
         <v>0.197</v>
       </c>
       <c r="N64" t="n">
-        <v>156.296</v>
+        <v>171.965</v>
       </c>
       <c r="O64" t="n">
-        <v>342.543</v>
+        <v>358.205</v>
       </c>
       <c r="P64" t="n">
-        <v>0.57</v>
+        <v>0.596</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.052</v>
+        <v>3.125</v>
       </c>
       <c r="R64" t="n">
         <v>4.871</v>
@@ -15664,13 +15664,13 @@
         <v>0.793</v>
       </c>
       <c r="Z64" t="n">
-        <v>17.057</v>
+        <v>17.977</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.98</v>
+        <v>4.709</v>
       </c>
       <c r="AB64" t="n">
-        <v>32.86</v>
+        <v>33.779</v>
       </c>
       <c r="AC64" t="inlineStr"/>
     </row>
@@ -15796,7 +15796,7 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>248.232</v>
+        <v>257.376</v>
       </c>
       <c r="I66" t="n">
         <v>1.578</v>
@@ -15814,10 +15814,10 @@
         <v>0.197</v>
       </c>
       <c r="N66" t="n">
-        <v>155.114</v>
+        <v>164.255</v>
       </c>
       <c r="O66" t="n">
-        <v>341.354</v>
+        <v>350.496</v>
       </c>
       <c r="P66" t="n">
         <v>0.546</v>
@@ -15850,13 +15850,13 @@
         <v>0.793</v>
       </c>
       <c r="Z66" t="n">
-        <v>16.667</v>
+        <v>17.033</v>
       </c>
       <c r="AA66" t="n">
-        <v>3.816</v>
+        <v>4.181</v>
       </c>
       <c r="AB66" t="n">
-        <v>32.469</v>
+        <v>32.835</v>
       </c>
       <c r="AC66" t="inlineStr"/>
     </row>
@@ -16168,7 +16168,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>208.63</v>
+        <v>216.938</v>
       </c>
       <c r="I70" t="n">
         <v>1.543</v>
@@ -16186,10 +16186,10 @@
         <v>0.213</v>
       </c>
       <c r="N70" t="n">
-        <v>115.506</v>
+        <v>123.816</v>
       </c>
       <c r="O70" t="n">
-        <v>301.753</v>
+        <v>310.056</v>
       </c>
       <c r="P70" t="n">
         <v>0.534</v>
@@ -16222,13 +16222,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="Z70" t="n">
-        <v>16.824</v>
+        <v>17.156</v>
       </c>
       <c r="AA70" t="n">
-        <v>3.256</v>
+        <v>3.589</v>
       </c>
       <c r="AB70" t="n">
-        <v>32.204</v>
+        <v>32.536</v>
       </c>
       <c r="AC70" t="inlineStr"/>
     </row>
@@ -17110,7 +17110,7 @@
         <v>0.138</v>
       </c>
       <c r="L80" t="n">
-        <v>0.545</v>
+        <v>0.546</v>
       </c>
       <c r="M80" t="n">
         <v>0.2</v>
@@ -17152,13 +17152,13 @@
         <v>0.796</v>
       </c>
       <c r="Z80" t="n">
-        <v>12.501</v>
+        <v>12.5</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.355</v>
+        <v>1.354</v>
       </c>
       <c r="AB80" t="n">
-        <v>28.019</v>
+        <v>28.018</v>
       </c>
       <c r="AC80" t="inlineStr"/>
     </row>
@@ -17245,7 +17245,7 @@
         <v>0.796</v>
       </c>
       <c r="Z81" t="n">
-        <v>13.634</v>
+        <v>13.633</v>
       </c>
       <c r="AA81" t="n">
         <v>2.164</v>
@@ -17338,10 +17338,10 @@
         <v>0.796</v>
       </c>
       <c r="Z82" t="n">
-        <v>13.36</v>
+        <v>13.359</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.934</v>
+        <v>1.933</v>
       </c>
       <c r="AB82" t="n">
         <v>28.879</v>
@@ -17515,7 +17515,7 @@
         <v>0.189</v>
       </c>
       <c r="W84" t="n">
-        <v>1.681</v>
+        <v>1.682</v>
       </c>
       <c r="X84" t="n">
         <v>0.06900000000000001</v>
@@ -17524,10 +17524,10 @@
         <v>0.796</v>
       </c>
       <c r="Z84" t="n">
-        <v>13.004</v>
+        <v>13.003</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.809</v>
+        <v>1.807</v>
       </c>
       <c r="AB84" t="n">
         <v>28.523</v>
@@ -17563,10 +17563,10 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>204.351</v>
+        <v>220.017</v>
       </c>
       <c r="I85" t="n">
-        <v>1.082</v>
+        <v>1.155</v>
       </c>
       <c r="J85" t="n">
         <v>10.479</v>
@@ -17581,16 +17581,16 @@
         <v>0.2</v>
       </c>
       <c r="N85" t="n">
-        <v>111.234</v>
+        <v>126.895</v>
       </c>
       <c r="O85" t="n">
-        <v>297.474</v>
+        <v>313.136</v>
       </c>
       <c r="P85" t="n">
-        <v>0.374</v>
+        <v>0.4</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.486</v>
+        <v>2.559</v>
       </c>
       <c r="R85" t="n">
         <v>3.627</v>
@@ -17608,7 +17608,7 @@
         <v>0.189</v>
       </c>
       <c r="W85" t="n">
-        <v>1.681</v>
+        <v>1.682</v>
       </c>
       <c r="X85" t="n">
         <v>0.06900000000000001</v>
@@ -17617,13 +17617,13 @@
         <v>0.796</v>
       </c>
       <c r="Z85" t="n">
-        <v>13.05</v>
+        <v>13.969</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.7</v>
+        <v>2.426</v>
       </c>
       <c r="AB85" t="n">
-        <v>28.568</v>
+        <v>29.486</v>
       </c>
       <c r="AC85" t="inlineStr"/>
     </row>
@@ -17749,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>211.585</v>
+        <v>212.199</v>
       </c>
       <c r="I87" t="n">
         <v>1.138</v>
@@ -17767,10 +17767,10 @@
         <v>0.2</v>
       </c>
       <c r="N87" t="n">
-        <v>118.465</v>
+        <v>119.076</v>
       </c>
       <c r="O87" t="n">
-        <v>304.705</v>
+        <v>305.316</v>
       </c>
       <c r="P87" t="n">
         <v>0.394</v>
@@ -17803,13 +17803,13 @@
         <v>0.796</v>
       </c>
       <c r="Z87" t="n">
-        <v>13.504</v>
+        <v>13.528</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.046</v>
+        <v>2.07</v>
       </c>
       <c r="AB87" t="n">
-        <v>29.02</v>
+        <v>29.044</v>
       </c>
       <c r="AC87" t="inlineStr"/>
     </row>
@@ -17947,7 +17947,7 @@
         <v>0.135</v>
       </c>
       <c r="L89" t="n">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="M89" t="n">
         <v>0.2</v>
@@ -18073,7 +18073,7 @@
         <v>0.189</v>
       </c>
       <c r="W90" t="n">
-        <v>1.68</v>
+        <v>1.681</v>
       </c>
       <c r="X90" t="n">
         <v>0.07099999999999999</v>
@@ -18085,7 +18085,7 @@
         <v>11.996</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.024</v>
+        <v>1.023</v>
       </c>
       <c r="AB90" t="n">
         <v>27.519</v>
@@ -18121,7 +18121,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>260.496</v>
+        <v>269.64</v>
       </c>
       <c r="I91" t="n">
         <v>1.971</v>
@@ -18139,10 +18139,10 @@
         <v>0.182</v>
       </c>
       <c r="N91" t="n">
-        <v>167.375</v>
+        <v>176.517</v>
       </c>
       <c r="O91" t="n">
-        <v>353.615</v>
+        <v>362.763</v>
       </c>
       <c r="P91" t="n">
         <v>0.6820000000000001</v>
@@ -18175,13 +18175,13 @@
         <v>0.778</v>
       </c>
       <c r="Z91" t="n">
-        <v>18.392</v>
+        <v>18.758</v>
       </c>
       <c r="AA91" t="n">
-        <v>4.812</v>
+        <v>5.178</v>
       </c>
       <c r="AB91" t="n">
-        <v>34.116</v>
+        <v>34.482</v>
       </c>
       <c r="AC91" t="inlineStr"/>
     </row>
@@ -18307,7 +18307,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>269.115</v>
+        <v>269.728</v>
       </c>
       <c r="I93" t="n">
         <v>2.117</v>
@@ -18325,10 +18325,10 @@
         <v>0.183</v>
       </c>
       <c r="N93" t="n">
-        <v>175.995</v>
+        <v>176.606</v>
       </c>
       <c r="O93" t="n">
-        <v>362.235</v>
+        <v>362.846</v>
       </c>
       <c r="P93" t="n">
         <v>0.733</v>
@@ -18361,13 +18361,13 @@
         <v>0.779</v>
       </c>
       <c r="Z93" t="n">
-        <v>19.395</v>
+        <v>19.419</v>
       </c>
       <c r="AA93" t="n">
-        <v>5.383</v>
+        <v>5.407</v>
       </c>
       <c r="AB93" t="n">
-        <v>35.116</v>
+        <v>35.141</v>
       </c>
       <c r="AC93" t="inlineStr"/>
     </row>
@@ -18400,10 +18400,10 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>271.071</v>
+        <v>268.367</v>
       </c>
       <c r="I94" t="n">
-        <v>2.035</v>
+        <v>2.016</v>
       </c>
       <c r="J94" t="n">
         <v>10.059</v>
@@ -18418,16 +18418,16 @@
         <v>0.183</v>
       </c>
       <c r="N94" t="n">
-        <v>177.947</v>
+        <v>175.246</v>
       </c>
       <c r="O94" t="n">
-        <v>364.194</v>
+        <v>361.486</v>
       </c>
       <c r="P94" t="n">
-        <v>0.704</v>
+        <v>0.698</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.439</v>
+        <v>3.42</v>
       </c>
       <c r="R94" t="n">
         <v>3.482</v>
@@ -18454,13 +18454,13 @@
         <v>0.779</v>
       </c>
       <c r="Z94" t="n">
-        <v>19.1</v>
+        <v>18.917</v>
       </c>
       <c r="AA94" t="n">
-        <v>5.332</v>
+        <v>5.198</v>
       </c>
       <c r="AB94" t="n">
-        <v>34.825</v>
+        <v>34.64</v>
       </c>
       <c r="AC94" t="inlineStr"/>
     </row>
@@ -18586,7 +18586,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>259.278</v>
+        <v>268.422</v>
       </c>
       <c r="I96" t="n">
         <v>1.975</v>
@@ -18604,10 +18604,10 @@
         <v>0.183</v>
       </c>
       <c r="N96" t="n">
-        <v>166.156</v>
+        <v>175.304</v>
       </c>
       <c r="O96" t="n">
-        <v>352.396</v>
+        <v>361.544</v>
       </c>
       <c r="P96" t="n">
         <v>0.6840000000000001</v>
@@ -18640,13 +18640,13 @@
         <v>0.779</v>
       </c>
       <c r="Z96" t="n">
-        <v>18.386</v>
+        <v>18.752</v>
       </c>
       <c r="AA96" t="n">
-        <v>4.775</v>
+        <v>5.141</v>
       </c>
       <c r="AB96" t="n">
-        <v>34.11</v>
+        <v>34.476</v>
       </c>
       <c r="AC96" t="inlineStr"/>
     </row>
@@ -18679,7 +18679,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>252.878</v>
+        <v>261.186</v>
       </c>
       <c r="I97" t="n">
         <v>1.917</v>
@@ -18697,10 +18697,10 @@
         <v>0.182</v>
       </c>
       <c r="N97" t="n">
-        <v>159.756</v>
+        <v>168.065</v>
       </c>
       <c r="O97" t="n">
-        <v>345.996</v>
+        <v>354.306</v>
       </c>
       <c r="P97" t="n">
         <v>0.664</v>
@@ -18733,13 +18733,13 @@
         <v>0.778</v>
       </c>
       <c r="Z97" t="n">
-        <v>17.803</v>
+        <v>18.135</v>
       </c>
       <c r="AA97" t="n">
-        <v>4.409</v>
+        <v>4.741</v>
       </c>
       <c r="AB97" t="n">
-        <v>33.525</v>
+        <v>33.857</v>
       </c>
       <c r="AC97" t="inlineStr"/>
     </row>
@@ -18958,7 +18958,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>254.956</v>
+        <v>255.877</v>
       </c>
       <c r="I100" t="n">
         <v>1.985</v>
@@ -18976,10 +18976,10 @@
         <v>0.183</v>
       </c>
       <c r="N100" t="n">
-        <v>161.835</v>
+        <v>162.756</v>
       </c>
       <c r="O100" t="n">
-        <v>348.076</v>
+        <v>348.996</v>
       </c>
       <c r="P100" t="n">
         <v>0.6870000000000001</v>
@@ -19012,13 +19012,13 @@
         <v>0.779</v>
       </c>
       <c r="Z100" t="n">
-        <v>18.252</v>
+        <v>18.289</v>
       </c>
       <c r="AA100" t="n">
-        <v>4.619</v>
+        <v>4.655</v>
       </c>
       <c r="AB100" t="n">
-        <v>33.974</v>
+        <v>34.011</v>
       </c>
       <c r="AC100" t="inlineStr"/>
     </row>
@@ -19051,10 +19051,10 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>256.197</v>
+        <v>271.862</v>
       </c>
       <c r="I101" t="n">
-        <v>1.986</v>
+        <v>2.06</v>
       </c>
       <c r="J101" t="n">
         <v>10.356</v>
@@ -19069,16 +19069,16 @@
         <v>0.182</v>
       </c>
       <c r="N101" t="n">
-        <v>163.075</v>
+        <v>178.744</v>
       </c>
       <c r="O101" t="n">
-        <v>349.316</v>
+        <v>364.984</v>
       </c>
       <c r="P101" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.713</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.391</v>
+        <v>3.464</v>
       </c>
       <c r="R101" t="n">
         <v>3.585</v>
@@ -19105,13 +19105,13 @@
         <v>0.778</v>
       </c>
       <c r="Z101" t="n">
-        <v>18.25</v>
+        <v>19.169</v>
       </c>
       <c r="AA101" t="n">
-        <v>4.652</v>
+        <v>5.38</v>
       </c>
       <c r="AB101" t="n">
-        <v>33.972</v>
+        <v>34.891</v>
       </c>
       <c r="AC101" t="inlineStr"/>
     </row>
@@ -19609,7 +19609,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>224.496</v>
+        <v>225.417</v>
       </c>
       <c r="I107" t="n">
         <v>1.34</v>
@@ -19627,10 +19627,10 @@
         <v>0.206</v>
       </c>
       <c r="N107" t="n">
-        <v>131.375</v>
+        <v>132.295</v>
       </c>
       <c r="O107" t="n">
-        <v>317.616</v>
+        <v>318.536</v>
       </c>
       <c r="P107" t="n">
         <v>0.464</v>
@@ -19663,13 +19663,13 @@
         <v>0.802</v>
       </c>
       <c r="Z107" t="n">
-        <v>15.306</v>
+        <v>15.343</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.869</v>
+        <v>2.906</v>
       </c>
       <c r="AB107" t="n">
-        <v>30.96</v>
+        <v>30.997</v>
       </c>
       <c r="AC107" t="inlineStr"/>
     </row>
@@ -19702,7 +19702,7 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>225.981</v>
+        <v>235.125</v>
       </c>
       <c r="I108" t="n">
         <v>1.261</v>
@@ -19720,10 +19720,10 @@
         <v>0.205</v>
       </c>
       <c r="N108" t="n">
-        <v>132.864</v>
+        <v>142.005</v>
       </c>
       <c r="O108" t="n">
-        <v>319.104</v>
+        <v>328.245</v>
       </c>
       <c r="P108" t="n">
         <v>0.437</v>
@@ -19756,13 +19756,13 @@
         <v>0.801</v>
       </c>
       <c r="Z108" t="n">
-        <v>15.105</v>
+        <v>15.471</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.842</v>
+        <v>3.208</v>
       </c>
       <c r="AB108" t="n">
-        <v>30.757</v>
+        <v>31.123</v>
       </c>
       <c r="AC108" t="inlineStr"/>
     </row>
@@ -20818,7 +20818,7 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>195.537</v>
+        <v>196.458</v>
       </c>
       <c r="I120" t="n">
         <v>1.166</v>
@@ -20836,10 +20836,10 @@
         <v>0.247</v>
       </c>
       <c r="N120" t="n">
-        <v>102.415</v>
+        <v>103.336</v>
       </c>
       <c r="O120" t="n">
-        <v>288.656</v>
+        <v>289.576</v>
       </c>
       <c r="P120" t="n">
         <v>0.404</v>
@@ -20872,13 +20872,13 @@
         <v>0.843</v>
       </c>
       <c r="Z120" t="n">
-        <v>15.957</v>
+        <v>15.994</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.616</v>
+        <v>2.653</v>
       </c>
       <c r="AB120" t="n">
-        <v>31.517</v>
+        <v>31.554</v>
       </c>
       <c r="AC120" t="inlineStr"/>
     </row>
@@ -21004,7 +21004,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>206.464</v>
+        <v>207.077</v>
       </c>
       <c r="I122" t="n">
         <v>1.2</v>
@@ -21022,10 +21022,10 @@
         <v>0.247</v>
       </c>
       <c r="N122" t="n">
-        <v>113.345</v>
+        <v>113.956</v>
       </c>
       <c r="O122" t="n">
-        <v>299.585</v>
+        <v>300.196</v>
       </c>
       <c r="P122" t="n">
         <v>0.415</v>
@@ -21058,13 +21058,13 @@
         <v>0.843</v>
       </c>
       <c r="Z122" t="n">
-        <v>16.652</v>
+        <v>16.677</v>
       </c>
       <c r="AA122" t="n">
-        <v>3.191</v>
+        <v>3.215</v>
       </c>
       <c r="AB122" t="n">
-        <v>32.212</v>
+        <v>32.237</v>
       </c>
       <c r="AC122" t="inlineStr"/>
     </row>
@@ -23422,7 +23422,7 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>216.374</v>
+        <v>224.682</v>
       </c>
       <c r="I148" t="n">
         <v>1.265</v>
@@ -23440,10 +23440,10 @@
         <v>0.229</v>
       </c>
       <c r="N148" t="n">
-        <v>123.255</v>
+        <v>131.564</v>
       </c>
       <c r="O148" t="n">
-        <v>309.495</v>
+        <v>317.804</v>
       </c>
       <c r="P148" t="n">
         <v>0.438</v>
@@ -23476,13 +23476,13 @@
         <v>0.825</v>
       </c>
       <c r="Z148" t="n">
-        <v>14.048</v>
+        <v>14.38</v>
       </c>
       <c r="AA148" t="n">
-        <v>2.183</v>
+        <v>2.516</v>
       </c>
       <c r="AB148" t="n">
-        <v>29.741</v>
+        <v>30.073</v>
       </c>
       <c r="AC148" t="inlineStr"/>
     </row>
@@ -23701,10 +23701,10 @@
         <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>221.687</v>
+        <v>237.352</v>
       </c>
       <c r="I151" t="n">
-        <v>1.377</v>
+        <v>1.45</v>
       </c>
       <c r="J151" t="n">
         <v>12.358</v>
@@ -23719,16 +23719,16 @@
         <v>0.229</v>
       </c>
       <c r="N151" t="n">
-        <v>128.565</v>
+        <v>144.234</v>
       </c>
       <c r="O151" t="n">
-        <v>314.806</v>
+        <v>330.474</v>
       </c>
       <c r="P151" t="n">
-        <v>0.476</v>
+        <v>0.502</v>
       </c>
       <c r="Q151" t="n">
-        <v>2.781</v>
+        <v>2.854</v>
       </c>
       <c r="R151" t="n">
         <v>4.278</v>
@@ -23755,13 +23755,13 @@
         <v>0.825</v>
       </c>
       <c r="Z151" t="n">
-        <v>14.808</v>
+        <v>15.728</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.583</v>
+        <v>3.311</v>
       </c>
       <c r="AB151" t="n">
-        <v>30.504</v>
+        <v>31.423</v>
       </c>
       <c r="AC151" t="inlineStr"/>
     </row>
@@ -23794,7 +23794,7 @@
         <v>1</v>
       </c>
       <c r="H152" t="n">
-        <v>219.983</v>
+        <v>229.127</v>
       </c>
       <c r="I152" t="n">
         <v>1.298</v>
@@ -23812,10 +23812,10 @@
         <v>0.229</v>
       </c>
       <c r="N152" t="n">
-        <v>126.864</v>
+        <v>136.005</v>
       </c>
       <c r="O152" t="n">
-        <v>313.104</v>
+        <v>322.246</v>
       </c>
       <c r="P152" t="n">
         <v>0.449</v>
@@ -23848,13 +23848,13 @@
         <v>0.825</v>
       </c>
       <c r="Z152" t="n">
-        <v>14.431</v>
+        <v>14.796</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.408</v>
+        <v>2.773</v>
       </c>
       <c r="AB152" t="n">
-        <v>30.126</v>
+        <v>30.492</v>
       </c>
       <c r="AC152" t="inlineStr"/>
     </row>
@@ -24166,10 +24166,10 @@
         <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>228.413</v>
+        <v>225.709</v>
       </c>
       <c r="I156" t="n">
-        <v>1.305</v>
+        <v>1.286</v>
       </c>
       <c r="J156" t="n">
         <v>12.426</v>
@@ -24184,16 +24184,16 @@
         <v>0.229</v>
       </c>
       <c r="N156" t="n">
-        <v>135.294</v>
+        <v>132.586</v>
       </c>
       <c r="O156" t="n">
-        <v>321.534</v>
+        <v>318.827</v>
       </c>
       <c r="P156" t="n">
-        <v>0.452</v>
+        <v>0.445</v>
       </c>
       <c r="Q156" t="n">
-        <v>2.709</v>
+        <v>2.69</v>
       </c>
       <c r="R156" t="n">
         <v>4.301</v>
@@ -24220,13 +24220,13 @@
         <v>0.825</v>
       </c>
       <c r="Z156" t="n">
-        <v>14.741</v>
+        <v>14.557</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.738</v>
+        <v>2.604</v>
       </c>
       <c r="AB156" t="n">
-        <v>30.434</v>
+        <v>30.25</v>
       </c>
       <c r="AC156" t="inlineStr"/>
     </row>
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>217.071</v>
+        <v>226.216</v>
       </c>
       <c r="I158" t="n">
         <v>1.429</v>
@@ -24370,10 +24370,10 @@
         <v>0.228</v>
       </c>
       <c r="N158" t="n">
-        <v>123.954</v>
+        <v>133.095</v>
       </c>
       <c r="O158" t="n">
-        <v>310.194</v>
+        <v>319.335</v>
       </c>
       <c r="P158" t="n">
         <v>0.495</v>
@@ -24406,13 +24406,13 @@
         <v>0.824</v>
       </c>
       <c r="Z158" t="n">
-        <v>14.245</v>
+        <v>14.611</v>
       </c>
       <c r="AA158" t="n">
-        <v>2.086</v>
+        <v>2.452</v>
       </c>
       <c r="AB158" t="n">
-        <v>30.124</v>
+        <v>30.489</v>
       </c>
       <c r="AC158" t="inlineStr"/>
     </row>
@@ -24445,10 +24445,10 @@
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>216.825</v>
+        <v>232.49</v>
       </c>
       <c r="I159" t="n">
-        <v>1.494</v>
+        <v>1.567</v>
       </c>
       <c r="J159" t="n">
         <v>11.736</v>
@@ -24463,16 +24463,16 @@
         <v>0.228</v>
       </c>
       <c r="N159" t="n">
-        <v>123.705</v>
+        <v>139.367</v>
       </c>
       <c r="O159" t="n">
-        <v>309.945</v>
+        <v>325.614</v>
       </c>
       <c r="P159" t="n">
-        <v>0.517</v>
+        <v>0.543</v>
       </c>
       <c r="Q159" t="n">
-        <v>2.899</v>
+        <v>2.972</v>
       </c>
       <c r="R159" t="n">
         <v>4.062</v>
@@ -24499,13 +24499,13 @@
         <v>0.824</v>
       </c>
       <c r="Z159" t="n">
-        <v>14.584</v>
+        <v>15.503</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.196</v>
+        <v>2.924</v>
       </c>
       <c r="AB159" t="n">
-        <v>30.459</v>
+        <v>31.38</v>
       </c>
       <c r="AC159" t="inlineStr"/>
     </row>
@@ -24631,7 +24631,7 @@
         <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>224.344</v>
+        <v>224.957</v>
       </c>
       <c r="I161" t="n">
         <v>1.548</v>
@@ -24649,10 +24649,10 @@
         <v>0.23</v>
       </c>
       <c r="N161" t="n">
-        <v>131.224</v>
+        <v>131.835</v>
       </c>
       <c r="O161" t="n">
-        <v>317.465</v>
+        <v>318.076</v>
       </c>
       <c r="P161" t="n">
         <v>0.536</v>
@@ -24685,13 +24685,13 @@
         <v>0.826</v>
       </c>
       <c r="Z161" t="n">
-        <v>15.01</v>
+        <v>15.035</v>
       </c>
       <c r="AA161" t="n">
-        <v>2.536</v>
+        <v>2.561</v>
       </c>
       <c r="AB161" t="n">
-        <v>30.891</v>
+        <v>30.916</v>
       </c>
       <c r="AC161" t="inlineStr"/>
     </row>
@@ -24724,10 +24724,10 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>226.741</v>
+        <v>224.037</v>
       </c>
       <c r="I162" t="n">
-        <v>1.46</v>
+        <v>1.441</v>
       </c>
       <c r="J162" t="n">
         <v>11.686</v>
@@ -24742,16 +24742,16 @@
         <v>0.228</v>
       </c>
       <c r="N162" t="n">
-        <v>133.617</v>
+        <v>130.916</v>
       </c>
       <c r="O162" t="n">
-        <v>319.864</v>
+        <v>317.156</v>
       </c>
       <c r="P162" t="n">
-        <v>0.505</v>
+        <v>0.499</v>
       </c>
       <c r="Q162" t="n">
-        <v>2.864</v>
+        <v>2.845</v>
       </c>
       <c r="R162" t="n">
         <v>4.045</v>
@@ -24778,13 +24778,13 @@
         <v>0.824</v>
       </c>
       <c r="Z162" t="n">
-        <v>14.818</v>
+        <v>14.635</v>
       </c>
       <c r="AA162" t="n">
-        <v>2.536</v>
+        <v>2.402</v>
       </c>
       <c r="AB162" t="n">
-        <v>30.695</v>
+        <v>30.511</v>
       </c>
       <c r="AC162" t="inlineStr"/>
     </row>
@@ -24817,7 +24817,7 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>208.844</v>
+        <v>217.152</v>
       </c>
       <c r="I163" t="n">
         <v>1.356</v>
@@ -24835,10 +24835,10 @@
         <v>0.228</v>
       </c>
       <c r="N163" t="n">
-        <v>115.725</v>
+        <v>124.034</v>
       </c>
       <c r="O163" t="n">
-        <v>301.965</v>
+        <v>310.274</v>
       </c>
       <c r="P163" t="n">
         <v>0.469</v>
@@ -24871,13 +24871,13 @@
         <v>0.824</v>
       </c>
       <c r="Z163" t="n">
-        <v>13.619</v>
+        <v>13.951</v>
       </c>
       <c r="AA163" t="n">
-        <v>1.653</v>
+        <v>1.986</v>
       </c>
       <c r="AB163" t="n">
-        <v>29.499</v>
+        <v>29.831</v>
       </c>
       <c r="AC163" t="inlineStr"/>
     </row>
@@ -25189,7 +25189,7 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>211.758</v>
+        <v>220.903</v>
       </c>
       <c r="I167" t="n">
         <v>1.364</v>
@@ -25207,10 +25207,10 @@
         <v>0.228</v>
       </c>
       <c r="N167" t="n">
-        <v>118.636</v>
+        <v>127.784</v>
       </c>
       <c r="O167" t="n">
-        <v>304.876</v>
+        <v>314.024</v>
       </c>
       <c r="P167" t="n">
         <v>0.472</v>
@@ -25243,13 +25243,13 @@
         <v>0.824</v>
       </c>
       <c r="Z167" t="n">
-        <v>13.847</v>
+        <v>14.213</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.811</v>
+        <v>2.177</v>
       </c>
       <c r="AB167" t="n">
-        <v>29.725</v>
+        <v>30.091</v>
       </c>
       <c r="AC167" t="inlineStr"/>
     </row>
@@ -26119,7 +26119,7 @@
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>257.478</v>
+        <v>258.399</v>
       </c>
       <c r="I177" t="n">
         <v>1.809</v>
@@ -26137,10 +26137,10 @@
         <v>0.143</v>
       </c>
       <c r="N177" t="n">
-        <v>164.356</v>
+        <v>165.276</v>
       </c>
       <c r="O177" t="n">
-        <v>350.596</v>
+        <v>351.516</v>
       </c>
       <c r="P177" t="n">
         <v>0.626</v>
@@ -26173,13 +26173,13 @@
         <v>0.739</v>
       </c>
       <c r="Z177" t="n">
-        <v>16.864</v>
+        <v>16.901</v>
       </c>
       <c r="AA177" t="n">
-        <v>4.51</v>
+        <v>4.547</v>
       </c>
       <c r="AB177" t="n">
-        <v>32.283</v>
+        <v>32.32</v>
       </c>
       <c r="AC177" t="inlineStr"/>
     </row>
@@ -26398,67 +26398,67 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>214.363</v>
+        <v>223.055</v>
       </c>
       <c r="I180" t="n">
-        <v>1.441</v>
+        <v>1.381</v>
       </c>
       <c r="J180" t="n">
-        <v>52.359</v>
+        <v>46.073</v>
       </c>
       <c r="K180" t="n">
-        <v>0.418</v>
+        <v>0.379</v>
       </c>
       <c r="L180" t="n">
-        <v>0.593</v>
+        <v>0.553</v>
       </c>
       <c r="M180" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N180" t="n">
-        <v>121.244</v>
+        <v>129.935</v>
       </c>
       <c r="O180" t="n">
-        <v>307.484</v>
+        <v>316.175</v>
       </c>
       <c r="P180" t="n">
-        <v>0.499</v>
+        <v>0.478</v>
       </c>
       <c r="Q180" t="n">
-        <v>2.845</v>
+        <v>2.786</v>
       </c>
       <c r="R180" t="n">
-        <v>31.469</v>
+        <v>25.18</v>
       </c>
       <c r="S180" t="n">
-        <v>73.251</v>
+        <v>66.968</v>
       </c>
       <c r="T180" t="n">
-        <v>0.145</v>
+        <v>0.131</v>
       </c>
       <c r="U180" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.898</v>
       </c>
       <c r="V180" t="n">
-        <v>0.205</v>
+        <v>0.192</v>
       </c>
       <c r="W180" t="n">
-        <v>1.728</v>
+        <v>1.689</v>
       </c>
       <c r="X180" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y180" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z180" t="n">
-        <v>20.42</v>
+        <v>19.835</v>
       </c>
       <c r="AA180" t="n">
-        <v>5.736</v>
+        <v>5.457</v>
       </c>
       <c r="AB180" t="n">
-        <v>36.046</v>
+        <v>35.357</v>
       </c>
       <c r="AC180" t="inlineStr"/>
     </row>
@@ -26491,67 +26491,67 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>218.34</v>
+        <v>217.887</v>
       </c>
       <c r="I181" t="n">
-        <v>1.563</v>
+        <v>1.503</v>
       </c>
       <c r="J181" t="n">
-        <v>52.333</v>
+        <v>46.047</v>
       </c>
       <c r="K181" t="n">
-        <v>0.423</v>
+        <v>0.385</v>
       </c>
       <c r="L181" t="n">
-        <v>0.593</v>
+        <v>0.553</v>
       </c>
       <c r="M181" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N181" t="n">
-        <v>125.217</v>
+        <v>124.766</v>
       </c>
       <c r="O181" t="n">
-        <v>311.463</v>
+        <v>311.006</v>
       </c>
       <c r="P181" t="n">
-        <v>0.541</v>
+        <v>0.52</v>
       </c>
       <c r="Q181" t="n">
-        <v>2.967</v>
+        <v>2.907</v>
       </c>
       <c r="R181" t="n">
-        <v>31.44</v>
+        <v>25.151</v>
       </c>
       <c r="S181" t="n">
-        <v>73.22799999999999</v>
+        <v>66.94</v>
       </c>
       <c r="T181" t="n">
-        <v>0.147</v>
+        <v>0.133</v>
       </c>
       <c r="U181" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.904</v>
       </c>
       <c r="V181" t="n">
-        <v>0.205</v>
+        <v>0.192</v>
       </c>
       <c r="W181" t="n">
-        <v>1.728</v>
+        <v>1.689</v>
       </c>
       <c r="X181" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y181" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z181" t="n">
-        <v>21.097</v>
+        <v>20.146</v>
       </c>
       <c r="AA181" t="n">
-        <v>6.072</v>
+        <v>5.428</v>
       </c>
       <c r="AB181" t="n">
-        <v>36.726</v>
+        <v>35.667</v>
       </c>
       <c r="AC181" t="inlineStr"/>
     </row>
@@ -26584,67 +26584,67 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>210.447</v>
+        <v>210.916</v>
       </c>
       <c r="I182" t="n">
-        <v>1.485</v>
+        <v>1.425</v>
       </c>
       <c r="J182" t="n">
-        <v>51.924</v>
+        <v>45.638</v>
       </c>
       <c r="K182" t="n">
-        <v>0.413</v>
+        <v>0.375</v>
       </c>
       <c r="L182" t="n">
-        <v>0.593</v>
+        <v>0.554</v>
       </c>
       <c r="M182" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N182" t="n">
-        <v>117.326</v>
+        <v>117.795</v>
       </c>
       <c r="O182" t="n">
-        <v>303.566</v>
+        <v>304.035</v>
       </c>
       <c r="P182" t="n">
-        <v>0.514</v>
+        <v>0.493</v>
       </c>
       <c r="Q182" t="n">
-        <v>2.889</v>
+        <v>2.83</v>
       </c>
       <c r="R182" t="n">
-        <v>31.03</v>
+        <v>24.748</v>
       </c>
       <c r="S182" t="n">
-        <v>72.819</v>
+        <v>66.53</v>
       </c>
       <c r="T182" t="n">
-        <v>0.143</v>
+        <v>0.13</v>
       </c>
       <c r="U182" t="n">
-        <v>0.931</v>
+        <v>0.893</v>
       </c>
       <c r="V182" t="n">
-        <v>0.205</v>
+        <v>0.192</v>
       </c>
       <c r="W182" t="n">
-        <v>1.729</v>
+        <v>1.689</v>
       </c>
       <c r="X182" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y182" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z182" t="n">
-        <v>20.365</v>
+        <v>19.451</v>
       </c>
       <c r="AA182" t="n">
-        <v>5.584</v>
+        <v>4.978</v>
       </c>
       <c r="AB182" t="n">
-        <v>35.992</v>
+        <v>34.97</v>
       </c>
       <c r="AC182" t="inlineStr"/>
     </row>
@@ -26677,67 +26677,67 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>222.091</v>
+        <v>221.639</v>
       </c>
       <c r="I183" t="n">
-        <v>1.521</v>
+        <v>1.461</v>
       </c>
       <c r="J183" t="n">
-        <v>52.379</v>
+        <v>46.093</v>
       </c>
       <c r="K183" t="n">
-        <v>0.432</v>
+        <v>0.394</v>
       </c>
       <c r="L183" t="n">
-        <v>0.594</v>
+        <v>0.554</v>
       </c>
       <c r="M183" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N183" t="n">
-        <v>128.974</v>
+        <v>128.516</v>
       </c>
       <c r="O183" t="n">
-        <v>315.214</v>
+        <v>314.756</v>
       </c>
       <c r="P183" t="n">
-        <v>0.526</v>
+        <v>0.506</v>
       </c>
       <c r="Q183" t="n">
-        <v>2.925</v>
+        <v>2.866</v>
       </c>
       <c r="R183" t="n">
-        <v>31.489</v>
+        <v>25.2</v>
       </c>
       <c r="S183" t="n">
-        <v>73.271</v>
+        <v>66.988</v>
       </c>
       <c r="T183" t="n">
-        <v>0.15</v>
+        <v>0.136</v>
       </c>
       <c r="U183" t="n">
-        <v>0.951</v>
+        <v>0.912</v>
       </c>
       <c r="V183" t="n">
-        <v>0.205</v>
+        <v>0.192</v>
       </c>
       <c r="W183" t="n">
-        <v>1.729</v>
+        <v>1.689</v>
       </c>
       <c r="X183" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y183" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z183" t="n">
-        <v>21.135</v>
+        <v>20.185</v>
       </c>
       <c r="AA183" t="n">
-        <v>6.186</v>
+        <v>5.542</v>
       </c>
       <c r="AB183" t="n">
-        <v>36.765</v>
+        <v>35.704</v>
       </c>
       <c r="AC183" t="inlineStr"/>
     </row>
@@ -26770,67 +26770,67 @@
         <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>230.486</v>
+        <v>230.033</v>
       </c>
       <c r="I184" t="n">
-        <v>1.562</v>
+        <v>1.502</v>
       </c>
       <c r="J184" t="n">
-        <v>51.844</v>
+        <v>45.558</v>
       </c>
       <c r="K184" t="n">
-        <v>0.43</v>
+        <v>0.391</v>
       </c>
       <c r="L184" t="n">
-        <v>0.594</v>
+        <v>0.554</v>
       </c>
       <c r="M184" t="n">
-        <v>0.242</v>
+        <v>0.201</v>
       </c>
       <c r="N184" t="n">
-        <v>137.365</v>
+        <v>136.914</v>
       </c>
       <c r="O184" t="n">
-        <v>323.605</v>
+        <v>323.155</v>
       </c>
       <c r="P184" t="n">
-        <v>0.541</v>
+        <v>0.52</v>
       </c>
       <c r="Q184" t="n">
-        <v>2.966</v>
+        <v>2.907</v>
       </c>
       <c r="R184" t="n">
-        <v>30.951</v>
+        <v>24.668</v>
       </c>
       <c r="S184" t="n">
-        <v>72.739</v>
+        <v>66.45</v>
       </c>
       <c r="T184" t="n">
-        <v>0.149</v>
+        <v>0.135</v>
       </c>
       <c r="U184" t="n">
-        <v>0.948</v>
+        <v>0.91</v>
       </c>
       <c r="V184" t="n">
-        <v>0.206</v>
+        <v>0.192</v>
       </c>
       <c r="W184" t="n">
-        <v>1.729</v>
+        <v>1.69</v>
       </c>
       <c r="X184" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y184" t="n">
-        <v>0.838</v>
+        <v>0.797</v>
       </c>
       <c r="Z184" t="n">
-        <v>21.558</v>
+        <v>20.604</v>
       </c>
       <c r="AA184" t="n">
-        <v>6.511</v>
+        <v>5.863</v>
       </c>
       <c r="AB184" t="n">
-        <v>37.192</v>
+        <v>36.135</v>
       </c>
       <c r="AC184" t="inlineStr"/>
     </row>
@@ -26863,67 +26863,67 @@
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>216.674</v>
+        <v>216.222</v>
       </c>
       <c r="I185" t="n">
-        <v>1.552</v>
+        <v>1.492</v>
       </c>
       <c r="J185" t="n">
-        <v>51.848</v>
+        <v>45.562</v>
       </c>
       <c r="K185" t="n">
-        <v>0.418</v>
+        <v>0.38</v>
       </c>
       <c r="L185" t="n">
-        <v>0.593</v>
+        <v>0.554</v>
       </c>
       <c r="M185" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N185" t="n">
-        <v>123.555</v>
+        <v>123.104</v>
       </c>
       <c r="O185" t="n">
-        <v>309.795</v>
+        <v>309.344</v>
       </c>
       <c r="P185" t="n">
-        <v>0.537</v>
+        <v>0.517</v>
       </c>
       <c r="Q185" t="n">
-        <v>2.956</v>
+        <v>2.897</v>
       </c>
       <c r="R185" t="n">
-        <v>30.958</v>
+        <v>24.67</v>
       </c>
       <c r="S185" t="n">
-        <v>72.73999999999999</v>
+        <v>66.452</v>
       </c>
       <c r="T185" t="n">
-        <v>0.145</v>
+        <v>0.131</v>
       </c>
       <c r="U185" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.898</v>
       </c>
       <c r="V185" t="n">
-        <v>0.205</v>
+        <v>0.192</v>
       </c>
       <c r="W185" t="n">
-        <v>1.729</v>
+        <v>1.689</v>
       </c>
       <c r="X185" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y185" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z185" t="n">
-        <v>20.905</v>
+        <v>19.955</v>
       </c>
       <c r="AA185" t="n">
-        <v>5.93</v>
+        <v>5.286</v>
       </c>
       <c r="AB185" t="n">
-        <v>36.532</v>
+        <v>35.476</v>
       </c>
       <c r="AC185" t="inlineStr"/>
     </row>
@@ -26956,67 +26956,67 @@
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>204.474</v>
+        <v>204.022</v>
       </c>
       <c r="I186" t="n">
-        <v>1.445</v>
+        <v>1.385</v>
       </c>
       <c r="J186" t="n">
-        <v>52.747</v>
+        <v>46.461</v>
       </c>
       <c r="K186" t="n">
-        <v>0.422</v>
+        <v>0.383</v>
       </c>
       <c r="L186" t="n">
-        <v>0.593</v>
+        <v>0.554</v>
       </c>
       <c r="M186" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N186" t="n">
-        <v>111.355</v>
+        <v>110.904</v>
       </c>
       <c r="O186" t="n">
-        <v>297.595</v>
+        <v>297.144</v>
       </c>
       <c r="P186" t="n">
-        <v>0.5</v>
+        <v>0.479</v>
       </c>
       <c r="Q186" t="n">
-        <v>2.849</v>
+        <v>2.79</v>
       </c>
       <c r="R186" t="n">
-        <v>31.852</v>
+        <v>25.569</v>
       </c>
       <c r="S186" t="n">
-        <v>73.64</v>
+        <v>67.351</v>
       </c>
       <c r="T186" t="n">
-        <v>0.146</v>
+        <v>0.133</v>
       </c>
       <c r="U186" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.902</v>
       </c>
       <c r="V186" t="n">
-        <v>0.205</v>
+        <v>0.192</v>
       </c>
       <c r="W186" t="n">
-        <v>1.728</v>
+        <v>1.689</v>
       </c>
       <c r="X186" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y186" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z186" t="n">
-        <v>20.103</v>
+        <v>19.152</v>
       </c>
       <c r="AA186" t="n">
-        <v>5.392</v>
+        <v>4.748</v>
       </c>
       <c r="AB186" t="n">
-        <v>35.73</v>
+        <v>34.674</v>
       </c>
       <c r="AC186" t="inlineStr"/>
     </row>
@@ -27049,67 +27049,67 @@
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>214.265</v>
+        <v>213.813</v>
       </c>
       <c r="I187" t="n">
-        <v>1.469</v>
+        <v>1.409</v>
       </c>
       <c r="J187" t="n">
-        <v>52.747</v>
+        <v>46.461</v>
       </c>
       <c r="K187" t="n">
-        <v>0.423</v>
+        <v>0.384</v>
       </c>
       <c r="L187" t="n">
-        <v>0.593</v>
+        <v>0.553</v>
       </c>
       <c r="M187" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N187" t="n">
-        <v>121.145</v>
+        <v>120.694</v>
       </c>
       <c r="O187" t="n">
-        <v>307.385</v>
+        <v>306.934</v>
       </c>
       <c r="P187" t="n">
-        <v>0.508</v>
+        <v>0.488</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.873</v>
+        <v>2.814</v>
       </c>
       <c r="R187" t="n">
-        <v>31.852</v>
+        <v>25.569</v>
       </c>
       <c r="S187" t="n">
-        <v>73.64</v>
+        <v>67.351</v>
       </c>
       <c r="T187" t="n">
-        <v>0.146</v>
+        <v>0.133</v>
       </c>
       <c r="U187" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.903</v>
       </c>
       <c r="V187" t="n">
-        <v>0.205</v>
+        <v>0.191</v>
       </c>
       <c r="W187" t="n">
-        <v>1.728</v>
+        <v>1.689</v>
       </c>
       <c r="X187" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y187" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z187" t="n">
-        <v>20.596</v>
+        <v>19.646</v>
       </c>
       <c r="AA187" t="n">
-        <v>5.819</v>
+        <v>5.175</v>
       </c>
       <c r="AB187" t="n">
-        <v>36.223</v>
+        <v>35.167</v>
       </c>
       <c r="AC187" t="inlineStr"/>
     </row>
@@ -27142,67 +27142,67 @@
         <v>1</v>
       </c>
       <c r="H188" t="n">
-        <v>211.894</v>
+        <v>211.442</v>
       </c>
       <c r="I188" t="n">
-        <v>1.355</v>
+        <v>1.296</v>
       </c>
       <c r="J188" t="n">
-        <v>51.751</v>
+        <v>45.465</v>
       </c>
       <c r="K188" t="n">
-        <v>0.412</v>
+        <v>0.374</v>
       </c>
       <c r="L188" t="n">
-        <v>0.593</v>
+        <v>0.554</v>
       </c>
       <c r="M188" t="n">
-        <v>0.242</v>
+        <v>0.201</v>
       </c>
       <c r="N188" t="n">
-        <v>118.775</v>
+        <v>118.324</v>
       </c>
       <c r="O188" t="n">
-        <v>305.015</v>
+        <v>304.564</v>
       </c>
       <c r="P188" t="n">
-        <v>0.469</v>
+        <v>0.449</v>
       </c>
       <c r="Q188" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="R188" t="n">
-        <v>30.859</v>
+        <v>24.571</v>
       </c>
       <c r="S188" t="n">
-        <v>72.64100000000001</v>
+        <v>66.35899999999999</v>
       </c>
       <c r="T188" t="n">
-        <v>0.143</v>
+        <v>0.129</v>
       </c>
       <c r="U188" t="n">
-        <v>0.93</v>
+        <v>0.892</v>
       </c>
       <c r="V188" t="n">
-        <v>0.205</v>
+        <v>0.192</v>
       </c>
       <c r="W188" t="n">
-        <v>1.728</v>
+        <v>1.689</v>
       </c>
       <c r="X188" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y188" t="n">
-        <v>0.838</v>
+        <v>0.797</v>
       </c>
       <c r="Z188" t="n">
-        <v>19.874</v>
+        <v>18.92</v>
       </c>
       <c r="AA188" t="n">
-        <v>5.437</v>
+        <v>4.789</v>
       </c>
       <c r="AB188" t="n">
-        <v>35.507</v>
+        <v>34.448</v>
       </c>
       <c r="AC188" t="inlineStr"/>
     </row>
@@ -27235,67 +27235,67 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>216.555</v>
+        <v>216.103</v>
       </c>
       <c r="I189" t="n">
-        <v>1.412</v>
+        <v>1.352</v>
       </c>
       <c r="J189" t="n">
-        <v>51.802</v>
+        <v>45.516</v>
       </c>
       <c r="K189" t="n">
-        <v>0.401</v>
+        <v>0.363</v>
       </c>
       <c r="L189" t="n">
-        <v>0.592</v>
+        <v>0.553</v>
       </c>
       <c r="M189" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N189" t="n">
-        <v>123.435</v>
+        <v>122.984</v>
       </c>
       <c r="O189" t="n">
-        <v>309.675</v>
+        <v>309.224</v>
       </c>
       <c r="P189" t="n">
-        <v>0.489</v>
+        <v>0.468</v>
       </c>
       <c r="Q189" t="n">
-        <v>2.816</v>
+        <v>2.757</v>
       </c>
       <c r="R189" t="n">
-        <v>30.91</v>
+        <v>24.621</v>
       </c>
       <c r="S189" t="n">
-        <v>72.69199999999999</v>
+        <v>66.41</v>
       </c>
       <c r="T189" t="n">
-        <v>0.139</v>
+        <v>0.126</v>
       </c>
       <c r="U189" t="n">
-        <v>0.92</v>
+        <v>0.881</v>
       </c>
       <c r="V189" t="n">
-        <v>0.205</v>
+        <v>0.191</v>
       </c>
       <c r="W189" t="n">
-        <v>1.728</v>
+        <v>1.688</v>
       </c>
       <c r="X189" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y189" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z189" t="n">
-        <v>20.237</v>
+        <v>19.287</v>
       </c>
       <c r="AA189" t="n">
-        <v>5.694</v>
+        <v>5.05</v>
       </c>
       <c r="AB189" t="n">
-        <v>35.865</v>
+        <v>34.804</v>
       </c>
       <c r="AC189" t="inlineStr"/>
     </row>
@@ -27328,67 +27328,67 @@
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>222.638</v>
+        <v>222.186</v>
       </c>
       <c r="I190" t="n">
-        <v>1.502</v>
+        <v>1.443</v>
       </c>
       <c r="J190" t="n">
-        <v>52.726</v>
+        <v>46.44</v>
       </c>
       <c r="K190" t="n">
-        <v>0.402</v>
+        <v>0.364</v>
       </c>
       <c r="L190" t="n">
-        <v>0.592</v>
+        <v>0.552</v>
       </c>
       <c r="M190" t="n">
-        <v>0.237</v>
+        <v>0.195</v>
       </c>
       <c r="N190" t="n">
-        <v>129.516</v>
+        <v>129.065</v>
       </c>
       <c r="O190" t="n">
-        <v>315.756</v>
+        <v>315.305</v>
       </c>
       <c r="P190" t="n">
-        <v>0.52</v>
+        <v>0.499</v>
       </c>
       <c r="Q190" t="n">
-        <v>2.907</v>
+        <v>2.847</v>
       </c>
       <c r="R190" t="n">
-        <v>31.831</v>
+        <v>25.549</v>
       </c>
       <c r="S190" t="n">
-        <v>73.62</v>
+        <v>67.331</v>
       </c>
       <c r="T190" t="n">
-        <v>0.139</v>
+        <v>0.126</v>
       </c>
       <c r="U190" t="n">
-        <v>0.921</v>
+        <v>0.882</v>
       </c>
       <c r="V190" t="n">
-        <v>0.205</v>
+        <v>0.191</v>
       </c>
       <c r="W190" t="n">
-        <v>1.727</v>
+        <v>1.688</v>
       </c>
       <c r="X190" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
       <c r="Y190" t="n">
-        <v>0.833</v>
+        <v>0.791</v>
       </c>
       <c r="Z190" t="n">
-        <v>20.942</v>
+        <v>19.991</v>
       </c>
       <c r="AA190" t="n">
-        <v>6.158</v>
+        <v>5.514</v>
       </c>
       <c r="AB190" t="n">
-        <v>36.571</v>
+        <v>35.509</v>
       </c>
       <c r="AC190" t="inlineStr"/>
     </row>
@@ -27793,10 +27793,10 @@
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>254.028</v>
+        <v>269.693</v>
       </c>
       <c r="I195" t="n">
-        <v>1.98</v>
+        <v>2.053</v>
       </c>
       <c r="J195" t="n">
         <v>9.863</v>
@@ -27811,16 +27811,16 @@
         <v>0.156</v>
       </c>
       <c r="N195" t="n">
-        <v>160.906</v>
+        <v>176.574</v>
       </c>
       <c r="O195" t="n">
-        <v>347.146</v>
+        <v>362.814</v>
       </c>
       <c r="P195" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.384</v>
+        <v>3.458</v>
       </c>
       <c r="R195" t="n">
         <v>3.414</v>
@@ -27847,13 +27847,13 @@
         <v>0.752</v>
       </c>
       <c r="Z195" t="n">
-        <v>18.388</v>
+        <v>19.307</v>
       </c>
       <c r="AA195" t="n">
-        <v>4.884</v>
+        <v>5.612</v>
       </c>
       <c r="AB195" t="n">
-        <v>33.866</v>
+        <v>34.787</v>
       </c>
       <c r="AC195" t="inlineStr"/>
     </row>
@@ -28258,7 +28258,7 @@
         <v>1</v>
       </c>
       <c r="H200" t="n">
-        <v>260.152</v>
+        <v>260.765</v>
       </c>
       <c r="I200" t="n">
         <v>2.005</v>
@@ -28276,10 +28276,10 @@
         <v>0.155</v>
       </c>
       <c r="N200" t="n">
-        <v>167.034</v>
+        <v>167.645</v>
       </c>
       <c r="O200" t="n">
-        <v>353.274</v>
+        <v>353.885</v>
       </c>
       <c r="P200" t="n">
         <v>0.694</v>
@@ -28312,13 +28312,13 @@
         <v>0.751</v>
       </c>
       <c r="Z200" t="n">
-        <v>18.669</v>
+        <v>18.694</v>
       </c>
       <c r="AA200" t="n">
-        <v>5.142</v>
+        <v>5.167</v>
       </c>
       <c r="AB200" t="n">
-        <v>34.146</v>
+        <v>34.17</v>
       </c>
       <c r="AC200" t="inlineStr"/>
     </row>
@@ -31234,10 +31234,10 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>194.947</v>
+        <v>192.243</v>
       </c>
       <c r="I232" t="n">
-        <v>1.317</v>
+        <v>1.298</v>
       </c>
       <c r="J232" t="n">
         <v>22.984</v>
@@ -31252,16 +31252,16 @@
         <v>0.185</v>
       </c>
       <c r="N232" t="n">
-        <v>101.825</v>
+        <v>99.124</v>
       </c>
       <c r="O232" t="n">
-        <v>288.066</v>
+        <v>285.365</v>
       </c>
       <c r="P232" t="n">
-        <v>0.456</v>
+        <v>0.449</v>
       </c>
       <c r="Q232" t="n">
-        <v>2.722</v>
+        <v>2.703</v>
       </c>
       <c r="R232" t="n">
         <v>7.956</v>
@@ -31288,13 +31288,13 @@
         <v>0.781</v>
       </c>
       <c r="Z232" t="n">
-        <v>14.952</v>
+        <v>14.769</v>
       </c>
       <c r="AA232" t="n">
-        <v>2.091</v>
+        <v>1.957</v>
       </c>
       <c r="AB232" t="n">
-        <v>30.493</v>
+        <v>30.309</v>
       </c>
       <c r="AC232" t="inlineStr"/>
     </row>
@@ -32629,7 +32629,7 @@
         <v>1</v>
       </c>
       <c r="H247" t="n">
-        <v>212.317</v>
+        <v>212.93</v>
       </c>
       <c r="I247" t="n">
         <v>1.342</v>
@@ -32647,10 +32647,10 @@
         <v>0.198</v>
       </c>
       <c r="N247" t="n">
-        <v>119.195</v>
+        <v>119.807</v>
       </c>
       <c r="O247" t="n">
-        <v>305.436</v>
+        <v>306.053</v>
       </c>
       <c r="P247" t="n">
         <v>0.465</v>
@@ -32683,13 +32683,13 @@
         <v>0.794</v>
       </c>
       <c r="Z247" t="n">
-        <v>16.904</v>
+        <v>16.928</v>
       </c>
       <c r="AA247" t="n">
-        <v>3.284</v>
+        <v>3.308</v>
       </c>
       <c r="AB247" t="n">
-        <v>32.376</v>
+        <v>32.401</v>
       </c>
       <c r="AC247" t="inlineStr"/>
     </row>
@@ -33001,10 +33001,10 @@
         <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>214.194</v>
+        <v>211.49</v>
       </c>
       <c r="I251" t="n">
-        <v>1.259</v>
+        <v>1.24</v>
       </c>
       <c r="J251" t="n">
         <v>31.609</v>
@@ -33019,16 +33019,16 @@
         <v>0.189</v>
       </c>
       <c r="N251" t="n">
-        <v>121.074</v>
+        <v>118.367</v>
       </c>
       <c r="O251" t="n">
-        <v>307.315</v>
+        <v>304.614</v>
       </c>
       <c r="P251" t="n">
-        <v>0.436</v>
+        <v>0.429</v>
       </c>
       <c r="Q251" t="n">
-        <v>2.663</v>
+        <v>2.644</v>
       </c>
       <c r="R251" t="n">
         <v>10.941</v>
@@ -33055,13 +33055,13 @@
         <v>0.785</v>
       </c>
       <c r="Z251" t="n">
-        <v>16.616</v>
+        <v>16.433</v>
       </c>
       <c r="AA251" t="n">
-        <v>3.243</v>
+        <v>3.109</v>
       </c>
       <c r="AB251" t="n">
-        <v>32.08</v>
+        <v>31.896</v>
       </c>
       <c r="AC251" t="inlineStr"/>
     </row>
@@ -33466,10 +33466,10 @@
         <v>1</v>
       </c>
       <c r="H256" t="n">
-        <v>201.956</v>
+        <v>217.622</v>
       </c>
       <c r="I256" t="n">
-        <v>1.245</v>
+        <v>1.318</v>
       </c>
       <c r="J256" t="n">
         <v>31.228</v>
@@ -33484,16 +33484,16 @@
         <v>0.198</v>
       </c>
       <c r="N256" t="n">
-        <v>108.835</v>
+        <v>124.504</v>
       </c>
       <c r="O256" t="n">
-        <v>295.076</v>
+        <v>310.744</v>
       </c>
       <c r="P256" t="n">
-        <v>0.431</v>
+        <v>0.456</v>
       </c>
       <c r="Q256" t="n">
-        <v>2.65</v>
+        <v>2.723</v>
       </c>
       <c r="R256" t="n">
         <v>10.809</v>
@@ -33520,13 +33520,13 @@
         <v>0.794</v>
       </c>
       <c r="Z256" t="n">
-        <v>16.037</v>
+        <v>16.956</v>
       </c>
       <c r="AA256" t="n">
-        <v>2.713</v>
+        <v>3.441</v>
       </c>
       <c r="AB256" t="n">
-        <v>31.51</v>
+        <v>32.432</v>
       </c>
       <c r="AC256" t="inlineStr"/>
     </row>
@@ -35047,7 +35047,7 @@
         <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>202.562</v>
+        <v>203.175</v>
       </c>
       <c r="I273" t="n">
         <v>1.205</v>
@@ -35065,10 +35065,10 @@
         <v>0.249</v>
       </c>
       <c r="N273" t="n">
-        <v>109.444</v>
+        <v>110.055</v>
       </c>
       <c r="O273" t="n">
-        <v>295.684</v>
+        <v>296.295</v>
       </c>
       <c r="P273" t="n">
         <v>0.417</v>
@@ -35101,13 +35101,13 @@
         <v>0.845</v>
       </c>
       <c r="Z273" t="n">
-        <v>15.683</v>
+        <v>15.707</v>
       </c>
       <c r="AA273" t="n">
-        <v>2.338</v>
+        <v>2.362</v>
       </c>
       <c r="AB273" t="n">
-        <v>31.645</v>
+        <v>31.67</v>
       </c>
       <c r="AC273" t="inlineStr"/>
     </row>
@@ -36070,10 +36070,10 @@
         <v>0</v>
       </c>
       <c r="H284" t="n">
-        <v>270.508</v>
+        <v>286.173</v>
       </c>
       <c r="I284" t="n">
-        <v>2.204</v>
+        <v>2.277</v>
       </c>
       <c r="J284" t="n">
         <v>2.238</v>
@@ -36088,16 +36088,16 @@
         <v>0.138</v>
       </c>
       <c r="N284" t="n">
-        <v>177.386</v>
+        <v>193.054</v>
       </c>
       <c r="O284" t="n">
-        <v>363.626</v>
+        <v>379.295</v>
       </c>
       <c r="P284" t="n">
-        <v>0.799</v>
+        <v>0.872</v>
       </c>
       <c r="Q284" t="n">
-        <v>3.608</v>
+        <v>3.681</v>
       </c>
       <c r="R284" t="n">
         <v>0.775</v>
@@ -36124,13 +36124,13 @@
         <v>0.734</v>
       </c>
       <c r="Z284" t="n">
-        <v>18.732</v>
+        <v>19.651</v>
       </c>
       <c r="AA284" t="n">
-        <v>5.502</v>
+        <v>6.423</v>
       </c>
       <c r="AB284" t="n">
-        <v>34.287</v>
+        <v>35.206</v>
       </c>
       <c r="AC284" t="inlineStr"/>
     </row>
@@ -36442,10 +36442,10 @@
         <v>0</v>
       </c>
       <c r="H288" t="n">
-        <v>278.683</v>
+        <v>275.979</v>
       </c>
       <c r="I288" t="n">
-        <v>2.159</v>
+        <v>2.14</v>
       </c>
       <c r="J288" t="n">
         <v>2.205</v>
@@ -36460,16 +36460,16 @@
         <v>0.138</v>
       </c>
       <c r="N288" t="n">
-        <v>185.564</v>
+        <v>182.856</v>
       </c>
       <c r="O288" t="n">
-        <v>371.804</v>
+        <v>369.103</v>
       </c>
       <c r="P288" t="n">
-        <v>0.754</v>
+        <v>0.741</v>
       </c>
       <c r="Q288" t="n">
-        <v>3.563</v>
+        <v>3.544</v>
       </c>
       <c r="R288" t="n">
         <v>0.763</v>
@@ -36496,13 +36496,13 @@
         <v>0.734</v>
       </c>
       <c r="Z288" t="n">
-        <v>18.905</v>
+        <v>18.722</v>
       </c>
       <c r="AA288" t="n">
-        <v>5.658</v>
+        <v>5.497</v>
       </c>
       <c r="AB288" t="n">
-        <v>34.461</v>
+        <v>34.277</v>
       </c>
       <c r="AC288" t="inlineStr"/>
     </row>
@@ -36628,7 +36628,7 @@
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>261.093</v>
+        <v>269.401</v>
       </c>
       <c r="I290" t="n">
         <v>2.058</v>
@@ -36646,10 +36646,10 @@
         <v>0.138</v>
       </c>
       <c r="N290" t="n">
-        <v>167.974</v>
+        <v>176.284</v>
       </c>
       <c r="O290" t="n">
-        <v>354.215</v>
+        <v>362.524</v>
       </c>
       <c r="P290" t="n">
         <v>0.712</v>
@@ -36682,13 +36682,13 @@
         <v>0.734</v>
       </c>
       <c r="Z290" t="n">
-        <v>17.787</v>
+        <v>18.119</v>
       </c>
       <c r="AA290" t="n">
-        <v>4.784</v>
+        <v>5.117</v>
       </c>
       <c r="AB290" t="n">
-        <v>33.344</v>
+        <v>33.676</v>
       </c>
       <c r="AC290" t="inlineStr"/>
     </row>
@@ -36814,7 +36814,7 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>258.6</v>
+        <v>266.908</v>
       </c>
       <c r="I292" t="n">
         <v>2.013</v>
@@ -36832,10 +36832,10 @@
         <v>0.138</v>
       </c>
       <c r="N292" t="n">
-        <v>165.477</v>
+        <v>173.786</v>
       </c>
       <c r="O292" t="n">
-        <v>351.723</v>
+        <v>360.026</v>
       </c>
       <c r="P292" t="n">
         <v>0.697</v>
@@ -36868,13 +36868,13 @@
         <v>0.734</v>
       </c>
       <c r="Z292" t="n">
-        <v>17.572</v>
+        <v>17.904</v>
       </c>
       <c r="AA292" t="n">
-        <v>4.646</v>
+        <v>4.978</v>
       </c>
       <c r="AB292" t="n">
-        <v>33.127</v>
+        <v>33.459</v>
       </c>
       <c r="AC292" t="inlineStr"/>
     </row>
@@ -36907,10 +36907,10 @@
         <v>1</v>
       </c>
       <c r="H293" t="n">
-        <v>242.965</v>
+        <v>240.262</v>
       </c>
       <c r="I293" t="n">
-        <v>1.445</v>
+        <v>1.426</v>
       </c>
       <c r="J293" t="n">
         <v>5.423</v>
@@ -36925,16 +36925,16 @@
         <v>0.199</v>
       </c>
       <c r="N293" t="n">
-        <v>149.845</v>
+        <v>147.144</v>
       </c>
       <c r="O293" t="n">
-        <v>336.085</v>
+        <v>333.384</v>
       </c>
       <c r="P293" t="n">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="Q293" t="n">
-        <v>2.849</v>
+        <v>2.83</v>
       </c>
       <c r="R293" t="n">
         <v>1.877</v>
@@ -36961,13 +36961,13 @@
         <v>0.795</v>
       </c>
       <c r="Z293" t="n">
-        <v>15.13</v>
+        <v>14.946</v>
       </c>
       <c r="AA293" t="n">
-        <v>3.269</v>
+        <v>3.135</v>
       </c>
       <c r="AB293" t="n">
-        <v>30.806</v>
+        <v>30.622</v>
       </c>
       <c r="AC293" t="inlineStr"/>
     </row>
@@ -37558,10 +37558,10 @@
         <v>0</v>
       </c>
       <c r="H300" t="n">
-        <v>229.865</v>
+        <v>245.531</v>
       </c>
       <c r="I300" t="n">
-        <v>1.461</v>
+        <v>1.534</v>
       </c>
       <c r="J300" t="n">
         <v>5.937</v>
@@ -37576,16 +37576,16 @@
         <v>0.198</v>
       </c>
       <c r="N300" t="n">
-        <v>136.745</v>
+        <v>152.407</v>
       </c>
       <c r="O300" t="n">
-        <v>322.985</v>
+        <v>338.654</v>
       </c>
       <c r="P300" t="n">
-        <v>0.506</v>
+        <v>0.531</v>
       </c>
       <c r="Q300" t="n">
-        <v>2.865</v>
+        <v>2.939</v>
       </c>
       <c r="R300" t="n">
         <v>2.055</v>
@@ -37612,13 +37612,13 @@
         <v>0.794</v>
       </c>
       <c r="Z300" t="n">
-        <v>14.628</v>
+        <v>15.547</v>
       </c>
       <c r="AA300" t="n">
-        <v>2.753</v>
+        <v>3.48</v>
       </c>
       <c r="AB300" t="n">
-        <v>30.302</v>
+        <v>31.221</v>
       </c>
       <c r="AC300" t="inlineStr"/>
     </row>
@@ -37930,7 +37930,7 @@
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>238.525</v>
+        <v>246.833</v>
       </c>
       <c r="I304" t="n">
         <v>1.565</v>
@@ -37948,10 +37948,10 @@
         <v>0.183</v>
       </c>
       <c r="N304" t="n">
-        <v>145.405</v>
+        <v>153.714</v>
       </c>
       <c r="O304" t="n">
-        <v>331.645</v>
+        <v>339.955</v>
       </c>
       <c r="P304" t="n">
         <v>0.542</v>
@@ -37984,13 +37984,13 @@
         <v>0.779</v>
       </c>
       <c r="Z304" t="n">
-        <v>16.89</v>
+        <v>17.222</v>
       </c>
       <c r="AA304" t="n">
-        <v>3.879</v>
+        <v>4.212</v>
       </c>
       <c r="AB304" t="n">
-        <v>32.449</v>
+        <v>32.781</v>
       </c>
       <c r="AC304" t="inlineStr"/>
     </row>
@@ -38767,10 +38767,10 @@
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>253.122</v>
+        <v>250.418</v>
       </c>
       <c r="I313" t="n">
-        <v>1.611</v>
+        <v>1.592</v>
       </c>
       <c r="J313" t="n">
         <v>16.565</v>
@@ -38785,16 +38785,16 @@
         <v>0.183</v>
       </c>
       <c r="N313" t="n">
-        <v>160.004</v>
+        <v>157.296</v>
       </c>
       <c r="O313" t="n">
-        <v>346.244</v>
+        <v>343.536</v>
       </c>
       <c r="P313" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="Q313" t="n">
-        <v>3.016</v>
+        <v>2.997</v>
       </c>
       <c r="R313" t="n">
         <v>5.734</v>
@@ -38821,13 +38821,13 @@
         <v>0.779</v>
       </c>
       <c r="Z313" t="n">
-        <v>17.748</v>
+        <v>17.565</v>
       </c>
       <c r="AA313" t="n">
-        <v>4.56</v>
+        <v>4.426</v>
       </c>
       <c r="AB313" t="n">
-        <v>33.309</v>
+        <v>33.124</v>
       </c>
       <c r="AC313" t="inlineStr"/>
     </row>
@@ -39418,10 +39418,10 @@
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>227.515</v>
+        <v>224.811</v>
       </c>
       <c r="I320" t="n">
-        <v>1.433</v>
+        <v>1.414</v>
       </c>
       <c r="J320" t="n">
         <v>9.538</v>
@@ -39436,16 +39436,16 @@
         <v>0.213</v>
       </c>
       <c r="N320" t="n">
-        <v>134.395</v>
+        <v>131.694</v>
       </c>
       <c r="O320" t="n">
-        <v>320.635</v>
+        <v>317.934</v>
       </c>
       <c r="P320" t="n">
-        <v>0.496</v>
+        <v>0.489</v>
       </c>
       <c r="Q320" t="n">
-        <v>2.837</v>
+        <v>2.819</v>
       </c>
       <c r="R320" t="n">
         <v>3.302</v>
@@ -39472,13 +39472,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="Z320" t="n">
-        <v>14.905</v>
+        <v>14.722</v>
       </c>
       <c r="AA320" t="n">
-        <v>2.91</v>
+        <v>2.776</v>
       </c>
       <c r="AB320" t="n">
-        <v>30.46</v>
+        <v>30.276</v>
       </c>
       <c r="AC320" t="inlineStr"/>
     </row>
@@ -39604,7 +39604,7 @@
         <v>0</v>
       </c>
       <c r="H322" t="n">
-        <v>211.725</v>
+        <v>212.646</v>
       </c>
       <c r="I322" t="n">
         <v>1.434</v>
@@ -39622,10 +39622,10 @@
         <v>0.213</v>
       </c>
       <c r="N322" t="n">
-        <v>118.605</v>
+        <v>119.525</v>
       </c>
       <c r="O322" t="n">
-        <v>304.845</v>
+        <v>305.765</v>
       </c>
       <c r="P322" t="n">
         <v>0.496</v>
@@ -39658,13 +39658,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="Z322" t="n">
-        <v>14.429</v>
+        <v>14.466</v>
       </c>
       <c r="AA322" t="n">
-        <v>2.332</v>
+        <v>2.369</v>
       </c>
       <c r="AB322" t="n">
-        <v>29.983</v>
+        <v>30.019</v>
       </c>
       <c r="AC322" t="inlineStr"/>
     </row>
@@ -39697,7 +39697,7 @@
         <v>0</v>
       </c>
       <c r="H323" t="n">
-        <v>214.683</v>
+        <v>223.828</v>
       </c>
       <c r="I323" t="n">
         <v>1.353</v>
@@ -39715,10 +39715,10 @@
         <v>0.213</v>
       </c>
       <c r="N323" t="n">
-        <v>121.564</v>
+        <v>130.706</v>
       </c>
       <c r="O323" t="n">
-        <v>307.805</v>
+        <v>316.946</v>
       </c>
       <c r="P323" t="n">
         <v>0.468</v>
@@ -39751,13 +39751,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="Z323" t="n">
-        <v>14.085</v>
+        <v>14.451</v>
       </c>
       <c r="AA323" t="n">
-        <v>2.291</v>
+        <v>2.656</v>
       </c>
       <c r="AB323" t="n">
-        <v>29.639</v>
+        <v>30.005</v>
       </c>
       <c r="AC323" t="inlineStr"/>
     </row>
@@ -40162,10 +40162,10 @@
         <v>0</v>
       </c>
       <c r="H328" t="n">
-        <v>213.925</v>
+        <v>229.591</v>
       </c>
       <c r="I328" t="n">
-        <v>1.421</v>
+        <v>1.494</v>
       </c>
       <c r="J328" t="n">
         <v>2.996</v>
@@ -40180,16 +40180,16 @@
         <v>0.198</v>
       </c>
       <c r="N328" t="n">
-        <v>120.805</v>
+        <v>136.467</v>
       </c>
       <c r="O328" t="n">
-        <v>307.045</v>
+        <v>322.714</v>
       </c>
       <c r="P328" t="n">
-        <v>0.492</v>
+        <v>0.517</v>
       </c>
       <c r="Q328" t="n">
-        <v>2.826</v>
+        <v>2.899</v>
       </c>
       <c r="R328" t="n">
         <v>1.037</v>
@@ -40216,13 +40216,13 @@
         <v>0.794</v>
       </c>
       <c r="Z328" t="n">
-        <v>13.323</v>
+        <v>14.242</v>
       </c>
       <c r="AA328" t="n">
-        <v>1.694</v>
+        <v>2.422</v>
       </c>
       <c r="AB328" t="n">
-        <v>29.191</v>
+        <v>30.109</v>
       </c>
       <c r="AC328" t="inlineStr"/>
     </row>
@@ -40255,7 +40255,7 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>210.256</v>
+        <v>211.177</v>
       </c>
       <c r="I329" t="n">
         <v>1.424</v>
@@ -40273,10 +40273,10 @@
         <v>0.198</v>
       </c>
       <c r="N329" t="n">
-        <v>117.135</v>
+        <v>118.056</v>
       </c>
       <c r="O329" t="n">
-        <v>303.376</v>
+        <v>304.296</v>
       </c>
       <c r="P329" t="n">
         <v>0.493</v>
@@ -40309,13 +40309,13 @@
         <v>0.794</v>
       </c>
       <c r="Z329" t="n">
-        <v>13.251</v>
+        <v>13.288</v>
       </c>
       <c r="AA329" t="n">
-        <v>1.572</v>
+        <v>1.609</v>
       </c>
       <c r="AB329" t="n">
-        <v>29.118</v>
+        <v>29.155</v>
       </c>
       <c r="AC329" t="inlineStr"/>
     </row>
@@ -40627,7 +40627,7 @@
         <v>0</v>
       </c>
       <c r="H333" t="n">
-        <v>219.014</v>
+        <v>219.627</v>
       </c>
       <c r="I333" t="n">
         <v>1.476</v>
@@ -40645,10 +40645,10 @@
         <v>0.198</v>
       </c>
       <c r="N333" t="n">
-        <v>125.894</v>
+        <v>126.505</v>
       </c>
       <c r="O333" t="n">
-        <v>312.135</v>
+        <v>312.746</v>
       </c>
       <c r="P333" t="n">
         <v>0.511</v>
@@ -40681,13 +40681,13 @@
         <v>0.794</v>
       </c>
       <c r="Z333" t="n">
-        <v>13.838</v>
+        <v>13.863</v>
       </c>
       <c r="AA333" t="n">
-        <v>2.004</v>
+        <v>2.029</v>
       </c>
       <c r="AB333" t="n">
-        <v>29.705</v>
+        <v>29.73</v>
       </c>
       <c r="AC333" t="inlineStr"/>
     </row>
@@ -40720,7 +40720,7 @@
         <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>204.987</v>
+        <v>213.295</v>
       </c>
       <c r="I334" t="n">
         <v>1.302</v>
@@ -40738,10 +40738,10 @@
         <v>0.198</v>
       </c>
       <c r="N334" t="n">
-        <v>111.866</v>
+        <v>120.175</v>
       </c>
       <c r="O334" t="n">
-        <v>298.106</v>
+        <v>306.415</v>
       </c>
       <c r="P334" t="n">
         <v>0.451</v>
@@ -40774,13 +40774,13 @@
         <v>0.794</v>
       </c>
       <c r="Z334" t="n">
-        <v>12.586</v>
+        <v>12.918</v>
       </c>
       <c r="AA334" t="n">
-        <v>1.205</v>
+        <v>1.537</v>
       </c>
       <c r="AB334" t="n">
-        <v>28.454</v>
+        <v>28.786</v>
       </c>
       <c r="AC334" t="inlineStr"/>
     </row>
@@ -40906,10 +40906,10 @@
         <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>221.927</v>
+        <v>219.224</v>
       </c>
       <c r="I336" t="n">
-        <v>1.365</v>
+        <v>1.346</v>
       </c>
       <c r="J336" t="n">
         <v>2.733</v>
@@ -40924,16 +40924,16 @@
         <v>0.198</v>
       </c>
       <c r="N336" t="n">
-        <v>128.806</v>
+        <v>126.104</v>
       </c>
       <c r="O336" t="n">
-        <v>315.046</v>
+        <v>312.345</v>
       </c>
       <c r="P336" t="n">
-        <v>0.472</v>
+        <v>0.466</v>
       </c>
       <c r="Q336" t="n">
-        <v>2.769</v>
+        <v>2.75</v>
       </c>
       <c r="R336" t="n">
         <v>0.946</v>
@@ -40960,13 +40960,13 @@
         <v>0.794</v>
       </c>
       <c r="Z336" t="n">
-        <v>13.278</v>
+        <v>13.095</v>
       </c>
       <c r="AA336" t="n">
-        <v>1.888</v>
+        <v>1.754</v>
       </c>
       <c r="AB336" t="n">
-        <v>29.144</v>
+        <v>28.96</v>
       </c>
       <c r="AC336" t="inlineStr"/>
     </row>
@@ -40999,7 +40999,7 @@
         <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>204.943</v>
+        <v>205.864</v>
       </c>
       <c r="I337" t="n">
         <v>1.38</v>
@@ -41017,10 +41017,10 @@
         <v>0.198</v>
       </c>
       <c r="N337" t="n">
-        <v>111.824</v>
+        <v>112.744</v>
       </c>
       <c r="O337" t="n">
-        <v>298.065</v>
+        <v>298.985</v>
       </c>
       <c r="P337" t="n">
         <v>0.478</v>
@@ -41053,13 +41053,13 @@
         <v>0.794</v>
       </c>
       <c r="Z337" t="n">
-        <v>12.66</v>
+        <v>12.697</v>
       </c>
       <c r="AA337" t="n">
-        <v>1.23</v>
+        <v>1.267</v>
       </c>
       <c r="AB337" t="n">
-        <v>28.524</v>
+        <v>28.561</v>
       </c>
       <c r="AC337" t="inlineStr"/>
     </row>
@@ -41092,7 +41092,7 @@
         <v>0</v>
       </c>
       <c r="H338" t="n">
-        <v>252.174</v>
+        <v>252.787</v>
       </c>
       <c r="I338" t="n">
         <v>1.965</v>
@@ -41110,10 +41110,10 @@
         <v>0.21</v>
       </c>
       <c r="N338" t="n">
-        <v>159.054</v>
+        <v>159.665</v>
       </c>
       <c r="O338" t="n">
-        <v>345.295</v>
+        <v>345.906</v>
       </c>
       <c r="P338" t="n">
         <v>0.68</v>
@@ -41146,13 +41146,13 @@
         <v>0.806</v>
       </c>
       <c r="Z338" t="n">
-        <v>19.255</v>
+        <v>19.279</v>
       </c>
       <c r="AA338" t="n">
-        <v>4.946</v>
+        <v>4.971</v>
       </c>
       <c r="AB338" t="n">
-        <v>34.924</v>
+        <v>34.948</v>
       </c>
       <c r="AC338" t="inlineStr"/>
     </row>
@@ -41371,7 +41371,7 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>239.56</v>
+        <v>240.481</v>
       </c>
       <c r="I341" t="n">
         <v>1.904</v>
@@ -41389,10 +41389,10 @@
         <v>0.21</v>
       </c>
       <c r="N341" t="n">
-        <v>146.437</v>
+        <v>147.363</v>
       </c>
       <c r="O341" t="n">
-        <v>332.683</v>
+        <v>333.604</v>
       </c>
       <c r="P341" t="n">
         <v>0.659</v>
@@ -41425,13 +41425,13 @@
         <v>0.806</v>
       </c>
       <c r="Z341" t="n">
-        <v>18.446</v>
+        <v>18.483</v>
       </c>
       <c r="AA341" t="n">
-        <v>4.336</v>
+        <v>4.373</v>
       </c>
       <c r="AB341" t="n">
-        <v>34.118</v>
+        <v>34.155</v>
       </c>
       <c r="AC341" t="inlineStr"/>
     </row>
@@ -41929,10 +41929,10 @@
         <v>0</v>
       </c>
       <c r="H347" t="n">
-        <v>241.813</v>
+        <v>257.479</v>
       </c>
       <c r="I347" t="n">
-        <v>1.862</v>
+        <v>1.935</v>
       </c>
       <c r="J347" t="n">
         <v>17.104</v>
@@ -41947,16 +41947,16 @@
         <v>0.21</v>
       </c>
       <c r="N347" t="n">
-        <v>148.694</v>
+        <v>164.356</v>
       </c>
       <c r="O347" t="n">
-        <v>334.935</v>
+        <v>350.596</v>
       </c>
       <c r="P347" t="n">
-        <v>0.644</v>
+        <v>0.67</v>
       </c>
       <c r="Q347" t="n">
-        <v>3.266</v>
+        <v>3.34</v>
       </c>
       <c r="R347" t="n">
         <v>5.92</v>
@@ -41983,13 +41983,13 @@
         <v>0.806</v>
       </c>
       <c r="Z347" t="n">
-        <v>18.391</v>
+        <v>19.311</v>
       </c>
       <c r="AA347" t="n">
-        <v>4.378</v>
+        <v>5.106</v>
       </c>
       <c r="AB347" t="n">
-        <v>34.058</v>
+        <v>34.977</v>
       </c>
       <c r="AC347" t="inlineStr"/>
     </row>
@@ -42022,7 +42022,7 @@
         <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>246.925</v>
+        <v>247.539</v>
       </c>
       <c r="I348" t="n">
         <v>1.927</v>
@@ -42040,10 +42040,10 @@
         <v>0.212</v>
       </c>
       <c r="N348" t="n">
-        <v>153.805</v>
+        <v>154.416</v>
       </c>
       <c r="O348" t="n">
-        <v>340.045</v>
+        <v>340.656</v>
       </c>
       <c r="P348" t="n">
         <v>0.667</v>
@@ -42076,13 +42076,13 @@
         <v>0.8080000000000001</v>
       </c>
       <c r="Z348" t="n">
-        <v>18.738</v>
+        <v>18.762</v>
       </c>
       <c r="AA348" t="n">
-        <v>4.626</v>
+        <v>4.651</v>
       </c>
       <c r="AB348" t="n">
-        <v>34.411</v>
+        <v>34.435</v>
       </c>
       <c r="AC348" t="inlineStr"/>
     </row>
@@ -50578,10 +50578,10 @@
         <v>0</v>
       </c>
       <c r="H440" t="n">
-        <v>240.364</v>
+        <v>236.985</v>
       </c>
       <c r="I440" t="n">
-        <v>1.185</v>
+        <v>1.161</v>
       </c>
       <c r="J440" t="n">
         <v>13.632</v>
@@ -50596,16 +50596,16 @@
         <v>0.216</v>
       </c>
       <c r="N440" t="n">
-        <v>147.245</v>
+        <v>143.865</v>
       </c>
       <c r="O440" t="n">
-        <v>333.485</v>
+        <v>330.105</v>
       </c>
       <c r="P440" t="n">
-        <v>0.41</v>
+        <v>0.402</v>
       </c>
       <c r="Q440" t="n">
-        <v>2.589</v>
+        <v>2.566</v>
       </c>
       <c r="R440" t="n">
         <v>4.719</v>
@@ -50632,13 +50632,13 @@
         <v>0.8120000000000001</v>
       </c>
       <c r="Z440" t="n">
-        <v>15.019</v>
+        <v>14.79</v>
       </c>
       <c r="AA440" t="n">
-        <v>3.128</v>
+        <v>2.961</v>
       </c>
       <c r="AB440" t="n">
-        <v>30.729</v>
+        <v>30.498</v>
       </c>
       <c r="AC440" t="inlineStr"/>
     </row>
@@ -50671,7 +50671,7 @@
         <v>1</v>
       </c>
       <c r="H441" t="n">
-        <v>217.18</v>
+        <v>227.565</v>
       </c>
       <c r="I441" t="n">
         <v>1.052</v>
@@ -50689,10 +50689,10 @@
         <v>0.219</v>
       </c>
       <c r="N441" t="n">
-        <v>124.057</v>
+        <v>134.445</v>
       </c>
       <c r="O441" t="n">
-        <v>310.303</v>
+        <v>320.685</v>
       </c>
       <c r="P441" t="n">
         <v>0.364</v>
@@ -50725,13 +50725,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="Z441" t="n">
-        <v>13.788</v>
+        <v>14.203</v>
       </c>
       <c r="AA441" t="n">
-        <v>2.09</v>
+        <v>2.506</v>
       </c>
       <c r="AB441" t="n">
-        <v>29.502</v>
+        <v>29.917</v>
       </c>
       <c r="AC441" t="inlineStr"/>
     </row>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -2456,7 +2456,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2468,55 +2468,59 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3785.7</v>
+        <v>3611.1</v>
       </c>
       <c r="E29" t="n">
-        <v>2420.5</v>
+        <v>2307.6</v>
       </c>
       <c r="F29" t="n">
-        <v>25.04</v>
+        <v>19.07</v>
       </c>
       <c r="G29" t="n">
-        <v>15.83</v>
+        <v>11.88</v>
       </c>
       <c r="H29" t="n">
-        <v>190.7</v>
+        <v>389.8</v>
       </c>
       <c r="I29" t="n">
-        <v>124</v>
+        <v>252.8</v>
       </c>
       <c r="J29" t="n">
-        <v>2.24</v>
+        <v>3.54</v>
       </c>
       <c r="K29" t="n">
-        <v>1.46</v>
+        <v>2.35</v>
       </c>
       <c r="L29" t="n">
-        <v>13.49</v>
+        <v>11.42</v>
       </c>
       <c r="M29" t="n">
-        <v>8.720000000000001</v>
+        <v>7.39</v>
       </c>
       <c r="N29" t="n">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
       <c r="O29" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="P29" t="n">
-        <v>249.36</v>
+        <v>250.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>158.82</v>
+        <v>159.26</v>
       </c>
       <c r="R29" t="n">
-        <v>102</v>
+        <v>101.15</v>
       </c>
       <c r="S29" t="n">
-        <v>217.01</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+        <v>217.28</v>
+      </c>
+      <c r="T29" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="U29" t="n">
+        <v>140.04</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
     </row>
@@ -3414,55 +3418,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3463.8</v>
+        <v>3182.7</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>18.14</v>
+        <v>16.15</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>384.9</v>
+        <v>565.9</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>11.44</v>
+        <v>13.89</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.93</v>
+        <v>3.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>240.1</v>
+        <v>238.72</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3473,67 +3477,63 @@
       <c r="S43" t="n">
         <v>0</v>
       </c>
-      <c r="T43" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="U43" t="n">
-        <v>-19.22</v>
-      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3182.7</v>
+        <v>3638.4</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>16.15</v>
+        <v>24.12</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>565.9</v>
+        <v>186.1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>13.89</v>
+        <v>13.5</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>238.72</v>
+        <v>239.25</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7027,55 +7027,59 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3785.7</v>
+        <v>3611.1</v>
       </c>
       <c r="E29" t="n">
-        <v>2420.5</v>
+        <v>2307.6</v>
       </c>
       <c r="F29" t="n">
-        <v>25.04</v>
+        <v>19.07</v>
       </c>
       <c r="G29" t="n">
-        <v>15.83</v>
+        <v>11.88</v>
       </c>
       <c r="H29" t="n">
-        <v>190.7</v>
+        <v>389.8</v>
       </c>
       <c r="I29" t="n">
-        <v>124</v>
+        <v>252.8</v>
       </c>
       <c r="J29" t="n">
-        <v>2.24</v>
+        <v>3.54</v>
       </c>
       <c r="K29" t="n">
-        <v>1.46</v>
+        <v>2.35</v>
       </c>
       <c r="L29" t="n">
-        <v>13.49</v>
+        <v>11.42</v>
       </c>
       <c r="M29" t="n">
-        <v>8.720000000000001</v>
+        <v>7.39</v>
       </c>
       <c r="N29" t="n">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
       <c r="O29" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="P29" t="n">
-        <v>249.36</v>
+        <v>250.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>158.82</v>
+        <v>159.26</v>
       </c>
       <c r="R29" t="n">
-        <v>102</v>
+        <v>101.15</v>
       </c>
       <c r="S29" t="n">
-        <v>217.01</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+        <v>217.28</v>
+      </c>
+      <c r="T29" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="U29" t="n">
+        <v>140.04</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
     </row>
@@ -8104,55 +8108,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3463.8</v>
+        <v>3182.7</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>18.14</v>
+        <v>16.15</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>384.9</v>
+        <v>565.9</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11.44</v>
+        <v>13.89</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.93</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>240.1</v>
+        <v>238.72</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8163,67 +8167,63 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-19.22</v>
-      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3182.7</v>
+        <v>3638.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>16.15</v>
+        <v>24.12</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>565.9</v>
+        <v>186.1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13.89</v>
+        <v>13.5</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>238.72</v>
+        <v>239.25</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -23210,12 +23210,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -23226,647 +23226,647 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>212.759</v>
+        <v>199.366</v>
       </c>
       <c r="I146" t="n">
-        <v>1.255</v>
+        <v>1.111</v>
       </c>
       <c r="J146" t="n">
-        <v>12.359</v>
+        <v>22.53</v>
       </c>
       <c r="K146" t="n">
-        <v>0.156</v>
+        <v>0.213</v>
       </c>
       <c r="L146" t="n">
-        <v>0.652</v>
+        <v>0.672</v>
       </c>
       <c r="M146" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N146" t="n">
-        <v>119.636</v>
+        <v>106.245</v>
       </c>
       <c r="O146" t="n">
-        <v>305.877</v>
+        <v>292.485</v>
       </c>
       <c r="P146" t="n">
-        <v>0.434</v>
+        <v>0.384</v>
       </c>
       <c r="Q146" t="n">
-        <v>2.659</v>
+        <v>2.515</v>
       </c>
       <c r="R146" t="n">
-        <v>4.278</v>
+        <v>7.798</v>
       </c>
       <c r="S146" t="n">
-        <v>33.251</v>
+        <v>43.421</v>
       </c>
       <c r="T146" t="n">
-        <v>0.054</v>
+        <v>0.074</v>
       </c>
       <c r="U146" t="n">
-        <v>0.674</v>
+        <v>0.731</v>
       </c>
       <c r="V146" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="W146" t="n">
-        <v>1.787</v>
+        <v>1.807</v>
       </c>
       <c r="X146" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y146" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z146" t="n">
-        <v>13.94</v>
+        <v>14.132</v>
       </c>
       <c r="AA146" t="n">
-        <v>2.05</v>
+        <v>1.733</v>
       </c>
       <c r="AB146" t="n">
-        <v>29.631</v>
+        <v>29.859</v>
       </c>
       <c r="AC146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F147" t="n">
         <v>-1</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>235.478</v>
+        <v>215.946</v>
       </c>
       <c r="I147" t="n">
-        <v>1.436</v>
+        <v>1.063</v>
       </c>
       <c r="J147" t="n">
-        <v>12.613</v>
+        <v>22.616</v>
       </c>
       <c r="K147" t="n">
-        <v>0.155</v>
+        <v>0.204</v>
       </c>
       <c r="L147" t="n">
-        <v>0.652</v>
+        <v>0.672</v>
       </c>
       <c r="M147" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N147" t="n">
-        <v>142.356</v>
+        <v>122.825</v>
       </c>
       <c r="O147" t="n">
-        <v>328.596</v>
+        <v>309.066</v>
       </c>
       <c r="P147" t="n">
-        <v>0.497</v>
+        <v>0.368</v>
       </c>
       <c r="Q147" t="n">
-        <v>2.841</v>
+        <v>2.468</v>
       </c>
       <c r="R147" t="n">
-        <v>4.366</v>
+        <v>7.828</v>
       </c>
       <c r="S147" t="n">
-        <v>33.509</v>
+        <v>43.509</v>
       </c>
       <c r="T147" t="n">
-        <v>0.054</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U147" t="n">
-        <v>0.674</v>
+        <v>0.723</v>
       </c>
       <c r="V147" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="W147" t="n">
-        <v>1.787</v>
+        <v>1.807</v>
       </c>
       <c r="X147" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y147" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z147" t="n">
-        <v>15.595</v>
+        <v>14.566</v>
       </c>
       <c r="AA147" t="n">
-        <v>3.217</v>
+        <v>2.317</v>
       </c>
       <c r="AB147" t="n">
-        <v>31.289</v>
+        <v>30.292</v>
       </c>
       <c r="AC147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>224.682</v>
+        <v>222.221</v>
       </c>
       <c r="I148" t="n">
-        <v>1.265</v>
+        <v>1.196</v>
       </c>
       <c r="J148" t="n">
-        <v>12.698</v>
+        <v>23.448</v>
       </c>
       <c r="K148" t="n">
-        <v>0.138</v>
+        <v>0.231</v>
       </c>
       <c r="L148" t="n">
-        <v>0.652</v>
+        <v>0.672</v>
       </c>
       <c r="M148" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N148" t="n">
-        <v>131.564</v>
+        <v>129.104</v>
       </c>
       <c r="O148" t="n">
-        <v>317.804</v>
+        <v>315.344</v>
       </c>
       <c r="P148" t="n">
-        <v>0.438</v>
+        <v>0.414</v>
       </c>
       <c r="Q148" t="n">
-        <v>2.669</v>
+        <v>2.6</v>
       </c>
       <c r="R148" t="n">
-        <v>4.395</v>
+        <v>8.116</v>
       </c>
       <c r="S148" t="n">
-        <v>33.59</v>
+        <v>44.34</v>
       </c>
       <c r="T148" t="n">
-        <v>0.048</v>
+        <v>0.08</v>
       </c>
       <c r="U148" t="n">
-        <v>0.656</v>
+        <v>0.75</v>
       </c>
       <c r="V148" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="W148" t="n">
-        <v>1.787</v>
+        <v>1.807</v>
       </c>
       <c r="X148" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y148" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z148" t="n">
-        <v>14.38</v>
+        <v>15.591</v>
       </c>
       <c r="AA148" t="n">
-        <v>2.516</v>
+        <v>2.836</v>
       </c>
       <c r="AB148" t="n">
-        <v>30.073</v>
+        <v>31.32</v>
       </c>
       <c r="AC148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F149" t="n">
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>224.736</v>
+        <v>210.411</v>
       </c>
       <c r="I149" t="n">
-        <v>1.458</v>
+        <v>1.09</v>
       </c>
       <c r="J149" t="n">
-        <v>12.392</v>
+        <v>23.432</v>
       </c>
       <c r="K149" t="n">
-        <v>0.159</v>
+        <v>0.229</v>
       </c>
       <c r="L149" t="n">
-        <v>0.652</v>
+        <v>0.672</v>
       </c>
       <c r="M149" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N149" t="n">
-        <v>131.615</v>
+        <v>117.287</v>
       </c>
       <c r="O149" t="n">
-        <v>317.855</v>
+        <v>303.534</v>
       </c>
       <c r="P149" t="n">
-        <v>0.505</v>
+        <v>0.377</v>
       </c>
       <c r="Q149" t="n">
-        <v>2.862</v>
+        <v>2.495</v>
       </c>
       <c r="R149" t="n">
-        <v>4.289</v>
+        <v>8.111000000000001</v>
       </c>
       <c r="S149" t="n">
-        <v>33.282</v>
+        <v>44.322</v>
       </c>
       <c r="T149" t="n">
-        <v>0.055</v>
+        <v>0.079</v>
       </c>
       <c r="U149" t="n">
-        <v>0.677</v>
+        <v>0.748</v>
       </c>
       <c r="V149" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="W149" t="n">
-        <v>1.788</v>
+        <v>1.808</v>
       </c>
       <c r="X149" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y149" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z149" t="n">
-        <v>15.248</v>
+        <v>14.682</v>
       </c>
       <c r="AA149" t="n">
-        <v>2.815</v>
+        <v>2.211</v>
       </c>
       <c r="AB149" t="n">
-        <v>30.942</v>
+        <v>30.412</v>
       </c>
       <c r="AC149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F150" t="n">
         <v>-1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>215.404</v>
+        <v>214.688</v>
       </c>
       <c r="I150" t="n">
-        <v>1.284</v>
+        <v>1.179</v>
       </c>
       <c r="J150" t="n">
-        <v>12.681</v>
+        <v>22.601</v>
       </c>
       <c r="K150" t="n">
-        <v>0.138</v>
+        <v>0.222</v>
       </c>
       <c r="L150" t="n">
-        <v>0.652</v>
+        <v>0.673</v>
       </c>
       <c r="M150" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N150" t="n">
-        <v>122.285</v>
+        <v>121.566</v>
       </c>
       <c r="O150" t="n">
-        <v>308.525</v>
+        <v>307.806</v>
       </c>
       <c r="P150" t="n">
-        <v>0.444</v>
+        <v>0.408</v>
       </c>
       <c r="Q150" t="n">
-        <v>2.688</v>
+        <v>2.583</v>
       </c>
       <c r="R150" t="n">
-        <v>4.389</v>
+        <v>7.823</v>
       </c>
       <c r="S150" t="n">
-        <v>33.571</v>
+        <v>43.491</v>
       </c>
       <c r="T150" t="n">
-        <v>0.048</v>
+        <v>0.077</v>
       </c>
       <c r="U150" t="n">
-        <v>0.657</v>
+        <v>0.74</v>
       </c>
       <c r="V150" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="W150" t="n">
-        <v>1.788</v>
+        <v>1.808</v>
       </c>
       <c r="X150" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y150" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z150" t="n">
-        <v>14.085</v>
+        <v>15.079</v>
       </c>
       <c r="AA150" t="n">
-        <v>2.17</v>
+        <v>2.461</v>
       </c>
       <c r="AB150" t="n">
-        <v>29.781</v>
+        <v>30.806</v>
       </c>
       <c r="AC150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F151" t="n">
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>237.352</v>
+        <v>213.768</v>
       </c>
       <c r="I151" t="n">
-        <v>1.45</v>
+        <v>1.076</v>
       </c>
       <c r="J151" t="n">
-        <v>12.358</v>
+        <v>23.398</v>
       </c>
       <c r="K151" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="L151" t="n">
-        <v>0.653</v>
+        <v>0.672</v>
       </c>
       <c r="M151" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N151" t="n">
-        <v>144.234</v>
+        <v>120.646</v>
       </c>
       <c r="O151" t="n">
-        <v>330.474</v>
+        <v>306.886</v>
       </c>
       <c r="P151" t="n">
-        <v>0.502</v>
+        <v>0.372</v>
       </c>
       <c r="Q151" t="n">
-        <v>2.854</v>
+        <v>2.48</v>
       </c>
       <c r="R151" t="n">
-        <v>4.278</v>
+        <v>8.099</v>
       </c>
       <c r="S151" t="n">
-        <v>33.25</v>
+        <v>44.29</v>
       </c>
       <c r="T151" t="n">
-        <v>0.056</v>
+        <v>0.083</v>
       </c>
       <c r="U151" t="n">
-        <v>0.679</v>
+        <v>0.759</v>
       </c>
       <c r="V151" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="W151" t="n">
-        <v>1.788</v>
+        <v>1.807</v>
       </c>
       <c r="X151" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y151" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z151" t="n">
-        <v>15.728</v>
+        <v>14.824</v>
       </c>
       <c r="AA151" t="n">
-        <v>3.311</v>
+        <v>2.35</v>
       </c>
       <c r="AB151" t="n">
-        <v>31.423</v>
+        <v>30.551</v>
       </c>
       <c r="AC151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>229.127</v>
+        <v>206.883</v>
       </c>
       <c r="I152" t="n">
-        <v>1.298</v>
+        <v>0.991</v>
       </c>
       <c r="J152" t="n">
-        <v>12.36</v>
+        <v>22.791</v>
       </c>
       <c r="K152" t="n">
-        <v>0.161</v>
+        <v>0.215</v>
       </c>
       <c r="L152" t="n">
-        <v>0.652</v>
+        <v>0.672</v>
       </c>
       <c r="M152" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N152" t="n">
-        <v>136.005</v>
+        <v>113.764</v>
       </c>
       <c r="O152" t="n">
-        <v>322.246</v>
+        <v>300.005</v>
       </c>
       <c r="P152" t="n">
-        <v>0.449</v>
+        <v>0.343</v>
       </c>
       <c r="Q152" t="n">
-        <v>2.702</v>
+        <v>2.395</v>
       </c>
       <c r="R152" t="n">
-        <v>4.278</v>
+        <v>7.889</v>
       </c>
       <c r="S152" t="n">
-        <v>33.251</v>
+        <v>43.681</v>
       </c>
       <c r="T152" t="n">
-        <v>0.056</v>
+        <v>0.074</v>
       </c>
       <c r="U152" t="n">
-        <v>0.68</v>
+        <v>0.733</v>
       </c>
       <c r="V152" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="W152" t="n">
-        <v>1.788</v>
+        <v>1.808</v>
       </c>
       <c r="X152" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y152" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z152" t="n">
-        <v>14.796</v>
+        <v>13.994</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.773</v>
+        <v>1.881</v>
       </c>
       <c r="AB152" t="n">
-        <v>30.492</v>
+        <v>29.719</v>
       </c>
       <c r="AC152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -23877,89 +23877,89 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F153" t="n">
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>236.226</v>
+        <v>197.426</v>
       </c>
       <c r="I153" t="n">
-        <v>1.423</v>
+        <v>1.031</v>
       </c>
       <c r="J153" t="n">
-        <v>12.356</v>
+        <v>23.527</v>
       </c>
       <c r="K153" t="n">
-        <v>0.159</v>
+        <v>0.235</v>
       </c>
       <c r="L153" t="n">
-        <v>0.652</v>
+        <v>0.671</v>
       </c>
       <c r="M153" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N153" t="n">
-        <v>143.105</v>
+        <v>104.305</v>
       </c>
       <c r="O153" t="n">
-        <v>329.346</v>
+        <v>290.546</v>
       </c>
       <c r="P153" t="n">
-        <v>0.493</v>
+        <v>0.357</v>
       </c>
       <c r="Q153" t="n">
-        <v>2.828</v>
+        <v>2.435</v>
       </c>
       <c r="R153" t="n">
-        <v>4.277</v>
+        <v>8.144</v>
       </c>
       <c r="S153" t="n">
-        <v>33.25</v>
+        <v>44.42</v>
       </c>
       <c r="T153" t="n">
-        <v>0.055</v>
+        <v>0.081</v>
       </c>
       <c r="U153" t="n">
-        <v>0.678</v>
+        <v>0.753</v>
       </c>
       <c r="V153" t="n">
-        <v>0.226</v>
+        <v>0.232</v>
       </c>
       <c r="W153" t="n">
-        <v>1.787</v>
+        <v>1.807</v>
       </c>
       <c r="X153" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y153" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z153" t="n">
-        <v>15.573</v>
+        <v>13.971</v>
       </c>
       <c r="AA153" t="n">
-        <v>3.229</v>
+        <v>1.627</v>
       </c>
       <c r="AB153" t="n">
-        <v>31.268</v>
+        <v>29.696</v>
       </c>
       <c r="AC153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -23980,79 +23980,79 @@
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>223.43</v>
+        <v>198.715</v>
       </c>
       <c r="I154" t="n">
-        <v>1.396</v>
+        <v>0.988</v>
       </c>
       <c r="J154" t="n">
-        <v>12.54</v>
+        <v>22.507</v>
       </c>
       <c r="K154" t="n">
-        <v>0.157</v>
+        <v>0.187</v>
       </c>
       <c r="L154" t="n">
-        <v>0.652</v>
+        <v>0.672</v>
       </c>
       <c r="M154" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N154" t="n">
-        <v>130.307</v>
+        <v>105.595</v>
       </c>
       <c r="O154" t="n">
-        <v>316.554</v>
+        <v>291.835</v>
       </c>
       <c r="P154" t="n">
-        <v>0.483</v>
+        <v>0.342</v>
       </c>
       <c r="Q154" t="n">
-        <v>2.801</v>
+        <v>2.392</v>
       </c>
       <c r="R154" t="n">
-        <v>4.341</v>
+        <v>7.791</v>
       </c>
       <c r="S154" t="n">
-        <v>33.431</v>
+        <v>43.4</v>
       </c>
       <c r="T154" t="n">
-        <v>0.054</v>
+        <v>0.065</v>
       </c>
       <c r="U154" t="n">
-        <v>0.675</v>
+        <v>0.706</v>
       </c>
       <c r="V154" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="W154" t="n">
-        <v>1.787</v>
+        <v>1.807</v>
       </c>
       <c r="X154" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y154" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z154" t="n">
-        <v>14.953</v>
+        <v>13.46</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.679</v>
+        <v>1.484</v>
       </c>
       <c r="AB154" t="n">
-        <v>30.646</v>
+        <v>29.189</v>
       </c>
       <c r="AC154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -24063,89 +24063,89 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>228.202</v>
+        <v>217.506</v>
       </c>
       <c r="I155" t="n">
-        <v>1.415</v>
+        <v>1.14</v>
       </c>
       <c r="J155" t="n">
-        <v>12.426</v>
+        <v>22.537</v>
       </c>
       <c r="K155" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="L155" t="n">
-        <v>0.651</v>
+        <v>0.671</v>
       </c>
       <c r="M155" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N155" t="n">
-        <v>135.084</v>
+        <v>124.385</v>
       </c>
       <c r="O155" t="n">
-        <v>321.324</v>
+        <v>310.626</v>
       </c>
       <c r="P155" t="n">
-        <v>0.49</v>
+        <v>0.395</v>
       </c>
       <c r="Q155" t="n">
-        <v>2.82</v>
+        <v>2.545</v>
       </c>
       <c r="R155" t="n">
-        <v>4.301</v>
+        <v>7.801</v>
       </c>
       <c r="S155" t="n">
-        <v>33.32</v>
+        <v>43.43</v>
       </c>
       <c r="T155" t="n">
-        <v>0.055</v>
+        <v>0.064</v>
       </c>
       <c r="U155" t="n">
-        <v>0.677</v>
+        <v>0.705</v>
       </c>
       <c r="V155" t="n">
-        <v>0.225</v>
+        <v>0.232</v>
       </c>
       <c r="W155" t="n">
-        <v>1.786</v>
+        <v>1.807</v>
       </c>
       <c r="X155" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y155" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z155" t="n">
-        <v>15.222</v>
+        <v>14.821</v>
       </c>
       <c r="AA155" t="n">
-        <v>2.899</v>
+        <v>2.447</v>
       </c>
       <c r="AB155" t="n">
-        <v>30.917</v>
+        <v>30.55</v>
       </c>
       <c r="AC155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -24156,89 +24156,89 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>225.709</v>
+        <v>210.633</v>
       </c>
       <c r="I156" t="n">
-        <v>1.286</v>
+        <v>1.017</v>
       </c>
       <c r="J156" t="n">
-        <v>12.426</v>
+        <v>23.434</v>
       </c>
       <c r="K156" t="n">
-        <v>0.15</v>
+        <v>0.188</v>
       </c>
       <c r="L156" t="n">
-        <v>0.651</v>
+        <v>0.67</v>
       </c>
       <c r="M156" t="n">
-        <v>0.229</v>
+        <v>0.234</v>
       </c>
       <c r="N156" t="n">
-        <v>132.586</v>
+        <v>117.514</v>
       </c>
       <c r="O156" t="n">
-        <v>318.827</v>
+        <v>303.755</v>
       </c>
       <c r="P156" t="n">
-        <v>0.445</v>
+        <v>0.352</v>
       </c>
       <c r="Q156" t="n">
-        <v>2.69</v>
+        <v>2.421</v>
       </c>
       <c r="R156" t="n">
-        <v>4.301</v>
+        <v>8.111000000000001</v>
       </c>
       <c r="S156" t="n">
-        <v>33.32</v>
+        <v>44.329</v>
       </c>
       <c r="T156" t="n">
-        <v>0.052</v>
+        <v>0.065</v>
       </c>
       <c r="U156" t="n">
-        <v>0.669</v>
+        <v>0.707</v>
       </c>
       <c r="V156" t="n">
-        <v>0.225</v>
+        <v>0.232</v>
       </c>
       <c r="W156" t="n">
-        <v>1.786</v>
+        <v>1.806</v>
       </c>
       <c r="X156" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Y156" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="Z156" t="n">
-        <v>14.557</v>
+        <v>14.156</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.604</v>
+        <v>2.038</v>
       </c>
       <c r="AB156" t="n">
-        <v>30.25</v>
+        <v>29.882</v>
       </c>
       <c r="AC156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -24249,647 +24249,647 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>209.635</v>
+        <v>212.759</v>
       </c>
       <c r="I157" t="n">
-        <v>1.454</v>
+        <v>1.255</v>
       </c>
       <c r="J157" t="n">
-        <v>10.819</v>
+        <v>12.359</v>
       </c>
       <c r="K157" t="n">
-        <v>0.136</v>
+        <v>0.156</v>
       </c>
       <c r="L157" t="n">
-        <v>0.793</v>
+        <v>0.652</v>
       </c>
       <c r="M157" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="N157" t="n">
-        <v>116.515</v>
+        <v>119.636</v>
       </c>
       <c r="O157" t="n">
-        <v>302.755</v>
+        <v>305.877</v>
       </c>
       <c r="P157" t="n">
-        <v>0.503</v>
+        <v>0.434</v>
       </c>
       <c r="Q157" t="n">
-        <v>2.859</v>
+        <v>2.659</v>
       </c>
       <c r="R157" t="n">
-        <v>3.745</v>
+        <v>4.278</v>
       </c>
       <c r="S157" t="n">
-        <v>31.711</v>
+        <v>33.251</v>
       </c>
       <c r="T157" t="n">
-        <v>0.047</v>
+        <v>0.054</v>
       </c>
       <c r="U157" t="n">
-        <v>0.654</v>
+        <v>0.674</v>
       </c>
       <c r="V157" t="n">
-        <v>0.275</v>
+        <v>0.226</v>
       </c>
       <c r="W157" t="n">
-        <v>1.928</v>
+        <v>1.787</v>
       </c>
       <c r="X157" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="Y157" t="n">
-        <v>0.826</v>
+        <v>0.825</v>
       </c>
       <c r="Z157" t="n">
-        <v>14.052</v>
+        <v>13.94</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.821</v>
+        <v>2.05</v>
       </c>
       <c r="AB157" t="n">
-        <v>29.93</v>
+        <v>29.631</v>
       </c>
       <c r="AC157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C158" t="n">
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F158" t="n">
         <v>-1</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>226.216</v>
+        <v>235.478</v>
       </c>
       <c r="I158" t="n">
-        <v>1.429</v>
+        <v>1.436</v>
       </c>
       <c r="J158" t="n">
-        <v>10.904</v>
+        <v>12.613</v>
       </c>
       <c r="K158" t="n">
-        <v>0.133</v>
+        <v>0.155</v>
       </c>
       <c r="L158" t="n">
-        <v>0.793</v>
+        <v>0.652</v>
       </c>
       <c r="M158" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="N158" t="n">
-        <v>133.095</v>
+        <v>142.356</v>
       </c>
       <c r="O158" t="n">
-        <v>319.335</v>
+        <v>328.596</v>
       </c>
       <c r="P158" t="n">
-        <v>0.495</v>
+        <v>0.497</v>
       </c>
       <c r="Q158" t="n">
-        <v>2.833</v>
+        <v>2.841</v>
       </c>
       <c r="R158" t="n">
-        <v>3.774</v>
+        <v>4.366</v>
       </c>
       <c r="S158" t="n">
-        <v>31.799</v>
+        <v>33.509</v>
       </c>
       <c r="T158" t="n">
-        <v>0.046</v>
+        <v>0.054</v>
       </c>
       <c r="U158" t="n">
-        <v>0.652</v>
+        <v>0.674</v>
       </c>
       <c r="V158" t="n">
-        <v>0.275</v>
+        <v>0.226</v>
       </c>
       <c r="W158" t="n">
-        <v>1.928</v>
+        <v>1.787</v>
       </c>
       <c r="X158" t="n">
         <v>0.079</v>
       </c>
       <c r="Y158" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="Z158" t="n">
-        <v>14.611</v>
+        <v>15.595</v>
       </c>
       <c r="AA158" t="n">
-        <v>2.452</v>
+        <v>3.217</v>
       </c>
       <c r="AB158" t="n">
-        <v>30.489</v>
+        <v>31.289</v>
       </c>
       <c r="AC158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C159" t="n">
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>232.49</v>
+        <v>224.682</v>
       </c>
       <c r="I159" t="n">
-        <v>1.567</v>
+        <v>1.265</v>
       </c>
       <c r="J159" t="n">
-        <v>11.736</v>
+        <v>12.698</v>
       </c>
       <c r="K159" t="n">
-        <v>0.134</v>
+        <v>0.138</v>
       </c>
       <c r="L159" t="n">
-        <v>0.793</v>
+        <v>0.652</v>
       </c>
       <c r="M159" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="N159" t="n">
-        <v>139.367</v>
+        <v>131.564</v>
       </c>
       <c r="O159" t="n">
-        <v>325.614</v>
+        <v>317.804</v>
       </c>
       <c r="P159" t="n">
-        <v>0.543</v>
+        <v>0.438</v>
       </c>
       <c r="Q159" t="n">
-        <v>2.972</v>
+        <v>2.669</v>
       </c>
       <c r="R159" t="n">
-        <v>4.062</v>
+        <v>4.395</v>
       </c>
       <c r="S159" t="n">
-        <v>32.63</v>
+        <v>33.59</v>
       </c>
       <c r="T159" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="U159" t="n">
-        <v>0.652</v>
+        <v>0.656</v>
       </c>
       <c r="V159" t="n">
-        <v>0.275</v>
+        <v>0.226</v>
       </c>
       <c r="W159" t="n">
-        <v>1.929</v>
+        <v>1.787</v>
       </c>
       <c r="X159" t="n">
         <v>0.079</v>
       </c>
       <c r="Y159" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="Z159" t="n">
-        <v>15.503</v>
+        <v>14.38</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.924</v>
+        <v>2.516</v>
       </c>
       <c r="AB159" t="n">
-        <v>31.38</v>
+        <v>30.073</v>
       </c>
       <c r="AC159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F160" t="n">
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160" t="n">
-        <v>220.68</v>
+        <v>224.736</v>
       </c>
       <c r="I160" t="n">
-        <v>1.452</v>
+        <v>1.458</v>
       </c>
       <c r="J160" t="n">
-        <v>11.721</v>
+        <v>12.392</v>
       </c>
       <c r="K160" t="n">
-        <v>0.13</v>
+        <v>0.159</v>
       </c>
       <c r="L160" t="n">
-        <v>0.794</v>
+        <v>0.652</v>
       </c>
       <c r="M160" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="N160" t="n">
-        <v>127.556</v>
+        <v>131.615</v>
       </c>
       <c r="O160" t="n">
-        <v>313.803</v>
+        <v>317.855</v>
       </c>
       <c r="P160" t="n">
-        <v>0.503</v>
+        <v>0.505</v>
       </c>
       <c r="Q160" t="n">
-        <v>2.856</v>
+        <v>2.862</v>
       </c>
       <c r="R160" t="n">
-        <v>4.057</v>
+        <v>4.289</v>
       </c>
       <c r="S160" t="n">
-        <v>32.611</v>
+        <v>33.282</v>
       </c>
       <c r="T160" t="n">
-        <v>0.045</v>
+        <v>0.055</v>
       </c>
       <c r="U160" t="n">
-        <v>0.649</v>
+        <v>0.677</v>
       </c>
       <c r="V160" t="n">
-        <v>0.275</v>
+        <v>0.226</v>
       </c>
       <c r="W160" t="n">
-        <v>1.929</v>
+        <v>1.788</v>
       </c>
       <c r="X160" t="n">
         <v>0.079</v>
       </c>
       <c r="Y160" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="Z160" t="n">
-        <v>14.546</v>
+        <v>15.248</v>
       </c>
       <c r="AA160" t="n">
-        <v>2.283</v>
+        <v>2.815</v>
       </c>
       <c r="AB160" t="n">
-        <v>30.424</v>
+        <v>30.942</v>
       </c>
       <c r="AC160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F161" t="n">
         <v>-1</v>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>224.957</v>
+        <v>215.404</v>
       </c>
       <c r="I161" t="n">
-        <v>1.548</v>
+        <v>1.284</v>
       </c>
       <c r="J161" t="n">
-        <v>10.889</v>
+        <v>12.681</v>
       </c>
       <c r="K161" t="n">
-        <v>0.134</v>
+        <v>0.138</v>
       </c>
       <c r="L161" t="n">
-        <v>0.794</v>
+        <v>0.652</v>
       </c>
       <c r="M161" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="N161" t="n">
-        <v>131.835</v>
+        <v>122.285</v>
       </c>
       <c r="O161" t="n">
-        <v>318.076</v>
+        <v>308.525</v>
       </c>
       <c r="P161" t="n">
-        <v>0.536</v>
+        <v>0.444</v>
       </c>
       <c r="Q161" t="n">
-        <v>2.953</v>
+        <v>2.688</v>
       </c>
       <c r="R161" t="n">
-        <v>3.769</v>
+        <v>4.389</v>
       </c>
       <c r="S161" t="n">
-        <v>31.781</v>
+        <v>33.571</v>
       </c>
       <c r="T161" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="U161" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="V161" t="n">
-        <v>0.275</v>
+        <v>0.226</v>
       </c>
       <c r="W161" t="n">
-        <v>1.929</v>
+        <v>1.788</v>
       </c>
       <c r="X161" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="Y161" t="n">
-        <v>0.826</v>
+        <v>0.825</v>
       </c>
       <c r="Z161" t="n">
-        <v>15.035</v>
+        <v>14.085</v>
       </c>
       <c r="AA161" t="n">
-        <v>2.561</v>
+        <v>2.17</v>
       </c>
       <c r="AB161" t="n">
-        <v>30.916</v>
+        <v>29.781</v>
       </c>
       <c r="AC161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C162" t="n">
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>224.037</v>
+        <v>237.352</v>
       </c>
       <c r="I162" t="n">
-        <v>1.441</v>
+        <v>1.45</v>
       </c>
       <c r="J162" t="n">
-        <v>11.686</v>
+        <v>12.358</v>
       </c>
       <c r="K162" t="n">
-        <v>0.131</v>
+        <v>0.16</v>
       </c>
       <c r="L162" t="n">
-        <v>0.793</v>
+        <v>0.653</v>
       </c>
       <c r="M162" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="N162" t="n">
-        <v>130.916</v>
+        <v>144.234</v>
       </c>
       <c r="O162" t="n">
-        <v>317.156</v>
+        <v>330.474</v>
       </c>
       <c r="P162" t="n">
-        <v>0.499</v>
+        <v>0.502</v>
       </c>
       <c r="Q162" t="n">
-        <v>2.845</v>
+        <v>2.854</v>
       </c>
       <c r="R162" t="n">
-        <v>4.045</v>
+        <v>4.278</v>
       </c>
       <c r="S162" t="n">
-        <v>32.58</v>
+        <v>33.25</v>
       </c>
       <c r="T162" t="n">
-        <v>0.045</v>
+        <v>0.056</v>
       </c>
       <c r="U162" t="n">
-        <v>0.649</v>
+        <v>0.679</v>
       </c>
       <c r="V162" t="n">
-        <v>0.275</v>
+        <v>0.226</v>
       </c>
       <c r="W162" t="n">
-        <v>1.929</v>
+        <v>1.788</v>
       </c>
       <c r="X162" t="n">
         <v>0.079</v>
       </c>
       <c r="Y162" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="Z162" t="n">
-        <v>14.635</v>
+        <v>15.728</v>
       </c>
       <c r="AA162" t="n">
-        <v>2.402</v>
+        <v>3.311</v>
       </c>
       <c r="AB162" t="n">
-        <v>30.511</v>
+        <v>31.423</v>
       </c>
       <c r="AC162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C163" t="n">
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>217.152</v>
+        <v>229.127</v>
       </c>
       <c r="I163" t="n">
-        <v>1.356</v>
+        <v>1.298</v>
       </c>
       <c r="J163" t="n">
-        <v>11.08</v>
+        <v>12.36</v>
       </c>
       <c r="K163" t="n">
-        <v>0.129</v>
+        <v>0.161</v>
       </c>
       <c r="L163" t="n">
-        <v>0.794</v>
+        <v>0.652</v>
       </c>
       <c r="M163" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="N163" t="n">
-        <v>124.034</v>
+        <v>136.005</v>
       </c>
       <c r="O163" t="n">
-        <v>310.274</v>
+        <v>322.246</v>
       </c>
       <c r="P163" t="n">
-        <v>0.469</v>
+        <v>0.449</v>
       </c>
       <c r="Q163" t="n">
-        <v>2.761</v>
+        <v>2.702</v>
       </c>
       <c r="R163" t="n">
-        <v>3.835</v>
+        <v>4.278</v>
       </c>
       <c r="S163" t="n">
-        <v>31.971</v>
+        <v>33.251</v>
       </c>
       <c r="T163" t="n">
-        <v>0.045</v>
+        <v>0.056</v>
       </c>
       <c r="U163" t="n">
-        <v>0.648</v>
+        <v>0.68</v>
       </c>
       <c r="V163" t="n">
-        <v>0.275</v>
+        <v>0.226</v>
       </c>
       <c r="W163" t="n">
-        <v>1.929</v>
+        <v>1.788</v>
       </c>
       <c r="X163" t="n">
         <v>0.079</v>
       </c>
       <c r="Y163" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="Z163" t="n">
-        <v>13.951</v>
+        <v>14.796</v>
       </c>
       <c r="AA163" t="n">
-        <v>1.986</v>
+        <v>2.773</v>
       </c>
       <c r="AB163" t="n">
-        <v>29.831</v>
+        <v>30.492</v>
       </c>
       <c r="AC163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -24900,89 +24900,89 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" t="n">
-        <v>207.696</v>
+        <v>236.226</v>
       </c>
       <c r="I164" t="n">
-        <v>1.381</v>
+        <v>1.423</v>
       </c>
       <c r="J164" t="n">
-        <v>11.816</v>
+        <v>12.356</v>
       </c>
       <c r="K164" t="n">
-        <v>0.137</v>
+        <v>0.159</v>
       </c>
       <c r="L164" t="n">
-        <v>0.793</v>
+        <v>0.652</v>
       </c>
       <c r="M164" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="N164" t="n">
-        <v>114.575</v>
+        <v>143.105</v>
       </c>
       <c r="O164" t="n">
-        <v>300.815</v>
+        <v>329.346</v>
       </c>
       <c r="P164" t="n">
-        <v>0.478</v>
+        <v>0.493</v>
       </c>
       <c r="Q164" t="n">
-        <v>2.786</v>
+        <v>2.828</v>
       </c>
       <c r="R164" t="n">
-        <v>4.09</v>
+        <v>4.277</v>
       </c>
       <c r="S164" t="n">
-        <v>32.709</v>
+        <v>33.25</v>
       </c>
       <c r="T164" t="n">
-        <v>0.047</v>
+        <v>0.055</v>
       </c>
       <c r="U164" t="n">
-        <v>0.655</v>
+        <v>0.678</v>
       </c>
       <c r="V164" t="n">
-        <v>0.274</v>
+        <v>0.226</v>
       </c>
       <c r="W164" t="n">
-        <v>1.928</v>
+        <v>1.787</v>
       </c>
       <c r="X164" t="n">
         <v>0.079</v>
       </c>
       <c r="Y164" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="Z164" t="n">
-        <v>13.794</v>
+        <v>15.573</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.685</v>
+        <v>3.229</v>
       </c>
       <c r="AB164" t="n">
-        <v>29.668</v>
+        <v>31.268</v>
       </c>
       <c r="AC164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -25003,79 +25003,79 @@
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>208.984</v>
+        <v>223.43</v>
       </c>
       <c r="I165" t="n">
-        <v>1.351</v>
+        <v>1.396</v>
       </c>
       <c r="J165" t="n">
-        <v>10.796</v>
+        <v>12.54</v>
       </c>
       <c r="K165" t="n">
-        <v>0.13</v>
+        <v>0.157</v>
       </c>
       <c r="L165" t="n">
-        <v>0.793</v>
+        <v>0.652</v>
       </c>
       <c r="M165" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="N165" t="n">
-        <v>115.865</v>
+        <v>130.307</v>
       </c>
       <c r="O165" t="n">
-        <v>302.105</v>
+        <v>316.554</v>
       </c>
       <c r="P165" t="n">
-        <v>0.468</v>
+        <v>0.483</v>
       </c>
       <c r="Q165" t="n">
-        <v>2.756</v>
+        <v>2.801</v>
       </c>
       <c r="R165" t="n">
-        <v>3.737</v>
+        <v>4.341</v>
       </c>
       <c r="S165" t="n">
-        <v>31.69</v>
+        <v>33.431</v>
       </c>
       <c r="T165" t="n">
-        <v>0.045</v>
+        <v>0.054</v>
       </c>
       <c r="U165" t="n">
-        <v>0.648</v>
+        <v>0.675</v>
       </c>
       <c r="V165" t="n">
-        <v>0.275</v>
+        <v>0.226</v>
       </c>
       <c r="W165" t="n">
-        <v>1.929</v>
+        <v>1.787</v>
       </c>
       <c r="X165" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="Y165" t="n">
-        <v>0.826</v>
+        <v>0.825</v>
       </c>
       <c r="Z165" t="n">
-        <v>13.577</v>
+        <v>14.953</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.639</v>
+        <v>2.679</v>
       </c>
       <c r="AB165" t="n">
-        <v>29.457</v>
+        <v>30.646</v>
       </c>
       <c r="AC165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -25086,89 +25086,89 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
         <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>227.775</v>
+        <v>228.202</v>
       </c>
       <c r="I166" t="n">
-        <v>1.488</v>
+        <v>1.415</v>
       </c>
       <c r="J166" t="n">
-        <v>10.826</v>
+        <v>12.426</v>
       </c>
       <c r="K166" t="n">
-        <v>0.132</v>
+        <v>0.158</v>
       </c>
       <c r="L166" t="n">
-        <v>0.793</v>
+        <v>0.651</v>
       </c>
       <c r="M166" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="N166" t="n">
-        <v>134.655</v>
+        <v>135.084</v>
       </c>
       <c r="O166" t="n">
-        <v>320.895</v>
+        <v>321.324</v>
       </c>
       <c r="P166" t="n">
-        <v>0.515</v>
+        <v>0.49</v>
       </c>
       <c r="Q166" t="n">
-        <v>2.892</v>
+        <v>2.82</v>
       </c>
       <c r="R166" t="n">
-        <v>3.747</v>
+        <v>4.301</v>
       </c>
       <c r="S166" t="n">
-        <v>31.719</v>
+        <v>33.32</v>
       </c>
       <c r="T166" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
       <c r="U166" t="n">
-        <v>0.65</v>
+        <v>0.677</v>
       </c>
       <c r="V166" t="n">
-        <v>0.274</v>
+        <v>0.225</v>
       </c>
       <c r="W166" t="n">
-        <v>1.928</v>
+        <v>1.786</v>
       </c>
       <c r="X166" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="Y166" t="n">
-        <v>0.826</v>
+        <v>0.825</v>
       </c>
       <c r="Z166" t="n">
-        <v>14.89</v>
+        <v>15.222</v>
       </c>
       <c r="AA166" t="n">
-        <v>2.586</v>
+        <v>2.899</v>
       </c>
       <c r="AB166" t="n">
-        <v>30.768</v>
+        <v>30.917</v>
       </c>
       <c r="AC166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -25179,77 +25179,77 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>220.903</v>
+        <v>225.709</v>
       </c>
       <c r="I167" t="n">
-        <v>1.364</v>
+        <v>1.286</v>
       </c>
       <c r="J167" t="n">
-        <v>11.722</v>
+        <v>12.426</v>
       </c>
       <c r="K167" t="n">
-        <v>0.131</v>
+        <v>0.15</v>
       </c>
       <c r="L167" t="n">
-        <v>0.792</v>
+        <v>0.651</v>
       </c>
       <c r="M167" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="N167" t="n">
-        <v>127.784</v>
+        <v>132.586</v>
       </c>
       <c r="O167" t="n">
-        <v>314.024</v>
+        <v>318.827</v>
       </c>
       <c r="P167" t="n">
-        <v>0.472</v>
+        <v>0.445</v>
       </c>
       <c r="Q167" t="n">
-        <v>2.769</v>
+        <v>2.69</v>
       </c>
       <c r="R167" t="n">
-        <v>4.058</v>
+        <v>4.301</v>
       </c>
       <c r="S167" t="n">
-        <v>32.612</v>
+        <v>33.32</v>
       </c>
       <c r="T167" t="n">
-        <v>0.045</v>
+        <v>0.052</v>
       </c>
       <c r="U167" t="n">
-        <v>0.65</v>
+        <v>0.669</v>
       </c>
       <c r="V167" t="n">
-        <v>0.274</v>
+        <v>0.225</v>
       </c>
       <c r="W167" t="n">
-        <v>1.927</v>
+        <v>1.786</v>
       </c>
       <c r="X167" t="n">
         <v>0.079</v>
       </c>
       <c r="Y167" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="Z167" t="n">
-        <v>14.213</v>
+        <v>14.557</v>
       </c>
       <c r="AA167" t="n">
-        <v>2.177</v>
+        <v>2.604</v>
       </c>
       <c r="AB167" t="n">
-        <v>30.091</v>
+        <v>30.25</v>
       </c>
       <c r="AC167" t="inlineStr"/>
     </row>
@@ -52412,12 +52412,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -52428,14 +52428,14 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F460" t="n">
         <v>-1</v>
       </c>
       <c r="G460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -52505,27 +52505,27 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C461" t="n">
         <v>2</v>
       </c>
       <c r="D461" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F461" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G461" t="n">
         <v>0</v>
@@ -52598,27 +52598,27 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C462" t="n">
         <v>2</v>
       </c>
       <c r="D462" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F462" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G462" t="n">
         <v>0</v>
@@ -52691,12 +52691,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -52707,14 +52707,14 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F463" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -52784,12 +52784,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -52800,14 +52800,14 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="F464" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -52877,12 +52877,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -52893,7 +52893,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="F465" t="n">
@@ -52970,12 +52970,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -52986,7 +52986,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F466" t="n">
@@ -53063,12 +53063,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -53079,7 +53079,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F467" t="n">
@@ -53156,12 +53156,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -53172,7 +53172,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F468" t="n">
@@ -53249,12 +53249,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -53265,14 +53265,14 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="F469" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -53342,12 +53342,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -53358,14 +53358,14 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F470" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -53435,12 +53435,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -53451,14 +53451,14 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F471" t="n">
         <v>-1</v>
       </c>
       <c r="G471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -53528,27 +53528,27 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C472" t="n">
         <v>2</v>
       </c>
       <c r="D472" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G472" t="n">
         <v>0</v>
@@ -53621,27 +53621,27 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C473" t="n">
         <v>2</v>
       </c>
       <c r="D473" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G473" t="n">
         <v>0</v>
@@ -53714,12 +53714,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -53730,14 +53730,14 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G474" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -53807,12 +53807,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -53823,14 +53823,14 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -53900,12 +53900,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -53916,7 +53916,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -53993,12 +53993,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -54009,7 +54009,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -54086,12 +54086,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -54102,7 +54102,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -54179,12 +54179,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -54195,7 +54195,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -54272,12 +54272,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -54288,14 +54288,14 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -54365,12 +54365,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -54381,14 +54381,14 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G481" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>

--- a/projections/qb_2026_combined.xlsx
+++ b/projections/qb_2026_combined.xlsx
@@ -610,70 +610,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lamar Jackson</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3882.6</v>
+        <v>4374.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2505.6</v>
+        <v>3081.6</v>
       </c>
       <c r="F3" t="n">
-        <v>30.89</v>
+        <v>33.34</v>
       </c>
       <c r="G3" t="n">
-        <v>19.84</v>
+        <v>23.39</v>
       </c>
       <c r="H3" t="n">
-        <v>765</v>
+        <v>171.3</v>
       </c>
       <c r="I3" t="n">
-        <v>496.4</v>
+        <v>121.9</v>
       </c>
       <c r="J3" t="n">
-        <v>4.33</v>
+        <v>2.24</v>
       </c>
       <c r="K3" t="n">
-        <v>2.83</v>
+        <v>1.59</v>
       </c>
       <c r="L3" t="n">
-        <v>9.25</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>5.98</v>
+        <v>6.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="P3" t="n">
-        <v>357.3</v>
+        <v>314.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>230.66</v>
+        <v>221.37</v>
       </c>
       <c r="R3" t="n">
-        <v>171.76</v>
+        <v>158.51</v>
       </c>
       <c r="S3" t="n">
-        <v>289.5</v>
+        <v>285.47</v>
       </c>
       <c r="T3" t="n">
-        <v>217.28</v>
+        <v>234.35</v>
       </c>
       <c r="U3" t="n">
-        <v>13.38</v>
+        <v>-12.98</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -681,70 +681,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4374.8</v>
+        <v>3715.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3081.6</v>
+        <v>2387.3</v>
       </c>
       <c r="F4" t="n">
-        <v>33.34</v>
+        <v>24.38</v>
       </c>
       <c r="G4" t="n">
-        <v>23.39</v>
+        <v>15.65</v>
       </c>
       <c r="H4" t="n">
-        <v>171.3</v>
+        <v>779.2</v>
       </c>
       <c r="I4" t="n">
-        <v>121.9</v>
+        <v>505.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.24</v>
+        <v>6.46</v>
       </c>
       <c r="K4" t="n">
-        <v>1.59</v>
+        <v>4.17</v>
       </c>
       <c r="L4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="M4" t="n">
-        <v>6.72</v>
+        <v>6.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>3.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="P4" t="n">
-        <v>314.56</v>
+        <v>337.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>221.37</v>
+        <v>217.16</v>
       </c>
       <c r="R4" t="n">
-        <v>158.51</v>
+        <v>158.29</v>
       </c>
       <c r="S4" t="n">
-        <v>285.47</v>
+        <v>275.7</v>
       </c>
       <c r="T4" t="n">
-        <v>234.35</v>
+        <v>213.59</v>
       </c>
       <c r="U4" t="n">
-        <v>-12.98</v>
+        <v>3.57</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -752,70 +752,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3715.7</v>
+        <v>4139.3</v>
       </c>
       <c r="E5" t="n">
-        <v>2387.3</v>
+        <v>2666.4</v>
       </c>
       <c r="F5" t="n">
-        <v>24.38</v>
+        <v>34.45</v>
       </c>
       <c r="G5" t="n">
-        <v>15.65</v>
+        <v>22.1</v>
       </c>
       <c r="H5" t="n">
-        <v>779.2</v>
+        <v>349.1</v>
       </c>
       <c r="I5" t="n">
-        <v>505.3</v>
+        <v>225.8</v>
       </c>
       <c r="J5" t="n">
-        <v>6.46</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>4.17</v>
+        <v>2.3</v>
       </c>
       <c r="L5" t="n">
-        <v>9.41</v>
+        <v>8.09</v>
       </c>
       <c r="M5" t="n">
-        <v>6.09</v>
+        <v>5.23</v>
       </c>
       <c r="N5" t="n">
-        <v>3.33</v>
+        <v>3.03</v>
       </c>
       <c r="O5" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="P5" t="n">
-        <v>337.35</v>
+        <v>337.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>217.16</v>
+        <v>217.06</v>
       </c>
       <c r="R5" t="n">
-        <v>158.29</v>
+        <v>158.44</v>
       </c>
       <c r="S5" t="n">
-        <v>275.7</v>
+        <v>275.8</v>
       </c>
       <c r="T5" t="n">
-        <v>213.59</v>
+        <v>206.74</v>
       </c>
       <c r="U5" t="n">
-        <v>3.57</v>
+        <v>10.32</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -823,70 +823,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4139.3</v>
+        <v>4239.1</v>
       </c>
       <c r="E6" t="n">
-        <v>2666.4</v>
+        <v>2991.3</v>
       </c>
       <c r="F6" t="n">
-        <v>34.45</v>
+        <v>28.62</v>
       </c>
       <c r="G6" t="n">
-        <v>22.1</v>
+        <v>19.99</v>
       </c>
       <c r="H6" t="n">
-        <v>349.1</v>
+        <v>270.4</v>
       </c>
       <c r="I6" t="n">
-        <v>225.8</v>
+        <v>191.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="L6" t="n">
-        <v>8.09</v>
+        <v>10.11</v>
       </c>
       <c r="M6" t="n">
-        <v>5.23</v>
+        <v>7.13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.03</v>
+        <v>3.13</v>
       </c>
       <c r="O6" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="P6" t="n">
-        <v>337.34</v>
+        <v>302.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>217.06</v>
+        <v>212.87</v>
       </c>
       <c r="R6" t="n">
-        <v>158.44</v>
+        <v>148.95</v>
       </c>
       <c r="S6" t="n">
-        <v>275.8</v>
+        <v>276.85</v>
       </c>
       <c r="T6" t="n">
-        <v>206.74</v>
+        <v>215.65</v>
       </c>
       <c r="U6" t="n">
-        <v>10.32</v>
+        <v>-2.78</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -894,70 +894,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Lamar Jackson</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4239.1</v>
+        <v>3882.6</v>
       </c>
       <c r="E7" t="n">
-        <v>2991.3</v>
+        <v>2272</v>
       </c>
       <c r="F7" t="n">
-        <v>28.62</v>
+        <v>30.89</v>
       </c>
       <c r="G7" t="n">
-        <v>19.99</v>
+        <v>17.98</v>
       </c>
       <c r="H7" t="n">
-        <v>270.4</v>
+        <v>765</v>
       </c>
       <c r="I7" t="n">
-        <v>191.6</v>
+        <v>451.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="K7" t="n">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="L7" t="n">
-        <v>10.11</v>
+        <v>9.25</v>
       </c>
       <c r="M7" t="n">
-        <v>7.13</v>
+        <v>5.44</v>
       </c>
       <c r="N7" t="n">
-        <v>3.13</v>
+        <v>2.77</v>
       </c>
       <c r="O7" t="n">
-        <v>2.21</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>302.6</v>
+        <v>357.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>212.87</v>
+        <v>209.13</v>
       </c>
       <c r="R7" t="n">
-        <v>148.95</v>
+        <v>155.73</v>
       </c>
       <c r="S7" t="n">
-        <v>276.85</v>
+        <v>262.48</v>
       </c>
       <c r="T7" t="n">
-        <v>215.65</v>
+        <v>217.28</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.78</v>
+        <v>-8.15</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -2878,64 +2878,64 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3472.8</v>
+        <v>3412.4</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>205.9</v>
       </c>
       <c r="F35" t="n">
-        <v>17.17</v>
+        <v>19.7</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H35" t="n">
-        <v>828.6</v>
+        <v>691.2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J35" t="n">
-        <v>7.93</v>
+        <v>4.11</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="L35" t="n">
-        <v>14.18</v>
+        <v>9.33</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="N35" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="P35" t="n">
-        <v>301.37</v>
+        <v>283.42</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>17.06</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>11.59</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
@@ -2945,55 +2945,55 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3181.7</v>
+        <v>3472.8</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>14.38</v>
+        <v>17.17</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>187.6</v>
+        <v>828.6</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>17.39</v>
+        <v>14.18</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.71</v>
+        <v>4.15</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>179.83</v>
+        <v>301.37</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -3004,67 +3004,63 @@
       <c r="S36" t="n">
         <v>0</v>
       </c>
-      <c r="T36" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="U36" t="n">
-        <v>-15.53</v>
-      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3414.1</v>
+        <v>3181.7</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>21.38</v>
+        <v>14.38</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>230.4</v>
+        <v>187.6</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.45</v>
+        <v>17.39</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>230.48</v>
+        <v>179.83</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3075,63 +3071,67 @@
       <c r="S37" t="n">
         <v>0</v>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-15.53</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cole Payton</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3314</v>
+        <v>3414.1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>14.91</v>
+        <v>21.38</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>192</v>
+        <v>230.4</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>17.33</v>
+        <v>10.45</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>187.86</v>
+        <v>230.48</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3150,31 +3150,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Cole Payton</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3071.8</v>
+        <v>3314</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>14.13</v>
+        <v>14.91</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>17.28</v>
+        <v>17.33</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>174.15</v>
+        <v>187.86</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3217,55 +3217,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3584.8</v>
+        <v>3071.8</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>21.04</v>
+        <v>14.13</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>143.6</v>
+        <v>182</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>12.93</v>
+        <v>17.28</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>220.69</v>
+        <v>174.15</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3284,55 +3284,55 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3519.9</v>
+        <v>3584.8</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>19.32</v>
+        <v>21.04</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>255.9</v>
+        <v>143.6</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>11.22</v>
+        <v>12.93</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.58</v>
+        <v>3.38</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>232.09</v>
+        <v>220.69</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3351,55 +3351,55 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3390.1</v>
+        <v>3519.9</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>15.52</v>
+        <v>19.32</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>109.8</v>
+        <v>255.9</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>11.81</v>
+        <v>11.22</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.34</v>
+        <v>2.58</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>189.34</v>
+        <v>232.09</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3418,55 +3418,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3175.9</v>
+        <v>3390.1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>16.14</v>
+        <v>15.52</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>565.9</v>
+        <v>109.8</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>13.89</v>
+        <v>11.81</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>238.41</v>
+        <v>189.34</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3485,55 +3485,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3638.4</v>
+        <v>3175.9</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>24.12</v>
+        <v>16.14</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>186.1</v>
+        <v>565.9</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>13.5</v>
+        <v>13.89</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.91</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>239.25</v>
+        <v>238.41</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3552,55 +3552,55 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>3721.6</v>
+        <v>3638.4</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>19.68</v>
+        <v>24.12</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>322.3</v>
+        <v>186.1</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>12.08</v>
+        <v>13.5</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.11</v>
+        <v>3.91</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>243.41</v>
+        <v>239.25</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3619,55 +3619,55 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3595.5</v>
+        <v>3721.6</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>25.5</v>
+        <v>19.68</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>33.5</v>
+        <v>322.3</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>11.5</v>
+        <v>12.08</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.51</v>
+        <v>3.11</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>229.65</v>
+        <v>243.41</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3686,55 +3686,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3434.9</v>
+        <v>3595.5</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>17.82</v>
+        <v>25.5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>550</v>
+        <v>33.5</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>4.93</v>
+        <v>1.75</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>10.89</v>
+        <v>11.5</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.14</v>
+        <v>3.51</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>265.2</v>
+        <v>229.65</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3753,55 +3753,55 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3265.2</v>
+        <v>3434.9</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>18.3</v>
+        <v>17.82</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>840.5</v>
+        <v>550</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>7.23</v>
+        <v>4.93</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>8.84</v>
+        <v>10.89</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.51</v>
+        <v>3.14</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>306.54</v>
+        <v>265.2</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3820,55 +3820,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3312.3</v>
+        <v>3265.2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>16.07</v>
+        <v>18.3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>189.2</v>
+        <v>840.5</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1.88</v>
+        <v>7.23</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>10.45</v>
+        <v>8.84</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.34</v>
+        <v>3.51</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>199.39</v>
+        <v>306.54</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3887,55 +3887,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3425.4</v>
+        <v>3312.3</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>17.95</v>
+        <v>16.07</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>184.3</v>
+        <v>189.2</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>12.9</v>
+        <v>10.45</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>209.55</v>
+        <v>199.39</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3954,55 +3954,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3260.6</v>
+        <v>3425.4</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>14</v>
+        <v>17.95</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>182.3</v>
+        <v>184.3</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>17.38</v>
+        <v>12.9</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>180.99</v>
+        <v>209.55</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4021,55 +4021,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3638</v>
+        <v>3260.6</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>22.94</v>
+        <v>14</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>176.6</v>
+        <v>182.3</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2.17</v>
+        <v>3.09</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>10.8</v>
+        <v>17.38</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.61</v>
+        <v>3.72</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>241.14</v>
+        <v>180.99</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4088,55 +4088,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>3654.2</v>
+        <v>3638</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>25.16</v>
+        <v>22.94</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>581.6</v>
+        <v>176.6</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>14.88</v>
+        <v>10.8</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>290.17</v>
+        <v>241.14</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4155,55 +4155,55 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3480.2</v>
+        <v>3654.2</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>20.11</v>
+        <v>25.16</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>148.9</v>
+        <v>581.6</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>9.720000000000001</v>
+        <v>14.88</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>219.18</v>
+        <v>290.17</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4222,55 +4222,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3510.9</v>
+        <v>3480.2</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>22.29</v>
+        <v>20.11</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>201.9</v>
+        <v>148.9</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>3.03</v>
+        <v>1.78</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>11.39</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>240.59</v>
+        <v>219.18</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4289,55 +4289,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3364.3</v>
+        <v>3510.9</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>17.34</v>
+        <v>22.29</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>153.2</v>
+        <v>201.9</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>12.87</v>
+        <v>11.39</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.11</v>
+        <v>2.3</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>199.69</v>
+        <v>240.59</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4356,55 +4356,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3387</v>
+        <v>3364.3</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>15.38</v>
+        <v>17.34</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>205</v>
+        <v>153.2</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>17.31</v>
+        <v>12.87</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>194.32</v>
+        <v>199.69</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4423,55 +4423,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3295.2</v>
+        <v>3387</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>16.26</v>
+        <v>15.38</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>293.8</v>
+        <v>205</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>2.69</v>
+        <v>3.16</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>10.12</v>
+        <v>17.31</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.18</v>
+        <v>3.76</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>213.77</v>
+        <v>194.32</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4482,67 +4482,63 @@
       <c r="S58" t="n">
         <v>0</v>
       </c>
-      <c r="T58" t="n">
-        <v>68.14</v>
-      </c>
-      <c r="U58" t="n">
-        <v>-68.14</v>
-      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>3346.9</v>
+        <v>3295.2</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>16.52</v>
+        <v>16.26</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>287.7</v>
+        <v>293.8</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>11.45</v>
+        <v>10.12</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>213.35</v>
+        <v>213.77</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4553,63 +4549,67 @@
       <c r="S59" t="n">
         <v>0</v>
       </c>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
+      <c r="T59" t="n">
+        <v>68.14</v>
+      </c>
+      <c r="U59" t="n">
+        <v>-68.14</v>
+      </c>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3413.8</v>
+        <v>3346.9</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>16.01</v>
+        <v>16.52</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>183.5</v>
+        <v>287.7</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>16.17</v>
+        <v>11.45</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5.63</v>
+        <v>4.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>191.24</v>
+        <v>213.35</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4628,55 +4628,55 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>3282.1</v>
+        <v>3413.8</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>15.74</v>
+        <v>16.01</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>443.2</v>
+        <v>183.5</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>10.57</v>
+        <v>16.17</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.69</v>
+        <v>5.63</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>229.84</v>
+        <v>191.24</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4695,55 +4695,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>3661.3</v>
+        <v>3282.1</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>21.09</v>
+        <v>15.74</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>38.9</v>
+        <v>443.2</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>9.34</v>
+        <v>10.57</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.17</v>
+        <v>3.69</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>219.34</v>
+        <v>229.84</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4754,67 +4754,63 @@
       <c r="S62" t="n">
         <v>0</v>
       </c>
-      <c r="T62" t="n">
-        <v>52.15</v>
-      </c>
-      <c r="U62" t="n">
-        <v>-52.15</v>
-      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>3412.4</v>
+        <v>3661.3</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>19.7</v>
+        <v>21.09</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>691.2</v>
+        <v>38.9</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>4.11</v>
+        <v>1.61</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>9.33</v>
+        <v>9.34</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>283.42</v>
+        <v>219.34</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -4825,8 +4821,12 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
+      <c r="T63" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="U63" t="n">
+        <v>-52.15</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
     </row>
@@ -5169,70 +5169,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lamar Jackson</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3882.6</v>
+        <v>4374.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2505.6</v>
+        <v>3081.6</v>
       </c>
       <c r="F3" t="n">
-        <v>30.89</v>
+        <v>33.34</v>
       </c>
       <c r="G3" t="n">
-        <v>19.84</v>
+        <v>23.39</v>
       </c>
       <c r="H3" t="n">
-        <v>765</v>
+        <v>171.3</v>
       </c>
       <c r="I3" t="n">
-        <v>496.4</v>
+        <v>121.9</v>
       </c>
       <c r="J3" t="n">
-        <v>4.33</v>
+        <v>2.24</v>
       </c>
       <c r="K3" t="n">
-        <v>2.83</v>
+        <v>1.59</v>
       </c>
       <c r="L3" t="n">
-        <v>9.25</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>5.98</v>
+        <v>6.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="P3" t="n">
-        <v>357.3</v>
+        <v>314.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>230.66</v>
+        <v>221.37</v>
       </c>
       <c r="R3" t="n">
-        <v>171.76</v>
+        <v>158.51</v>
       </c>
       <c r="S3" t="n">
-        <v>289.5</v>
+        <v>285.47</v>
       </c>
       <c r="T3" t="n">
-        <v>217.28</v>
+        <v>234.35</v>
       </c>
       <c r="U3" t="n">
-        <v>13.38</v>
+        <v>-12.98</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -5240,70 +5240,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4374.8</v>
+        <v>3715.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3081.6</v>
+        <v>2387.3</v>
       </c>
       <c r="F4" t="n">
-        <v>33.34</v>
+        <v>24.38</v>
       </c>
       <c r="G4" t="n">
-        <v>23.39</v>
+        <v>15.65</v>
       </c>
       <c r="H4" t="n">
-        <v>171.3</v>
+        <v>779.2</v>
       </c>
       <c r="I4" t="n">
-        <v>121.9</v>
+        <v>505.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.24</v>
+        <v>6.46</v>
       </c>
       <c r="K4" t="n">
-        <v>1.59</v>
+        <v>4.17</v>
       </c>
       <c r="L4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="M4" t="n">
-        <v>6.72</v>
+        <v>6.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>3.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="P4" t="n">
-        <v>314.56</v>
+        <v>337.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>221.37</v>
+        <v>217.16</v>
       </c>
       <c r="R4" t="n">
-        <v>158.51</v>
+        <v>158.29</v>
       </c>
       <c r="S4" t="n">
-        <v>285.47</v>
+        <v>275.7</v>
       </c>
       <c r="T4" t="n">
-        <v>234.35</v>
+        <v>213.59</v>
       </c>
       <c r="U4" t="n">
-        <v>-12.98</v>
+        <v>3.57</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -5311,70 +5311,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3715.7</v>
+        <v>4139.3</v>
       </c>
       <c r="E5" t="n">
-        <v>2387.3</v>
+        <v>2666.4</v>
       </c>
       <c r="F5" t="n">
-        <v>24.38</v>
+        <v>34.45</v>
       </c>
       <c r="G5" t="n">
-        <v>15.65</v>
+        <v>22.1</v>
       </c>
       <c r="H5" t="n">
-        <v>779.2</v>
+        <v>349.1</v>
       </c>
       <c r="I5" t="n">
-        <v>505.3</v>
+        <v>225.8</v>
       </c>
       <c r="J5" t="n">
-        <v>6.46</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>4.17</v>
+        <v>2.3</v>
       </c>
       <c r="L5" t="n">
-        <v>9.41</v>
+        <v>8.09</v>
       </c>
       <c r="M5" t="n">
-        <v>6.09</v>
+        <v>5.23</v>
       </c>
       <c r="N5" t="n">
-        <v>3.33</v>
+        <v>3.03</v>
       </c>
       <c r="O5" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="P5" t="n">
-        <v>337.35</v>
+        <v>337.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>217.16</v>
+        <v>217.06</v>
       </c>
       <c r="R5" t="n">
-        <v>158.29</v>
+        <v>158.44</v>
       </c>
       <c r="S5" t="n">
-        <v>275.7</v>
+        <v>275.8</v>
       </c>
       <c r="T5" t="n">
-        <v>213.59</v>
+        <v>206.74</v>
       </c>
       <c r="U5" t="n">
-        <v>3.57</v>
+        <v>10.32</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -5382,70 +5382,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4139.3</v>
+        <v>4239.1</v>
       </c>
       <c r="E6" t="n">
-        <v>2666.4</v>
+        <v>2991.3</v>
       </c>
       <c r="F6" t="n">
-        <v>34.45</v>
+        <v>28.62</v>
       </c>
       <c r="G6" t="n">
-        <v>22.1</v>
+        <v>19.99</v>
       </c>
       <c r="H6" t="n">
-        <v>349.1</v>
+        <v>270.4</v>
       </c>
       <c r="I6" t="n">
-        <v>225.8</v>
+        <v>191.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="L6" t="n">
-        <v>8.09</v>
+        <v>10.11</v>
       </c>
       <c r="M6" t="n">
-        <v>5.23</v>
+        <v>7.13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.03</v>
+        <v>3.13</v>
       </c>
       <c r="O6" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="P6" t="n">
-        <v>337.34</v>
+        <v>302.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>217.06</v>
+        <v>212.87</v>
       </c>
       <c r="R6" t="n">
-        <v>158.44</v>
+        <v>148.95</v>
       </c>
       <c r="S6" t="n">
-        <v>275.8</v>
+        <v>276.85</v>
       </c>
       <c r="T6" t="n">
-        <v>206.74</v>
+        <v>215.65</v>
       </c>
       <c r="U6" t="n">
-        <v>10.32</v>
+        <v>-2.78</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -5453,70 +5453,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Lamar Jackson</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4239.1</v>
+        <v>3882.6</v>
       </c>
       <c r="E7" t="n">
-        <v>2991.3</v>
+        <v>2272</v>
       </c>
       <c r="F7" t="n">
-        <v>28.62</v>
+        <v>30.89</v>
       </c>
       <c r="G7" t="n">
-        <v>19.99</v>
+        <v>17.98</v>
       </c>
       <c r="H7" t="n">
-        <v>270.4</v>
+        <v>765</v>
       </c>
       <c r="I7" t="n">
-        <v>191.6</v>
+        <v>451.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="K7" t="n">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="L7" t="n">
-        <v>10.11</v>
+        <v>9.25</v>
       </c>
       <c r="M7" t="n">
-        <v>7.13</v>
+        <v>5.44</v>
       </c>
       <c r="N7" t="n">
-        <v>3.13</v>
+        <v>2.77</v>
       </c>
       <c r="O7" t="n">
-        <v>2.21</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>302.6</v>
+        <v>357.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>212.87</v>
+        <v>209.13</v>
       </c>
       <c r="R7" t="n">
-        <v>148.95</v>
+        <v>155.73</v>
       </c>
       <c r="S7" t="n">
-        <v>276.85</v>
+        <v>262.48</v>
       </c>
       <c r="T7" t="n">
-        <v>215.65</v>
+        <v>217.28</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.78</v>
+        <v>-8.15</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -7568,64 +7568,64 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anthony Richardson Sr.</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3472.8</v>
+        <v>3412.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>205.9</v>
       </c>
       <c r="F3" t="n">
-        <v>17.17</v>
+        <v>19.7</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H3" t="n">
-        <v>828.6</v>
+        <v>691.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J3" t="n">
-        <v>7.93</v>
+        <v>4.11</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="L3" t="n">
-        <v>14.18</v>
+        <v>9.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="N3" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="P3" t="n">
-        <v>301.37</v>
+        <v>283.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>17.06</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>11.59</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -7635,55 +7635,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Anthony Richardson Sr.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3181.7</v>
+        <v>3472.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>14.38</v>
+        <v>17.17</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>187.6</v>
+        <v>828.6</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>17.39</v>
+        <v>14.18</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.71</v>
+        <v>4.15</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>179.83</v>
+        <v>301.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -7694,67 +7694,63 @@
       <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-15.53</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3414.1</v>
+        <v>3181.7</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>21.38</v>
+        <v>14.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>230.4</v>
+        <v>187.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>10.45</v>
+        <v>17.39</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>230.48</v>
+        <v>179.83</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -7765,63 +7761,67 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-15.53</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cole Payton</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3314</v>
+        <v>3414.1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>14.91</v>
+        <v>21.38</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>192</v>
+        <v>230.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.09</v>
+        <v>2.17</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>17.33</v>
+        <v>10.45</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>187.86</v>
+        <v>230.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -7840,31 +7840,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DJ Uiagalelei</t>
+          <t>Cole Payton</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3071.8</v>
+        <v>3314</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>14.13</v>
+        <v>14.91</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7876,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>17.28</v>
+        <v>17.33</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7888,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>174.15</v>
+        <v>187.86</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -7907,55 +7907,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Davis Mills</t>
+          <t>DJ Uiagalelei</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3584.8</v>
+        <v>3071.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>21.04</v>
+        <v>14.13</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>143.6</v>
+        <v>182</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>12.93</v>
+        <v>17.28</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.38</v>
+        <v>3.71</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>220.69</v>
+        <v>174.15</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -7974,55 +7974,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Davis Mills</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3519.9</v>
+        <v>3584.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>19.32</v>
+        <v>21.04</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>255.9</v>
+        <v>143.6</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>11.22</v>
+        <v>12.93</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>3.38</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>232.09</v>
+        <v>220.69</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8041,55 +8041,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3390.1</v>
+        <v>3519.9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>15.52</v>
+        <v>19.32</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>109.8</v>
+        <v>255.9</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11.81</v>
+        <v>11.22</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.34</v>
+        <v>2.58</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>189.34</v>
+        <v>232.09</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -8108,55 +8108,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3175.9</v>
+        <v>3390.1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>16.14</v>
+        <v>15.52</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>565.9</v>
+        <v>109.8</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13.89</v>
+        <v>11.81</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>238.41</v>
+        <v>189.34</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8175,55 +8175,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jameis Winston</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3638.4</v>
+        <v>3175.9</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>24.12</v>
+        <v>16.14</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>186.1</v>
+        <v>565.9</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13.5</v>
+        <v>13.89</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.91</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>239.25</v>
+        <v>238.41</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8242,55 +8242,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jarrett Stidham</t>
+          <t>Jameis Winston</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3721.6</v>
+        <v>3638.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>19.68</v>
+        <v>24.12</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>322.3</v>
+        <v>186.1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>12.08</v>
+        <v>13.5</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.11</v>
+        <v>3.91</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>243.41</v>
+        <v>239.25</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -8309,55 +8309,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Joe Flacco</t>
+          <t>Jarrett Stidham</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3595.5</v>
+        <v>3721.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>25.5</v>
+        <v>19.68</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>33.5</v>
+        <v>322.3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11.5</v>
+        <v>12.08</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.51</v>
+        <v>3.11</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>229.65</v>
+        <v>243.41</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8376,55 +8376,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Joe Flacco</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3434.9</v>
+        <v>3595.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>17.82</v>
+        <v>25.5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>550</v>
+        <v>33.5</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>4.93</v>
+        <v>1.75</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>10.89</v>
+        <v>11.5</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.14</v>
+        <v>3.51</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>265.2</v>
+        <v>229.65</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8443,55 +8443,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3265.2</v>
+        <v>3434.9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>18.3</v>
+        <v>17.82</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>840.5</v>
+        <v>550</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>7.23</v>
+        <v>4.93</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8.84</v>
+        <v>10.89</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.51</v>
+        <v>3.14</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>306.54</v>
+        <v>265.2</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -8510,55 +8510,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3312.3</v>
+        <v>3265.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16.07</v>
+        <v>18.3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>189.2</v>
+        <v>840.5</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.88</v>
+        <v>7.23</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10.45</v>
+        <v>8.84</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.34</v>
+        <v>3.51</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>199.39</v>
+        <v>306.54</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -8577,55 +8577,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kyle Allen</t>
+          <t>Kenny Pickett</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3425.4</v>
+        <v>3312.3</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>17.95</v>
+        <v>16.07</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>184.3</v>
+        <v>189.2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>12.9</v>
+        <v>10.45</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>209.55</v>
+        <v>199.39</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -8644,55 +8644,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kyle McCord</t>
+          <t>Kyle Allen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3260.6</v>
+        <v>3425.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>17.95</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>182.3</v>
+        <v>184.3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>17.38</v>
+        <v>12.9</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>180.99</v>
+        <v>209.55</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -8711,55 +8711,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Kyle McCord</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3638</v>
+        <v>3260.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>22.94</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>176.6</v>
+        <v>182.3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.17</v>
+        <v>3.09</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>10.8</v>
+        <v>17.38</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.61</v>
+        <v>3.72</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>241.14</v>
+        <v>180.99</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -8778,55 +8778,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marcus Mariota</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3654.2</v>
+        <v>3638</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>25.16</v>
+        <v>22.94</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>581.6</v>
+        <v>176.6</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>14.88</v>
+        <v>10.8</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>290.17</v>
+        <v>241.14</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -8845,55 +8845,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mason Rudolph</t>
+          <t>Marcus Mariota</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3480.2</v>
+        <v>3654.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>20.11</v>
+        <v>25.16</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>148.9</v>
+        <v>581.6</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.78</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>9.720000000000001</v>
+        <v>14.88</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>219.18</v>
+        <v>290.17</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -8912,55 +8912,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Mason Rudolph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3510.9</v>
+        <v>3480.2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>22.29</v>
+        <v>20.11</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>201.9</v>
+        <v>148.9</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.03</v>
+        <v>1.78</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>11.39</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>240.59</v>
+        <v>219.18</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -8979,55 +8979,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3364.3</v>
+        <v>3510.9</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>17.34</v>
+        <v>22.29</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>153.2</v>
+        <v>201.9</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>12.87</v>
+        <v>11.39</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.11</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>199.69</v>
+        <v>240.59</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -9046,55 +9046,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sam Howell</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3387</v>
+        <v>3364.3</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>15.38</v>
+        <v>17.34</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>205</v>
+        <v>153.2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>17.31</v>
+        <v>12.87</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.76</v>
+        <v>4.11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>194.32</v>
+        <v>199.69</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -9113,55 +9113,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Sam Howell</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3295.2</v>
+        <v>3387</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>16.26</v>
+        <v>15.38</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>293.8</v>
+        <v>205</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2.69</v>
+        <v>3.16</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>10.12</v>
+        <v>17.31</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.18</v>
+        <v>3.76</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>213.77</v>
+        <v>194.32</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -9172,67 +9172,63 @@
       <c r="S26" t="n">
         <v>0</v>
       </c>
-      <c r="T26" t="n">
-        <v>68.14</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-68.14</v>
-      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3346.9</v>
+        <v>3295.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>16.52</v>
+        <v>16.26</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>287.7</v>
+        <v>293.8</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>11.45</v>
+        <v>10.12</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>213.35</v>
+        <v>213.77</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -9243,63 +9239,67 @@
       <c r="S27" t="n">
         <v>0</v>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>68.14</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-68.14</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stetson Bennett IV</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3413.8</v>
+        <v>3346.9</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>16.01</v>
+        <v>16.52</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>183.5</v>
+        <v>287.7</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>16.17</v>
+        <v>11.45</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.63</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>191.24</v>
+        <v>213.35</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -9318,55 +9318,55 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tommy DeVito</t>
+          <t>Stetson Bennett IV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3282.1</v>
+        <v>3413.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>15.74</v>
+        <v>16.01</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>443.2</v>
+        <v>183.5</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>10.57</v>
+        <v>16.17</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.69</v>
+        <v>5.63</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>229.84</v>
+        <v>191.24</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -9385,55 +9385,55 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Tommy DeVito</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3661.3</v>
+        <v>3282.1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>21.09</v>
+        <v>15.74</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>38.9</v>
+        <v>443.2</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>9.34</v>
+        <v>10.57</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.17</v>
+        <v>3.69</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>219.34</v>
+        <v>229.84</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -9444,67 +9444,63 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="T30" t="n">
-        <v>52.15</v>
-      </c>
-      <c r="U30" t="n">
-        <v>-52.15</v>
-      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3412.4</v>
+        <v>3661.3</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>19.7</v>
+        <v>21.09</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>691.2</v>
+        <v>38.9</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4.11</v>
+        <v>1.61</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.33</v>
+        <v>9.34</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>283.42</v>
+        <v>219.34</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -9515,8 +9511,12 @@
       <c r="S31" t="n">
         <v>0</v>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-52.15</v>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
     </row>
@@ -33559,67 +33559,67 @@
         <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>233.558</v>
+        <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>1.854</v>
+        <v>0</v>
       </c>
       <c r="J257" t="n">
-        <v>45.3</v>
+        <v>0</v>
       </c>
       <c r="K257" t="n">
-        <v>0.264</v>
+        <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0.544</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>140.436</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
-        <v>326.676</v>
+        <v>0</v>
       </c>
       <c r="P257" t="n">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="Q257" t="n">
-        <v>3.259</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>24.409</v>
+        <v>0</v>
       </c>
       <c r="S257" t="n">
-        <v>66.191</v>
+        <v>0</v>
       </c>
       <c r="T257" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="U257" t="n">
-        <v>0.782</v>
+        <v>0</v>
       </c>
       <c r="V257" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="W257" t="n">
-        <v>1.679</v>
+        <v>0</v>
       </c>
       <c r="X257" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>0.758</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>21.462</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AB257" t="n">
-        <v>36.926</v>
+        <v>0</v>
       </c>
       <c r="AC257" t="inlineStr"/>
     </row>
@@ -73084,67 +73084,67 @@
         <v>0</v>
       </c>
       <c r="H682" t="n">
-        <v>0</v>
+        <v>205.897</v>
       </c>
       <c r="I682" t="n">
-        <v>0</v>
+        <v>1.198</v>
       </c>
       <c r="J682" t="n">
-        <v>0</v>
+        <v>40.956</v>
       </c>
       <c r="K682" t="n">
-        <v>0</v>
+        <v>0.244</v>
       </c>
       <c r="L682" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="M682" t="n">
-        <v>0</v>
+        <v>0.205</v>
       </c>
       <c r="N682" t="n">
-        <v>0</v>
+        <v>112.775</v>
       </c>
       <c r="O682" t="n">
-        <v>0</v>
+        <v>299.016</v>
       </c>
       <c r="P682" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="Q682" t="n">
-        <v>0</v>
+        <v>2.602</v>
       </c>
       <c r="R682" t="n">
-        <v>0</v>
+        <v>20.061</v>
       </c>
       <c r="S682" t="n">
-        <v>0</v>
+        <v>61.85</v>
       </c>
       <c r="T682" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="U682" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="V682" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W682" t="n">
-        <v>0</v>
+        <v>1.684</v>
       </c>
       <c r="X682" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Y682" t="n">
-        <v>0</v>
+        <v>0.801</v>
       </c>
       <c r="Z682" t="n">
-        <v>0</v>
+        <v>17.08</v>
       </c>
       <c r="AA682" t="n">
-        <v>0</v>
+        <v>3.713</v>
       </c>
       <c r="AB682" t="n">
-        <v>0</v>
+        <v>32.605</v>
       </c>
       <c r="AC682" t="inlineStr"/>
     </row>
